--- a/data/global/2026-06-week02/titles.xlsx
+++ b/data/global/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L193"/>
+  <dimension ref="A1:L206"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
+        <v>שמוליק סוכות - נשאר רק הלב</v>
       </c>
       <c r="B2" t="str">
-        <v>14 hours ago</v>
+        <v>2026-06-08</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411271&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-08</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>14 hours ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>שמוליק סוכות - נשאר רק הלב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
+        <v>שלומי ימין - תודה על הכל</v>
       </c>
       <c r="B3" t="str">
-        <v>14 hours ago</v>
+        <v>2026-06-08</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411270&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-08</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>14 hours ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>שלומי ימין - תודה על הכל</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
+        <v>עידו כנפי - נגמרה המלחמה</v>
       </c>
       <c r="B4" t="str">
-        <v>16 hours ago</v>
+        <v>2026-06-08</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411269&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-08</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>16 hours ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>עידו כנפי - נגמרה המלחמה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
+        <v>מורן מצליח - אהבה בשתי שפות</v>
       </c>
       <c r="B5" t="str">
-        <v>16 hours ago</v>
+        <v>2026-06-08</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411268&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
       </c>
       <c r="D5" t="str">
         <v>2026-06-08</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>16 hours ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>מורן מצליח - אהבה בשתי שפות</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
+        <v>יוסף חיים - טאטע תציל</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-08</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411267&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
       </c>
       <c r="D6" t="str">
         <v>2026-06-08</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>יוסף חיים - טאטע תציל</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
+        <v>בנימין משה - הכל היסטוריה</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-08</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411266&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-08</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>בנימין משה - הכל היסטוריה</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
+        <v>חן כהן – תל גיבורים</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-08</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
+        <v>https://yosmusic.com/%d7%97%d7%9f-%d7%9b%d7%94%d7%9f-%d7%aa%d7%9c-%d7%92%d7%99%d7%91%d7%95%d7%a8%d7%99%d7%9d/</v>
       </c>
       <c r="D8" t="str">
         <v>2026-06-08</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>תל גיבורים" של  חן כהן הוא שיר חשוף  כואב ומזכך. זהו מסע בזמן אל מחוזות הילדות וההתבגרות בשכונת תל גיבורים בחולון, שעיקרו הוא מסע פנימי אל נבכי דימוי הגוף, החרדה והחיפוש העיקש אחר קבלה עצמית ו"בית" בתוך הנפש. הטקסט והמוזיקה</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>חן כהן – תל גיבורים</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
+        <v>סהראת – שמש כחולה</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-08</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
+        <v>https://yosmusic.com/%d7%a1%d7%94%d7%a8%d7%90%d7%aa-%d7%a9%d7%9e%d7%a9-%d7%9b%d7%97%d7%95%d7%9c%d7%94/</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-08</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>השיר "שמש כחולה" של להקת "סהראת" בביצועה של אורטל חאיק פינקל, הוא יצירה מקורית יוצאת דופן בנוף המוזיקלי המקומי. השיר, שנכתב על ידי מקימת ההרכב אתי נאור והולחן על ידי אדיר לוי, מביא  חשיפה רגשית  המטופלת ברגישות ובעוצמה יוצאת דופן.</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>סהראת – שמש כחולה</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
+        <v>עילאי גניש - השריטה שלי קאבר</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-08</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411275&amp;sid=06589a542a79f09e4f3f508659a66da9</v>
       </c>
       <c r="D10" t="str">
         <v>2026-06-08</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>עילאי גניש - השריטה שלי קאבר</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
+        <v>ליהיא - לב לבן קאבר</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-08</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411274&amp;sid=06589a542a79f09e4f3f508659a66da9</v>
       </c>
       <c r="D11" t="str">
         <v>2026-06-08</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>ליהיא - לב לבן קאבר</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
+        <v>יעקב הראל - ככה באמת קאבר</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-08</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411273&amp;sid=06589a542a79f09e4f3f508659a66da9</v>
       </c>
       <c r="D12" t="str">
         <v>2026-06-08</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>יעקב הראל - ככה באמת קאבר</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
+        <v>אפיק מרחום - אני רוצה קאבר</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-08</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411272&amp;sid=06589a542a79f09e4f3f508659a66da9</v>
       </c>
       <c r="D13" t="str">
         <v>2026-06-08</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים זמרים מתחילים</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>אפיק מרחום - אני רוצה קאבר</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>8h ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
+        <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
       </c>
       <c r="D14" t="str">
         <v>2026-06-08</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>8h ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>8h ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
+        <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
       </c>
       <c r="D15" t="str">
         <v>2026-06-08</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>8h ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>8h ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
+        <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
       </c>
       <c r="D16" t="str">
         <v>2026-06-08</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>8h ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>8h ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
+        <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
       </c>
       <c r="D17" t="str">
         <v>2026-06-08</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>8h ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
+        <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
       </c>
       <c r="D18" t="str">
         <v>2026-06-08</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
+        <v>DEEP PURPLE - DIABLO (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
+        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
       </c>
       <c r="D19" t="str">
         <v>2026-06-08</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
+        <v>Reba McEntire - You Never Gave Up On Me</v>
       </c>
       <c r="B20" t="str">
-        <v>1 day ago</v>
+        <v>19h ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
+        <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
       </c>
       <c r="D20" t="str">
         <v>2026-06-08</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1 day ago</v>
+        <v>19h ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Capital FM</v>
+        <v>Reba McEntire</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Reba McEntire - You Never Gave Up On Me - Reba McEntire</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
+        <v>elijah woods - Wonder (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>1 day ago</v>
+        <v>22h ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
+        <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
       </c>
       <c r="D21" t="str">
         <v>2026-06-08</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>1 day ago</v>
+        <v>22h ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Capital FM</v>
+        <v>elijah woods</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>elijah woods - Wonder (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B22" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
+        <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
       </c>
       <c r="D22" t="str">
         <v>2026-06-08</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B23" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
+        <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
       </c>
       <c r="D23" t="str">
         <v>2026-06-08</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B24" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
+        <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
       </c>
       <c r="D24" t="str">
         <v>2026-06-08</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
+        <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
       </c>
       <c r="D25" t="str">
         <v>2026-06-08</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B26" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
+        <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
       </c>
       <c r="D26" t="str">
         <v>2026-06-08</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
+        <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
       </c>
       <c r="D27" t="str">
         <v>2026-06-08</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
+        <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
       </c>
       <c r="D28" t="str">
         <v>2026-06-08</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>TheCranberriesTV</v>
+        <v>Capital FM</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
+        <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
       </c>
       <c r="D29" t="str">
         <v>2026-06-08</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Jordana Bryant</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
+        <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-06-08</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Grace Enger</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
+        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
+        <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
       </c>
       <c r="D31" t="str">
         <v>2026-06-08</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>The Offspring</v>
+        <v>Capital FM</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
+        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Lola Young – From Down Here (From The Pool)</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
+        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
       </c>
       <c r="D32" t="str">
         <v>2026-06-08</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>CAIN - Living Water (Music Video)</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
+        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
       </c>
       <c r="D33" t="str">
         <v>2026-06-08</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>CAIN</v>
+        <v>Capital FM</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>CAIN - Living Water (Music Video) - CAIN</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
+        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B34" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
+        <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
       </c>
       <c r="D34" t="str">
         <v>2026-06-08</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Eric Clapton</v>
+        <v>Capital FM</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
+        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video)</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B35" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
+        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
       </c>
       <c r="D35" t="str">
         <v>2026-06-08</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Blu DeTiger</v>
+        <v>Capital FM</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
+        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
       </c>
       <c r="D36" t="str">
         <v>2026-06-08</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Capital FM</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B37" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
+        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
       </c>
       <c r="D37" t="str">
         <v>2026-06-08</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Capital FM</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
+        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
       </c>
       <c r="D38" t="str">
         <v>2026-06-08</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Pink Floyd</v>
+        <v>Capital FM</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Holly Humberstone - it’s just White Noise</v>
+        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B39" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
+        <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
       </c>
       <c r="D39" t="str">
         <v>2026-06-08</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Holly Humberstone</v>
+        <v>Capital FM</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
+        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B40" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
+        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
       </c>
       <c r="D40" t="str">
         <v>2026-06-08</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Freya Ridings</v>
+        <v>Capital FM</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
+        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
       </c>
       <c r="D41" t="str">
         <v>2026-06-08</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Muse</v>
+        <v>Capital FM</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B42" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
+        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
       </c>
       <c r="D42" t="str">
         <v>2026-06-08</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Ellie Goulding</v>
+        <v>Capital FM</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video)</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>6 hours ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
+        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
       </c>
       <c r="D43" t="str">
         <v>2026-06-08</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6 hours ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Capital FM</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer)</v>
+        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B44" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
+        <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
       </c>
       <c r="D44" t="str">
         <v>2026-06-08</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Evanescence</v>
+        <v>Capital FM</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
+        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B45" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
+        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
       </c>
       <c r="D45" t="str">
         <v>2026-06-08</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>The Beaches</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Bella White - Stuff (Official Music Video)</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B46" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
+        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
       </c>
       <c r="D46" t="str">
         <v>2026-06-08</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Bella White</v>
+        <v>Capital FM</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer)</v>
+        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B47" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
+        <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-06-08</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Meduza and 2 more</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
+        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>CAIN - Living Water (Lyric Video)</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B48" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
+        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
       </c>
       <c r="D48" t="str">
         <v>2026-06-08</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>CAIN</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B49" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
+        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
       </c>
       <c r="D49" t="str">
         <v>2026-06-08</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Fitz and the Tantrums</v>
+        <v>Capital FM</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video)</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B50" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
+        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
       </c>
       <c r="D50" t="str">
         <v>2026-06-08</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Jeremy Camp</v>
+        <v>Capital FM</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
+        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B51" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
+        <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
       </c>
       <c r="D51" t="str">
         <v>2026-06-08</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Alesso</v>
+        <v>Capital FM</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
+        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B52" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
+        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
       </c>
       <c r="D52" t="str">
         <v>2026-06-08</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Malcolm Todd</v>
+        <v>Capital FM</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer)</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B53" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
+        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
       </c>
       <c r="D53" t="str">
         <v>2026-06-08</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Capital FM</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video)</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B54" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
+        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
       </c>
       <c r="D54" t="str">
         <v>2026-06-08</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Wyatt Flores</v>
+        <v>Capital FM</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video) - Wyatt Flores</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
+        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
       </c>
       <c r="D55" t="str">
         <v>2026-06-08</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Mckenna Grace</v>
+        <v>Capital FM</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video) - Mckenna Grace</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B56" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
+        <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
       </c>
       <c r="D56" t="str">
         <v>2026-06-08</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Robert Grace</v>
+        <v>Capital FM</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Boyzone - No Matter What (Live)</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
       </c>
       <c r="B57" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
+        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
       </c>
       <c r="D57" t="str">
         <v>2026-06-08</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Boyzone</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Boyzone - No Matter What (Live) - Boyzone</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Florrie - The Times (Official Video)</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
       </c>
       <c r="B58" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
+        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
       </c>
       <c r="D58" t="str">
         <v>2026-06-08</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>florriemusic</v>
+        <v>TheCranberriesTV</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Florrie - The Times (Official Video) - florriemusic</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer)</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
+        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
       </c>
       <c r="D59" t="str">
         <v>2026-06-08</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Madonna</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer) - Madonna</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>DMA'S - Hurracane (Official Video)</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
+        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
       </c>
       <c r="D60" t="str">
         <v>2026-06-08</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>DMA'S</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>DMA'S - Hurracane (Official Video) - DMA'S</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B61" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
+        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
       </c>
       <c r="D61" t="str">
         <v>2026-06-08</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Lainey Wilson and John Mayer</v>
+        <v>The Offspring</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio) - Lainey Wilson and John Mayer</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
+        <v>Lola Young – From Down Here (From The Pool)</v>
       </c>
       <c r="B62" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
+        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
       </c>
       <c r="D62" t="str">
         <v>2026-06-08</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>ROLE MODEL</v>
+        <v>Lola Young</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video) - ROLE MODEL</v>
+        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York)</v>
+        <v>CAIN - Living Water (Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
+        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
       </c>
       <c r="D63" t="str">
         <v>2026-06-08</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Shawn Mendes</v>
+        <v>CAIN</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York) - Shawn Mendes</v>
+        <v>CAIN - Living Water (Music Video) - CAIN</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
+        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
       </c>
       <c r="D64" t="str">
         <v>2026-06-08</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Eric Clapton</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video) - SIENNA SPIRO</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
+        <v>Blu DeTiger - Whisper (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
+        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
       </c>
       <c r="D65" t="str">
         <v>2026-06-08</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video)</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
+        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
       </c>
       <c r="D66" t="str">
         <v>2026-06-08</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Europe</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
+        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
       </c>
       <c r="D67" t="str">
         <v>2026-06-08</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Air Supply</v>
+        <v>Pink Floyd</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
+        <v>Holly Humberstone - it’s just White Noise</v>
       </c>
       <c r="B68" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
+        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
       </c>
       <c r="D68" t="str">
         <v>2026-06-08</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Julia Cole Music</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
+        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
+        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
       </c>
       <c r="D69" t="str">
         <v>2026-06-08</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Allen Stone and Placeholder Sessions</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
+        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
       </c>
       <c r="D70" t="str">
         <v>2026-06-08</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Morgan Wallen</v>
+        <v>Muse</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
       </c>
       <c r="B71" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
+        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
       </c>
       <c r="D71" t="str">
         <v>2026-06-08</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Billy Idol</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
+        <v>Evanescence - Sanctuary (Official Visualizer)</v>
       </c>
       <c r="B72" t="str">
-        <v>9 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
+        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
       </c>
       <c r="D72" t="str">
         <v>2026-06-08</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Evanescence</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
       </c>
       <c r="B73" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
+        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
       </c>
       <c r="D73" t="str">
         <v>2026-06-08</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>5 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Icona Pop</v>
+        <v>The Beaches</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Hippo Campus - South</v>
+        <v>Bella White - Stuff (Official Music Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>6 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
+        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
       </c>
       <c r="D74" t="str">
         <v>2026-06-08</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>6 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Hippo Campus</v>
+        <v>Bella White</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Hippo Campus - South - Hippo Campus</v>
+        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>elijah woods - Old (Treehouse Sessions)</v>
+        <v>Meduza, Rani - Silence (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>6 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
+        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
       </c>
       <c r="D75" t="str">
         <v>2026-06-08</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>6 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>elijah woods</v>
+        <v>Meduza and 2 more</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
+        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video)</v>
+        <v>CAIN - Living Water (Lyric Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>6 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
+        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
       </c>
       <c r="D76" t="str">
         <v>2026-06-08</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>6 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Nothing But Thieves</v>
+        <v>CAIN</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
+        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video)</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
       </c>
       <c r="B77" t="str">
-        <v>6 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
+        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
       </c>
       <c r="D77" t="str">
         <v>2026-06-08</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>6 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Ariana Grande</v>
+        <v>Fitz and the Tantrums</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>LAUREL - Fire Breather</v>
+        <v>Jeremy Camp - Reflector (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>6 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
+        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
       </c>
       <c r="D78" t="str">
         <v>2026-06-08</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>6 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>LAUREL</v>
+        <v>Jeremy Camp</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>LAUREL - Fire Breather - LAUREL</v>
+        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>The Warning - Ego (Performance Video)</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
       </c>
       <c r="B79" t="str">
-        <v>8 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
+        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
       </c>
       <c r="D79" t="str">
         <v>2026-06-08</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>8 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>The Warning</v>
+        <v>Alesso</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>The Warning - Ego (Performance Video) - The Warning</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
       </c>
       <c r="B80" t="str">
-        <v>8 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
+        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
       </c>
       <c r="D80" t="str">
         <v>2026-06-08</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>8 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
+        <v>Isabel LaRosa - Every Life (Visualizer)</v>
       </c>
       <c r="B81" t="str">
-        <v>8 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
+        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
       </c>
       <c r="D81" t="str">
         <v>2026-06-08</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>8 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Armin van Buuren</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
+        <v>Wyatt Flores - Half The Man (Official Music Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>9 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
+        <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
       </c>
       <c r="D82" t="str">
         <v>2026-06-08</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>9 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Andrew Bird</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
+        <v>Wyatt Flores - Half The Man (Official Music Video) - Wyatt Flores</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video)</v>
+        <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>9 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
+        <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
       </c>
       <c r="D83" t="str">
         <v>2026-06-08</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>9 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Danny Gokey</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
+        <v>Mckenna Grace - Ugly and Rotten (Official Music Video) - Mckenna Grace</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B84" t="str">
-        <v>9 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
+        <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
       </c>
       <c r="D84" t="str">
         <v>2026-06-08</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>9 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Armik</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
+        <v>Boyzone - No Matter What (Live)</v>
       </c>
       <c r="B85" t="str">
-        <v>9 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
+        <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
       </c>
       <c r="D85" t="str">
         <v>2026-06-08</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>9 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Holly Humberstone and Free People</v>
+        <v>Boyzone</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
+        <v>Boyzone - No Matter What (Live) - Boyzone</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>The Offspring - Why Don’t You Get a Job? | Live at BeachLife Festival 2026</v>
+        <v>Florrie - The Times (Official Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>9 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=zRJ2etb_rpI</v>
+        <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
       </c>
       <c r="D86" t="str">
         <v>2026-06-08</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>9 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>The Offspring</v>
+        <v>florriemusic</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>The Offspring - Why Don’t You Get a Job? | Live at BeachLife Festival 2026 - The Offspring</v>
+        <v>Florrie - The Times (Official Video) - florriemusic</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Jagwar Twin, sir lucius - bad feeling (oompa loompa) (Visualizer)</v>
+        <v>Madonna - Love Sensation (Official Visualizer)</v>
       </c>
       <c r="B87" t="str">
-        <v>9 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=XGgI5HvR-gg</v>
+        <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
       </c>
       <c r="D87" t="str">
         <v>2026-06-08</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>9 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Jagwar Twin</v>
+        <v>Madonna</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Jagwar Twin, sir lucius - bad feeling (oompa loompa) (Visualizer) - Jagwar Twin</v>
+        <v>Madonna - Love Sensation (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Nathan Evans x SAINT PHNX - Home (World Cup 2026) (Official Music Video)</v>
+        <v>DMA'S - Hurracane (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>9 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=lRBNYETENNg</v>
+        <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
       </c>
       <c r="D88" t="str">
         <v>2026-06-08</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>9 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>NathanEvanss</v>
+        <v>DMA'S</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Nathan Evans x SAINT PHNX - Home (World Cup 2026) (Official Music Video) - NathanEvanss</v>
+        <v>DMA'S - Hurracane (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Greta Van Fleet - Play Your Games (Official Video)</v>
+        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
       </c>
       <c r="B89" t="str">
-        <v>9 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=CJsfI1QVBEM</v>
+        <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
       </c>
       <c r="D89" t="str">
         <v>2026-06-08</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>9 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Greta Van Fleet</v>
+        <v>Lainey Wilson and John Mayer</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Greta Van Fleet - Play Your Games (Official Video) - Greta Van Fleet</v>
+        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio) - Lainey Wilson and John Mayer</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Lola Young – From Down Here (From a Living Room)</v>
+        <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=uF5HUfho2NU</v>
+        <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
       </c>
       <c r="D90" t="str">
         <v>2026-06-08</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Lola Young</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Lola Young – From Down Here (From a Living Room) - Lola Young</v>
+        <v>ROLE MODEL - High Hopes 3000 (Official Music Video) - ROLE MODEL</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Lawrence - Rain Check ft. Quinn XCII (Lyric Video)</v>
+        <v>Shawn Mendes - Treat You Better (Live from New York)</v>
       </c>
       <c r="B91" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=xXeyznlIrFY</v>
+        <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
       </c>
       <c r="D91" t="str">
         <v>2026-06-08</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Lawrence and Quinn XCII</v>
+        <v>Shawn Mendes</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Lawrence - Rain Check ft. Quinn XCII (Lyric Video) - Lawrence and Quinn XCII</v>
+        <v>Shawn Mendes - Treat You Better (Live from New York) - Shawn Mendes</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>ANTONIA - NO HATE | Official Music Video</v>
+        <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=rhlONr1DTj0</v>
+        <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
       </c>
       <c r="D92" t="str">
         <v>2026-06-08</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>ANTONIA</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>ANTONIA - NO HATE | Official Music Video - ANTONIA</v>
+        <v>SIENNA SPIRO - The Visitor (Official Music Video) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>R3HAB - "Lost in translation..." (Official Lyric Video)</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
       </c>
       <c r="B93" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=TbJtz0oy2cI</v>
+        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
       </c>
       <c r="D93" t="str">
         <v>2026-06-08</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>R3HAB</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>R3HAB - "Lost in translation..." (Official Lyric Video) - R3HAB</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Pink Floyd - Shine On You Crazy Diamond (Parts 1-5) - Live in Venice (Official Video)</v>
+        <v>Europe - The Cult of Ignorance (Official Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=kwiawhDk2TM</v>
+        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
       </c>
       <c r="D94" t="str">
         <v>2026-06-08</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Pink Floyd</v>
+        <v>Europe</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Pink Floyd - Shine On You Crazy Diamond (Parts 1-5) - Live in Venice (Official Video) - Pink Floyd</v>
+        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>SHADE - TOXIC</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=A3km0zrBKSg</v>
+        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
       </c>
       <c r="D95" t="str">
         <v>2026-06-08</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Shade Official Channel</v>
+        <v>Air Supply</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>SHADE - TOXIC - Shade Official Channel</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico)</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>10 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=xZAe-d3bXTs</v>
+        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
       </c>
       <c r="D96" t="str">
         <v>2026-06-08</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>10 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Dua Lipa</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Dua Lipa - Physical (Live From Mexico) - Dua Lipa</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Dagny - Rain (Lyric Video)</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
       </c>
       <c r="B97" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=j3ZJwczZoUQ</v>
+        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
       </c>
       <c r="D97" t="str">
         <v>2026-06-08</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>9 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Dagny</v>
+        <v>Allen Stone and Placeholder Sessions</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Dagny - Rain (Lyric Video) - Dagny</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985)</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
       </c>
       <c r="B98" t="str">
-        <v>9 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=c0LtTVKNwNA</v>
+        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
       </c>
       <c r="D98" t="str">
         <v>2026-06-08</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>9 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Morgan Wallen</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Modern Talking - Cheri Cheri Lady (Auf los geht's los, 14.09.1985) - Modern Talking Offiziell</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>The Chemical Brothers - Go (Live Show Visual)</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>9 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=fHCIchBq8CM</v>
+        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
       </c>
       <c r="D99" t="str">
         <v>2026-06-08</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>9 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>The Chemical Brothers</v>
+        <v>Billy Idol</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>The Chemical Brothers - Go (Live Show Visual) - The Chemical Brothers</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video)</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
       </c>
       <c r="B100" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=FTUe3jzUqXU</v>
+        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
       </c>
       <c r="D100" t="str">
         <v>2026-06-08</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Defected Records and Jonas Blue</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Jonas Blue - Girl (Official Lyric Video) - Defected Records and Jonas Blue</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Dogpark - Don't Lie (Visualizer)</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>9 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=is7qKBRycJI</v>
+        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
       </c>
       <c r="D101" t="str">
         <v>2026-06-08</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>9 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Dogpark</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Dogpark - Don't Lie (Visualizer) - Dogpark</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Too Easy</v>
+        <v>Hippo Campus - South</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>7d ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/too-easy/6774752170</v>
+        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
       </c>
       <c r="D102" t="str">
         <v>2026-06-08</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Too Easy - Single</v>
+        <v>7d ago</v>
       </c>
       <c r="G102" t="str">
-        <v>1:54</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Tinashe</v>
+        <v>Hippo Campus</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/tinashe/464835513</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/too-easy/6774752168</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Too Easy - Tinashe</v>
+        <v>Hippo Campus - South - Hippo Campus</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>I Knew It, I Knew You</v>
+        <v>elijah woods - Old (Treehouse Sessions)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>7d ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
+        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
       </c>
       <c r="D103" t="str">
         <v>2026-06-08</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>I Knew It, I Knew You - Single</v>
+        <v>7d ago</v>
       </c>
       <c r="G103" t="str">
-        <v>2:58</v>
+        <v/>
       </c>
       <c r="H103" t="str">
-        <v>Taylor Swift</v>
+        <v>elijah woods</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/i-knew-it-i-knew-you/6775527442</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>I Knew It, I Knew You - Taylor Swift</v>
+        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Love Sensation</v>
+        <v>Nothing But Thieves - Evolution (Official Video)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>7d ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
+        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
       </c>
       <c r="D104" t="str">
         <v>2026-06-08</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Love Sensation - Single</v>
+        <v>7d ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:48</v>
+        <v/>
       </c>
       <c r="H104" t="str">
-        <v>Madonna</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/love-sensation/6774810102</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>Love Sensation - Madonna</v>
+        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Mi Yo De Antes</v>
+        <v>Ariana Grande - hate that i made you love me (official music video)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>7d ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
+        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
       </c>
       <c r="D105" t="str">
         <v>2026-06-08</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Mi Yo De Antes - Single</v>
+        <v>7d ago</v>
       </c>
       <c r="G105" t="str">
-        <v>3:04</v>
+        <v/>
       </c>
       <c r="H105" t="str">
-        <v>Ozuna</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/mi-yo-de-antes/6769193983</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>Mi Yo De Antes - Ozuna</v>
+        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Three Nations</v>
+        <v>LAUREL - Fire Breather</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>7d ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/three-nations/6776010602</v>
+        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
       </c>
       <c r="D106" t="str">
         <v>2026-06-08</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Official FIFA World Cup 2026™ Album</v>
+        <v>7d ago</v>
       </c>
       <c r="G106" t="str">
-        <v>3:30</v>
+        <v/>
       </c>
       <c r="H106" t="str">
-        <v>21 Savage</v>
+        <v>LAUREL</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/21-savage/894820464</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/three-nations/6776010591</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>Three Nations - 21 Savage</v>
+        <v>LAUREL - Fire Breather - LAUREL</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Champions (WC 26)</v>
+        <v>The Warning - Ego (Performance Video)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>8d ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
+        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
       </c>
       <c r="D107" t="str">
         <v>2026-06-08</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Champions (WC 26) - Single</v>
+        <v>8d ago</v>
       </c>
       <c r="G107" t="str">
-        <v>4:15</v>
+        <v/>
       </c>
       <c r="H107" t="str">
-        <v>IShowSpeed</v>
+        <v>The Warning</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ishowspeed/1574723975</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/champions-wc-26/6775282246</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>Champions (WC 26) - IShowSpeed</v>
+        <v>The Warning - Ego (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>ENCERRONES</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>9d ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/encerrones/6771854522</v>
+        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
       </c>
       <c r="D108" t="str">
         <v>2026-06-08</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>TEOFANIA</v>
+        <v>9d ago</v>
       </c>
       <c r="G108" t="str">
-        <v>2:23</v>
+        <v/>
       </c>
       <c r="H108" t="str">
-        <v>LENCHO</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/encerrones/6771854517</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>ENCERRONES - LENCHO</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Cowgirl</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>9d ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
+        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
       </c>
       <c r="D109" t="str">
         <v>2026-06-08</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>The Outlaw Cherie Lee &amp; Other Western Tales</v>
+        <v>9d ago</v>
       </c>
       <c r="G109" t="str">
-        <v>2:56</v>
+        <v/>
       </c>
       <c r="H109" t="str">
-        <v>Shaboozey</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/cowgirl/1894906682</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>Cowgirl - Shaboozey</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>PASSENGER</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>10d ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/passenger/6773456081</v>
+        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
       </c>
       <c r="D110" t="str">
         <v>2026-06-08</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>WILDCHILD</v>
+        <v>10d ago</v>
       </c>
       <c r="G110" t="str">
-        <v>2:39</v>
+        <v/>
       </c>
       <c r="H110" t="str">
-        <v>Alex Warren</v>
+        <v>Andrew Bird</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/passenger/6773456078</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>PASSENGER - Alex Warren</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Secret Language</v>
+        <v>Danny Gokey - God's Not (Official Music Video)</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>10d ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/secret-language/6774223667</v>
+        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
       </c>
       <c r="D111" t="str">
         <v>2026-06-08</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Sweet Fortune</v>
+        <v>10d ago</v>
       </c>
       <c r="G111" t="str">
-        <v>3:53</v>
+        <v/>
       </c>
       <c r="H111" t="str">
-        <v>Ryan Beatty</v>
+        <v>Danny Gokey</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/ryan-beatty/483234172</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/secret-language/6774223660</v>
+        <v/>
       </c>
       <c r="L111" t="str">
-        <v>Secret Language - Ryan Beatty</v>
+        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>High Hopes 3000</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>10d ago</v>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
+        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
       </c>
       <c r="D112" t="str">
         <v>2026-06-08</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Chuck Timely &amp; The Hourglass</v>
+        <v>10d ago</v>
       </c>
       <c r="G112" t="str">
-        <v>4:05</v>
+        <v/>
       </c>
       <c r="H112" t="str">
-        <v>ROLE MODEL</v>
+        <v>Armik</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/role-model/199215762</v>
+        <v/>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
+        <v/>
       </c>
       <c r="L112" t="str">
-        <v>High Hopes 3000 - ROLE MODEL</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Vertical</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>10d ago</v>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/vertical/1892436336</v>
+        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
       </c>
       <c r="D113" t="str">
         <v>2026-06-08</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Emotional Junglist</v>
+        <v>10d ago</v>
       </c>
       <c r="G113" t="str">
-        <v>2:36</v>
+        <v/>
       </c>
       <c r="H113" t="str">
-        <v>Nia Archives</v>
+        <v>Holly Humberstone and Free People</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v/>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/vertical/1892436329</v>
+        <v/>
       </c>
       <c r="L113" t="str">
-        <v>Vertical - Nia Archives</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>snake the drain</v>
+        <v>True Colors</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
+        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
       </c>
       <c r="D114" t="str">
         <v>2026-06-08</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>this time it’s different / snake the drain - Single</v>
+        <v>Thank You</v>
       </c>
       <c r="G114" t="str">
-        <v>3:08</v>
+        <v>3:39</v>
       </c>
       <c r="H114" t="str">
-        <v>Devon Again</v>
+        <v>Mike D</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
+        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
+        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
       </c>
       <c r="L114" t="str">
-        <v>snake the drain - Devon Again</v>
+        <v>True Colors - Mike D</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Every Single Weekend (feat. Jamie xx)</v>
+        <v>Too Easy</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
+        <v>https://music.apple.com/us/song/too-easy/6774752170</v>
       </c>
       <c r="D115" t="str">
         <v>2026-06-08</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
+        <v>Too Easy - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>2:10</v>
+        <v>1:54</v>
       </c>
       <c r="H115" t="str">
-        <v>The Avalanches</v>
+        <v>Tinashe</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/tinashe/464835513</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
+        <v>https://music.apple.com/us/album/too-easy/6774752168</v>
       </c>
       <c r="L115" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
+        <v>Too Easy - Tinashe</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Bluffin'</v>
+        <v>I Knew It, I Knew You</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
+        <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
       </c>
       <c r="D116" t="str">
         <v>2026-06-08</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Piss In The Wind (Deluxe)</v>
+        <v>I Knew It, I Knew You - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>2:34</v>
+        <v>2:58</v>
       </c>
       <c r="H116" t="str">
-        <v>Joji</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
+        <v>https://music.apple.com/us/album/i-knew-it-i-knew-you/6775527442</v>
       </c>
       <c r="L116" t="str">
-        <v>Bluffin' - Joji</v>
+        <v>I Knew It, I Knew You - Taylor Swift</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Dreams</v>
+        <v>Love Sensation</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/dreams/1884731028</v>
+        <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
       </c>
       <c r="D117" t="str">
         <v>2026-06-08</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Free Your Mind</v>
+        <v>Love Sensation - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:56</v>
+        <v>3:48</v>
       </c>
       <c r="H117" t="str">
-        <v>Prospa</v>
+        <v>Madonna</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/dreams/1884730177</v>
+        <v>https://music.apple.com/us/album/love-sensation/6774810102</v>
       </c>
       <c r="L117" t="str">
-        <v>Dreams - Prospa</v>
+        <v>Love Sensation - Madonna</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Cotton</v>
+        <v>Mi Yo De Antes</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/cotton/1887627941</v>
+        <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
       </c>
       <c r="D118" t="str">
         <v>2026-06-08</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Cry Baby</v>
+        <v>Mi Yo De Antes - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:43</v>
+        <v>3:04</v>
       </c>
       <c r="H118" t="str">
-        <v>Vince Staples</v>
+        <v>Ozuna</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/cotton/1887627836</v>
+        <v>https://music.apple.com/us/album/mi-yo-de-antes/6769193983</v>
       </c>
       <c r="L118" t="str">
-        <v>Cotton - Vince Staples</v>
+        <v>Mi Yo De Antes - Ozuna</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Black Prada Dress</v>
+        <v>Three Nations</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
+        <v>https://music.apple.com/us/song/three-nations/6776010602</v>
       </c>
       <c r="D119" t="str">
         <v>2026-06-08</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>I Know Too Much</v>
+        <v>Official FIFA World Cup 2026™ Album</v>
       </c>
       <c r="G119" t="str">
-        <v>3:19</v>
+        <v>3:30</v>
       </c>
       <c r="H119" t="str">
-        <v>Ellie Goulding</v>
+        <v>21 Savage</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
+        <v>https://music.apple.com/us/artist/21-savage/894820464</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
+        <v>https://music.apple.com/us/album/three-nations/6776010591</v>
       </c>
       <c r="L119" t="str">
-        <v>Black Prada Dress - Ellie Goulding</v>
+        <v>Three Nations - 21 Savage</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Don’t Break Her Heart</v>
+        <v>Champions (WC 26)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
+        <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
       </c>
       <c r="D120" t="str">
         <v>2026-06-08</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>THERAPY AT THE CLUB</v>
+        <v>Champions (WC 26) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:44</v>
+        <v>4:15</v>
       </c>
       <c r="H120" t="str">
-        <v>FLO</v>
+        <v>IShowSpeed</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/ishowspeed/1574723975</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
+        <v>https://music.apple.com/us/album/champions-wc-26/6775282246</v>
       </c>
       <c r="L120" t="str">
-        <v>Don’t Break Her Heart - FLO</v>
+        <v>Champions (WC 26) - IShowSpeed</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Sexy Ladies (feat. UCB)</v>
+        <v>ENCERRONES</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
+        <v>https://music.apple.com/us/song/encerrones/6771854522</v>
       </c>
       <c r="D121" t="str">
         <v>2026-06-08</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>BITCH</v>
+        <v>TEOFANIA</v>
       </c>
       <c r="G121" t="str">
-        <v>2:50</v>
+        <v>2:23</v>
       </c>
       <c r="H121" t="str">
-        <v>Lizzo</v>
+        <v>LENCHO</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
+        <v>https://music.apple.com/us/album/encerrones/6771854517</v>
       </c>
       <c r="L121" t="str">
-        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
+        <v>ENCERRONES - LENCHO</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Noche Without You</v>
+        <v>Cowgirl</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
+        <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
       </c>
       <c r="D122" t="str">
         <v>2026-06-08</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>SOMA</v>
+        <v>The Outlaw Cherie Lee &amp; Other Western Tales</v>
       </c>
       <c r="G122" t="str">
-        <v>3:23</v>
+        <v>2:56</v>
       </c>
       <c r="H122" t="str">
-        <v>Skrillex</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
+        <v>https://music.apple.com/us/album/cowgirl/1894906682</v>
       </c>
       <c r="L122" t="str">
-        <v>Noche Without You - Skrillex</v>
+        <v>Cowgirl - Shaboozey</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Difficult Love</v>
+        <v>PASSENGER</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
+        <v>https://music.apple.com/us/song/passenger/6773456081</v>
       </c>
       <c r="D123" t="str">
         <v>2026-06-08</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Do That Again</v>
+        <v>WILDCHILD</v>
       </c>
       <c r="G123" t="str">
-        <v>2:33</v>
+        <v>2:39</v>
       </c>
       <c r="H123" t="str">
-        <v>Malcolm Todd</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
+        <v>https://music.apple.com/us/album/passenger/6773456078</v>
       </c>
       <c r="L123" t="str">
-        <v>Difficult Love - Malcolm Todd</v>
+        <v>PASSENGER - Alex Warren</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Tastes So Good</v>
+        <v>Secret Language</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
+        <v>https://music.apple.com/us/song/secret-language/6774223667</v>
       </c>
       <c r="D124" t="str">
         <v>2026-06-08</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Dinner Party</v>
+        <v>Sweet Fortune</v>
       </c>
       <c r="G124" t="str">
-        <v>3:05</v>
+        <v>3:53</v>
       </c>
       <c r="H124" t="str">
-        <v>Niall Horan</v>
+        <v>Ryan Beatty</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/ryan-beatty/483234172</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
+        <v>https://music.apple.com/us/album/secret-language/6774223660</v>
       </c>
       <c r="L124" t="str">
-        <v>Tastes So Good - Niall Horan</v>
+        <v>Secret Language - Ryan Beatty</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Phone, Keys, Wallet</v>
+        <v>High Hopes 3000</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
+        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
       </c>
       <c r="D125" t="str">
         <v>2026-06-08</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Phone, Keys, Wallet - Single</v>
+        <v>Chuck Timely &amp; The Hourglass</v>
       </c>
       <c r="G125" t="str">
-        <v>2:52</v>
+        <v>4:05</v>
       </c>
       <c r="H125" t="str">
-        <v>Lainey Wilson</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/role-model/199215762</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
+        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
       </c>
       <c r="L125" t="str">
-        <v>Phone, Keys, Wallet - Lainey Wilson</v>
+        <v>High Hopes 3000 - ROLE MODEL</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Madrugada</v>
+        <v>Vertical</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
+        <v>https://music.apple.com/us/song/vertical/1892436336</v>
       </c>
       <c r="D126" t="str">
         <v>2026-06-08</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Madrugada - Single</v>
+        <v>Emotional Junglist</v>
       </c>
       <c r="G126" t="str">
-        <v>2:58</v>
+        <v>2:36</v>
       </c>
       <c r="H126" t="str">
-        <v>Chino Pacas</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
+        <v>https://music.apple.com/us/album/vertical/1892436329</v>
       </c>
       <c r="L126" t="str">
-        <v>Madrugada - Chino Pacas</v>
+        <v>Vertical - Nia Archives</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Oh Chet (feat. Travis Scott)</v>
+        <v>snake the drain</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
+        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
       </c>
       <c r="D127" t="str">
         <v>2026-06-08</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Single</v>
+        <v>this time it’s different / snake the drain - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:23</v>
+        <v>3:08</v>
       </c>
       <c r="H127" t="str">
-        <v>Jey One</v>
+        <v>Devon Again</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
+        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
+        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
       </c>
       <c r="L127" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
+        <v>snake the drain - Devon Again</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>An Hour or So (Live at Apple Music Radio)</v>
+        <v>Every Single Weekend (feat. Jamie xx)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
+        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D128" t="str">
         <v>2026-06-08</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:02</v>
+        <v>2:10</v>
       </c>
       <c r="H128" t="str">
-        <v>Benny G</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
+        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
       </c>
       <c r="L128" t="str">
-        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
+        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>it’s just White Noise</v>
+        <v>Bluffin'</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
+        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
       </c>
       <c r="D129" t="str">
         <v>2026-06-08</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>it’s a real Cruel World - EP</v>
+        <v>Piss In The Wind (Deluxe)</v>
       </c>
       <c r="G129" t="str">
-        <v>3:57</v>
+        <v>2:34</v>
       </c>
       <c r="H129" t="str">
-        <v>Holly Humberstone</v>
+        <v>Joji</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
+        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
       </c>
       <c r="L129" t="str">
-        <v>it’s just White Noise - Holly Humberstone</v>
+        <v>Bluffin' - Joji</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>the feeling</v>
+        <v>Dreams</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
+        <v>https://music.apple.com/us/song/dreams/1884731028</v>
       </c>
       <c r="D130" t="str">
         <v>2026-06-08</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Oh yeah?</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="G130" t="str">
-        <v>4:35</v>
+        <v>3:56</v>
       </c>
       <c r="H130" t="str">
-        <v>Steve Lacy</v>
+        <v>Prospa</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
+        <v>https://music.apple.com/us/album/dreams/1884730177</v>
       </c>
       <c r="L130" t="str">
-        <v>the feeling - Steve Lacy</v>
+        <v>Dreams - Prospa</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>baby (Live at Apple Music Radio)</v>
+        <v>Cotton</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
+        <v>https://music.apple.com/us/song/cotton/1887627941</v>
       </c>
       <c r="D131" t="str">
         <v>2026-06-08</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G131" t="str">
-        <v>3:14</v>
+        <v>3:43</v>
       </c>
       <c r="H131" t="str">
-        <v>Gabriel Jacoby</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
+        <v>https://music.apple.com/us/album/cotton/1887627836</v>
       </c>
       <c r="L131" t="str">
-        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
+        <v>Cotton - Vince Staples</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Drop The Lo</v>
+        <v>Black Prada Dress</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
+        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
       </c>
       <c r="D132" t="str">
         <v>2026-06-08</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Drop The Lo - Single</v>
+        <v>I Know Too Much</v>
       </c>
       <c r="G132" t="str">
-        <v>2:41</v>
+        <v>3:19</v>
       </c>
       <c r="H132" t="str">
-        <v>Bryson Tiller</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
+        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
       </c>
       <c r="L132" t="str">
-        <v>Drop The Lo - Bryson Tiller</v>
+        <v>Black Prada Dress - Ellie Goulding</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>GANG BIZNESS feat paygotti</v>
+        <v>Don’t Break Her Heart</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
+        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
       </c>
       <c r="D133" t="str">
         <v>2026-06-08</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>GANG BIZNESS feat paygotti - Single</v>
+        <v>THERAPY AT THE CLUB</v>
       </c>
       <c r="G133" t="str">
-        <v>2:47</v>
+        <v>3:44</v>
       </c>
       <c r="H133" t="str">
-        <v>YG</v>
+        <v>FLO</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
+        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
       </c>
       <c r="L133" t="str">
-        <v>GANG BIZNESS feat paygotti - YG</v>
+        <v>Don’t Break Her Heart - FLO</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Lay It Down</v>
+        <v>Sexy Ladies (feat. UCB)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
+        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
       </c>
       <c r="D134" t="str">
         <v>2026-06-08</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Lay It Down - Single</v>
+        <v>BITCH</v>
       </c>
       <c r="G134" t="str">
-        <v>2:38</v>
+        <v>2:50</v>
       </c>
       <c r="H134" t="str">
-        <v>FattMack</v>
+        <v>Lizzo</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
+        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
       </c>
       <c r="L134" t="str">
-        <v>Lay It Down - FattMack</v>
+        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>WAX PAPER</v>
+        <v>Noche Without You</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
+        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
       </c>
       <c r="D135" t="str">
         <v>2026-06-08</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>WHACK'S MUSEUM</v>
+        <v>SOMA</v>
       </c>
       <c r="G135" t="str">
-        <v>2:43</v>
+        <v>3:23</v>
       </c>
       <c r="H135" t="str">
-        <v>Tierra Whack</v>
+        <v>Skrillex</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
+        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
       </c>
       <c r="L135" t="str">
-        <v>WAX PAPER - Tierra Whack</v>
+        <v>Noche Without You - Skrillex</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>abusadOra (tambores)</v>
+        <v>Difficult Love</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
+        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
       </c>
       <c r="D136" t="str">
         <v>2026-06-08</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>ANTES DE QUE SEA TARDE</v>
+        <v>Do That Again</v>
       </c>
       <c r="G136" t="str">
-        <v>3:11</v>
+        <v>2:33</v>
       </c>
       <c r="H136" t="str">
-        <v>Yorghaki</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
+        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
       </c>
       <c r="L136" t="str">
-        <v>abusadOra (tambores) - Yorghaki</v>
+        <v>Difficult Love - Malcolm Todd</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Ruin</v>
+        <v>Tastes So Good</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/ruin/6763176090</v>
+        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
       </c>
       <c r="D137" t="str">
         <v>2026-06-08</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Labor Of Love</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G137" t="str">
-        <v>3:19</v>
+        <v>3:05</v>
       </c>
       <c r="H137" t="str">
-        <v>Blxst</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/ruin/1895199881</v>
+        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
       </c>
       <c r="L137" t="str">
-        <v>Ruin - Blxst</v>
+        <v>Tastes So Good - Niall Horan</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Do Today</v>
+        <v>Phone, Keys, Wallet</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/do-today/1893402864</v>
+        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
       </c>
       <c r="D138" t="str">
         <v>2026-06-08</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Grateful</v>
+        <v>Phone, Keys, Wallet - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>4:14</v>
+        <v>2:52</v>
       </c>
       <c r="H138" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/do-today/1893402542</v>
+        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
       </c>
       <c r="L138" t="str">
-        <v>Do Today - The Red Clay Strays</v>
+        <v>Phone, Keys, Wallet - Lainey Wilson</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Stone Over Water</v>
+        <v>Madrugada</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
+        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
       </c>
       <c r="D139" t="str">
         <v>2026-06-08</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>I Built You A Tower</v>
+        <v>Madrugada - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:14</v>
+        <v>2:58</v>
       </c>
       <c r="H139" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Chino Pacas</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
+        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
       </c>
       <c r="L139" t="str">
-        <v>Stone Over Water - Death Cab for Cutie</v>
+        <v>Madrugada - Chino Pacas</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
+        <v>Oh Chet (feat. Travis Scott)</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
+        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
       </c>
       <c r="D140" t="str">
         <v>2026-06-08</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Weezer</v>
+        <v>Oh Chet (feat. Travis Scott) - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:34</v>
+        <v>2:23</v>
       </c>
       <c r="H140" t="str">
-        <v>Weezer</v>
+        <v>Jey One</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/weezer/115234</v>
+        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
+        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
       </c>
       <c r="L140" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
+        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Tell Me When You've Had Enough</v>
+        <v>An Hour or So (Live at Apple Music Radio)</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
+        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
       </c>
       <c r="D141" t="str">
         <v>2026-06-08</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Sanctuary</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G141" t="str">
-        <v>3:19</v>
+        <v>3:02</v>
       </c>
       <c r="H141" t="str">
-        <v>Evanescence</v>
+        <v>Benny G</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
+        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
       </c>
       <c r="L141" t="str">
-        <v>Tell Me When You've Had Enough - Evanescence</v>
+        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Your Ghost Again</v>
+        <v>it’s just White Noise</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
+        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
       </c>
       <c r="D142" t="str">
         <v>2026-06-08</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Your Ghost Again - Single</v>
+        <v>it’s a real Cruel World - EP</v>
       </c>
       <c r="G142" t="str">
-        <v>4:35</v>
+        <v>3:57</v>
       </c>
       <c r="H142" t="str">
-        <v>Mastodon</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
+        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
       </c>
       <c r="L142" t="str">
-        <v>Your Ghost Again - Mastodon</v>
+        <v>it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Nightshift Superstar</v>
+        <v>the feeling</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
+        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
       </c>
       <c r="D143" t="str">
         <v>2026-06-08</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>The Wow! Signal</v>
+        <v>Oh yeah?</v>
       </c>
       <c r="G143" t="str">
-        <v>4:07</v>
+        <v>4:35</v>
       </c>
       <c r="H143" t="str">
-        <v>Muse</v>
+        <v>Steve Lacy</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
+        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
       </c>
       <c r="L143" t="str">
-        <v>Nightshift Superstar - Muse</v>
+        <v>the feeling - Steve Lacy</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>UNDER THE RHYTHM</v>
+        <v>baby (Live at Apple Music Radio)</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
+        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
       </c>
       <c r="D144" t="str">
         <v>2026-06-08</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>ADAM</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G144" t="str">
-        <v>2:50</v>
+        <v>3:14</v>
       </c>
       <c r="H144" t="str">
-        <v>Adam Lambert</v>
+        <v>Gabriel Jacoby</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
+        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
+        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
       </c>
       <c r="L144" t="str">
-        <v>UNDER THE RHYTHM - Adam Lambert</v>
+        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>You’re Mine</v>
+        <v>Drop The Lo</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
+        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
       </c>
       <c r="D145" t="str">
         <v>2026-06-08</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Papercut</v>
+        <v>Drop The Lo - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>4:25</v>
+        <v>2:41</v>
       </c>
       <c r="H145" t="str">
-        <v>Imani Imani</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
+        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
       </c>
       <c r="L145" t="str">
-        <v>You’re Mine - Imani Imani</v>
+        <v>Drop The Lo - Bryson Tiller</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>point blank</v>
+        <v>GANG BIZNESS feat paygotti</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
+        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
       </c>
       <c r="D146" t="str">
         <v>2026-06-08</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>new avatar</v>
+        <v>GANG BIZNESS feat paygotti - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>4:26</v>
+        <v>2:47</v>
       </c>
       <c r="H146" t="str">
-        <v>Kelela</v>
+        <v>YG</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
+        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
       </c>
       <c r="L146" t="str">
-        <v>point blank - Kelela</v>
+        <v>GANG BIZNESS feat paygotti - YG</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>that's my beach!</v>
+        <v>Lay It Down</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
+        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
       </c>
       <c r="D147" t="str">
         <v>2026-06-08</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>Lay It Down - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:18</v>
+        <v>2:38</v>
       </c>
       <c r="H147" t="str">
-        <v>horsegiirL</v>
+        <v>FattMack</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
+        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
       </c>
       <c r="L147" t="str">
-        <v>that's my beach! - horsegiirL</v>
+        <v>Lay It Down - FattMack</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>In Your Eyes</v>
+        <v>WAX PAPER</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
+        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
       </c>
       <c r="D148" t="str">
         <v>2026-06-08</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>In Your Eyes - Single</v>
+        <v>WHACK'S MUSEUM</v>
       </c>
       <c r="G148" t="str">
-        <v>3:36</v>
+        <v>2:43</v>
       </c>
       <c r="H148" t="str">
-        <v>Alesso</v>
+        <v>Tierra Whack</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/alesso/432464201</v>
+        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
+        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
       </c>
       <c r="L148" t="str">
-        <v>In Your Eyes - Alesso</v>
+        <v>WAX PAPER - Tierra Whack</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>ALL OR NOTHING</v>
+        <v>abusadOra (tambores)</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
+        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
       </c>
       <c r="D149" t="str">
         <v>2026-06-08</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>ALL OR NOTHING - Single</v>
+        <v>ANTES DE QUE SEA TARDE</v>
       </c>
       <c r="G149" t="str">
-        <v>3:17</v>
+        <v>3:11</v>
       </c>
       <c r="H149" t="str">
-        <v>Tobe Nwigwe</v>
+        <v>Yorghaki</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
+        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
+        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
       </c>
       <c r="L149" t="str">
-        <v>ALL OR NOTHING - Tobe Nwigwe</v>
+        <v>abusadOra (tambores) - Yorghaki</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>IN MY HANDS</v>
+        <v>Ruin</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
+        <v>https://music.apple.com/us/song/ruin/6763176090</v>
       </c>
       <c r="D150" t="str">
         <v>2026-06-08</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>IN MY HANDS - Single</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G150" t="str">
-        <v>3:14</v>
+        <v>3:19</v>
       </c>
       <c r="H150" t="str">
-        <v>Alessia Cara</v>
+        <v>Blxst</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
+        <v>https://music.apple.com/us/album/ruin/1895199881</v>
       </c>
       <c r="L150" t="str">
-        <v>IN MY HANDS - Alessia Cara</v>
+        <v>Ruin - Blxst</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Life's a Dream</v>
+        <v>Do Today</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
+        <v>https://music.apple.com/us/song/do-today/1893402864</v>
       </c>
       <c r="D151" t="str">
         <v>2026-06-08</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>Grateful</v>
       </c>
       <c r="G151" t="str">
-        <v>5:31</v>
+        <v>4:14</v>
       </c>
       <c r="H151" t="str">
-        <v>Modest Mouse</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
+        <v>https://music.apple.com/us/album/do-today/1893402542</v>
       </c>
       <c r="L151" t="str">
-        <v>Life's a Dream - Modest Mouse</v>
+        <v>Do Today - The Red Clay Strays</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
+        <v>Stone Over Water</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
+        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
       </c>
       <c r="D152" t="str">
         <v>2026-06-08</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Season of Surrender</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G152" t="str">
-        <v>4:47</v>
+        <v>3:14</v>
       </c>
       <c r="H152" t="str">
-        <v>August Burns Red</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
+        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
       </c>
       <c r="L152" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
+        <v>Stone Over Water - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Shine</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/shine/6764654536</v>
+        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
       </c>
       <c r="D153" t="str">
         <v>2026-06-08</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Black Mozart</v>
+        <v>Weezer</v>
       </c>
       <c r="G153" t="str">
-        <v>2:27</v>
+        <v>3:34</v>
       </c>
       <c r="H153" t="str">
-        <v>Jon Batiste</v>
+        <v>Weezer</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/weezer/115234</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/shine/1895866355</v>
+        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
       </c>
       <c r="L153" t="str">
-        <v>Shine - Jon Batiste</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Half The Man</v>
+        <v>Tell Me When You've Had Enough</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
+        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
       </c>
       <c r="D154" t="str">
         <v>2026-06-08</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Scared of Heights</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G154" t="str">
-        <v>3:56</v>
+        <v>3:19</v>
       </c>
       <c r="H154" t="str">
-        <v>Wyatt Flores</v>
+        <v>Evanescence</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
+        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
       </c>
       <c r="L154" t="str">
-        <v>Half The Man - Wyatt Flores</v>
+        <v>Tell Me When You've Had Enough - Evanescence</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Preacher’s Kid</v>
+        <v>Your Ghost Again</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
+        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
       </c>
       <c r="D155" t="str">
         <v>2026-06-08</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Preacher’s Kid - Single</v>
+        <v>Your Ghost Again - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>5:02</v>
+        <v>4:35</v>
       </c>
       <c r="H155" t="str">
-        <v>Stephen Wilson Jr.</v>
+        <v>Mastodon</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
+        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
+        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
       </c>
       <c r="L155" t="str">
-        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
+        <v>Your Ghost Again - Mastodon</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Weak</v>
+        <v>Nightshift Superstar</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/weak/6771151098</v>
+        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
       </c>
       <c r="D156" t="str">
         <v>2026-06-08</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Weak - Single</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G156" t="str">
-        <v>3:28</v>
+        <v>4:07</v>
       </c>
       <c r="H156" t="str">
-        <v>Naomi Sharon</v>
+        <v>Muse</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/weak/6771151088</v>
+        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
       </c>
       <c r="L156" t="str">
-        <v>Weak - Naomi Sharon</v>
+        <v>Nightshift Superstar - Muse</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>ALL NIGHT LONG</v>
+        <v>UNDER THE RHYTHM</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
+        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
       </c>
       <c r="D157" t="str">
         <v>2026-06-08</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>A Rii Set</v>
+        <v>ADAM</v>
       </c>
       <c r="G157" t="str">
-        <v>2:28</v>
+        <v>2:50</v>
       </c>
       <c r="H157" t="str">
-        <v>Pheelz</v>
+        <v>Adam Lambert</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
+        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
       </c>
       <c r="L157" t="str">
-        <v>ALL NIGHT LONG - Pheelz</v>
+        <v>UNDER THE RHYTHM - Adam Lambert</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Every Life</v>
+        <v>You’re Mine</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/every-life/6764110978</v>
+        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
       </c>
       <c r="D158" t="str">
         <v>2026-06-08</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>Papercut</v>
       </c>
       <c r="G158" t="str">
-        <v>3:18</v>
+        <v>4:25</v>
       </c>
       <c r="H158" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Imani Imani</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/every-life/1895644574</v>
+        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
       </c>
       <c r="L158" t="str">
-        <v>Every Life - Isabel LaRosa</v>
+        <v>You’re Mine - Imani Imani</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Home</v>
+        <v>point blank</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/home/6774718029</v>
+        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
       </c>
       <c r="D159" t="str">
         <v>2026-06-08</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Good Grief</v>
+        <v>new avatar</v>
       </c>
       <c r="G159" t="str">
-        <v>4:53</v>
+        <v>4:26</v>
       </c>
       <c r="H159" t="str">
-        <v>Sara Bareilles</v>
+        <v>Kelela</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/home/6774718027</v>
+        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
       </c>
       <c r="L159" t="str">
-        <v>Home - Sara Bareilles</v>
+        <v>point blank - Kelela</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Satalanaaa</v>
+        <v>that's my beach!</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
+        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
       </c>
       <c r="D160" t="str">
         <v>2026-06-08</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Satalanaaa - Single</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G160" t="str">
-        <v>2:06</v>
+        <v>3:18</v>
       </c>
       <c r="H160" t="str">
-        <v>Pitbull</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
+        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
       </c>
       <c r="L160" t="str">
-        <v>Satalanaaa - Pitbull</v>
+        <v>that's my beach! - horsegiirL</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Miss Me More</v>
+        <v>In Your Eyes</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
+        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
       </c>
       <c r="D161" t="str">
         <v>2026-06-08</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Confessions of a Lonely Heart</v>
+        <v>In Your Eyes - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:43</v>
+        <v>3:36</v>
       </c>
       <c r="H161" t="str">
-        <v>Eric Nam</v>
+        <v>Alesso</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
+        <v>https://music.apple.com/us/artist/alesso/432464201</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
+        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
       </c>
       <c r="L161" t="str">
-        <v>Miss Me More - Eric Nam</v>
+        <v>In Your Eyes - Alesso</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Rituals</v>
+        <v>ALL OR NOTHING</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/rituals/6769628916</v>
+        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
       </c>
       <c r="D162" t="str">
         <v>2026-06-08</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Rituals - Single</v>
+        <v>ALL OR NOTHING - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:10</v>
+        <v>3:17</v>
       </c>
       <c r="H162" t="str">
-        <v>Rico Nasty</v>
+        <v>Tobe Nwigwe</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
+        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/rituals/6769628915</v>
+        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
       </c>
       <c r="L162" t="str">
-        <v>Rituals - Rico Nasty</v>
+        <v>ALL OR NOTHING - Tobe Nwigwe</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Honeysuckle</v>
+        <v>IN MY HANDS</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
+        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
       </c>
       <c r="D163" t="str">
         <v>2026-06-08</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Honeysuckle - Single</v>
+        <v>IN MY HANDS - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:15</v>
+        <v>3:14</v>
       </c>
       <c r="H163" t="str">
-        <v>Dylan Gossett</v>
+        <v>Alessia Cara</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
+        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
+        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
       </c>
       <c r="L163" t="str">
-        <v>Honeysuckle - Dylan Gossett</v>
+        <v>IN MY HANDS - Alessia Cara</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>listen…</v>
+        <v>Life's a Dream</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/listen/6775576508</v>
+        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
       </c>
       <c r="D164" t="str">
         <v>2026-06-08</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G164" t="str">
-        <v>4:08</v>
+        <v>5:31</v>
       </c>
       <c r="H164" t="str">
-        <v>John Williams</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/john-williams/63748</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/listen/6775576506</v>
+        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
       </c>
       <c r="L164" t="str">
-        <v>listen… - John Williams</v>
+        <v>Life's a Dream - Modest Mouse</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>DEADMEAT</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
+        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
       </c>
       <c r="D165" t="str">
         <v>2026-06-08</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>DEADMEAT - Single</v>
+        <v>Season of Surrender</v>
       </c>
       <c r="G165" t="str">
-        <v>2:52</v>
+        <v>4:47</v>
       </c>
       <c r="H165" t="str">
-        <v>South Arcade</v>
+        <v>August Burns Red</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
+        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
       </c>
       <c r="L165" t="str">
-        <v>DEADMEAT - South Arcade</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Ugly and Rotten</v>
+        <v>Shine</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
+        <v>https://music.apple.com/us/song/shine/6764654536</v>
       </c>
       <c r="D166" t="str">
         <v>2026-06-08</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Ugly and Rotten - Single</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G166" t="str">
-        <v>2:49</v>
+        <v>2:27</v>
       </c>
       <c r="H166" t="str">
-        <v>Mckenna Grace</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
+        <v>https://music.apple.com/us/album/shine/1895866355</v>
       </c>
       <c r="L166" t="str">
-        <v>Ugly and Rotten - Mckenna Grace</v>
+        <v>Shine - Jon Batiste</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Whisper</v>
+        <v>Half The Man</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/whisper/6772254272</v>
+        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
       </c>
       <c r="D167" t="str">
         <v>2026-06-08</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Whisper - Single</v>
+        <v>Scared of Heights</v>
       </c>
       <c r="G167" t="str">
-        <v>2:47</v>
+        <v>3:56</v>
       </c>
       <c r="H167" t="str">
-        <v>Blu DeTiger</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/whisper/6772254268</v>
+        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
       </c>
       <c r="L167" t="str">
-        <v>Whisper - Blu DeTiger</v>
+        <v>Half The Man - Wyatt Flores</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Gecko (feat. Haley Bridge)</v>
+        <v>Preacher’s Kid</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
+        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
       </c>
       <c r="D168" t="str">
         <v>2026-06-08</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>How dare you tryna love me? - EP</v>
+        <v>Preacher’s Kid - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:46</v>
+        <v>5:02</v>
       </c>
       <c r="H168" t="str">
-        <v>Olga Myko</v>
+        <v>Stephen Wilson Jr.</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
+        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
+        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
       </c>
       <c r="L168" t="str">
-        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
+        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Compa Primo</v>
+        <v>Weak</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
+        <v>https://music.apple.com/us/song/weak/6771151098</v>
       </c>
       <c r="D169" t="str">
         <v>2026-06-08</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Compa Primo - Single</v>
+        <v>Weak - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:12</v>
+        <v>3:28</v>
       </c>
       <c r="H169" t="str">
-        <v>Nueva H</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
+        <v>https://music.apple.com/us/album/weak/6771151088</v>
       </c>
       <c r="L169" t="str">
-        <v>Compa Primo - Nueva H</v>
+        <v>Weak - Naomi Sharon</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Parachute</v>
+        <v>ALL NIGHT LONG</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/parachute/6768841410</v>
+        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
       </c>
       <c r="D170" t="str">
         <v>2026-06-08</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Parachute - Single</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G170" t="str">
-        <v>3:11</v>
+        <v>2:28</v>
       </c>
       <c r="H170" t="str">
-        <v>Tyler James Bellinger</v>
+        <v>Pheelz</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/parachute/6768841409</v>
+        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
       </c>
       <c r="L170" t="str">
-        <v>Parachute - Tyler James Bellinger</v>
+        <v>ALL NIGHT LONG - Pheelz</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Like a Bubble</v>
+        <v>Every Life</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
+        <v>https://music.apple.com/us/song/every-life/6764110978</v>
       </c>
       <c r="D171" t="str">
         <v>2026-06-08</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Imperfect-I'mperfect - EP</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G171" t="str">
-        <v>3:08</v>
+        <v>3:18</v>
       </c>
       <c r="H171" t="str">
-        <v>FIFTY FIFTY</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
+        <v>https://music.apple.com/us/album/every-life/1895644574</v>
       </c>
       <c r="L171" t="str">
-        <v>Like a Bubble - FIFTY FIFTY</v>
+        <v>Every Life - Isabel LaRosa</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Hustle and Opulence in America</v>
+        <v>Home</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
+        <v>https://music.apple.com/us/song/home/6774718029</v>
       </c>
       <c r="D172" t="str">
         <v>2026-06-08</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>AK Cuts: Vol. 4 - EP</v>
+        <v>Good Grief</v>
       </c>
       <c r="G172" t="str">
-        <v>3:07</v>
+        <v>4:53</v>
       </c>
       <c r="H172" t="str">
-        <v>Anish Kumar</v>
+        <v>Sara Bareilles</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
+        <v>https://music.apple.com/us/album/home/6774718027</v>
       </c>
       <c r="L172" t="str">
-        <v>Hustle and Opulence in America - Anish Kumar</v>
+        <v>Home - Sara Bareilles</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
+        <v>Satalanaaa</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
+        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
       </c>
       <c r="D173" t="str">
         <v>2026-06-08</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
+        <v>Satalanaaa - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:47</v>
+        <v>2:06</v>
       </c>
       <c r="H173" t="str">
-        <v>ivri</v>
+        <v>Pitbull</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
+        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
       </c>
       <c r="L173" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
+        <v>Satalanaaa - Pitbull</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>CLEAN SWEEP</v>
+        <v>Miss Me More</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
+        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
       </c>
       <c r="D174" t="str">
         <v>2026-06-08</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>CLEAN SWEEP - Single</v>
+        <v>Confessions of a Lonely Heart</v>
       </c>
       <c r="G174" t="str">
-        <v>3:11</v>
+        <v>2:43</v>
       </c>
       <c r="H174" t="str">
-        <v>Storm Reid</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
+        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
       </c>
       <c r="L174" t="str">
-        <v>CLEAN SWEEP - Storm Reid</v>
+        <v>Miss Me More - Eric Nam</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>CANDYLAND!</v>
+        <v>Rituals</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/candyland/6766927008</v>
+        <v>https://music.apple.com/us/song/rituals/6769628916</v>
       </c>
       <c r="D175" t="str">
         <v>2026-06-08</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>CANDYLAND! - Single</v>
+        <v>Rituals - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:15</v>
+        <v>2:10</v>
       </c>
       <c r="H175" t="str">
-        <v>Natanya</v>
+        <v>Rico Nasty</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
+        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/candyland/6766927000</v>
+        <v>https://music.apple.com/us/album/rituals/6769628915</v>
       </c>
       <c r="L175" t="str">
-        <v>CANDYLAND! - Natanya</v>
+        <v>Rituals - Rico Nasty</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Double C</v>
+        <v>Honeysuckle</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/double-c/6771836555</v>
+        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
       </c>
       <c r="D176" t="str">
         <v>2026-06-08</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Double C - Single</v>
+        <v>Honeysuckle - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:21</v>
+        <v>3:15</v>
       </c>
       <c r="H176" t="str">
-        <v>Sk8star</v>
+        <v>Dylan Gossett</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
+        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/double-c/6771836554</v>
+        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
       </c>
       <c r="L176" t="str">
-        <v>Double C - Sk8star</v>
+        <v>Honeysuckle - Dylan Gossett</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>madera</v>
+        <v>listen…</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/madera/6764638112</v>
+        <v>https://music.apple.com/us/song/listen/6775576508</v>
       </c>
       <c r="D177" t="str">
         <v>2026-06-08</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>madera/un camino luminoso - Single</v>
+        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G177" t="str">
-        <v>5:41</v>
+        <v>4:08</v>
       </c>
       <c r="H177" t="str">
-        <v>Lumtz</v>
+        <v>John Williams</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
+        <v>https://music.apple.com/us/artist/john-williams/63748</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/madera/6764638109</v>
+        <v>https://music.apple.com/us/album/listen/6775576506</v>
       </c>
       <c r="L177" t="str">
-        <v>madera - Lumtz</v>
+        <v>listen… - John Williams</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Slip the Noose</v>
+        <v>DEADMEAT</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
+        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
       </c>
       <c r="D178" t="str">
         <v>2026-06-08</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Hum of Hurt</v>
+        <v>DEADMEAT - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>1:43</v>
+        <v>2:52</v>
       </c>
       <c r="H178" t="str">
-        <v>Converge</v>
+        <v>South Arcade</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
+        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
       </c>
       <c r="L178" t="str">
-        <v>Slip the Noose - Converge</v>
+        <v>DEADMEAT - South Arcade</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Crying Fire</v>
+        <v>Ugly and Rotten</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
+        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
       </c>
       <c r="D179" t="str">
         <v>2026-06-08</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Crying Fire - Single</v>
+        <v>Ugly and Rotten - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>4:08</v>
+        <v>2:49</v>
       </c>
       <c r="H179" t="str">
-        <v>Avatar</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/avatar/187616241</v>
+        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
+        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
       </c>
       <c r="L179" t="str">
-        <v>Crying Fire - Avatar</v>
+        <v>Ugly and Rotten - Mckenna Grace</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>NI NA’</v>
+        <v>Whisper</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
+        <v>https://music.apple.com/us/song/whisper/6772254272</v>
       </c>
       <c r="D180" t="str">
         <v>2026-06-08</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>sorry si soy GRRRIS</v>
+        <v>Whisper - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:53</v>
+        <v>2:47</v>
       </c>
       <c r="H180" t="str">
-        <v>ROBI</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/robi/1458047972</v>
+        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
+        <v>https://music.apple.com/us/album/whisper/6772254268</v>
       </c>
       <c r="L180" t="str">
-        <v>NI NA’ - ROBI</v>
+        <v>Whisper - Blu DeTiger</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Holding Back</v>
+        <v>Gecko (feat. Haley Bridge)</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
+        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
       </c>
       <c r="D181" t="str">
         <v>2026-06-08</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>AMA</v>
+        <v>How dare you tryna love me? - EP</v>
       </c>
       <c r="G181" t="str">
-        <v>3:19</v>
+        <v>2:46</v>
       </c>
       <c r="H181" t="str">
-        <v>Ama</v>
+        <v>Olga Myko</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
+        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
       </c>
       <c r="L181" t="str">
-        <v>Holding Back - Ama</v>
+        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>you're still mine</v>
+        <v>Compa Primo</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
+        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
       </c>
       <c r="D182" t="str">
         <v>2026-06-08</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>you're still mine - Single</v>
+        <v>Compa Primo - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:19</v>
+        <v>3:12</v>
       </c>
       <c r="H182" t="str">
-        <v>Lexi Jayde</v>
+        <v>Nueva H</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
+        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
+        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
       </c>
       <c r="L182" t="str">
-        <v>you're still mine - Lexi Jayde</v>
+        <v>Compa Primo - Nueva H</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>teksi</v>
+        <v>Parachute</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/teksi/6769899742</v>
+        <v>https://music.apple.com/us/song/parachute/6768841410</v>
       </c>
       <c r="D183" t="str">
         <v>2026-06-08</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>pOCHO</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:48</v>
+        <v>3:11</v>
       </c>
       <c r="H183" t="str">
-        <v>8onthebeat</v>
+        <v>Tyler James Bellinger</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
+        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/teksi/6769899739</v>
+        <v>https://music.apple.com/us/album/parachute/6768841409</v>
       </c>
       <c r="L183" t="str">
-        <v>teksi - 8onthebeat</v>
+        <v>Parachute - Tyler James Bellinger</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Let You Go</v>
+        <v>Like a Bubble</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
+        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
       </c>
       <c r="D184" t="str">
         <v>2026-06-08</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Let You Go - Single</v>
+        <v>Imperfect-I'mperfect - EP</v>
       </c>
       <c r="G184" t="str">
-        <v>1:37</v>
+        <v>3:08</v>
       </c>
       <c r="H184" t="str">
-        <v>Nate Sib</v>
+        <v>FIFTY FIFTY</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
+        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
+        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
       </c>
       <c r="L184" t="str">
-        <v>Let You Go - Nate Sib</v>
+        <v>Like a Bubble - FIFTY FIFTY</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Dis-Moi</v>
+        <v>Hustle and Opulence in America</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
+        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
       </c>
       <c r="D185" t="str">
         <v>2026-06-08</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>CINNA</v>
+        <v>AK Cuts: Vol. 4 - EP</v>
       </c>
       <c r="G185" t="str">
-        <v>2:27</v>
+        <v>3:07</v>
       </c>
       <c r="H185" t="str">
-        <v>Cannelle</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
+        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
       </c>
       <c r="L185" t="str">
-        <v>Dis-Moi - Cannelle</v>
+        <v>Hustle and Opulence in America - Anish Kumar</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Leverage</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/leverage/6776432312</v>
+        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
       </c>
       <c r="D186" t="str">
         <v>2026-06-08</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Heaven on Mars</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:04</v>
+        <v>2:47</v>
       </c>
       <c r="H186" t="str">
-        <v>NoCap</v>
+        <v>ivri</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/leverage/6776432217</v>
+        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
       </c>
       <c r="L186" t="str">
-        <v>Leverage - NoCap</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Kool Aid</v>
+        <v>CLEAN SWEEP</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
+        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
       </c>
       <c r="D187" t="str">
         <v>2026-06-08</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Where Have All The Good Men Gone? - EP</v>
+        <v>CLEAN SWEEP - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:40</v>
+        <v>3:11</v>
       </c>
       <c r="H187" t="str">
-        <v>Debbii Dawson</v>
+        <v>Storm Reid</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
+        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
+        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
       </c>
       <c r="L187" t="str">
-        <v>Kool Aid - Debbii Dawson</v>
+        <v>CLEAN SWEEP - Storm Reid</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Pieces</v>
+        <v>CANDYLAND!</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/pieces/6771861156</v>
+        <v>https://music.apple.com/us/song/candyland/6766927008</v>
       </c>
       <c r="D188" t="str">
         <v>2026-06-08</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Pieces - Single</v>
+        <v>CANDYLAND! - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:19</v>
+        <v>3:15</v>
       </c>
       <c r="H188" t="str">
-        <v>Dom Innarella</v>
+        <v>Natanya</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
+        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/pieces/6771861155</v>
+        <v>https://music.apple.com/us/album/candyland/6766927000</v>
       </c>
       <c r="L188" t="str">
-        <v>Pieces - Dom Innarella</v>
+        <v>CANDYLAND! - Natanya</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Mesmerized</v>
+        <v>Double C</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
+        <v>https://music.apple.com/us/song/double-c/6771836555</v>
       </c>
       <c r="D189" t="str">
         <v>2026-06-08</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Mesmerized - Single</v>
+        <v>Double C - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:38</v>
+        <v>2:21</v>
       </c>
       <c r="H189" t="str">
-        <v>The Aces</v>
+        <v>Sk8star</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
+        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
+        <v>https://music.apple.com/us/album/double-c/6771836554</v>
       </c>
       <c r="L189" t="str">
-        <v>Mesmerized - The Aces</v>
+        <v>Double C - Sk8star</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Perfect 10</v>
+        <v>madera</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
+        <v>https://music.apple.com/us/song/madera/6764638112</v>
       </c>
       <c r="D190" t="str">
         <v>2026-06-08</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>No Hard Feelings (Deluxe)</v>
+        <v>madera/un camino luminoso - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:51</v>
+        <v>5:41</v>
       </c>
       <c r="H190" t="str">
-        <v>The Beaches</v>
+        <v>Lumtz</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
+        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
+        <v>https://music.apple.com/us/album/madera/6764638109</v>
       </c>
       <c r="L190" t="str">
-        <v>Perfect 10 - The Beaches</v>
+        <v>madera - Lumtz</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Recognize</v>
+        <v>Slip the Noose</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/recognize/6769164705</v>
+        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
       </c>
       <c r="D191" t="str">
         <v>2026-06-08</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Recognize - Single</v>
+        <v>Hum of Hurt</v>
       </c>
       <c r="G191" t="str">
-        <v>2:05</v>
+        <v>1:43</v>
       </c>
       <c r="H191" t="str">
-        <v>Fana Hues</v>
+        <v>Converge</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/recognize/6769164704</v>
+        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
       </c>
       <c r="L191" t="str">
-        <v>Recognize - Fana Hues</v>
+        <v>Slip the Noose - Converge</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Feel The Vibe</v>
+        <v>Crying Fire</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
+        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
       </c>
       <c r="D192" t="str">
         <v>2026-06-08</v>
@@ -7671,68 +7671,562 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Feel The Vibe</v>
+        <v>Crying Fire - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:28</v>
+        <v>4:08</v>
       </c>
       <c r="H192" t="str">
-        <v>Above &amp; Beyond</v>
+        <v>Avatar</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
+        <v>https://music.apple.com/us/artist/avatar/187616241</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
+        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
       </c>
       <c r="L192" t="str">
-        <v>Feel The Vibe - Above &amp; Beyond</v>
+        <v>Crying Fire - Avatar</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
+        <v>NI NA’</v>
+      </c>
+      <c r="B193" t="str">
+        <v/>
+      </c>
+      <c r="C193" t="str">
+        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
+      </c>
+      <c r="D193" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="E193" t="str">
+        <v/>
+      </c>
+      <c r="F193" t="str">
+        <v>sorry si soy GRRRIS</v>
+      </c>
+      <c r="G193" t="str">
+        <v>2:53</v>
+      </c>
+      <c r="H193" t="str">
+        <v>ROBI</v>
+      </c>
+      <c r="I193" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J193" t="str">
+        <v>https://music.apple.com/us/artist/robi/1458047972</v>
+      </c>
+      <c r="K193" t="str">
+        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
+      </c>
+      <c r="L193" t="str">
+        <v>NI NA’ - ROBI</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>Holding Back</v>
+      </c>
+      <c r="B194" t="str">
+        <v/>
+      </c>
+      <c r="C194" t="str">
+        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
+      </c>
+      <c r="D194" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="E194" t="str">
+        <v/>
+      </c>
+      <c r="F194" t="str">
+        <v>AMA</v>
+      </c>
+      <c r="G194" t="str">
+        <v>3:19</v>
+      </c>
+      <c r="H194" t="str">
+        <v>Ama</v>
+      </c>
+      <c r="I194" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J194" t="str">
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+      </c>
+      <c r="K194" t="str">
+        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
+      </c>
+      <c r="L194" t="str">
+        <v>Holding Back - Ama</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>you're still mine</v>
+      </c>
+      <c r="B195" t="str">
+        <v/>
+      </c>
+      <c r="C195" t="str">
+        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
+      </c>
+      <c r="D195" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="E195" t="str">
+        <v/>
+      </c>
+      <c r="F195" t="str">
+        <v>you're still mine - Single</v>
+      </c>
+      <c r="G195" t="str">
+        <v>3:19</v>
+      </c>
+      <c r="H195" t="str">
+        <v>Lexi Jayde</v>
+      </c>
+      <c r="I195" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J195" t="str">
+        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
+      </c>
+      <c r="K195" t="str">
+        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
+      </c>
+      <c r="L195" t="str">
+        <v>you're still mine - Lexi Jayde</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>teksi</v>
+      </c>
+      <c r="B196" t="str">
+        <v/>
+      </c>
+      <c r="C196" t="str">
+        <v>https://music.apple.com/us/song/teksi/6769899742</v>
+      </c>
+      <c r="D196" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="E196" t="str">
+        <v/>
+      </c>
+      <c r="F196" t="str">
+        <v>pOCHO</v>
+      </c>
+      <c r="G196" t="str">
+        <v>2:48</v>
+      </c>
+      <c r="H196" t="str">
+        <v>8onthebeat</v>
+      </c>
+      <c r="I196" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J196" t="str">
+        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
+      </c>
+      <c r="K196" t="str">
+        <v>https://music.apple.com/us/album/teksi/6769899739</v>
+      </c>
+      <c r="L196" t="str">
+        <v>teksi - 8onthebeat</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>Let You Go</v>
+      </c>
+      <c r="B197" t="str">
+        <v/>
+      </c>
+      <c r="C197" t="str">
+        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
+      </c>
+      <c r="D197" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="E197" t="str">
+        <v/>
+      </c>
+      <c r="F197" t="str">
+        <v>Let You Go - Single</v>
+      </c>
+      <c r="G197" t="str">
+        <v>1:37</v>
+      </c>
+      <c r="H197" t="str">
+        <v>Nate Sib</v>
+      </c>
+      <c r="I197" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J197" t="str">
+        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
+      </c>
+      <c r="K197" t="str">
+        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
+      </c>
+      <c r="L197" t="str">
+        <v>Let You Go - Nate Sib</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>Dis-Moi</v>
+      </c>
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
+        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v>CINNA</v>
+      </c>
+      <c r="G198" t="str">
+        <v>2:27</v>
+      </c>
+      <c r="H198" t="str">
+        <v>Cannelle</v>
+      </c>
+      <c r="I198" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J198" t="str">
+        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
+      </c>
+      <c r="K198" t="str">
+        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
+      </c>
+      <c r="L198" t="str">
+        <v>Dis-Moi - Cannelle</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>Leverage</v>
+      </c>
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
+        <v>https://music.apple.com/us/song/leverage/6776432312</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v>Heaven on Mars</v>
+      </c>
+      <c r="G199" t="str">
+        <v>3:04</v>
+      </c>
+      <c r="H199" t="str">
+        <v>NoCap</v>
+      </c>
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
+        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
+      </c>
+      <c r="K199" t="str">
+        <v>https://music.apple.com/us/album/leverage/6776432217</v>
+      </c>
+      <c r="L199" t="str">
+        <v>Leverage - NoCap</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>Kool Aid</v>
+      </c>
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
+        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
+      </c>
+      <c r="D200" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v>Where Have All The Good Men Gone? - EP</v>
+      </c>
+      <c r="G200" t="str">
+        <v>3:40</v>
+      </c>
+      <c r="H200" t="str">
+        <v>Debbii Dawson</v>
+      </c>
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
+        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
+      </c>
+      <c r="K200" t="str">
+        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
+      </c>
+      <c r="L200" t="str">
+        <v>Kool Aid - Debbii Dawson</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Pieces</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/pieces/6771861156</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>Pieces - Single</v>
+      </c>
+      <c r="G201" t="str">
+        <v>2:19</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Dom Innarella</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/pieces/6771861155</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Pieces - Dom Innarella</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>Mesmerized</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>Mesmerized - Single</v>
+      </c>
+      <c r="G202" t="str">
+        <v>2:38</v>
+      </c>
+      <c r="H202" t="str">
+        <v>The Aces</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Mesmerized - The Aces</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Perfect 10</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v>No Hard Feelings (Deluxe)</v>
+      </c>
+      <c r="G203" t="str">
+        <v>2:51</v>
+      </c>
+      <c r="H203" t="str">
+        <v>The Beaches</v>
+      </c>
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
+      </c>
+      <c r="K203" t="str">
+        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Perfect 10 - The Beaches</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Recognize</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/recognize/6769164705</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>Recognize - Single</v>
+      </c>
+      <c r="G204" t="str">
+        <v>2:05</v>
+      </c>
+      <c r="H204" t="str">
+        <v>Fana Hues</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/recognize/6769164704</v>
+      </c>
+      <c r="L204" t="str">
+        <v>Recognize - Fana Hues</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>Feel The Vibe</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v>Feel The Vibe</v>
+      </c>
+      <c r="G205" t="str">
+        <v>3:28</v>
+      </c>
+      <c r="H205" t="str">
+        <v>Above &amp; Beyond</v>
+      </c>
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
+      </c>
+      <c r="K205" t="str">
+        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
+      </c>
+      <c r="L205" t="str">
+        <v>Feel The Vibe - Above &amp; Beyond</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
         <v>I Never Knew</v>
       </c>
-      <c r="B193" t="str">
-        <v/>
-      </c>
-      <c r="C193" t="str">
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
         <v>https://music.apple.com/us/song/i-never-knew/6764351468</v>
       </c>
-      <c r="D193" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E193" t="str">
-        <v/>
-      </c>
-      <c r="F193" t="str">
+      <c r="D206" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
         <v>I Never Knew - Single</v>
       </c>
-      <c r="G193" t="str">
+      <c r="G206" t="str">
         <v>3:51</v>
       </c>
-      <c r="H193" t="str">
+      <c r="H206" t="str">
         <v>Adam Ten</v>
       </c>
-      <c r="I193" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J193" t="str">
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
         <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
-      <c r="K193" t="str">
+      <c r="K206" t="str">
         <v>https://music.apple.com/us/album/i-never-knew/1895744479</v>
       </c>
-      <c r="L193" t="str">
+      <c r="L206" t="str">
         <v>I Never Knew - Adam Ten</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L193"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L206"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-06-week02/titles.xlsx
+++ b/data/global/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L206"/>
+  <dimension ref="A1:L194"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמוליק סוכות - נשאר רק הלב</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-08</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411271&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
+        <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-08</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>10 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Capital FM</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמוליק סוכות - נשאר רק הלב</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שלומי ימין - תודה על הכל</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-08</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411270&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
+        <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-08</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>10 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Capital FM</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שלומי ימין - תודה על הכל</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עידו כנפי - נגמרה המלחמה</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-06-08</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411269&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
+        <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-08</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>11 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Capital FM</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>עידו כנפי - נגמרה המלחמה</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מורן מצליח - אהבה בשתי שפות</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-06-08</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411268&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
+        <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
       </c>
       <c r="D5" t="str">
         <v>2026-06-08</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>11 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Capital FM</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מורן מצליח - אהבה בשתי שפות</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יוסף חיים - טאטע תציל</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-06-08</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411267&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
+        <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
       </c>
       <c r="D6" t="str">
         <v>2026-06-08</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Capital FM</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יוסף חיים - טאטע תציל</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>בנימין משה - הכל היסטוריה</v>
+        <v>DEEP PURPLE - DIABLO (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-06-08</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411266&amp;sid=feb98768f842ed263d3d4a5e209a9f0e</v>
+        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-08</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>בנימין משה - הכל היסטוריה</v>
+        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>חן כהן – תל גיבורים</v>
+        <v>Reba McEntire - You Never Gave Up On Me</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-06-08</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://yosmusic.com/%d7%97%d7%9f-%d7%9b%d7%94%d7%9f-%d7%aa%d7%9c-%d7%92%d7%99%d7%91%d7%95%d7%a8%d7%99%d7%9d/</v>
+        <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
       </c>
       <c r="D8" t="str">
         <v>2026-06-08</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>תל גיבורים" של  חן כהן הוא שיר חשוף  כואב ומזכך. זהו מסע בזמן אל מחוזות הילדות וההתבגרות בשכונת תל גיבורים בחולון, שעיקרו הוא מסע פנימי אל נבכי דימוי הגוף, החרדה והחיפוש העיקש אחר קבלה עצמית ו"בית" בתוך הנפש. הטקסט והמוזיקה</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Reba McEntire</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>חן כהן – תל גיבורים</v>
+        <v>Reba McEntire - You Never Gave Up On Me - Reba McEntire</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>סהראת – שמש כחולה</v>
+        <v>elijah woods - Wonder (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-06-08</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%94%d7%a8%d7%90%d7%aa-%d7%a9%d7%9e%d7%a9-%d7%9b%d7%97%d7%95%d7%9c%d7%94/</v>
+        <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-08</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>השיר "שמש כחולה" של להקת "סהראת" בביצועה של אורטל חאיק פינקל, הוא יצירה מקורית יוצאת דופן בנוף המוזיקלי המקומי. השיר, שנכתב על ידי מקימת ההרכב אתי נאור והולחן על ידי אדיר לוי, מביא  חשיפה רגשית  המטופלת ברגישות ובעוצמה יוצאת דופן.</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>elijah woods</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>סהראת – שמש כחולה</v>
+        <v>elijah woods - Wonder (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>עילאי גניש - השריטה שלי קאבר</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-06-08</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411275&amp;sid=06589a542a79f09e4f3f508659a66da9</v>
+        <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
       </c>
       <c r="D10" t="str">
         <v>2026-06-08</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I10" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>עילאי גניש - השריטה שלי קאבר</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ליהיא - לב לבן קאבר</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-06-08</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411274&amp;sid=06589a542a79f09e4f3f508659a66da9</v>
+        <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
       </c>
       <c r="D11" t="str">
         <v>2026-06-08</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>Capital FM</v>
       </c>
       <c r="I11" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>ליהיא - לב לבן קאבר</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>יעקב הראל - ככה באמת קאבר</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-06-08</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411273&amp;sid=06589a542a79f09e4f3f508659a66da9</v>
+        <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
       </c>
       <c r="D12" t="str">
         <v>2026-06-08</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>Capital FM</v>
       </c>
       <c r="I12" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>יעקב הראל - ככה באמת קאבר</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>אפיק מרחום - אני רוצה קאבר</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-06-08</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411272&amp;sid=06589a542a79f09e4f3f508659a66da9</v>
+        <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
       </c>
       <c r="D13" t="str">
         <v>2026-06-08</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>Capital FM</v>
       </c>
       <c r="I13" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>אפיק מרחום - אני רוצה קאבר</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B14" t="str">
-        <v>8h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
+        <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
       </c>
       <c r="D14" t="str">
         <v>2026-06-08</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>8h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B15" t="str">
-        <v>8h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
+        <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
       </c>
       <c r="D15" t="str">
         <v>2026-06-08</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>8h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B16" t="str">
-        <v>8h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
+        <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
       </c>
       <c r="D16" t="str">
         <v>2026-06-08</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>8h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B17" t="str">
-        <v>8h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
+        <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
       </c>
       <c r="D17" t="str">
         <v>2026-06-08</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>8h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B18" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
+        <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
       </c>
       <c r="D18" t="str">
         <v>2026-06-08</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video)</v>
+        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B19" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
+        <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
       </c>
       <c r="D19" t="str">
         <v>2026-06-08</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Capital FM</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Reba McEntire - You Never Gave Up On Me</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B20" t="str">
-        <v>19h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
+        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
       </c>
       <c r="D20" t="str">
         <v>2026-06-08</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>19h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Reba McEntire</v>
+        <v>Capital FM</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Reba McEntire - You Never Gave Up On Me - Reba McEntire</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>elijah woods - Wonder (Official Lyric Video)</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B21" t="str">
-        <v>22h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
+        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
       </c>
       <c r="D21" t="str">
         <v>2026-06-08</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>22h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>elijah woods</v>
+        <v>Capital FM</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>elijah woods - Wonder (Official Lyric Video) - elijah woods</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B22" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
+        <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
       </c>
       <c r="D22" t="str">
         <v>2026-06-08</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Capital FM and XG</v>
+        <v>Capital FM</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
+        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B23" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
+        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
       </c>
       <c r="D23" t="str">
         <v>2026-06-08</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B24" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
+        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
       </c>
       <c r="D24" t="str">
         <v>2026-06-08</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
+        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
       </c>
       <c r="D25" t="str">
         <v>2026-06-08</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B26" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
+        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
       </c>
       <c r="D26" t="str">
         <v>2026-06-08</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
+        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
+        <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
       </c>
       <c r="D27" t="str">
         <v>2026-06-08</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B28" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
+        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
       </c>
       <c r="D28" t="str">
         <v>2026-06-08</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B29" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
+        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
       </c>
       <c r="D29" t="str">
         <v>2026-06-08</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
+        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-06-08</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Capital FM and XG</v>
+        <v>Capital FM</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B31" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
+        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
       </c>
       <c r="D31" t="str">
         <v>2026-06-08</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
+        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B32" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
+        <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
       </c>
       <c r="D32" t="str">
         <v>2026-06-08</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B33" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
+        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
       </c>
       <c r="D33" t="str">
         <v>2026-06-08</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B34" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
+        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
       </c>
       <c r="D34" t="str">
         <v>2026-06-08</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B35" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
+        <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
       </c>
       <c r="D35" t="str">
         <v>2026-06-08</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
+        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
       </c>
       <c r="D36" t="str">
         <v>2026-06-08</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B37" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
+        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
       </c>
       <c r="D37" t="str">
         <v>2026-06-08</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
+        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
       </c>
       <c r="D38" t="str">
         <v>2026-06-08</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B39" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
+        <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
       </c>
       <c r="D39" t="str">
         <v>2026-06-08</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B40" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
+        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
       </c>
       <c r="D40" t="str">
         <v>2026-06-08</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
+        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
       </c>
       <c r="D41" t="str">
         <v>2026-06-08</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B42" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
+        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
       </c>
       <c r="D42" t="str">
         <v>2026-06-08</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
+        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
       </c>
       <c r="D43" t="str">
         <v>2026-06-08</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B44" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
+        <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
       </c>
       <c r="D44" t="str">
         <v>2026-06-08</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
       </c>
       <c r="B45" t="str">
-        <v>1d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
+        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
       </c>
       <c r="D45" t="str">
         <v>2026-06-08</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>1d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
       </c>
       <c r="B46" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
+        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-06-08</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Capital FM</v>
+        <v>TheCranberriesTV</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
+        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
       </c>
       <c r="D47" t="str">
         <v>2026-06-08</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
+        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
       </c>
       <c r="D48" t="str">
         <v>2026-06-08</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B49" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
+        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
       </c>
       <c r="D49" t="str">
         <v>2026-06-08</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Capital FM</v>
+        <v>The Offspring</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young – From Down Here (From The Pool)</v>
       </c>
       <c r="B50" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
+        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
       </c>
       <c r="D50" t="str">
         <v>2026-06-08</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Capital FM</v>
+        <v>Lola Young</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
+        <v>CAIN - Living Water (Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
+        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
       </c>
       <c r="D51" t="str">
         <v>2026-06-08</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Capital FM</v>
+        <v>CAIN</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>CAIN - Living Water (Music Video) - CAIN</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
+        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
       </c>
       <c r="D52" t="str">
         <v>2026-06-08</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Capital FM</v>
+        <v>Eric Clapton</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
+        <v>Blu DeTiger - Whisper (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
+        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
       </c>
       <c r="D53" t="str">
         <v>2026-06-08</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Capital FM</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
+        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
       </c>
       <c r="D54" t="str">
         <v>2026-06-08</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Capital FM</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
       </c>
       <c r="B55" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
+        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
       </c>
       <c r="D55" t="str">
         <v>2026-06-08</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Capital FM</v>
+        <v>Pink Floyd</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
+        <v>Holly Humberstone - it’s just White Noise</v>
       </c>
       <c r="B56" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
+        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
       </c>
       <c r="D56" t="str">
         <v>2026-06-08</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Capital FM</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
+        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
       </c>
       <c r="D57" t="str">
         <v>2026-06-08</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
+        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
       </c>
       <c r="D58" t="str">
         <v>2026-06-08</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>TheCranberriesTV</v>
+        <v>Muse</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
       </c>
       <c r="B59" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
+        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
       </c>
       <c r="D59" t="str">
         <v>2026-06-08</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Jordana Bryant</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
+        <v>Evanescence - Sanctuary (Official Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
+        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
       </c>
       <c r="D60" t="str">
         <v>2026-06-08</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Grace Enger</v>
+        <v>Evanescence</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
+        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
       </c>
       <c r="B61" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
+        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
       </c>
       <c r="D61" t="str">
         <v>2026-06-08</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>The Offspring</v>
+        <v>The Beaches</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Lola Young – From Down Here (From The Pool)</v>
+        <v>Bella White - Stuff (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
+        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
       </c>
       <c r="D62" t="str">
         <v>2026-06-08</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Lola Young</v>
+        <v>Bella White</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
+        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>CAIN - Living Water (Music Video)</v>
+        <v>Meduza, Rani - Silence (Official Visualizer)</v>
       </c>
       <c r="B63" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
+        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
       </c>
       <c r="D63" t="str">
         <v>2026-06-08</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>CAIN</v>
+        <v>Meduza and 2 more</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>CAIN - Living Water (Music Video) - CAIN</v>
+        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
+        <v>CAIN - Living Water (Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
+        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
       </c>
       <c r="D64" t="str">
         <v>2026-06-08</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Eric Clapton</v>
+        <v>CAIN</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
+        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video)</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
+        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
       </c>
       <c r="D65" t="str">
         <v>2026-06-08</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Blu DeTiger</v>
+        <v>Fitz and the Tantrums</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
+        <v>Jeremy Camp - Reflector (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
+        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
       </c>
       <c r="D66" t="str">
         <v>2026-06-08</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Jeremy Camp</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
+        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
       </c>
       <c r="D67" t="str">
         <v>2026-06-08</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Pink Floyd</v>
+        <v>Alesso</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Holly Humberstone - it’s just White Noise</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
       </c>
       <c r="B68" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
+        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
       </c>
       <c r="D68" t="str">
         <v>2026-06-08</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Holly Humberstone</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
+        <v>Isabel LaRosa - Every Life (Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
+        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
       </c>
       <c r="D69" t="str">
         <v>2026-06-08</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Freya Ridings</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
+        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
+        <v>Wyatt Flores - Half The Man (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
+        <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
       </c>
       <c r="D70" t="str">
         <v>2026-06-08</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Muse</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
+        <v>Wyatt Flores - Half The Man (Official Music Video) - Wyatt Flores</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
+        <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
+        <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
       </c>
       <c r="D71" t="str">
         <v>2026-06-08</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Ellie Goulding</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
+        <v>Mckenna Grace - Ugly and Rotten (Official Music Video) - Mckenna Grace</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer)</v>
+        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B72" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
+        <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
       </c>
       <c r="D72" t="str">
         <v>2026-06-08</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Evanescence</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
+        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
+        <v>Boyzone - No Matter What (Live)</v>
       </c>
       <c r="B73" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
+        <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
       </c>
       <c r="D73" t="str">
         <v>2026-06-08</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>The Beaches</v>
+        <v>Boyzone</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
+        <v>Boyzone - No Matter What (Live) - Boyzone</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Bella White - Stuff (Official Music Video)</v>
+        <v>Florrie - The Times (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
+        <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
       </c>
       <c r="D74" t="str">
         <v>2026-06-08</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Bella White</v>
+        <v>florriemusic</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
+        <v>Florrie - The Times (Official Video) - florriemusic</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer)</v>
+        <v>Madonna - Love Sensation (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
+        <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
       </c>
       <c r="D75" t="str">
         <v>2026-06-08</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Meduza and 2 more</v>
+        <v>Madonna</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
+        <v>Madonna - Love Sensation (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>CAIN - Living Water (Lyric Video)</v>
+        <v>DMA'S - Hurracane (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
+        <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
       </c>
       <c r="D76" t="str">
         <v>2026-06-08</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>CAIN</v>
+        <v>DMA'S</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
+        <v>DMA'S - Hurracane (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
+        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
       </c>
       <c r="B77" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
+        <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
       </c>
       <c r="D77" t="str">
         <v>2026-06-08</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Fitz and the Tantrums</v>
+        <v>Lainey Wilson and John Mayer</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
+        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio) - Lainey Wilson and John Mayer</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video)</v>
+        <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>3d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
+        <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
       </c>
       <c r="D78" t="str">
         <v>2026-06-08</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>3d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Jeremy Camp</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
+        <v>ROLE MODEL - High Hopes 3000 (Official Music Video) - ROLE MODEL</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
+        <v>Shawn Mendes - Treat You Better (Live from New York)</v>
       </c>
       <c r="B79" t="str">
-        <v>3d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
+        <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-06-08</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>3d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Alesso</v>
+        <v>Shawn Mendes</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
+        <v>Shawn Mendes - Treat You Better (Live from New York) - Shawn Mendes</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
+        <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>3d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
+        <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
       </c>
       <c r="D80" t="str">
         <v>2026-06-08</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>3d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Malcolm Todd</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
+        <v>SIENNA SPIRO - The Visitor (Official Music Video) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer)</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
       </c>
       <c r="B81" t="str">
-        <v>3d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
+        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
       </c>
       <c r="D81" t="str">
         <v>2026-06-08</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>3d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video)</v>
+        <v>Europe - The Cult of Ignorance (Official Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>3d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
+        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
       </c>
       <c r="D82" t="str">
         <v>2026-06-08</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>3d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Wyatt Flores</v>
+        <v>Europe</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video) - Wyatt Flores</v>
+        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>3d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
+        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
       </c>
       <c r="D83" t="str">
         <v>2026-06-08</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>3d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Mckenna Grace</v>
+        <v>Air Supply</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video) - Mckenna Grace</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>3d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
+        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
       </c>
       <c r="D84" t="str">
         <v>2026-06-08</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>3d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Robert Grace</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Boyzone - No Matter What (Live)</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
       </c>
       <c r="B85" t="str">
-        <v>3d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
+        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
       </c>
       <c r="D85" t="str">
         <v>2026-06-08</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>3d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Boyzone</v>
+        <v>Allen Stone and Placeholder Sessions</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Boyzone - No Matter What (Live) - Boyzone</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Florrie - The Times (Official Video)</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
       </c>
       <c r="B86" t="str">
-        <v>3d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
+        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
       </c>
       <c r="D86" t="str">
         <v>2026-06-08</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>3d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>florriemusic</v>
+        <v>Morgan Wallen</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Florrie - The Times (Official Video) - florriemusic</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer)</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>3d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
+        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
       </c>
       <c r="D87" t="str">
         <v>2026-06-08</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>3d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Madonna</v>
+        <v>Billy Idol</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer) - Madonna</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>DMA'S - Hurracane (Official Video)</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
       </c>
       <c r="B88" t="str">
-        <v>4d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
+        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
       </c>
       <c r="D88" t="str">
         <v>2026-06-08</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>4d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>DMA'S</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>DMA'S - Hurracane (Official Video) - DMA'S</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>4d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
+        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
       </c>
       <c r="D89" t="str">
         <v>2026-06-08</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>4d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Lainey Wilson and John Mayer</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio) - Lainey Wilson and John Mayer</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
+        <v>Hippo Campus - South</v>
       </c>
       <c r="B90" t="str">
-        <v>5d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
+        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
       </c>
       <c r="D90" t="str">
         <v>2026-06-08</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>5d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>ROLE MODEL</v>
+        <v>Hippo Campus</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video) - ROLE MODEL</v>
+        <v>Hippo Campus - South - Hippo Campus</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York)</v>
+        <v>elijah woods - Old (Treehouse Sessions)</v>
       </c>
       <c r="B91" t="str">
-        <v>5d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
+        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
       </c>
       <c r="D91" t="str">
         <v>2026-06-08</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>5d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Shawn Mendes</v>
+        <v>elijah woods</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York) - Shawn Mendes</v>
+        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
+        <v>Nothing But Thieves - Evolution (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>5d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
+        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
       </c>
       <c r="D92" t="str">
         <v>2026-06-08</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>5d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video) - SIENNA SPIRO</v>
+        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
+        <v>Ariana Grande - hate that i made you love me (official music video)</v>
       </c>
       <c r="B93" t="str">
-        <v>5d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
+        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
       </c>
       <c r="D93" t="str">
         <v>2026-06-08</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>5d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video)</v>
+        <v>LAUREL - Fire Breather</v>
       </c>
       <c r="B94" t="str">
-        <v>5d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
+        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
       </c>
       <c r="D94" t="str">
         <v>2026-06-08</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>5d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Europe</v>
+        <v>LAUREL</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
+        <v>LAUREL - Fire Breather - LAUREL</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
+        <v>The Warning - Ego (Performance Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>5d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
+        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
       </c>
       <c r="D95" t="str">
         <v>2026-06-08</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>5d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Air Supply</v>
+        <v>The Warning</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
+        <v>The Warning - Ego (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
       </c>
       <c r="B96" t="str">
-        <v>5d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
+        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
       </c>
       <c r="D96" t="str">
         <v>2026-06-08</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>5d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Julia Cole Music</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B97" t="str">
-        <v>5d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
+        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
       </c>
       <c r="D97" t="str">
         <v>2026-06-08</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>5d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Allen Stone and Placeholder Sessions</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
       </c>
       <c r="B98" t="str">
-        <v>6d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
+        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
       </c>
       <c r="D98" t="str">
         <v>2026-06-08</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>6d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Morgan Wallen</v>
+        <v>Andrew Bird</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
+        <v>Danny Gokey - God's Not (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>6d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
+        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
       </c>
       <c r="D99" t="str">
         <v>2026-06-08</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>6d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Billy Idol</v>
+        <v>Danny Gokey</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
+        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B100" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
+        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
       </c>
       <c r="D100" t="str">
         <v>2026-06-08</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Armik</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
       </c>
       <c r="B101" t="str">
-        <v>6d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
+        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
       </c>
       <c r="D101" t="str">
         <v>2026-06-08</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>6d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Icona Pop</v>
+        <v>Holly Humberstone and Free People</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Hippo Campus - South</v>
+        <v>True Colors</v>
       </c>
       <c r="B102" t="str">
-        <v>7d ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
+        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
       </c>
       <c r="D102" t="str">
         <v>2026-06-08</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>7d ago</v>
+        <v>Thank You</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>3:39</v>
       </c>
       <c r="H102" t="str">
-        <v>Hippo Campus</v>
+        <v>Mike D</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
       </c>
       <c r="L102" t="str">
-        <v>Hippo Campus - South - Hippo Campus</v>
+        <v>True Colors - Mike D</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>elijah woods - Old (Treehouse Sessions)</v>
+        <v>Too Easy</v>
       </c>
       <c r="B103" t="str">
-        <v>7d ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
+        <v>https://music.apple.com/us/song/too-easy/6774752170</v>
       </c>
       <c r="D103" t="str">
         <v>2026-06-08</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>7d ago</v>
+        <v>Too Easy - Single</v>
       </c>
       <c r="G103" t="str">
-        <v/>
+        <v>1:54</v>
       </c>
       <c r="H103" t="str">
-        <v>elijah woods</v>
+        <v>Tinashe</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/tinashe/464835513</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/too-easy/6774752168</v>
       </c>
       <c r="L103" t="str">
-        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
+        <v>Too Easy - Tinashe</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video)</v>
+        <v>I Knew It, I Knew You</v>
       </c>
       <c r="B104" t="str">
-        <v>7d ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
+        <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
       </c>
       <c r="D104" t="str">
         <v>2026-06-08</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>7d ago</v>
+        <v>I Knew It, I Knew You - Single</v>
       </c>
       <c r="G104" t="str">
-        <v/>
+        <v>2:58</v>
       </c>
       <c r="H104" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/i-knew-it-i-knew-you/6775527442</v>
       </c>
       <c r="L104" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
+        <v>I Knew It, I Knew You - Taylor Swift</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video)</v>
+        <v>Love Sensation</v>
       </c>
       <c r="B105" t="str">
-        <v>7d ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
+        <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
       </c>
       <c r="D105" t="str">
         <v>2026-06-08</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>7d ago</v>
+        <v>Love Sensation - Single</v>
       </c>
       <c r="G105" t="str">
-        <v/>
+        <v>3:48</v>
       </c>
       <c r="H105" t="str">
-        <v>Ariana Grande</v>
+        <v>Madonna</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/love-sensation/6774810102</v>
       </c>
       <c r="L105" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
+        <v>Love Sensation - Madonna</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>LAUREL - Fire Breather</v>
+        <v>Mi Yo De Antes</v>
       </c>
       <c r="B106" t="str">
-        <v>7d ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
+        <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
       </c>
       <c r="D106" t="str">
         <v>2026-06-08</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>7d ago</v>
+        <v>Mi Yo De Antes - Single</v>
       </c>
       <c r="G106" t="str">
-        <v/>
+        <v>3:04</v>
       </c>
       <c r="H106" t="str">
-        <v>LAUREL</v>
+        <v>Ozuna</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/mi-yo-de-antes/6769193983</v>
       </c>
       <c r="L106" t="str">
-        <v>LAUREL - Fire Breather - LAUREL</v>
+        <v>Mi Yo De Antes - Ozuna</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>The Warning - Ego (Performance Video)</v>
+        <v>Three Nations</v>
       </c>
       <c r="B107" t="str">
-        <v>8d ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
+        <v>https://music.apple.com/us/song/three-nations/6776010602</v>
       </c>
       <c r="D107" t="str">
         <v>2026-06-08</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>8d ago</v>
+        <v>Official FIFA World Cup 2026™ Album</v>
       </c>
       <c r="G107" t="str">
-        <v/>
+        <v>3:30</v>
       </c>
       <c r="H107" t="str">
-        <v>The Warning</v>
+        <v>21 Savage</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/21-savage/894820464</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/three-nations/6776010591</v>
       </c>
       <c r="L107" t="str">
-        <v>The Warning - Ego (Performance Video) - The Warning</v>
+        <v>Three Nations - 21 Savage</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
+        <v>Champions (WC 26)</v>
       </c>
       <c r="B108" t="str">
-        <v>9d ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
+        <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
       </c>
       <c r="D108" t="str">
         <v>2026-06-08</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>9d ago</v>
+        <v>Champions (WC 26) - Single</v>
       </c>
       <c r="G108" t="str">
-        <v/>
+        <v>4:15</v>
       </c>
       <c r="H108" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>IShowSpeed</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ishowspeed/1574723975</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/champions-wc-26/6775282246</v>
       </c>
       <c r="L108" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
+        <v>Champions (WC 26) - IShowSpeed</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
+        <v>ENCERRONES</v>
       </c>
       <c r="B109" t="str">
-        <v>9d ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
+        <v>https://music.apple.com/us/song/encerrones/6771854522</v>
       </c>
       <c r="D109" t="str">
         <v>2026-06-08</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>9d ago</v>
+        <v>TEOFANIA</v>
       </c>
       <c r="G109" t="str">
-        <v/>
+        <v>2:23</v>
       </c>
       <c r="H109" t="str">
-        <v>Armin van Buuren</v>
+        <v>LENCHO</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/encerrones/6771854517</v>
       </c>
       <c r="L109" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>ENCERRONES - LENCHO</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
+        <v>Cowgirl</v>
       </c>
       <c r="B110" t="str">
-        <v>10d ago</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
+        <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
       </c>
       <c r="D110" t="str">
         <v>2026-06-08</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>10d ago</v>
+        <v>The Outlaw Cherie Lee &amp; Other Western Tales</v>
       </c>
       <c r="G110" t="str">
-        <v/>
+        <v>2:56</v>
       </c>
       <c r="H110" t="str">
-        <v>Andrew Bird</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/cowgirl/1894906682</v>
       </c>
       <c r="L110" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
+        <v>Cowgirl - Shaboozey</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video)</v>
+        <v>PASSENGER</v>
       </c>
       <c r="B111" t="str">
-        <v>10d ago</v>
+        <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
+        <v>https://music.apple.com/us/song/passenger/6773456081</v>
       </c>
       <c r="D111" t="str">
         <v>2026-06-08</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>10d ago</v>
+        <v>WILDCHILD</v>
       </c>
       <c r="G111" t="str">
-        <v/>
+        <v>2:39</v>
       </c>
       <c r="H111" t="str">
-        <v>Danny Gokey</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/passenger/6773456078</v>
       </c>
       <c r="L111" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
+        <v>PASSENGER - Alex Warren</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Secret Language</v>
       </c>
       <c r="B112" t="str">
-        <v>10d ago</v>
+        <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
+        <v>https://music.apple.com/us/song/secret-language/6774223667</v>
       </c>
       <c r="D112" t="str">
         <v>2026-06-08</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>10d ago</v>
+        <v>Sweet Fortune</v>
       </c>
       <c r="G112" t="str">
-        <v/>
+        <v>3:53</v>
       </c>
       <c r="H112" t="str">
-        <v>Armik</v>
+        <v>Ryan Beatty</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ryan-beatty/483234172</v>
       </c>
       <c r="K112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/secret-language/6774223660</v>
       </c>
       <c r="L112" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Secret Language - Ryan Beatty</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
+        <v>High Hopes 3000</v>
       </c>
       <c r="B113" t="str">
-        <v>10d ago</v>
+        <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
+        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
       </c>
       <c r="D113" t="str">
         <v>2026-06-08</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>10d ago</v>
+        <v>Chuck Timely &amp; The Hourglass</v>
       </c>
       <c r="G113" t="str">
-        <v/>
+        <v>4:05</v>
       </c>
       <c r="H113" t="str">
-        <v>Holly Humberstone and Free People</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/role-model/199215762</v>
       </c>
       <c r="K113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
       </c>
       <c r="L113" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
+        <v>High Hopes 3000 - ROLE MODEL</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>True Colors</v>
+        <v>Vertical</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
+        <v>https://music.apple.com/us/song/vertical/1892436336</v>
       </c>
       <c r="D114" t="str">
         <v>2026-06-08</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Thank You</v>
+        <v>Emotional Junglist</v>
       </c>
       <c r="G114" t="str">
-        <v>3:39</v>
+        <v>2:36</v>
       </c>
       <c r="H114" t="str">
-        <v>Mike D</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
+        <v>https://music.apple.com/us/album/vertical/1892436329</v>
       </c>
       <c r="L114" t="str">
-        <v>True Colors - Mike D</v>
+        <v>Vertical - Nia Archives</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Too Easy</v>
+        <v>snake the drain</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/too-easy/6774752170</v>
+        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
       </c>
       <c r="D115" t="str">
         <v>2026-06-08</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Too Easy - Single</v>
+        <v>this time it’s different / snake the drain - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>1:54</v>
+        <v>3:08</v>
       </c>
       <c r="H115" t="str">
-        <v>Tinashe</v>
+        <v>Devon Again</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/tinashe/464835513</v>
+        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/too-easy/6774752168</v>
+        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
       </c>
       <c r="L115" t="str">
-        <v>Too Easy - Tinashe</v>
+        <v>snake the drain - Devon Again</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>I Knew It, I Knew You</v>
+        <v>Every Single Weekend (feat. Jamie xx)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
+        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D116" t="str">
         <v>2026-06-08</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>I Knew It, I Knew You - Single</v>
+        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>2:58</v>
+        <v>2:10</v>
       </c>
       <c r="H116" t="str">
-        <v>Taylor Swift</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/i-knew-it-i-knew-you/6775527442</v>
+        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
       </c>
       <c r="L116" t="str">
-        <v>I Knew It, I Knew You - Taylor Swift</v>
+        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Love Sensation</v>
+        <v>Bluffin'</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
+        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
       </c>
       <c r="D117" t="str">
         <v>2026-06-08</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Love Sensation - Single</v>
+        <v>Piss In The Wind (Deluxe)</v>
       </c>
       <c r="G117" t="str">
-        <v>3:48</v>
+        <v>2:34</v>
       </c>
       <c r="H117" t="str">
-        <v>Madonna</v>
+        <v>Joji</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/love-sensation/6774810102</v>
+        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
       </c>
       <c r="L117" t="str">
-        <v>Love Sensation - Madonna</v>
+        <v>Bluffin' - Joji</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Mi Yo De Antes</v>
+        <v>Dreams</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
+        <v>https://music.apple.com/us/song/dreams/1884731028</v>
       </c>
       <c r="D118" t="str">
         <v>2026-06-08</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Mi Yo De Antes - Single</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="G118" t="str">
-        <v>3:04</v>
+        <v>3:56</v>
       </c>
       <c r="H118" t="str">
-        <v>Ozuna</v>
+        <v>Prospa</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/mi-yo-de-antes/6769193983</v>
+        <v>https://music.apple.com/us/album/dreams/1884730177</v>
       </c>
       <c r="L118" t="str">
-        <v>Mi Yo De Antes - Ozuna</v>
+        <v>Dreams - Prospa</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Three Nations</v>
+        <v>Cotton</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/three-nations/6776010602</v>
+        <v>https://music.apple.com/us/song/cotton/1887627941</v>
       </c>
       <c r="D119" t="str">
         <v>2026-06-08</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Official FIFA World Cup 2026™ Album</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G119" t="str">
-        <v>3:30</v>
+        <v>3:43</v>
       </c>
       <c r="H119" t="str">
-        <v>21 Savage</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/21-savage/894820464</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/three-nations/6776010591</v>
+        <v>https://music.apple.com/us/album/cotton/1887627836</v>
       </c>
       <c r="L119" t="str">
-        <v>Three Nations - 21 Savage</v>
+        <v>Cotton - Vince Staples</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Champions (WC 26)</v>
+        <v>Black Prada Dress</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
+        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
       </c>
       <c r="D120" t="str">
         <v>2026-06-08</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Champions (WC 26) - Single</v>
+        <v>I Know Too Much</v>
       </c>
       <c r="G120" t="str">
-        <v>4:15</v>
+        <v>3:19</v>
       </c>
       <c r="H120" t="str">
-        <v>IShowSpeed</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/ishowspeed/1574723975</v>
+        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/champions-wc-26/6775282246</v>
+        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
       </c>
       <c r="L120" t="str">
-        <v>Champions (WC 26) - IShowSpeed</v>
+        <v>Black Prada Dress - Ellie Goulding</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>ENCERRONES</v>
+        <v>Don’t Break Her Heart</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/encerrones/6771854522</v>
+        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
       </c>
       <c r="D121" t="str">
         <v>2026-06-08</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>TEOFANIA</v>
+        <v>THERAPY AT THE CLUB</v>
       </c>
       <c r="G121" t="str">
-        <v>2:23</v>
+        <v>3:44</v>
       </c>
       <c r="H121" t="str">
-        <v>LENCHO</v>
+        <v>FLO</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/encerrones/6771854517</v>
+        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
       </c>
       <c r="L121" t="str">
-        <v>ENCERRONES - LENCHO</v>
+        <v>Don’t Break Her Heart - FLO</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Cowgirl</v>
+        <v>Sexy Ladies (feat. UCB)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
+        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
       </c>
       <c r="D122" t="str">
         <v>2026-06-08</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>The Outlaw Cherie Lee &amp; Other Western Tales</v>
+        <v>BITCH</v>
       </c>
       <c r="G122" t="str">
-        <v>2:56</v>
+        <v>2:50</v>
       </c>
       <c r="H122" t="str">
-        <v>Shaboozey</v>
+        <v>Lizzo</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/cowgirl/1894906682</v>
+        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
       </c>
       <c r="L122" t="str">
-        <v>Cowgirl - Shaboozey</v>
+        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>PASSENGER</v>
+        <v>Noche Without You</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/passenger/6773456081</v>
+        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
       </c>
       <c r="D123" t="str">
         <v>2026-06-08</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>WILDCHILD</v>
+        <v>SOMA</v>
       </c>
       <c r="G123" t="str">
-        <v>2:39</v>
+        <v>3:23</v>
       </c>
       <c r="H123" t="str">
-        <v>Alex Warren</v>
+        <v>Skrillex</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/passenger/6773456078</v>
+        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
       </c>
       <c r="L123" t="str">
-        <v>PASSENGER - Alex Warren</v>
+        <v>Noche Without You - Skrillex</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Secret Language</v>
+        <v>Difficult Love</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/secret-language/6774223667</v>
+        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
       </c>
       <c r="D124" t="str">
         <v>2026-06-08</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Sweet Fortune</v>
+        <v>Do That Again</v>
       </c>
       <c r="G124" t="str">
-        <v>3:53</v>
+        <v>2:33</v>
       </c>
       <c r="H124" t="str">
-        <v>Ryan Beatty</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/ryan-beatty/483234172</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/secret-language/6774223660</v>
+        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
       </c>
       <c r="L124" t="str">
-        <v>Secret Language - Ryan Beatty</v>
+        <v>Difficult Love - Malcolm Todd</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>High Hopes 3000</v>
+        <v>Tastes So Good</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
+        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
       </c>
       <c r="D125" t="str">
         <v>2026-06-08</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Chuck Timely &amp; The Hourglass</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G125" t="str">
-        <v>4:05</v>
+        <v>3:05</v>
       </c>
       <c r="H125" t="str">
-        <v>ROLE MODEL</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/role-model/199215762</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
+        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
       </c>
       <c r="L125" t="str">
-        <v>High Hopes 3000 - ROLE MODEL</v>
+        <v>Tastes So Good - Niall Horan</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Vertical</v>
+        <v>Phone, Keys, Wallet</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/vertical/1892436336</v>
+        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
       </c>
       <c r="D126" t="str">
         <v>2026-06-08</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Emotional Junglist</v>
+        <v>Phone, Keys, Wallet - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:36</v>
+        <v>2:52</v>
       </c>
       <c r="H126" t="str">
-        <v>Nia Archives</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/vertical/1892436329</v>
+        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
       </c>
       <c r="L126" t="str">
-        <v>Vertical - Nia Archives</v>
+        <v>Phone, Keys, Wallet - Lainey Wilson</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>snake the drain</v>
+        <v>Madrugada</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
+        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
       </c>
       <c r="D127" t="str">
         <v>2026-06-08</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>this time it’s different / snake the drain - Single</v>
+        <v>Madrugada - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:08</v>
+        <v>2:58</v>
       </c>
       <c r="H127" t="str">
-        <v>Devon Again</v>
+        <v>Chino Pacas</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
+        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
+        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
       </c>
       <c r="L127" t="str">
-        <v>snake the drain - Devon Again</v>
+        <v>Madrugada - Chino Pacas</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Every Single Weekend (feat. Jamie xx)</v>
+        <v>Oh Chet (feat. Travis Scott)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
+        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
       </c>
       <c r="D128" t="str">
         <v>2026-06-08</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
+        <v>Oh Chet (feat. Travis Scott) - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:10</v>
+        <v>2:23</v>
       </c>
       <c r="H128" t="str">
-        <v>The Avalanches</v>
+        <v>Jey One</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
+        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
       </c>
       <c r="L128" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
+        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Bluffin'</v>
+        <v>An Hour or So (Live at Apple Music Radio)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
+        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
       </c>
       <c r="D129" t="str">
         <v>2026-06-08</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Piss In The Wind (Deluxe)</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G129" t="str">
-        <v>2:34</v>
+        <v>3:02</v>
       </c>
       <c r="H129" t="str">
-        <v>Joji</v>
+        <v>Benny G</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
+        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
       </c>
       <c r="L129" t="str">
-        <v>Bluffin' - Joji</v>
+        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Dreams</v>
+        <v>it’s just White Noise</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/dreams/1884731028</v>
+        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
       </c>
       <c r="D130" t="str">
         <v>2026-06-08</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Free Your Mind</v>
+        <v>it’s a real Cruel World - EP</v>
       </c>
       <c r="G130" t="str">
-        <v>3:56</v>
+        <v>3:57</v>
       </c>
       <c r="H130" t="str">
-        <v>Prospa</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/dreams/1884730177</v>
+        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
       </c>
       <c r="L130" t="str">
-        <v>Dreams - Prospa</v>
+        <v>it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Cotton</v>
+        <v>the feeling</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/cotton/1887627941</v>
+        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
       </c>
       <c r="D131" t="str">
         <v>2026-06-08</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Cry Baby</v>
+        <v>Oh yeah?</v>
       </c>
       <c r="G131" t="str">
-        <v>3:43</v>
+        <v>4:35</v>
       </c>
       <c r="H131" t="str">
-        <v>Vince Staples</v>
+        <v>Steve Lacy</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/cotton/1887627836</v>
+        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
       </c>
       <c r="L131" t="str">
-        <v>Cotton - Vince Staples</v>
+        <v>the feeling - Steve Lacy</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Black Prada Dress</v>
+        <v>baby (Live at Apple Music Radio)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
+        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
       </c>
       <c r="D132" t="str">
         <v>2026-06-08</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>I Know Too Much</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G132" t="str">
-        <v>3:19</v>
+        <v>3:14</v>
       </c>
       <c r="H132" t="str">
-        <v>Ellie Goulding</v>
+        <v>Gabriel Jacoby</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
+        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
+        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
       </c>
       <c r="L132" t="str">
-        <v>Black Prada Dress - Ellie Goulding</v>
+        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Don’t Break Her Heart</v>
+        <v>Drop The Lo</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
+        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
       </c>
       <c r="D133" t="str">
         <v>2026-06-08</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>THERAPY AT THE CLUB</v>
+        <v>Drop The Lo - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:44</v>
+        <v>2:41</v>
       </c>
       <c r="H133" t="str">
-        <v>FLO</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
+        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
       </c>
       <c r="L133" t="str">
-        <v>Don’t Break Her Heart - FLO</v>
+        <v>Drop The Lo - Bryson Tiller</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Sexy Ladies (feat. UCB)</v>
+        <v>GANG BIZNESS feat paygotti</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
+        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
       </c>
       <c r="D134" t="str">
         <v>2026-06-08</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>BITCH</v>
+        <v>GANG BIZNESS feat paygotti - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:50</v>
+        <v>2:47</v>
       </c>
       <c r="H134" t="str">
-        <v>Lizzo</v>
+        <v>YG</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
+        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
       </c>
       <c r="L134" t="str">
-        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
+        <v>GANG BIZNESS feat paygotti - YG</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Noche Without You</v>
+        <v>Lay It Down</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
+        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
       </c>
       <c r="D135" t="str">
         <v>2026-06-08</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>SOMA</v>
+        <v>Lay It Down - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:23</v>
+        <v>2:38</v>
       </c>
       <c r="H135" t="str">
-        <v>Skrillex</v>
+        <v>FattMack</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
+        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
       </c>
       <c r="L135" t="str">
-        <v>Noche Without You - Skrillex</v>
+        <v>Lay It Down - FattMack</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Difficult Love</v>
+        <v>WAX PAPER</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
+        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
       </c>
       <c r="D136" t="str">
         <v>2026-06-08</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Do That Again</v>
+        <v>WHACK'S MUSEUM</v>
       </c>
       <c r="G136" t="str">
-        <v>2:33</v>
+        <v>2:43</v>
       </c>
       <c r="H136" t="str">
-        <v>Malcolm Todd</v>
+        <v>Tierra Whack</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
+        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
       </c>
       <c r="L136" t="str">
-        <v>Difficult Love - Malcolm Todd</v>
+        <v>WAX PAPER - Tierra Whack</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Tastes So Good</v>
+        <v>abusadOra (tambores)</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
+        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
       </c>
       <c r="D137" t="str">
         <v>2026-06-08</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Dinner Party</v>
+        <v>ANTES DE QUE SEA TARDE</v>
       </c>
       <c r="G137" t="str">
-        <v>3:05</v>
+        <v>3:11</v>
       </c>
       <c r="H137" t="str">
-        <v>Niall Horan</v>
+        <v>Yorghaki</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
+        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
       </c>
       <c r="L137" t="str">
-        <v>Tastes So Good - Niall Horan</v>
+        <v>abusadOra (tambores) - Yorghaki</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Phone, Keys, Wallet</v>
+        <v>Ruin</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
+        <v>https://music.apple.com/us/song/ruin/6763176090</v>
       </c>
       <c r="D138" t="str">
         <v>2026-06-08</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Phone, Keys, Wallet - Single</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G138" t="str">
-        <v>2:52</v>
+        <v>3:19</v>
       </c>
       <c r="H138" t="str">
-        <v>Lainey Wilson</v>
+        <v>Blxst</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
+        <v>https://music.apple.com/us/album/ruin/1895199881</v>
       </c>
       <c r="L138" t="str">
-        <v>Phone, Keys, Wallet - Lainey Wilson</v>
+        <v>Ruin - Blxst</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Madrugada</v>
+        <v>Do Today</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
+        <v>https://music.apple.com/us/song/do-today/1893402864</v>
       </c>
       <c r="D139" t="str">
         <v>2026-06-08</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Madrugada - Single</v>
+        <v>Grateful</v>
       </c>
       <c r="G139" t="str">
-        <v>2:58</v>
+        <v>4:14</v>
       </c>
       <c r="H139" t="str">
-        <v>Chino Pacas</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
+        <v>https://music.apple.com/us/album/do-today/1893402542</v>
       </c>
       <c r="L139" t="str">
-        <v>Madrugada - Chino Pacas</v>
+        <v>Do Today - The Red Clay Strays</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Oh Chet (feat. Travis Scott)</v>
+        <v>Stone Over Water</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
+        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
       </c>
       <c r="D140" t="str">
         <v>2026-06-08</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Single</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G140" t="str">
-        <v>2:23</v>
+        <v>3:14</v>
       </c>
       <c r="H140" t="str">
-        <v>Jey One</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
+        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
       </c>
       <c r="L140" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
+        <v>Stone Over Water - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>An Hour or So (Live at Apple Music Radio)</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
+        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
       </c>
       <c r="D141" t="str">
         <v>2026-06-08</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Weezer</v>
       </c>
       <c r="G141" t="str">
-        <v>3:02</v>
+        <v>3:34</v>
       </c>
       <c r="H141" t="str">
-        <v>Benny G</v>
+        <v>Weezer</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/weezer/115234</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
+        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
       </c>
       <c r="L141" t="str">
-        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>it’s just White Noise</v>
+        <v>Tell Me When You've Had Enough</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
+        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
       </c>
       <c r="D142" t="str">
         <v>2026-06-08</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>it’s a real Cruel World - EP</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G142" t="str">
-        <v>3:57</v>
+        <v>3:19</v>
       </c>
       <c r="H142" t="str">
-        <v>Holly Humberstone</v>
+        <v>Evanescence</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
+        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
       </c>
       <c r="L142" t="str">
-        <v>it’s just White Noise - Holly Humberstone</v>
+        <v>Tell Me When You've Had Enough - Evanescence</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>the feeling</v>
+        <v>Your Ghost Again</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
+        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
       </c>
       <c r="D143" t="str">
         <v>2026-06-08</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Oh yeah?</v>
+        <v>Your Ghost Again - Single</v>
       </c>
       <c r="G143" t="str">
         <v>4:35</v>
       </c>
       <c r="H143" t="str">
-        <v>Steve Lacy</v>
+        <v>Mastodon</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
+        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
+        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
       </c>
       <c r="L143" t="str">
-        <v>the feeling - Steve Lacy</v>
+        <v>Your Ghost Again - Mastodon</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>baby (Live at Apple Music Radio)</v>
+        <v>Nightshift Superstar</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
+        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
       </c>
       <c r="D144" t="str">
         <v>2026-06-08</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G144" t="str">
-        <v>3:14</v>
+        <v>4:07</v>
       </c>
       <c r="H144" t="str">
-        <v>Gabriel Jacoby</v>
+        <v>Muse</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
+        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
       </c>
       <c r="L144" t="str">
-        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
+        <v>Nightshift Superstar - Muse</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Drop The Lo</v>
+        <v>UNDER THE RHYTHM</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
+        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
       </c>
       <c r="D145" t="str">
         <v>2026-06-08</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Drop The Lo - Single</v>
+        <v>ADAM</v>
       </c>
       <c r="G145" t="str">
-        <v>2:41</v>
+        <v>2:50</v>
       </c>
       <c r="H145" t="str">
-        <v>Bryson Tiller</v>
+        <v>Adam Lambert</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
+        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
       </c>
       <c r="L145" t="str">
-        <v>Drop The Lo - Bryson Tiller</v>
+        <v>UNDER THE RHYTHM - Adam Lambert</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>GANG BIZNESS feat paygotti</v>
+        <v>You’re Mine</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
+        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
       </c>
       <c r="D146" t="str">
         <v>2026-06-08</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>GANG BIZNESS feat paygotti - Single</v>
+        <v>Papercut</v>
       </c>
       <c r="G146" t="str">
-        <v>2:47</v>
+        <v>4:25</v>
       </c>
       <c r="H146" t="str">
-        <v>YG</v>
+        <v>Imani Imani</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
+        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
       </c>
       <c r="L146" t="str">
-        <v>GANG BIZNESS feat paygotti - YG</v>
+        <v>You’re Mine - Imani Imani</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Lay It Down</v>
+        <v>point blank</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
+        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
       </c>
       <c r="D147" t="str">
         <v>2026-06-08</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Lay It Down - Single</v>
+        <v>new avatar</v>
       </c>
       <c r="G147" t="str">
-        <v>2:38</v>
+        <v>4:26</v>
       </c>
       <c r="H147" t="str">
-        <v>FattMack</v>
+        <v>Kelela</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
+        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
       </c>
       <c r="L147" t="str">
-        <v>Lay It Down - FattMack</v>
+        <v>point blank - Kelela</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>WAX PAPER</v>
+        <v>that's my beach!</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
+        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
       </c>
       <c r="D148" t="str">
         <v>2026-06-08</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>WHACK'S MUSEUM</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G148" t="str">
-        <v>2:43</v>
+        <v>3:18</v>
       </c>
       <c r="H148" t="str">
-        <v>Tierra Whack</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
+        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
       </c>
       <c r="L148" t="str">
-        <v>WAX PAPER - Tierra Whack</v>
+        <v>that's my beach! - horsegiirL</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>abusadOra (tambores)</v>
+        <v>In Your Eyes</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
+        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
       </c>
       <c r="D149" t="str">
         <v>2026-06-08</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>ANTES DE QUE SEA TARDE</v>
+        <v>In Your Eyes - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:11</v>
+        <v>3:36</v>
       </c>
       <c r="H149" t="str">
-        <v>Yorghaki</v>
+        <v>Alesso</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
+        <v>https://music.apple.com/us/artist/alesso/432464201</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
+        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
       </c>
       <c r="L149" t="str">
-        <v>abusadOra (tambores) - Yorghaki</v>
+        <v>In Your Eyes - Alesso</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Ruin</v>
+        <v>ALL OR NOTHING</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/ruin/6763176090</v>
+        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
       </c>
       <c r="D150" t="str">
         <v>2026-06-08</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Labor Of Love</v>
+        <v>ALL OR NOTHING - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:19</v>
+        <v>3:17</v>
       </c>
       <c r="H150" t="str">
-        <v>Blxst</v>
+        <v>Tobe Nwigwe</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/ruin/1895199881</v>
+        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
       </c>
       <c r="L150" t="str">
-        <v>Ruin - Blxst</v>
+        <v>ALL OR NOTHING - Tobe Nwigwe</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Do Today</v>
+        <v>IN MY HANDS</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/do-today/1893402864</v>
+        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
       </c>
       <c r="D151" t="str">
         <v>2026-06-08</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Grateful</v>
+        <v>IN MY HANDS - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>4:14</v>
+        <v>3:14</v>
       </c>
       <c r="H151" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Alessia Cara</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/do-today/1893402542</v>
+        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
       </c>
       <c r="L151" t="str">
-        <v>Do Today - The Red Clay Strays</v>
+        <v>IN MY HANDS - Alessia Cara</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Stone Over Water</v>
+        <v>Life's a Dream</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
+        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
       </c>
       <c r="D152" t="str">
         <v>2026-06-08</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>I Built You A Tower</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G152" t="str">
-        <v>3:14</v>
+        <v>5:31</v>
       </c>
       <c r="H152" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
+        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
       </c>
       <c r="L152" t="str">
-        <v>Stone Over Water - Death Cab for Cutie</v>
+        <v>Life's a Dream - Modest Mouse</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
+        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
       </c>
       <c r="D153" t="str">
         <v>2026-06-08</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Weezer</v>
+        <v>Season of Surrender</v>
       </c>
       <c r="G153" t="str">
-        <v>3:34</v>
+        <v>4:47</v>
       </c>
       <c r="H153" t="str">
-        <v>Weezer</v>
+        <v>August Burns Red</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/weezer/115234</v>
+        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
+        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
       </c>
       <c r="L153" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Tell Me When You've Had Enough</v>
+        <v>Shine</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
+        <v>https://music.apple.com/us/song/shine/6764654536</v>
       </c>
       <c r="D154" t="str">
         <v>2026-06-08</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Sanctuary</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G154" t="str">
-        <v>3:19</v>
+        <v>2:27</v>
       </c>
       <c r="H154" t="str">
-        <v>Evanescence</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
+        <v>https://music.apple.com/us/album/shine/1895866355</v>
       </c>
       <c r="L154" t="str">
-        <v>Tell Me When You've Had Enough - Evanescence</v>
+        <v>Shine - Jon Batiste</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Your Ghost Again</v>
+        <v>Half The Man</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
+        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
       </c>
       <c r="D155" t="str">
         <v>2026-06-08</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Your Ghost Again - Single</v>
+        <v>Scared of Heights</v>
       </c>
       <c r="G155" t="str">
-        <v>4:35</v>
+        <v>3:56</v>
       </c>
       <c r="H155" t="str">
-        <v>Mastodon</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
+        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
       </c>
       <c r="L155" t="str">
-        <v>Your Ghost Again - Mastodon</v>
+        <v>Half The Man - Wyatt Flores</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Nightshift Superstar</v>
+        <v>Preacher’s Kid</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
+        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
       </c>
       <c r="D156" t="str">
         <v>2026-06-08</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>The Wow! Signal</v>
+        <v>Preacher’s Kid - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>4:07</v>
+        <v>5:02</v>
       </c>
       <c r="H156" t="str">
-        <v>Muse</v>
+        <v>Stephen Wilson Jr.</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
+        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
       </c>
       <c r="L156" t="str">
-        <v>Nightshift Superstar - Muse</v>
+        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>UNDER THE RHYTHM</v>
+        <v>Weak</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
+        <v>https://music.apple.com/us/song/weak/6771151098</v>
       </c>
       <c r="D157" t="str">
         <v>2026-06-08</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>ADAM</v>
+        <v>Weak - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>2:50</v>
+        <v>3:28</v>
       </c>
       <c r="H157" t="str">
-        <v>Adam Lambert</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
+        <v>https://music.apple.com/us/album/weak/6771151088</v>
       </c>
       <c r="L157" t="str">
-        <v>UNDER THE RHYTHM - Adam Lambert</v>
+        <v>Weak - Naomi Sharon</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>You’re Mine</v>
+        <v>ALL NIGHT LONG</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
+        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
       </c>
       <c r="D158" t="str">
         <v>2026-06-08</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Papercut</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G158" t="str">
-        <v>4:25</v>
+        <v>2:28</v>
       </c>
       <c r="H158" t="str">
-        <v>Imani Imani</v>
+        <v>Pheelz</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
+        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
       </c>
       <c r="L158" t="str">
-        <v>You’re Mine - Imani Imani</v>
+        <v>ALL NIGHT LONG - Pheelz</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>point blank</v>
+        <v>Every Life</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
+        <v>https://music.apple.com/us/song/every-life/6764110978</v>
       </c>
       <c r="D159" t="str">
         <v>2026-06-08</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>new avatar</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G159" t="str">
-        <v>4:26</v>
+        <v>3:18</v>
       </c>
       <c r="H159" t="str">
-        <v>Kelela</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
+        <v>https://music.apple.com/us/album/every-life/1895644574</v>
       </c>
       <c r="L159" t="str">
-        <v>point blank - Kelela</v>
+        <v>Every Life - Isabel LaRosa</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>that's my beach!</v>
+        <v>Home</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
+        <v>https://music.apple.com/us/song/home/6774718029</v>
       </c>
       <c r="D160" t="str">
         <v>2026-06-08</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>Good Grief</v>
       </c>
       <c r="G160" t="str">
-        <v>3:18</v>
+        <v>4:53</v>
       </c>
       <c r="H160" t="str">
-        <v>horsegiirL</v>
+        <v>Sara Bareilles</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
+        <v>https://music.apple.com/us/album/home/6774718027</v>
       </c>
       <c r="L160" t="str">
-        <v>that's my beach! - horsegiirL</v>
+        <v>Home - Sara Bareilles</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>In Your Eyes</v>
+        <v>Satalanaaa</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
+        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
       </c>
       <c r="D161" t="str">
         <v>2026-06-08</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>In Your Eyes - Single</v>
+        <v>Satalanaaa - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:36</v>
+        <v>2:06</v>
       </c>
       <c r="H161" t="str">
-        <v>Alesso</v>
+        <v>Pitbull</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/alesso/432464201</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
+        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
       </c>
       <c r="L161" t="str">
-        <v>In Your Eyes - Alesso</v>
+        <v>Satalanaaa - Pitbull</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>ALL OR NOTHING</v>
+        <v>Miss Me More</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
+        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
       </c>
       <c r="D162" t="str">
         <v>2026-06-08</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>ALL OR NOTHING - Single</v>
+        <v>Confessions of a Lonely Heart</v>
       </c>
       <c r="G162" t="str">
-        <v>3:17</v>
+        <v>2:43</v>
       </c>
       <c r="H162" t="str">
-        <v>Tobe Nwigwe</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
+        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
       </c>
       <c r="L162" t="str">
-        <v>ALL OR NOTHING - Tobe Nwigwe</v>
+        <v>Miss Me More - Eric Nam</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>IN MY HANDS</v>
+        <v>Rituals</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
+        <v>https://music.apple.com/us/song/rituals/6769628916</v>
       </c>
       <c r="D163" t="str">
         <v>2026-06-08</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>IN MY HANDS - Single</v>
+        <v>Rituals - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:14</v>
+        <v>2:10</v>
       </c>
       <c r="H163" t="str">
-        <v>Alessia Cara</v>
+        <v>Rico Nasty</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
+        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
+        <v>https://music.apple.com/us/album/rituals/6769628915</v>
       </c>
       <c r="L163" t="str">
-        <v>IN MY HANDS - Alessia Cara</v>
+        <v>Rituals - Rico Nasty</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Life's a Dream</v>
+        <v>Honeysuckle</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
+        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
       </c>
       <c r="D164" t="str">
         <v>2026-06-08</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>Honeysuckle - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>5:31</v>
+        <v>3:15</v>
       </c>
       <c r="H164" t="str">
-        <v>Modest Mouse</v>
+        <v>Dylan Gossett</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
+        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
       </c>
       <c r="L164" t="str">
-        <v>Life's a Dream - Modest Mouse</v>
+        <v>Honeysuckle - Dylan Gossett</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
+        <v>listen…</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
+        <v>https://music.apple.com/us/song/listen/6775576508</v>
       </c>
       <c r="D165" t="str">
         <v>2026-06-08</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Season of Surrender</v>
+        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G165" t="str">
-        <v>4:47</v>
+        <v>4:08</v>
       </c>
       <c r="H165" t="str">
-        <v>August Burns Red</v>
+        <v>John Williams</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
+        <v>https://music.apple.com/us/artist/john-williams/63748</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
+        <v>https://music.apple.com/us/album/listen/6775576506</v>
       </c>
       <c r="L165" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
+        <v>listen… - John Williams</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Shine</v>
+        <v>DEADMEAT</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/shine/6764654536</v>
+        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
       </c>
       <c r="D166" t="str">
         <v>2026-06-08</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Black Mozart</v>
+        <v>DEADMEAT - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:27</v>
+        <v>2:52</v>
       </c>
       <c r="H166" t="str">
-        <v>Jon Batiste</v>
+        <v>South Arcade</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/shine/1895866355</v>
+        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
       </c>
       <c r="L166" t="str">
-        <v>Shine - Jon Batiste</v>
+        <v>DEADMEAT - South Arcade</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Half The Man</v>
+        <v>Ugly and Rotten</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
+        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
       </c>
       <c r="D167" t="str">
         <v>2026-06-08</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Scared of Heights</v>
+        <v>Ugly and Rotten - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:56</v>
+        <v>2:49</v>
       </c>
       <c r="H167" t="str">
-        <v>Wyatt Flores</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
+        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
       </c>
       <c r="L167" t="str">
-        <v>Half The Man - Wyatt Flores</v>
+        <v>Ugly and Rotten - Mckenna Grace</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Preacher’s Kid</v>
+        <v>Whisper</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
+        <v>https://music.apple.com/us/song/whisper/6772254272</v>
       </c>
       <c r="D168" t="str">
         <v>2026-06-08</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Preacher’s Kid - Single</v>
+        <v>Whisper - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>5:02</v>
+        <v>2:47</v>
       </c>
       <c r="H168" t="str">
-        <v>Stephen Wilson Jr.</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
+        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
+        <v>https://music.apple.com/us/album/whisper/6772254268</v>
       </c>
       <c r="L168" t="str">
-        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
+        <v>Whisper - Blu DeTiger</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Weak</v>
+        <v>Gecko (feat. Haley Bridge)</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/weak/6771151098</v>
+        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
       </c>
       <c r="D169" t="str">
         <v>2026-06-08</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Weak - Single</v>
+        <v>How dare you tryna love me? - EP</v>
       </c>
       <c r="G169" t="str">
-        <v>3:28</v>
+        <v>2:46</v>
       </c>
       <c r="H169" t="str">
-        <v>Naomi Sharon</v>
+        <v>Olga Myko</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/weak/6771151088</v>
+        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
       </c>
       <c r="L169" t="str">
-        <v>Weak - Naomi Sharon</v>
+        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>ALL NIGHT LONG</v>
+        <v>Compa Primo</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
+        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
       </c>
       <c r="D170" t="str">
         <v>2026-06-08</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>A Rii Set</v>
+        <v>Compa Primo - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:28</v>
+        <v>3:12</v>
       </c>
       <c r="H170" t="str">
-        <v>Pheelz</v>
+        <v>Nueva H</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
+        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
       </c>
       <c r="L170" t="str">
-        <v>ALL NIGHT LONG - Pheelz</v>
+        <v>Compa Primo - Nueva H</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Every Life</v>
+        <v>Parachute</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/every-life/6764110978</v>
+        <v>https://music.apple.com/us/song/parachute/6768841410</v>
       </c>
       <c r="D171" t="str">
         <v>2026-06-08</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:18</v>
+        <v>3:11</v>
       </c>
       <c r="H171" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Tyler James Bellinger</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/every-life/1895644574</v>
+        <v>https://music.apple.com/us/album/parachute/6768841409</v>
       </c>
       <c r="L171" t="str">
-        <v>Every Life - Isabel LaRosa</v>
+        <v>Parachute - Tyler James Bellinger</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Home</v>
+        <v>Like a Bubble</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/home/6774718029</v>
+        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
       </c>
       <c r="D172" t="str">
         <v>2026-06-08</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Good Grief</v>
+        <v>Imperfect-I'mperfect - EP</v>
       </c>
       <c r="G172" t="str">
-        <v>4:53</v>
+        <v>3:08</v>
       </c>
       <c r="H172" t="str">
-        <v>Sara Bareilles</v>
+        <v>FIFTY FIFTY</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
+        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/home/6774718027</v>
+        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
       </c>
       <c r="L172" t="str">
-        <v>Home - Sara Bareilles</v>
+        <v>Like a Bubble - FIFTY FIFTY</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Satalanaaa</v>
+        <v>Hustle and Opulence in America</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
+        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
       </c>
       <c r="D173" t="str">
         <v>2026-06-08</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Satalanaaa - Single</v>
+        <v>AK Cuts: Vol. 4 - EP</v>
       </c>
       <c r="G173" t="str">
-        <v>2:06</v>
+        <v>3:07</v>
       </c>
       <c r="H173" t="str">
-        <v>Pitbull</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
+        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
       </c>
       <c r="L173" t="str">
-        <v>Satalanaaa - Pitbull</v>
+        <v>Hustle and Opulence in America - Anish Kumar</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Miss Me More</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
+        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
       </c>
       <c r="D174" t="str">
         <v>2026-06-08</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Confessions of a Lonely Heart</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:43</v>
+        <v>2:47</v>
       </c>
       <c r="H174" t="str">
-        <v>Eric Nam</v>
+        <v>ivri</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
+        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
       </c>
       <c r="L174" t="str">
-        <v>Miss Me More - Eric Nam</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Rituals</v>
+        <v>CLEAN SWEEP</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/rituals/6769628916</v>
+        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
       </c>
       <c r="D175" t="str">
         <v>2026-06-08</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Rituals - Single</v>
+        <v>CLEAN SWEEP - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:10</v>
+        <v>3:11</v>
       </c>
       <c r="H175" t="str">
-        <v>Rico Nasty</v>
+        <v>Storm Reid</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
+        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/rituals/6769628915</v>
+        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
       </c>
       <c r="L175" t="str">
-        <v>Rituals - Rico Nasty</v>
+        <v>CLEAN SWEEP - Storm Reid</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Honeysuckle</v>
+        <v>CANDYLAND!</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
+        <v>https://music.apple.com/us/song/candyland/6766927008</v>
       </c>
       <c r="D176" t="str">
         <v>2026-06-08</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Honeysuckle - Single</v>
+        <v>CANDYLAND! - Single</v>
       </c>
       <c r="G176" t="str">
         <v>3:15</v>
       </c>
       <c r="H176" t="str">
-        <v>Dylan Gossett</v>
+        <v>Natanya</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
+        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
+        <v>https://music.apple.com/us/album/candyland/6766927000</v>
       </c>
       <c r="L176" t="str">
-        <v>Honeysuckle - Dylan Gossett</v>
+        <v>CANDYLAND! - Natanya</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>listen…</v>
+        <v>Double C</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/listen/6775576508</v>
+        <v>https://music.apple.com/us/song/double-c/6771836555</v>
       </c>
       <c r="D177" t="str">
         <v>2026-06-08</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
+        <v>Double C - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>4:08</v>
+        <v>2:21</v>
       </c>
       <c r="H177" t="str">
-        <v>John Williams</v>
+        <v>Sk8star</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/john-williams/63748</v>
+        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/listen/6775576506</v>
+        <v>https://music.apple.com/us/album/double-c/6771836554</v>
       </c>
       <c r="L177" t="str">
-        <v>listen… - John Williams</v>
+        <v>Double C - Sk8star</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>DEADMEAT</v>
+        <v>madera</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
+        <v>https://music.apple.com/us/song/madera/6764638112</v>
       </c>
       <c r="D178" t="str">
         <v>2026-06-08</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>DEADMEAT - Single</v>
+        <v>madera/un camino luminoso - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:52</v>
+        <v>5:41</v>
       </c>
       <c r="H178" t="str">
-        <v>South Arcade</v>
+        <v>Lumtz</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
+        <v>https://music.apple.com/us/album/madera/6764638109</v>
       </c>
       <c r="L178" t="str">
-        <v>DEADMEAT - South Arcade</v>
+        <v>madera - Lumtz</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Ugly and Rotten</v>
+        <v>Slip the Noose</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
+        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
       </c>
       <c r="D179" t="str">
         <v>2026-06-08</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Ugly and Rotten - Single</v>
+        <v>Hum of Hurt</v>
       </c>
       <c r="G179" t="str">
-        <v>2:49</v>
+        <v>1:43</v>
       </c>
       <c r="H179" t="str">
-        <v>Mckenna Grace</v>
+        <v>Converge</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
+        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
       </c>
       <c r="L179" t="str">
-        <v>Ugly and Rotten - Mckenna Grace</v>
+        <v>Slip the Noose - Converge</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Whisper</v>
+        <v>Crying Fire</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/whisper/6772254272</v>
+        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
       </c>
       <c r="D180" t="str">
         <v>2026-06-08</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Whisper - Single</v>
+        <v>Crying Fire - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:47</v>
+        <v>4:08</v>
       </c>
       <c r="H180" t="str">
-        <v>Blu DeTiger</v>
+        <v>Avatar</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
+        <v>https://music.apple.com/us/artist/avatar/187616241</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/whisper/6772254268</v>
+        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
       </c>
       <c r="L180" t="str">
-        <v>Whisper - Blu DeTiger</v>
+        <v>Crying Fire - Avatar</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Gecko (feat. Haley Bridge)</v>
+        <v>NI NA’</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
+        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
       </c>
       <c r="D181" t="str">
         <v>2026-06-08</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>How dare you tryna love me? - EP</v>
+        <v>sorry si soy GRRRIS</v>
       </c>
       <c r="G181" t="str">
-        <v>2:46</v>
+        <v>2:53</v>
       </c>
       <c r="H181" t="str">
-        <v>Olga Myko</v>
+        <v>ROBI</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
+        <v>https://music.apple.com/us/artist/robi/1458047972</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
+        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
       </c>
       <c r="L181" t="str">
-        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
+        <v>NI NA’ - ROBI</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Compa Primo</v>
+        <v>Holding Back</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
+        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
       </c>
       <c r="D182" t="str">
         <v>2026-06-08</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Compa Primo - Single</v>
+        <v>AMA</v>
       </c>
       <c r="G182" t="str">
-        <v>3:12</v>
+        <v>3:19</v>
       </c>
       <c r="H182" t="str">
-        <v>Nueva H</v>
+        <v>Ama</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
+        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
       </c>
       <c r="L182" t="str">
-        <v>Compa Primo - Nueva H</v>
+        <v>Holding Back - Ama</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Parachute</v>
+        <v>you're still mine</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/parachute/6768841410</v>
+        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
       </c>
       <c r="D183" t="str">
         <v>2026-06-08</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Parachute - Single</v>
+        <v>you're still mine - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:11</v>
+        <v>3:19</v>
       </c>
       <c r="H183" t="str">
-        <v>Tyler James Bellinger</v>
+        <v>Lexi Jayde</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
+        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/parachute/6768841409</v>
+        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
       </c>
       <c r="L183" t="str">
-        <v>Parachute - Tyler James Bellinger</v>
+        <v>you're still mine - Lexi Jayde</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Like a Bubble</v>
+        <v>teksi</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
+        <v>https://music.apple.com/us/song/teksi/6769899742</v>
       </c>
       <c r="D184" t="str">
         <v>2026-06-08</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Imperfect-I'mperfect - EP</v>
+        <v>pOCHO</v>
       </c>
       <c r="G184" t="str">
-        <v>3:08</v>
+        <v>2:48</v>
       </c>
       <c r="H184" t="str">
-        <v>FIFTY FIFTY</v>
+        <v>8onthebeat</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
+        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
+        <v>https://music.apple.com/us/album/teksi/6769899739</v>
       </c>
       <c r="L184" t="str">
-        <v>Like a Bubble - FIFTY FIFTY</v>
+        <v>teksi - 8onthebeat</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Hustle and Opulence in America</v>
+        <v>Let You Go</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
+        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
       </c>
       <c r="D185" t="str">
         <v>2026-06-08</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>AK Cuts: Vol. 4 - EP</v>
+        <v>Let You Go - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:07</v>
+        <v>1:37</v>
       </c>
       <c r="H185" t="str">
-        <v>Anish Kumar</v>
+        <v>Nate Sib</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
+        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
       </c>
       <c r="L185" t="str">
-        <v>Hustle and Opulence in America - Anish Kumar</v>
+        <v>Let You Go - Nate Sib</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
+        <v>Dis-Moi</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
+        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
       </c>
       <c r="D186" t="str">
         <v>2026-06-08</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
+        <v>CINNA</v>
       </c>
       <c r="G186" t="str">
-        <v>2:47</v>
+        <v>2:27</v>
       </c>
       <c r="H186" t="str">
-        <v>ivri</v>
+        <v>Cannelle</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
+        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
+        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
       </c>
       <c r="L186" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
+        <v>Dis-Moi - Cannelle</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>CLEAN SWEEP</v>
+        <v>Leverage</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
+        <v>https://music.apple.com/us/song/leverage/6776432312</v>
       </c>
       <c r="D187" t="str">
         <v>2026-06-08</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>CLEAN SWEEP - Single</v>
+        <v>Heaven on Mars</v>
       </c>
       <c r="G187" t="str">
-        <v>3:11</v>
+        <v>3:04</v>
       </c>
       <c r="H187" t="str">
-        <v>Storm Reid</v>
+        <v>NoCap</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
+        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
+        <v>https://music.apple.com/us/album/leverage/6776432217</v>
       </c>
       <c r="L187" t="str">
-        <v>CLEAN SWEEP - Storm Reid</v>
+        <v>Leverage - NoCap</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>CANDYLAND!</v>
+        <v>Kool Aid</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/candyland/6766927008</v>
+        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
       </c>
       <c r="D188" t="str">
         <v>2026-06-08</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>CANDYLAND! - Single</v>
+        <v>Where Have All The Good Men Gone? - EP</v>
       </c>
       <c r="G188" t="str">
-        <v>3:15</v>
+        <v>3:40</v>
       </c>
       <c r="H188" t="str">
-        <v>Natanya</v>
+        <v>Debbii Dawson</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
+        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/candyland/6766927000</v>
+        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
       </c>
       <c r="L188" t="str">
-        <v>CANDYLAND! - Natanya</v>
+        <v>Kool Aid - Debbii Dawson</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Double C</v>
+        <v>Pieces</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/double-c/6771836555</v>
+        <v>https://music.apple.com/us/song/pieces/6771861156</v>
       </c>
       <c r="D189" t="str">
         <v>2026-06-08</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Double C - Single</v>
+        <v>Pieces - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:21</v>
+        <v>2:19</v>
       </c>
       <c r="H189" t="str">
-        <v>Sk8star</v>
+        <v>Dom Innarella</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
+        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/double-c/6771836554</v>
+        <v>https://music.apple.com/us/album/pieces/6771861155</v>
       </c>
       <c r="L189" t="str">
-        <v>Double C - Sk8star</v>
+        <v>Pieces - Dom Innarella</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>madera</v>
+        <v>Mesmerized</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/madera/6764638112</v>
+        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
       </c>
       <c r="D190" t="str">
         <v>2026-06-08</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>madera/un camino luminoso - Single</v>
+        <v>Mesmerized - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>5:41</v>
+        <v>2:38</v>
       </c>
       <c r="H190" t="str">
-        <v>Lumtz</v>
+        <v>The Aces</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
+        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/madera/6764638109</v>
+        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
       </c>
       <c r="L190" t="str">
-        <v>madera - Lumtz</v>
+        <v>Mesmerized - The Aces</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Slip the Noose</v>
+        <v>Perfect 10</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
+        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
       </c>
       <c r="D191" t="str">
         <v>2026-06-08</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Hum of Hurt</v>
+        <v>No Hard Feelings (Deluxe)</v>
       </c>
       <c r="G191" t="str">
-        <v>1:43</v>
+        <v>2:51</v>
       </c>
       <c r="H191" t="str">
-        <v>Converge</v>
+        <v>The Beaches</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
+        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
       </c>
       <c r="L191" t="str">
-        <v>Slip the Noose - Converge</v>
+        <v>Perfect 10 - The Beaches</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Crying Fire</v>
+        <v>Recognize</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
+        <v>https://music.apple.com/us/song/recognize/6769164705</v>
       </c>
       <c r="D192" t="str">
         <v>2026-06-08</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Crying Fire - Single</v>
+        <v>Recognize - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>4:08</v>
+        <v>2:05</v>
       </c>
       <c r="H192" t="str">
-        <v>Avatar</v>
+        <v>Fana Hues</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/avatar/187616241</v>
+        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
+        <v>https://music.apple.com/us/album/recognize/6769164704</v>
       </c>
       <c r="L192" t="str">
-        <v>Crying Fire - Avatar</v>
+        <v>Recognize - Fana Hues</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>NI NA’</v>
+        <v>Feel The Vibe</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
+        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
       </c>
       <c r="D193" t="str">
         <v>2026-06-08</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>sorry si soy GRRRIS</v>
+        <v>Feel The Vibe</v>
       </c>
       <c r="G193" t="str">
-        <v>2:53</v>
+        <v>3:28</v>
       </c>
       <c r="H193" t="str">
-        <v>ROBI</v>
+        <v>Above &amp; Beyond</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/robi/1458047972</v>
+        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
+        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
       </c>
       <c r="L193" t="str">
-        <v>NI NA’ - ROBI</v>
+        <v>Feel The Vibe - Above &amp; Beyond</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Holding Back</v>
+        <v>I Never Knew</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
+        <v>https://music.apple.com/us/song/i-never-knew/6764351468</v>
       </c>
       <c r="D194" t="str">
         <v>2026-06-08</v>
@@ -7747,486 +7747,30 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>AMA</v>
+        <v>I Never Knew - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:19</v>
+        <v>3:51</v>
       </c>
       <c r="H194" t="str">
-        <v>Ama</v>
+        <v>Adam Ten</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
+        <v>https://music.apple.com/us/album/i-never-knew/1895744479</v>
       </c>
       <c r="L194" t="str">
-        <v>Holding Back - Ama</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v>you're still mine</v>
-      </c>
-      <c r="B195" t="str">
-        <v/>
-      </c>
-      <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
-      </c>
-      <c r="D195" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E195" t="str">
-        <v/>
-      </c>
-      <c r="F195" t="str">
-        <v>you're still mine - Single</v>
-      </c>
-      <c r="G195" t="str">
-        <v>3:19</v>
-      </c>
-      <c r="H195" t="str">
-        <v>Lexi Jayde</v>
-      </c>
-      <c r="I195" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
-      </c>
-      <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
-      </c>
-      <c r="L195" t="str">
-        <v>you're still mine - Lexi Jayde</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>teksi</v>
-      </c>
-      <c r="B196" t="str">
-        <v/>
-      </c>
-      <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/teksi/6769899742</v>
-      </c>
-      <c r="D196" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E196" t="str">
-        <v/>
-      </c>
-      <c r="F196" t="str">
-        <v>pOCHO</v>
-      </c>
-      <c r="G196" t="str">
-        <v>2:48</v>
-      </c>
-      <c r="H196" t="str">
-        <v>8onthebeat</v>
-      </c>
-      <c r="I196" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
-      </c>
-      <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/teksi/6769899739</v>
-      </c>
-      <c r="L196" t="str">
-        <v>teksi - 8onthebeat</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>Let You Go</v>
-      </c>
-      <c r="B197" t="str">
-        <v/>
-      </c>
-      <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
-      </c>
-      <c r="D197" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E197" t="str">
-        <v/>
-      </c>
-      <c r="F197" t="str">
-        <v>Let You Go - Single</v>
-      </c>
-      <c r="G197" t="str">
-        <v>1:37</v>
-      </c>
-      <c r="H197" t="str">
-        <v>Nate Sib</v>
-      </c>
-      <c r="I197" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
-      </c>
-      <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
-      </c>
-      <c r="L197" t="str">
-        <v>Let You Go - Nate Sib</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>Dis-Moi</v>
-      </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
-      </c>
-      <c r="D198" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
-        <v>CINNA</v>
-      </c>
-      <c r="G198" t="str">
-        <v>2:27</v>
-      </c>
-      <c r="H198" t="str">
-        <v>Cannelle</v>
-      </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
-      </c>
-      <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
-      </c>
-      <c r="L198" t="str">
-        <v>Dis-Moi - Cannelle</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Leverage</v>
-      </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/leverage/6776432312</v>
-      </c>
-      <c r="D199" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>Heaven on Mars</v>
-      </c>
-      <c r="G199" t="str">
-        <v>3:04</v>
-      </c>
-      <c r="H199" t="str">
-        <v>NoCap</v>
-      </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
-      </c>
-      <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/leverage/6776432217</v>
-      </c>
-      <c r="L199" t="str">
-        <v>Leverage - NoCap</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Kool Aid</v>
-      </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
-      </c>
-      <c r="D200" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>Where Have All The Good Men Gone? - EP</v>
-      </c>
-      <c r="G200" t="str">
-        <v>3:40</v>
-      </c>
-      <c r="H200" t="str">
-        <v>Debbii Dawson</v>
-      </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
-      </c>
-      <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
-      </c>
-      <c r="L200" t="str">
-        <v>Kool Aid - Debbii Dawson</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>Pieces</v>
-      </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/pieces/6771861156</v>
-      </c>
-      <c r="D201" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
-        <v>Pieces - Single</v>
-      </c>
-      <c r="G201" t="str">
-        <v>2:19</v>
-      </c>
-      <c r="H201" t="str">
-        <v>Dom Innarella</v>
-      </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
-      </c>
-      <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/pieces/6771861155</v>
-      </c>
-      <c r="L201" t="str">
-        <v>Pieces - Dom Innarella</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>Mesmerized</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>Mesmerized - Single</v>
-      </c>
-      <c r="G202" t="str">
-        <v>2:38</v>
-      </c>
-      <c r="H202" t="str">
-        <v>The Aces</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
-      </c>
-      <c r="L202" t="str">
-        <v>Mesmerized - The Aces</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>Perfect 10</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>No Hard Feelings (Deluxe)</v>
-      </c>
-      <c r="G203" t="str">
-        <v>2:51</v>
-      </c>
-      <c r="H203" t="str">
-        <v>The Beaches</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
-      </c>
-      <c r="L203" t="str">
-        <v>Perfect 10 - The Beaches</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>Recognize</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/recognize/6769164705</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>Recognize - Single</v>
-      </c>
-      <c r="G204" t="str">
-        <v>2:05</v>
-      </c>
-      <c r="H204" t="str">
-        <v>Fana Hues</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/recognize/6769164704</v>
-      </c>
-      <c r="L204" t="str">
-        <v>Recognize - Fana Hues</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>Feel The Vibe</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>Feel The Vibe</v>
-      </c>
-      <c r="G205" t="str">
-        <v>3:28</v>
-      </c>
-      <c r="H205" t="str">
-        <v>Above &amp; Beyond</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
-      </c>
-      <c r="L205" t="str">
-        <v>Feel The Vibe - Above &amp; Beyond</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>I Never Knew</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/i-never-knew/6764351468</v>
-      </c>
-      <c r="D206" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>I Never Knew - Single</v>
-      </c>
-      <c r="G206" t="str">
-        <v>3:51</v>
-      </c>
-      <c r="H206" t="str">
-        <v>Adam Ten</v>
-      </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
-      </c>
-      <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/i-never-knew/1895744479</v>
-      </c>
-      <c r="L206" t="str">
         <v>I Never Knew - Adam Ten</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L206"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L194"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-06-week02/titles.xlsx
+++ b/data/global/2026-06-week02/titles.xlsx
@@ -439,19 +439,19 @@
         <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>10 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>10 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B3" t="str">
-        <v>10 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>10 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,19 +515,19 @@
         <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>11 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>11 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,19 +553,19 @@
         <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>11 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>11 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -667,19 +667,19 @@
         <v>Reba McEntire - You Never Gave Up On Me</v>
       </c>
       <c r="B8" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B23" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,19 +1275,19 @@
         <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B24" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,19 +1313,19 @@
         <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B26" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,19 +1427,19 @@
         <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B28" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,19 +1465,19 @@
         <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B29" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,19 +1503,19 @@
         <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,19 +1541,19 @@
         <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B31" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,19 +1579,19 @@
         <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B32" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2111,19 +2111,19 @@
         <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
       </c>
       <c r="B46" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3099,19 +3099,19 @@
         <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B72" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,19 +3137,19 @@
         <v>Boyzone - No Matter What (Live)</v>
       </c>
       <c r="B73" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,19 +3175,19 @@
         <v>Florrie - The Times (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
         <v>Madonna - Love Sensation (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3555,19 +3555,19 @@
         <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,19 +3593,19 @@
         <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
       </c>
       <c r="B85" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/true-colors/6776032892</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/too-easy/6774752170</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/three-nations/6776010602</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/encerrones/6771854522</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/passenger/6773456081</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/secret-language/6774223667</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/vertical/1892436336</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/bluffin/6772951032</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/dreams/1884731028</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/cotton/1887627941</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/madrugada/6773906244</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/ruin/6763176090</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/do-today/1893402864</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/point-blank/1888561542</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/shine/6764654536</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/weak/6771151098</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/every-life/6764110978</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/home/6774718029</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/rituals/6769628916</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/listen/6775576508</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/whisper/6772254272</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/parachute/6768841410</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/candyland/6766927008</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/double-c/6771836555</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/madera/6764638112</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/ni-na/6768820889</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/holding-back/6773986881</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/teksi/6769899742</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/leverage/6776432312</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/pieces/6771861156</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/recognize/6769164705</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/i-never-knew/6764351468</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-09</v>
       </c>
       <c r="E194" t="str">
         <v/>

--- a/data/global/2026-06-week02/titles.xlsx
+++ b/data/global/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L194"/>
+  <dimension ref="A1:L195"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
+        <v>אנוש ilnka x – קרבית</v>
       </c>
       <c r="B2" t="str">
-        <v>15 hours ago</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
+        <v>https://yosmusic.com/%d7%90%d7%a0%d7%95%d7%a9-ilnka-x-%d7%a7%d7%a8%d7%91%d7%99%d7%aa/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-09</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>15 hours ago</v>
+        <v>השיר "קרבית" של אנוש צוברי (באירוח ilanka, המגולמת על ידי השחקן והרקדן אילן זכרוב) הוא אחת היצירות המטורללות, המבריקות והאמיצות ביותר שידע הפופ הים-תיכוני בישראל. קל לפטור את השיר כרצועת דאנס-חפלה מועדונים קלילה המיועדת להרמות. אולם, "קרבית" הוא למעשה שיר</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>אנוש ilnka x – קרבית</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>15 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
+        <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-09</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>15 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B4" t="str">
-        <v>15 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
+        <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-09</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>15 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>15 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
+        <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
       </c>
       <c r="D5" t="str">
         <v>2026-06-09</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>15 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
+        <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
       </c>
       <c r="D6" t="str">
         <v>2026-06-09</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video)</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
+        <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-09</v>
@@ -647,7 +647,7 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Capital FM</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Reba McEntire - You Never Gave Up On Me</v>
+        <v>DEEP PURPLE - DIABLO (Official Video)</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
+        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
       </c>
       <c r="D8" t="str">
         <v>2026-06-09</v>
@@ -685,7 +685,7 @@
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Reba McEntire</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Reba McEntire - You Never Gave Up On Me - Reba McEntire</v>
+        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>elijah woods - Wonder (Official Lyric Video)</v>
+        <v>Reba McEntire - You Never Gave Up On Me</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
+        <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-09</v>
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>elijah woods</v>
+        <v>Reba McEntire</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>elijah woods - Wonder (Official Lyric Video) - elijah woods</v>
+        <v>Reba McEntire - You Never Gave Up On Me - Reba McEntire</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>elijah woods - Wonder (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
+        <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
       </c>
       <c r="D10" t="str">
         <v>2026-06-09</v>
@@ -761,7 +761,7 @@
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Capital FM and XG</v>
+        <v>elijah woods</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
+        <v>elijah woods - Wonder (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B11" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
+        <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
       </c>
       <c r="D11" t="str">
         <v>2026-06-09</v>
@@ -799,7 +799,7 @@
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B12" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
+        <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
       </c>
       <c r="D12" t="str">
         <v>2026-06-09</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B13" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
+        <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
       </c>
       <c r="D13" t="str">
         <v>2026-06-09</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B14" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
+        <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
       </c>
       <c r="D14" t="str">
         <v>2026-06-09</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B15" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
+        <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
       </c>
       <c r="D15" t="str">
         <v>2026-06-09</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B16" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
+        <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
       </c>
       <c r="D16" t="str">
         <v>2026-06-09</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B17" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
+        <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
       </c>
       <c r="D17" t="str">
         <v>2026-06-09</v>
@@ -1027,7 +1027,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B18" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
+        <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
       </c>
       <c r="D18" t="str">
         <v>2026-06-09</v>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Capital FM and XG</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B19" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
+        <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
       </c>
       <c r="D19" t="str">
         <v>2026-06-09</v>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B20" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
+        <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
       </c>
       <c r="D20" t="str">
         <v>2026-06-09</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B21" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
+        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
       </c>
       <c r="D21" t="str">
         <v>2026-06-09</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B22" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
+        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
       </c>
       <c r="D22" t="str">
         <v>2026-06-09</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
+        <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
       </c>
       <c r="D23" t="str">
         <v>2026-06-09</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
+        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
       </c>
       <c r="D24" t="str">
         <v>2026-06-09</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
+        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
       </c>
       <c r="D25" t="str">
         <v>2026-06-09</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
+        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
       </c>
       <c r="D26" t="str">
         <v>2026-06-09</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
+        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
       </c>
       <c r="D27" t="str">
         <v>2026-06-09</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
+        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
+        <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
       </c>
       <c r="D28" t="str">
         <v>2026-06-09</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
+        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
       </c>
       <c r="D29" t="str">
         <v>2026-06-09</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
+        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
       </c>
       <c r="D30" t="str">
         <v>2026-06-09</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B31" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
+        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
       </c>
       <c r="D31" t="str">
         <v>2026-06-09</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B32" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
+        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
       </c>
       <c r="D32" t="str">
         <v>2026-06-09</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
+        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B33" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
+        <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
       </c>
       <c r="D33" t="str">
         <v>2026-06-09</v>
@@ -1635,7 +1635,7 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B34" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
+        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
       </c>
       <c r="D34" t="str">
         <v>2026-06-09</v>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B35" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
+        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
       </c>
       <c r="D35" t="str">
         <v>2026-06-09</v>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B36" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
+        <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
       </c>
       <c r="D36" t="str">
         <v>2026-06-09</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B37" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
+        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
       </c>
       <c r="D37" t="str">
         <v>2026-06-09</v>
@@ -1787,7 +1787,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B38" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
+        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
       </c>
       <c r="D38" t="str">
         <v>2026-06-09</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B39" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
+        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
       </c>
       <c r="D39" t="str">
         <v>2026-06-09</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B40" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
+        <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
       </c>
       <c r="D40" t="str">
         <v>2026-06-09</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B41" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
+        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
       </c>
       <c r="D41" t="str">
         <v>2026-06-09</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B42" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
+        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
       </c>
       <c r="D42" t="str">
         <v>2026-06-09</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B43" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
+        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
       </c>
       <c r="D43" t="str">
         <v>2026-06-09</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B44" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
+        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
       </c>
       <c r="D44" t="str">
         <v>2026-06-09</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
+        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B45" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
+        <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
       </c>
       <c r="D45" t="str">
         <v>2026-06-09</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Capital FM</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
       </c>
       <c r="B46" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
+        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
       </c>
       <c r="D46" t="str">
         <v>2026-06-09</v>
@@ -2129,7 +2129,7 @@
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>TheCranberriesTV</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
       </c>
       <c r="B47" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
+        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-06-09</v>
@@ -2167,7 +2167,7 @@
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Jordana Bryant</v>
+        <v>TheCranberriesTV</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
       </c>
       <c r="B48" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
+        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
       </c>
       <c r="D48" t="str">
         <v>2026-06-09</v>
@@ -2205,7 +2205,7 @@
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Grace Enger</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
+        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
       </c>
       <c r="D49" t="str">
         <v>2026-06-09</v>
@@ -2243,7 +2243,7 @@
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>The Offspring</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Lola Young – From Down Here (From The Pool)</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B50" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
+        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
       </c>
       <c r="D50" t="str">
         <v>2026-06-09</v>
@@ -2281,7 +2281,7 @@
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Lola Young</v>
+        <v>The Offspring</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>CAIN - Living Water (Music Video)</v>
+        <v>Lola Young – From Down Here (From The Pool)</v>
       </c>
       <c r="B51" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
+        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
       </c>
       <c r="D51" t="str">
         <v>2026-06-09</v>
@@ -2319,7 +2319,7 @@
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>CAIN</v>
+        <v>Lola Young</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>CAIN - Living Water (Music Video) - CAIN</v>
+        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
+        <v>CAIN - Living Water (Music Video)</v>
       </c>
       <c r="B52" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
+        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
       </c>
       <c r="D52" t="str">
         <v>2026-06-09</v>
@@ -2357,7 +2357,7 @@
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Eric Clapton</v>
+        <v>CAIN</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
+        <v>CAIN - Living Water (Music Video) - CAIN</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video)</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
+        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
       </c>
       <c r="D53" t="str">
         <v>2026-06-09</v>
@@ -2395,7 +2395,7 @@
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Blu DeTiger</v>
+        <v>Eric Clapton</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
+        <v>Blu DeTiger - Whisper (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
+        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
       </c>
       <c r="D54" t="str">
         <v>2026-06-09</v>
@@ -2433,7 +2433,7 @@
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
       </c>
       <c r="B55" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
+        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
       </c>
       <c r="D55" t="str">
         <v>2026-06-09</v>
@@ -2471,7 +2471,7 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Pink Floyd</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Holly Humberstone - it’s just White Noise</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
       </c>
       <c r="B56" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
+        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
       </c>
       <c r="D56" t="str">
         <v>2026-06-09</v>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Holly Humberstone</v>
+        <v>Pink Floyd</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
+        <v>Holly Humberstone - it’s just White Noise</v>
       </c>
       <c r="B57" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
+        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
       </c>
       <c r="D57" t="str">
         <v>2026-06-09</v>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Freya Ridings</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
+        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
       </c>
       <c r="B58" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
+        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
       </c>
       <c r="D58" t="str">
         <v>2026-06-09</v>
@@ -2585,7 +2585,7 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Muse</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
       </c>
       <c r="B59" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
+        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
       </c>
       <c r="D59" t="str">
         <v>2026-06-09</v>
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Ellie Goulding</v>
+        <v>Muse</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer)</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
       </c>
       <c r="B60" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
+        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
       </c>
       <c r="D60" t="str">
         <v>2026-06-09</v>
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Evanescence</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
+        <v>Evanescence - Sanctuary (Official Visualizer)</v>
       </c>
       <c r="B61" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
+        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
       </c>
       <c r="D61" t="str">
         <v>2026-06-09</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>The Beaches</v>
+        <v>Evanescence</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
+        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Bella White - Stuff (Official Music Video)</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
+        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
       </c>
       <c r="D62" t="str">
         <v>2026-06-09</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Bella White</v>
+        <v>The Beaches</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer)</v>
+        <v>Bella White - Stuff (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
+        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
       </c>
       <c r="D63" t="str">
         <v>2026-06-09</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Meduza and 2 more</v>
+        <v>Bella White</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
+        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>CAIN - Living Water (Lyric Video)</v>
+        <v>Meduza, Rani - Silence (Official Visualizer)</v>
       </c>
       <c r="B64" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
+        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
       </c>
       <c r="D64" t="str">
         <v>2026-06-09</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>CAIN</v>
+        <v>Meduza and 2 more</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
+        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
+        <v>CAIN - Living Water (Lyric Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
+        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
       </c>
       <c r="D65" t="str">
         <v>2026-06-09</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Fitz and the Tantrums</v>
+        <v>CAIN</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
+        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video)</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
+        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
       </c>
       <c r="D66" t="str">
         <v>2026-06-09</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Jeremy Camp</v>
+        <v>Fitz and the Tantrums</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
+        <v>Jeremy Camp - Reflector (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
+        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
       </c>
       <c r="D67" t="str">
         <v>2026-06-09</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Alesso</v>
+        <v>Jeremy Camp</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
+        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
       </c>
       <c r="B68" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
+        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
       </c>
       <c r="D68" t="str">
         <v>2026-06-09</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Malcolm Todd</v>
+        <v>Alesso</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer)</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
+        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
       </c>
       <c r="D69" t="str">
         <v>2026-06-09</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video)</v>
+        <v>Isabel LaRosa - Every Life (Visualizer)</v>
       </c>
       <c r="B70" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
+        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
       </c>
       <c r="D70" t="str">
         <v>2026-06-09</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Wyatt Flores</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video) - Wyatt Flores</v>
+        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
+        <v>Wyatt Flores - Half The Man (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
+        <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
       </c>
       <c r="D71" t="str">
         <v>2026-06-09</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Mckenna Grace</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video) - Mckenna Grace</v>
+        <v>Wyatt Flores - Half The Man (Official Music Video) - Wyatt Flores</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
+        <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
       </c>
       <c r="D72" t="str">
         <v>2026-06-09</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Robert Grace</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>Mckenna Grace - Ugly and Rotten (Official Music Video) - Mckenna Grace</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Boyzone - No Matter What (Live)</v>
+        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B73" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
+        <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
       </c>
       <c r="D73" t="str">
         <v>2026-06-09</v>
@@ -3155,7 +3155,7 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Boyzone</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Boyzone - No Matter What (Live) - Boyzone</v>
+        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Florrie - The Times (Official Video)</v>
+        <v>Boyzone - No Matter What (Live)</v>
       </c>
       <c r="B74" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
+        <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
       </c>
       <c r="D74" t="str">
         <v>2026-06-09</v>
@@ -3193,7 +3193,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>florriemusic</v>
+        <v>Boyzone</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Florrie - The Times (Official Video) - florriemusic</v>
+        <v>Boyzone - No Matter What (Live) - Boyzone</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer)</v>
+        <v>Florrie - The Times (Official Video)</v>
       </c>
       <c r="B75" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
+        <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
       </c>
       <c r="D75" t="str">
         <v>2026-06-09</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Madonna</v>
+        <v>florriemusic</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer) - Madonna</v>
+        <v>Florrie - The Times (Official Video) - florriemusic</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DMA'S - Hurracane (Official Video)</v>
+        <v>Madonna - Love Sensation (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
+        <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
       </c>
       <c r="D76" t="str">
         <v>2026-06-09</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>DMA'S</v>
+        <v>Madonna</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>DMA'S - Hurracane (Official Video) - DMA'S</v>
+        <v>Madonna - Love Sensation (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
+        <v>DMA'S - Hurracane (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
+        <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
       </c>
       <c r="D77" t="str">
         <v>2026-06-09</v>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Lainey Wilson and John Mayer</v>
+        <v>DMA'S</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio) - Lainey Wilson and John Mayer</v>
+        <v>DMA'S - Hurracane (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
+        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
       </c>
       <c r="B78" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
+        <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
       </c>
       <c r="D78" t="str">
         <v>2026-06-09</v>
@@ -3345,7 +3345,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>ROLE MODEL</v>
+        <v>Lainey Wilson and John Mayer</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video) - ROLE MODEL</v>
+        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio) - Lainey Wilson and John Mayer</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York)</v>
+        <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
+        <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
       </c>
       <c r="D79" t="str">
         <v>2026-06-09</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Shawn Mendes</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York) - Shawn Mendes</v>
+        <v>ROLE MODEL - High Hopes 3000 (Official Music Video) - ROLE MODEL</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
+        <v>Shawn Mendes - Treat You Better (Live from New York)</v>
       </c>
       <c r="B80" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
+        <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
       </c>
       <c r="D80" t="str">
         <v>2026-06-09</v>
@@ -3421,7 +3421,7 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Shawn Mendes</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video) - SIENNA SPIRO</v>
+        <v>Shawn Mendes - Treat You Better (Live from New York) - Shawn Mendes</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
+        <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
+        <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
       </c>
       <c r="D81" t="str">
         <v>2026-06-09</v>
@@ -3459,7 +3459,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>SIENNA SPIRO - The Visitor (Official Music Video) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video)</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
       </c>
       <c r="B82" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
+        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
       </c>
       <c r="D82" t="str">
         <v>2026-06-09</v>
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Europe</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
+        <v>Europe - The Cult of Ignorance (Official Video)</v>
       </c>
       <c r="B83" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
+        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
       </c>
       <c r="D83" t="str">
         <v>2026-06-09</v>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Air Supply</v>
+        <v>Europe</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
+        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
+        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
       </c>
       <c r="D84" t="str">
         <v>2026-06-09</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Julia Cole Music</v>
+        <v>Air Supply</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
       </c>
       <c r="B85" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
+        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
       </c>
       <c r="D85" t="str">
         <v>2026-06-09</v>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Allen Stone and Placeholder Sessions</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
       </c>
       <c r="B86" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
+        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
       </c>
       <c r="D86" t="str">
         <v>2026-06-09</v>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Morgan Wallen</v>
+        <v>Allen Stone and Placeholder Sessions</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
       </c>
       <c r="B87" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
+        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
       </c>
       <c r="D87" t="str">
         <v>2026-06-09</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Billy Idol</v>
+        <v>Morgan Wallen</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
+        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
       </c>
       <c r="D88" t="str">
         <v>2026-06-09</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>10 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Billy Idol</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
       </c>
       <c r="B89" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
+        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
       </c>
       <c r="D89" t="str">
         <v>2026-06-09</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>6 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Icona Pop</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Hippo Campus - South</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
+        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
       </c>
       <c r="D90" t="str">
         <v>2026-06-09</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Hippo Campus</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Hippo Campus - South - Hippo Campus</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>elijah woods - Old (Treehouse Sessions)</v>
+        <v>Hippo Campus - South</v>
       </c>
       <c r="B91" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
+        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
       </c>
       <c r="D91" t="str">
         <v>2026-06-09</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>elijah woods</v>
+        <v>Hippo Campus</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
+        <v>Hippo Campus - South - Hippo Campus</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video)</v>
+        <v>elijah woods - Old (Treehouse Sessions)</v>
       </c>
       <c r="B92" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
+        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
       </c>
       <c r="D92" t="str">
         <v>2026-06-09</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Nothing But Thieves</v>
+        <v>elijah woods</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
+        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video)</v>
+        <v>Nothing But Thieves - Evolution (Official Video)</v>
       </c>
       <c r="B93" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
+        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
       </c>
       <c r="D93" t="str">
         <v>2026-06-09</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Ariana Grande</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
+        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>LAUREL - Fire Breather</v>
+        <v>Ariana Grande - hate that i made you love me (official music video)</v>
       </c>
       <c r="B94" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
+        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
       </c>
       <c r="D94" t="str">
         <v>2026-06-09</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>LAUREL</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>LAUREL - Fire Breather - LAUREL</v>
+        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>The Warning - Ego (Performance Video)</v>
+        <v>LAUREL - Fire Breather</v>
       </c>
       <c r="B95" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
+        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
       </c>
       <c r="D95" t="str">
         <v>2026-06-09</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>The Warning</v>
+        <v>LAUREL</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>The Warning - Ego (Performance Video) - The Warning</v>
+        <v>LAUREL - Fire Breather - LAUREL</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
+        <v>The Warning - Ego (Performance Video)</v>
       </c>
       <c r="B96" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
+        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
       </c>
       <c r="D96" t="str">
         <v>2026-06-09</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>The Warning</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
+        <v>The Warning - Ego (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
       </c>
       <c r="B97" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
+        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
       </c>
       <c r="D97" t="str">
         <v>2026-06-09</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Armin van Buuren</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B98" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
+        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
       </c>
       <c r="D98" t="str">
         <v>2026-06-09</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Andrew Bird</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video)</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
       </c>
       <c r="B99" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
+        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
       </c>
       <c r="D99" t="str">
         <v>2026-06-09</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Danny Gokey</v>
+        <v>Andrew Bird</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Danny Gokey - God's Not (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
+        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
       </c>
       <c r="D100" t="str">
         <v>2026-06-09</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Armik</v>
+        <v>Danny Gokey</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B101" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
+        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
       </c>
       <c r="D101" t="str">
         <v>2026-06-09</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Holly Humberstone and Free People</v>
+        <v>Armik</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>True Colors</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
+        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
       </c>
       <c r="D102" t="str">
         <v>2026-06-09</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Thank You</v>
+        <v>10 days ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:39</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Mike D</v>
+        <v>Holly Humberstone and Free People</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>True Colors - Mike D</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Too Easy</v>
+        <v>True Colors</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/too-easy/6774752170</v>
+        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
       </c>
       <c r="D103" t="str">
         <v>2026-06-09</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Too Easy - Single</v>
+        <v>Thank You</v>
       </c>
       <c r="G103" t="str">
-        <v>1:54</v>
+        <v>3:39</v>
       </c>
       <c r="H103" t="str">
-        <v>Tinashe</v>
+        <v>Mike D</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/tinashe/464835513</v>
+        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/too-easy/6774752168</v>
+        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
       </c>
       <c r="L103" t="str">
-        <v>Too Easy - Tinashe</v>
+        <v>True Colors - Mike D</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>I Knew It, I Knew You</v>
+        <v>Too Easy</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
+        <v>https://music.apple.com/us/song/too-easy/6774752170</v>
       </c>
       <c r="D104" t="str">
         <v>2026-06-09</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>I Knew It, I Knew You - Single</v>
+        <v>Too Easy - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>2:58</v>
+        <v>1:54</v>
       </c>
       <c r="H104" t="str">
-        <v>Taylor Swift</v>
+        <v>Tinashe</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/tinashe/464835513</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/i-knew-it-i-knew-you/6775527442</v>
+        <v>https://music.apple.com/us/album/too-easy/6774752168</v>
       </c>
       <c r="L104" t="str">
-        <v>I Knew It, I Knew You - Taylor Swift</v>
+        <v>Too Easy - Tinashe</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Love Sensation</v>
+        <v>I Knew It, I Knew You</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
+        <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
       </c>
       <c r="D105" t="str">
         <v>2026-06-09</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Love Sensation - Single</v>
+        <v>I Knew It, I Knew You - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:48</v>
+        <v>2:58</v>
       </c>
       <c r="H105" t="str">
-        <v>Madonna</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/love-sensation/6774810102</v>
+        <v>https://music.apple.com/us/album/i-knew-it-i-knew-you/6775527442</v>
       </c>
       <c r="L105" t="str">
-        <v>Love Sensation - Madonna</v>
+        <v>I Knew It, I Knew You - Taylor Swift</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Mi Yo De Antes</v>
+        <v>Love Sensation</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
+        <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
       </c>
       <c r="D106" t="str">
         <v>2026-06-09</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Mi Yo De Antes - Single</v>
+        <v>Love Sensation - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:04</v>
+        <v>3:48</v>
       </c>
       <c r="H106" t="str">
-        <v>Ozuna</v>
+        <v>Madonna</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/mi-yo-de-antes/6769193983</v>
+        <v>https://music.apple.com/us/album/love-sensation/6774810102</v>
       </c>
       <c r="L106" t="str">
-        <v>Mi Yo De Antes - Ozuna</v>
+        <v>Love Sensation - Madonna</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Three Nations</v>
+        <v>Mi Yo De Antes</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/three-nations/6776010602</v>
+        <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
       </c>
       <c r="D107" t="str">
         <v>2026-06-09</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Official FIFA World Cup 2026™ Album</v>
+        <v>Mi Yo De Antes - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:30</v>
+        <v>3:04</v>
       </c>
       <c r="H107" t="str">
-        <v>21 Savage</v>
+        <v>Ozuna</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/21-savage/894820464</v>
+        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/three-nations/6776010591</v>
+        <v>https://music.apple.com/us/album/mi-yo-de-antes/6769193983</v>
       </c>
       <c r="L107" t="str">
-        <v>Three Nations - 21 Savage</v>
+        <v>Mi Yo De Antes - Ozuna</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Champions (WC 26)</v>
+        <v>Three Nations</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
+        <v>https://music.apple.com/us/song/three-nations/6776010602</v>
       </c>
       <c r="D108" t="str">
         <v>2026-06-09</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Champions (WC 26) - Single</v>
+        <v>Official FIFA World Cup 2026™ Album</v>
       </c>
       <c r="G108" t="str">
-        <v>4:15</v>
+        <v>3:30</v>
       </c>
       <c r="H108" t="str">
-        <v>IShowSpeed</v>
+        <v>21 Savage</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/ishowspeed/1574723975</v>
+        <v>https://music.apple.com/us/artist/21-savage/894820464</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/champions-wc-26/6775282246</v>
+        <v>https://music.apple.com/us/album/three-nations/6776010591</v>
       </c>
       <c r="L108" t="str">
-        <v>Champions (WC 26) - IShowSpeed</v>
+        <v>Three Nations - 21 Savage</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>ENCERRONES</v>
+        <v>Champions (WC 26)</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/encerrones/6771854522</v>
+        <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
       </c>
       <c r="D109" t="str">
         <v>2026-06-09</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>TEOFANIA</v>
+        <v>Champions (WC 26) - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:23</v>
+        <v>4:15</v>
       </c>
       <c r="H109" t="str">
-        <v>LENCHO</v>
+        <v>IShowSpeed</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
+        <v>https://music.apple.com/us/artist/ishowspeed/1574723975</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/encerrones/6771854517</v>
+        <v>https://music.apple.com/us/album/champions-wc-26/6775282246</v>
       </c>
       <c r="L109" t="str">
-        <v>ENCERRONES - LENCHO</v>
+        <v>Champions (WC 26) - IShowSpeed</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Cowgirl</v>
+        <v>ENCERRONES</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
+        <v>https://music.apple.com/us/song/encerrones/6771854522</v>
       </c>
       <c r="D110" t="str">
         <v>2026-06-09</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>The Outlaw Cherie Lee &amp; Other Western Tales</v>
+        <v>TEOFANIA</v>
       </c>
       <c r="G110" t="str">
-        <v>2:56</v>
+        <v>2:23</v>
       </c>
       <c r="H110" t="str">
-        <v>Shaboozey</v>
+        <v>LENCHO</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
+        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/cowgirl/1894906682</v>
+        <v>https://music.apple.com/us/album/encerrones/6771854517</v>
       </c>
       <c r="L110" t="str">
-        <v>Cowgirl - Shaboozey</v>
+        <v>ENCERRONES - LENCHO</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>PASSENGER</v>
+        <v>Cowgirl</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/passenger/6773456081</v>
+        <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
       </c>
       <c r="D111" t="str">
         <v>2026-06-09</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>WILDCHILD</v>
+        <v>The Outlaw Cherie Lee &amp; Other Western Tales</v>
       </c>
       <c r="G111" t="str">
-        <v>2:39</v>
+        <v>2:56</v>
       </c>
       <c r="H111" t="str">
-        <v>Alex Warren</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/passenger/6773456078</v>
+        <v>https://music.apple.com/us/album/cowgirl/1894906682</v>
       </c>
       <c r="L111" t="str">
-        <v>PASSENGER - Alex Warren</v>
+        <v>Cowgirl - Shaboozey</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Secret Language</v>
+        <v>PASSENGER</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/secret-language/6774223667</v>
+        <v>https://music.apple.com/us/song/passenger/6773456081</v>
       </c>
       <c r="D112" t="str">
         <v>2026-06-09</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Sweet Fortune</v>
+        <v>WILDCHILD</v>
       </c>
       <c r="G112" t="str">
-        <v>3:53</v>
+        <v>2:39</v>
       </c>
       <c r="H112" t="str">
-        <v>Ryan Beatty</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/ryan-beatty/483234172</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/secret-language/6774223660</v>
+        <v>https://music.apple.com/us/album/passenger/6773456078</v>
       </c>
       <c r="L112" t="str">
-        <v>Secret Language - Ryan Beatty</v>
+        <v>PASSENGER - Alex Warren</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>High Hopes 3000</v>
+        <v>Secret Language</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
+        <v>https://music.apple.com/us/song/secret-language/6774223667</v>
       </c>
       <c r="D113" t="str">
         <v>2026-06-09</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Chuck Timely &amp; The Hourglass</v>
+        <v>Sweet Fortune</v>
       </c>
       <c r="G113" t="str">
-        <v>4:05</v>
+        <v>3:53</v>
       </c>
       <c r="H113" t="str">
-        <v>ROLE MODEL</v>
+        <v>Ryan Beatty</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/role-model/199215762</v>
+        <v>https://music.apple.com/us/artist/ryan-beatty/483234172</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
+        <v>https://music.apple.com/us/album/secret-language/6774223660</v>
       </c>
       <c r="L113" t="str">
-        <v>High Hopes 3000 - ROLE MODEL</v>
+        <v>Secret Language - Ryan Beatty</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Vertical</v>
+        <v>High Hopes 3000</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/vertical/1892436336</v>
+        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
       </c>
       <c r="D114" t="str">
         <v>2026-06-09</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Emotional Junglist</v>
+        <v>Chuck Timely &amp; The Hourglass</v>
       </c>
       <c r="G114" t="str">
-        <v>2:36</v>
+        <v>4:05</v>
       </c>
       <c r="H114" t="str">
-        <v>Nia Archives</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/role-model/199215762</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/vertical/1892436329</v>
+        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
       </c>
       <c r="L114" t="str">
-        <v>Vertical - Nia Archives</v>
+        <v>High Hopes 3000 - ROLE MODEL</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>snake the drain</v>
+        <v>Vertical</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
+        <v>https://music.apple.com/us/song/vertical/1892436336</v>
       </c>
       <c r="D115" t="str">
         <v>2026-06-09</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>this time it’s different / snake the drain - Single</v>
+        <v>Emotional Junglist</v>
       </c>
       <c r="G115" t="str">
-        <v>3:08</v>
+        <v>2:36</v>
       </c>
       <c r="H115" t="str">
-        <v>Devon Again</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
+        <v>https://music.apple.com/us/album/vertical/1892436329</v>
       </c>
       <c r="L115" t="str">
-        <v>snake the drain - Devon Again</v>
+        <v>Vertical - Nia Archives</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Every Single Weekend (feat. Jamie xx)</v>
+        <v>snake the drain</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
+        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
       </c>
       <c r="D116" t="str">
         <v>2026-06-09</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
+        <v>this time it’s different / snake the drain - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>2:10</v>
+        <v>3:08</v>
       </c>
       <c r="H116" t="str">
-        <v>The Avalanches</v>
+        <v>Devon Again</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
+        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
       </c>
       <c r="L116" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
+        <v>snake the drain - Devon Again</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Bluffin'</v>
+        <v>Every Single Weekend (feat. Jamie xx)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
+        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D117" t="str">
         <v>2026-06-09</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Piss In The Wind (Deluxe)</v>
+        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:34</v>
+        <v>2:10</v>
       </c>
       <c r="H117" t="str">
-        <v>Joji</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
+        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
       </c>
       <c r="L117" t="str">
-        <v>Bluffin' - Joji</v>
+        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Dreams</v>
+        <v>Bluffin'</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/dreams/1884731028</v>
+        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
       </c>
       <c r="D118" t="str">
         <v>2026-06-09</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Free Your Mind</v>
+        <v>Piss In The Wind (Deluxe)</v>
       </c>
       <c r="G118" t="str">
-        <v>3:56</v>
+        <v>2:34</v>
       </c>
       <c r="H118" t="str">
-        <v>Prospa</v>
+        <v>Joji</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/dreams/1884730177</v>
+        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
       </c>
       <c r="L118" t="str">
-        <v>Dreams - Prospa</v>
+        <v>Bluffin' - Joji</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Cotton</v>
+        <v>Dreams</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/cotton/1887627941</v>
+        <v>https://music.apple.com/us/song/dreams/1884731028</v>
       </c>
       <c r="D119" t="str">
         <v>2026-06-09</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Cry Baby</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="G119" t="str">
-        <v>3:43</v>
+        <v>3:56</v>
       </c>
       <c r="H119" t="str">
-        <v>Vince Staples</v>
+        <v>Prospa</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/cotton/1887627836</v>
+        <v>https://music.apple.com/us/album/dreams/1884730177</v>
       </c>
       <c r="L119" t="str">
-        <v>Cotton - Vince Staples</v>
+        <v>Dreams - Prospa</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Black Prada Dress</v>
+        <v>Cotton</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
+        <v>https://music.apple.com/us/song/cotton/1887627941</v>
       </c>
       <c r="D120" t="str">
         <v>2026-06-09</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>I Know Too Much</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G120" t="str">
-        <v>3:19</v>
+        <v>3:43</v>
       </c>
       <c r="H120" t="str">
-        <v>Ellie Goulding</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
+        <v>https://music.apple.com/us/album/cotton/1887627836</v>
       </c>
       <c r="L120" t="str">
-        <v>Black Prada Dress - Ellie Goulding</v>
+        <v>Cotton - Vince Staples</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Don’t Break Her Heart</v>
+        <v>Black Prada Dress</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
+        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
       </c>
       <c r="D121" t="str">
         <v>2026-06-09</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>THERAPY AT THE CLUB</v>
+        <v>I Know Too Much</v>
       </c>
       <c r="G121" t="str">
-        <v>3:44</v>
+        <v>3:19</v>
       </c>
       <c r="H121" t="str">
-        <v>FLO</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
+        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
       </c>
       <c r="L121" t="str">
-        <v>Don’t Break Her Heart - FLO</v>
+        <v>Black Prada Dress - Ellie Goulding</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Sexy Ladies (feat. UCB)</v>
+        <v>Don’t Break Her Heart</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
+        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
       </c>
       <c r="D122" t="str">
         <v>2026-06-09</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>BITCH</v>
+        <v>THERAPY AT THE CLUB</v>
       </c>
       <c r="G122" t="str">
-        <v>2:50</v>
+        <v>3:44</v>
       </c>
       <c r="H122" t="str">
-        <v>Lizzo</v>
+        <v>FLO</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
+        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
       </c>
       <c r="L122" t="str">
-        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
+        <v>Don’t Break Her Heart - FLO</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Noche Without You</v>
+        <v>Sexy Ladies (feat. UCB)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
+        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
       </c>
       <c r="D123" t="str">
         <v>2026-06-09</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>SOMA</v>
+        <v>BITCH</v>
       </c>
       <c r="G123" t="str">
-        <v>3:23</v>
+        <v>2:50</v>
       </c>
       <c r="H123" t="str">
-        <v>Skrillex</v>
+        <v>Lizzo</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
+        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
       </c>
       <c r="L123" t="str">
-        <v>Noche Without You - Skrillex</v>
+        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Difficult Love</v>
+        <v>Noche Without You</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
+        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
       </c>
       <c r="D124" t="str">
         <v>2026-06-09</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Do That Again</v>
+        <v>SOMA</v>
       </c>
       <c r="G124" t="str">
-        <v>2:33</v>
+        <v>3:23</v>
       </c>
       <c r="H124" t="str">
-        <v>Malcolm Todd</v>
+        <v>Skrillex</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
+        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
       </c>
       <c r="L124" t="str">
-        <v>Difficult Love - Malcolm Todd</v>
+        <v>Noche Without You - Skrillex</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Tastes So Good</v>
+        <v>Difficult Love</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
+        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
       </c>
       <c r="D125" t="str">
         <v>2026-06-09</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Dinner Party</v>
+        <v>Do That Again</v>
       </c>
       <c r="G125" t="str">
-        <v>3:05</v>
+        <v>2:33</v>
       </c>
       <c r="H125" t="str">
-        <v>Niall Horan</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
+        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
       </c>
       <c r="L125" t="str">
-        <v>Tastes So Good - Niall Horan</v>
+        <v>Difficult Love - Malcolm Todd</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Phone, Keys, Wallet</v>
+        <v>Tastes So Good</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
+        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
       </c>
       <c r="D126" t="str">
         <v>2026-06-09</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Phone, Keys, Wallet - Single</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G126" t="str">
-        <v>2:52</v>
+        <v>3:05</v>
       </c>
       <c r="H126" t="str">
-        <v>Lainey Wilson</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
+        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
       </c>
       <c r="L126" t="str">
-        <v>Phone, Keys, Wallet - Lainey Wilson</v>
+        <v>Tastes So Good - Niall Horan</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Madrugada</v>
+        <v>Phone, Keys, Wallet</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
+        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
       </c>
       <c r="D127" t="str">
         <v>2026-06-09</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Madrugada - Single</v>
+        <v>Phone, Keys, Wallet - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:58</v>
+        <v>2:52</v>
       </c>
       <c r="H127" t="str">
-        <v>Chino Pacas</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
+        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
       </c>
       <c r="L127" t="str">
-        <v>Madrugada - Chino Pacas</v>
+        <v>Phone, Keys, Wallet - Lainey Wilson</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Oh Chet (feat. Travis Scott)</v>
+        <v>Madrugada</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
+        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
       </c>
       <c r="D128" t="str">
         <v>2026-06-09</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Single</v>
+        <v>Madrugada - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:23</v>
+        <v>2:58</v>
       </c>
       <c r="H128" t="str">
-        <v>Jey One</v>
+        <v>Chino Pacas</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
+        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
+        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
       </c>
       <c r="L128" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
+        <v>Madrugada - Chino Pacas</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>An Hour or So (Live at Apple Music Radio)</v>
+        <v>Oh Chet (feat. Travis Scott)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
+        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
       </c>
       <c r="D129" t="str">
         <v>2026-06-09</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Oh Chet (feat. Travis Scott) - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:02</v>
+        <v>2:23</v>
       </c>
       <c r="H129" t="str">
-        <v>Benny G</v>
+        <v>Jey One</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
+        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
       </c>
       <c r="L129" t="str">
-        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
+        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>it’s just White Noise</v>
+        <v>An Hour or So (Live at Apple Music Radio)</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
+        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
       </c>
       <c r="D130" t="str">
         <v>2026-06-09</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>it’s a real Cruel World - EP</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G130" t="str">
-        <v>3:57</v>
+        <v>3:02</v>
       </c>
       <c r="H130" t="str">
-        <v>Holly Humberstone</v>
+        <v>Benny G</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
+        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
       </c>
       <c r="L130" t="str">
-        <v>it’s just White Noise - Holly Humberstone</v>
+        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>the feeling</v>
+        <v>it’s just White Noise</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
+        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
       </c>
       <c r="D131" t="str">
         <v>2026-06-09</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Oh yeah?</v>
+        <v>it’s a real Cruel World - EP</v>
       </c>
       <c r="G131" t="str">
-        <v>4:35</v>
+        <v>3:57</v>
       </c>
       <c r="H131" t="str">
-        <v>Steve Lacy</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
+        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
       </c>
       <c r="L131" t="str">
-        <v>the feeling - Steve Lacy</v>
+        <v>it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>baby (Live at Apple Music Radio)</v>
+        <v>the feeling</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
+        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
       </c>
       <c r="D132" t="str">
         <v>2026-06-09</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Oh yeah?</v>
       </c>
       <c r="G132" t="str">
-        <v>3:14</v>
+        <v>4:35</v>
       </c>
       <c r="H132" t="str">
-        <v>Gabriel Jacoby</v>
+        <v>Steve Lacy</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
+        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
+        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
       </c>
       <c r="L132" t="str">
-        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
+        <v>the feeling - Steve Lacy</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Drop The Lo</v>
+        <v>baby (Live at Apple Music Radio)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
+        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
       </c>
       <c r="D133" t="str">
         <v>2026-06-09</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Drop The Lo - Single</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G133" t="str">
-        <v>2:41</v>
+        <v>3:14</v>
       </c>
       <c r="H133" t="str">
-        <v>Bryson Tiller</v>
+        <v>Gabriel Jacoby</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
+        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
       </c>
       <c r="L133" t="str">
-        <v>Drop The Lo - Bryson Tiller</v>
+        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>GANG BIZNESS feat paygotti</v>
+        <v>Drop The Lo</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
+        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
       </c>
       <c r="D134" t="str">
         <v>2026-06-09</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>GANG BIZNESS feat paygotti - Single</v>
+        <v>Drop The Lo - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:47</v>
+        <v>2:41</v>
       </c>
       <c r="H134" t="str">
-        <v>YG</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
+        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
       </c>
       <c r="L134" t="str">
-        <v>GANG BIZNESS feat paygotti - YG</v>
+        <v>Drop The Lo - Bryson Tiller</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Lay It Down</v>
+        <v>GANG BIZNESS feat paygotti</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
+        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
       </c>
       <c r="D135" t="str">
         <v>2026-06-09</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Lay It Down - Single</v>
+        <v>GANG BIZNESS feat paygotti - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:38</v>
+        <v>2:47</v>
       </c>
       <c r="H135" t="str">
-        <v>FattMack</v>
+        <v>YG</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
+        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
       </c>
       <c r="L135" t="str">
-        <v>Lay It Down - FattMack</v>
+        <v>GANG BIZNESS feat paygotti - YG</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>WAX PAPER</v>
+        <v>Lay It Down</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
+        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
       </c>
       <c r="D136" t="str">
         <v>2026-06-09</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>WHACK'S MUSEUM</v>
+        <v>Lay It Down - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:43</v>
+        <v>2:38</v>
       </c>
       <c r="H136" t="str">
-        <v>Tierra Whack</v>
+        <v>FattMack</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
+        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
       </c>
       <c r="L136" t="str">
-        <v>WAX PAPER - Tierra Whack</v>
+        <v>Lay It Down - FattMack</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>abusadOra (tambores)</v>
+        <v>WAX PAPER</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
+        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
       </c>
       <c r="D137" t="str">
         <v>2026-06-09</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>ANTES DE QUE SEA TARDE</v>
+        <v>WHACK'S MUSEUM</v>
       </c>
       <c r="G137" t="str">
-        <v>3:11</v>
+        <v>2:43</v>
       </c>
       <c r="H137" t="str">
-        <v>Yorghaki</v>
+        <v>Tierra Whack</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
+        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
+        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
       </c>
       <c r="L137" t="str">
-        <v>abusadOra (tambores) - Yorghaki</v>
+        <v>WAX PAPER - Tierra Whack</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Ruin</v>
+        <v>abusadOra (tambores)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/ruin/6763176090</v>
+        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
       </c>
       <c r="D138" t="str">
         <v>2026-06-09</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Labor Of Love</v>
+        <v>ANTES DE QUE SEA TARDE</v>
       </c>
       <c r="G138" t="str">
-        <v>3:19</v>
+        <v>3:11</v>
       </c>
       <c r="H138" t="str">
-        <v>Blxst</v>
+        <v>Yorghaki</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/ruin/1895199881</v>
+        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
       </c>
       <c r="L138" t="str">
-        <v>Ruin - Blxst</v>
+        <v>abusadOra (tambores) - Yorghaki</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Do Today</v>
+        <v>Ruin</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/do-today/1893402864</v>
+        <v>https://music.apple.com/us/song/ruin/6763176090</v>
       </c>
       <c r="D139" t="str">
         <v>2026-06-09</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Grateful</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G139" t="str">
-        <v>4:14</v>
+        <v>3:19</v>
       </c>
       <c r="H139" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Blxst</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/do-today/1893402542</v>
+        <v>https://music.apple.com/us/album/ruin/1895199881</v>
       </c>
       <c r="L139" t="str">
-        <v>Do Today - The Red Clay Strays</v>
+        <v>Ruin - Blxst</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Stone Over Water</v>
+        <v>Do Today</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
+        <v>https://music.apple.com/us/song/do-today/1893402864</v>
       </c>
       <c r="D140" t="str">
         <v>2026-06-09</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>I Built You A Tower</v>
+        <v>Grateful</v>
       </c>
       <c r="G140" t="str">
-        <v>3:14</v>
+        <v>4:14</v>
       </c>
       <c r="H140" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
+        <v>https://music.apple.com/us/album/do-today/1893402542</v>
       </c>
       <c r="L140" t="str">
-        <v>Stone Over Water - Death Cab for Cutie</v>
+        <v>Do Today - The Red Clay Strays</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
+        <v>Stone Over Water</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
+        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
       </c>
       <c r="D141" t="str">
         <v>2026-06-09</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Weezer</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G141" t="str">
-        <v>3:34</v>
+        <v>3:14</v>
       </c>
       <c r="H141" t="str">
-        <v>Weezer</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/weezer/115234</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
+        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
       </c>
       <c r="L141" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
+        <v>Stone Over Water - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Tell Me When You've Had Enough</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
+        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
       </c>
       <c r="D142" t="str">
         <v>2026-06-09</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Sanctuary</v>
+        <v>Weezer</v>
       </c>
       <c r="G142" t="str">
-        <v>3:19</v>
+        <v>3:34</v>
       </c>
       <c r="H142" t="str">
-        <v>Evanescence</v>
+        <v>Weezer</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/weezer/115234</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
+        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
       </c>
       <c r="L142" t="str">
-        <v>Tell Me When You've Had Enough - Evanescence</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Your Ghost Again</v>
+        <v>Tell Me When You've Had Enough</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
+        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
       </c>
       <c r="D143" t="str">
         <v>2026-06-09</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Your Ghost Again - Single</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G143" t="str">
-        <v>4:35</v>
+        <v>3:19</v>
       </c>
       <c r="H143" t="str">
-        <v>Mastodon</v>
+        <v>Evanescence</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
+        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
       </c>
       <c r="L143" t="str">
-        <v>Your Ghost Again - Mastodon</v>
+        <v>Tell Me When You've Had Enough - Evanescence</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Nightshift Superstar</v>
+        <v>Your Ghost Again</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
+        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
       </c>
       <c r="D144" t="str">
         <v>2026-06-09</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>The Wow! Signal</v>
+        <v>Your Ghost Again - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>4:07</v>
+        <v>4:35</v>
       </c>
       <c r="H144" t="str">
-        <v>Muse</v>
+        <v>Mastodon</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
+        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
       </c>
       <c r="L144" t="str">
-        <v>Nightshift Superstar - Muse</v>
+        <v>Your Ghost Again - Mastodon</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>UNDER THE RHYTHM</v>
+        <v>Nightshift Superstar</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
+        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
       </c>
       <c r="D145" t="str">
         <v>2026-06-09</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>ADAM</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G145" t="str">
-        <v>2:50</v>
+        <v>4:07</v>
       </c>
       <c r="H145" t="str">
-        <v>Adam Lambert</v>
+        <v>Muse</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
+        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
       </c>
       <c r="L145" t="str">
-        <v>UNDER THE RHYTHM - Adam Lambert</v>
+        <v>Nightshift Superstar - Muse</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>You’re Mine</v>
+        <v>UNDER THE RHYTHM</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
+        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
       </c>
       <c r="D146" t="str">
         <v>2026-06-09</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Papercut</v>
+        <v>ADAM</v>
       </c>
       <c r="G146" t="str">
-        <v>4:25</v>
+        <v>2:50</v>
       </c>
       <c r="H146" t="str">
-        <v>Imani Imani</v>
+        <v>Adam Lambert</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
+        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
+        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
       </c>
       <c r="L146" t="str">
-        <v>You’re Mine - Imani Imani</v>
+        <v>UNDER THE RHYTHM - Adam Lambert</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>point blank</v>
+        <v>You’re Mine</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
+        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
       </c>
       <c r="D147" t="str">
         <v>2026-06-09</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>new avatar</v>
+        <v>Papercut</v>
       </c>
       <c r="G147" t="str">
-        <v>4:26</v>
+        <v>4:25</v>
       </c>
       <c r="H147" t="str">
-        <v>Kelela</v>
+        <v>Imani Imani</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
+        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
       </c>
       <c r="L147" t="str">
-        <v>point blank - Kelela</v>
+        <v>You’re Mine - Imani Imani</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>that's my beach!</v>
+        <v>point blank</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
+        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
       </c>
       <c r="D148" t="str">
         <v>2026-06-09</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>new avatar</v>
       </c>
       <c r="G148" t="str">
-        <v>3:18</v>
+        <v>4:26</v>
       </c>
       <c r="H148" t="str">
-        <v>horsegiirL</v>
+        <v>Kelela</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
+        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
       </c>
       <c r="L148" t="str">
-        <v>that's my beach! - horsegiirL</v>
+        <v>point blank - Kelela</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>In Your Eyes</v>
+        <v>that's my beach!</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
+        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
       </c>
       <c r="D149" t="str">
         <v>2026-06-09</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>In Your Eyes - Single</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G149" t="str">
-        <v>3:36</v>
+        <v>3:18</v>
       </c>
       <c r="H149" t="str">
-        <v>Alesso</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/alesso/432464201</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
+        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
       </c>
       <c r="L149" t="str">
-        <v>In Your Eyes - Alesso</v>
+        <v>that's my beach! - horsegiirL</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>ALL OR NOTHING</v>
+        <v>In Your Eyes</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
+        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
       </c>
       <c r="D150" t="str">
         <v>2026-06-09</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>ALL OR NOTHING - Single</v>
+        <v>In Your Eyes - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:17</v>
+        <v>3:36</v>
       </c>
       <c r="H150" t="str">
-        <v>Tobe Nwigwe</v>
+        <v>Alesso</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
+        <v>https://music.apple.com/us/artist/alesso/432464201</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
+        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
       </c>
       <c r="L150" t="str">
-        <v>ALL OR NOTHING - Tobe Nwigwe</v>
+        <v>In Your Eyes - Alesso</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>IN MY HANDS</v>
+        <v>ALL OR NOTHING</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
+        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
       </c>
       <c r="D151" t="str">
         <v>2026-06-09</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>IN MY HANDS - Single</v>
+        <v>ALL OR NOTHING - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:14</v>
+        <v>3:17</v>
       </c>
       <c r="H151" t="str">
-        <v>Alessia Cara</v>
+        <v>Tobe Nwigwe</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
+        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
+        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
       </c>
       <c r="L151" t="str">
-        <v>IN MY HANDS - Alessia Cara</v>
+        <v>ALL OR NOTHING - Tobe Nwigwe</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Life's a Dream</v>
+        <v>IN MY HANDS</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
+        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
       </c>
       <c r="D152" t="str">
         <v>2026-06-09</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>IN MY HANDS - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>5:31</v>
+        <v>3:14</v>
       </c>
       <c r="H152" t="str">
-        <v>Modest Mouse</v>
+        <v>Alessia Cara</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
+        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
       </c>
       <c r="L152" t="str">
-        <v>Life's a Dream - Modest Mouse</v>
+        <v>IN MY HANDS - Alessia Cara</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
+        <v>Life's a Dream</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
+        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
       </c>
       <c r="D153" t="str">
         <v>2026-06-09</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Season of Surrender</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G153" t="str">
-        <v>4:47</v>
+        <v>5:31</v>
       </c>
       <c r="H153" t="str">
-        <v>August Burns Red</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
+        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
       </c>
       <c r="L153" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
+        <v>Life's a Dream - Modest Mouse</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Shine</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/shine/6764654536</v>
+        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
       </c>
       <c r="D154" t="str">
         <v>2026-06-09</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Black Mozart</v>
+        <v>Season of Surrender</v>
       </c>
       <c r="G154" t="str">
-        <v>2:27</v>
+        <v>4:47</v>
       </c>
       <c r="H154" t="str">
-        <v>Jon Batiste</v>
+        <v>August Burns Red</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/shine/1895866355</v>
+        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
       </c>
       <c r="L154" t="str">
-        <v>Shine - Jon Batiste</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Half The Man</v>
+        <v>Shine</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
+        <v>https://music.apple.com/us/song/shine/6764654536</v>
       </c>
       <c r="D155" t="str">
         <v>2026-06-09</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Scared of Heights</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G155" t="str">
-        <v>3:56</v>
+        <v>2:27</v>
       </c>
       <c r="H155" t="str">
-        <v>Wyatt Flores</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
+        <v>https://music.apple.com/us/album/shine/1895866355</v>
       </c>
       <c r="L155" t="str">
-        <v>Half The Man - Wyatt Flores</v>
+        <v>Shine - Jon Batiste</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Preacher’s Kid</v>
+        <v>Half The Man</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
+        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
       </c>
       <c r="D156" t="str">
         <v>2026-06-09</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Preacher’s Kid - Single</v>
+        <v>Scared of Heights</v>
       </c>
       <c r="G156" t="str">
-        <v>5:02</v>
+        <v>3:56</v>
       </c>
       <c r="H156" t="str">
-        <v>Stephen Wilson Jr.</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
+        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
       </c>
       <c r="L156" t="str">
-        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
+        <v>Half The Man - Wyatt Flores</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Weak</v>
+        <v>Preacher’s Kid</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/weak/6771151098</v>
+        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
       </c>
       <c r="D157" t="str">
         <v>2026-06-09</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Weak - Single</v>
+        <v>Preacher’s Kid - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:28</v>
+        <v>5:02</v>
       </c>
       <c r="H157" t="str">
-        <v>Naomi Sharon</v>
+        <v>Stephen Wilson Jr.</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/weak/6771151088</v>
+        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
       </c>
       <c r="L157" t="str">
-        <v>Weak - Naomi Sharon</v>
+        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>ALL NIGHT LONG</v>
+        <v>Weak</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
+        <v>https://music.apple.com/us/song/weak/6771151098</v>
       </c>
       <c r="D158" t="str">
         <v>2026-06-09</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>A Rii Set</v>
+        <v>Weak - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:28</v>
+        <v>3:28</v>
       </c>
       <c r="H158" t="str">
-        <v>Pheelz</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
+        <v>https://music.apple.com/us/album/weak/6771151088</v>
       </c>
       <c r="L158" t="str">
-        <v>ALL NIGHT LONG - Pheelz</v>
+        <v>Weak - Naomi Sharon</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Every Life</v>
+        <v>ALL NIGHT LONG</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/every-life/6764110978</v>
+        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
       </c>
       <c r="D159" t="str">
         <v>2026-06-09</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G159" t="str">
-        <v>3:18</v>
+        <v>2:28</v>
       </c>
       <c r="H159" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Pheelz</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/every-life/1895644574</v>
+        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
       </c>
       <c r="L159" t="str">
-        <v>Every Life - Isabel LaRosa</v>
+        <v>ALL NIGHT LONG - Pheelz</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Home</v>
+        <v>Every Life</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/home/6774718029</v>
+        <v>https://music.apple.com/us/song/every-life/6764110978</v>
       </c>
       <c r="D160" t="str">
         <v>2026-06-09</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Good Grief</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G160" t="str">
-        <v>4:53</v>
+        <v>3:18</v>
       </c>
       <c r="H160" t="str">
-        <v>Sara Bareilles</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/home/6774718027</v>
+        <v>https://music.apple.com/us/album/every-life/1895644574</v>
       </c>
       <c r="L160" t="str">
-        <v>Home - Sara Bareilles</v>
+        <v>Every Life - Isabel LaRosa</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Satalanaaa</v>
+        <v>Home</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
+        <v>https://music.apple.com/us/song/home/6774718029</v>
       </c>
       <c r="D161" t="str">
         <v>2026-06-09</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Satalanaaa - Single</v>
+        <v>Good Grief</v>
       </c>
       <c r="G161" t="str">
-        <v>2:06</v>
+        <v>4:53</v>
       </c>
       <c r="H161" t="str">
-        <v>Pitbull</v>
+        <v>Sara Bareilles</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
+        <v>https://music.apple.com/us/album/home/6774718027</v>
       </c>
       <c r="L161" t="str">
-        <v>Satalanaaa - Pitbull</v>
+        <v>Home - Sara Bareilles</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Miss Me More</v>
+        <v>Satalanaaa</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
+        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
       </c>
       <c r="D162" t="str">
         <v>2026-06-09</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Confessions of a Lonely Heart</v>
+        <v>Satalanaaa - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:43</v>
+        <v>2:06</v>
       </c>
       <c r="H162" t="str">
-        <v>Eric Nam</v>
+        <v>Pitbull</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
+        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
       </c>
       <c r="L162" t="str">
-        <v>Miss Me More - Eric Nam</v>
+        <v>Satalanaaa - Pitbull</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Rituals</v>
+        <v>Miss Me More</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/rituals/6769628916</v>
+        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
       </c>
       <c r="D163" t="str">
         <v>2026-06-09</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Rituals - Single</v>
+        <v>Confessions of a Lonely Heart</v>
       </c>
       <c r="G163" t="str">
-        <v>2:10</v>
+        <v>2:43</v>
       </c>
       <c r="H163" t="str">
-        <v>Rico Nasty</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/rituals/6769628915</v>
+        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
       </c>
       <c r="L163" t="str">
-        <v>Rituals - Rico Nasty</v>
+        <v>Miss Me More - Eric Nam</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Honeysuckle</v>
+        <v>Rituals</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
+        <v>https://music.apple.com/us/song/rituals/6769628916</v>
       </c>
       <c r="D164" t="str">
         <v>2026-06-09</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Honeysuckle - Single</v>
+        <v>Rituals - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:15</v>
+        <v>2:10</v>
       </c>
       <c r="H164" t="str">
-        <v>Dylan Gossett</v>
+        <v>Rico Nasty</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
+        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
+        <v>https://music.apple.com/us/album/rituals/6769628915</v>
       </c>
       <c r="L164" t="str">
-        <v>Honeysuckle - Dylan Gossett</v>
+        <v>Rituals - Rico Nasty</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>listen…</v>
+        <v>Honeysuckle</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/listen/6775576508</v>
+        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
       </c>
       <c r="D165" t="str">
         <v>2026-06-09</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
+        <v>Honeysuckle - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>4:08</v>
+        <v>3:15</v>
       </c>
       <c r="H165" t="str">
-        <v>John Williams</v>
+        <v>Dylan Gossett</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/john-williams/63748</v>
+        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/listen/6775576506</v>
+        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
       </c>
       <c r="L165" t="str">
-        <v>listen… - John Williams</v>
+        <v>Honeysuckle - Dylan Gossett</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>DEADMEAT</v>
+        <v>listen…</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
+        <v>https://music.apple.com/us/song/listen/6775576508</v>
       </c>
       <c r="D166" t="str">
         <v>2026-06-09</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>DEADMEAT - Single</v>
+        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G166" t="str">
-        <v>2:52</v>
+        <v>4:08</v>
       </c>
       <c r="H166" t="str">
-        <v>South Arcade</v>
+        <v>John Williams</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/john-williams/63748</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
+        <v>https://music.apple.com/us/album/listen/6775576506</v>
       </c>
       <c r="L166" t="str">
-        <v>DEADMEAT - South Arcade</v>
+        <v>listen… - John Williams</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Ugly and Rotten</v>
+        <v>DEADMEAT</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
+        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
       </c>
       <c r="D167" t="str">
         <v>2026-06-09</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Ugly and Rotten - Single</v>
+        <v>DEADMEAT - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:49</v>
+        <v>2:52</v>
       </c>
       <c r="H167" t="str">
-        <v>Mckenna Grace</v>
+        <v>South Arcade</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
+        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
       </c>
       <c r="L167" t="str">
-        <v>Ugly and Rotten - Mckenna Grace</v>
+        <v>DEADMEAT - South Arcade</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Whisper</v>
+        <v>Ugly and Rotten</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/whisper/6772254272</v>
+        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
       </c>
       <c r="D168" t="str">
         <v>2026-06-09</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Whisper - Single</v>
+        <v>Ugly and Rotten - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:47</v>
+        <v>2:49</v>
       </c>
       <c r="H168" t="str">
-        <v>Blu DeTiger</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
+        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/whisper/6772254268</v>
+        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
       </c>
       <c r="L168" t="str">
-        <v>Whisper - Blu DeTiger</v>
+        <v>Ugly and Rotten - Mckenna Grace</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Gecko (feat. Haley Bridge)</v>
+        <v>Whisper</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
+        <v>https://music.apple.com/us/song/whisper/6772254272</v>
       </c>
       <c r="D169" t="str">
         <v>2026-06-09</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>How dare you tryna love me? - EP</v>
+        <v>Whisper - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:46</v>
+        <v>2:47</v>
       </c>
       <c r="H169" t="str">
-        <v>Olga Myko</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
+        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
+        <v>https://music.apple.com/us/album/whisper/6772254268</v>
       </c>
       <c r="L169" t="str">
-        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
+        <v>Whisper - Blu DeTiger</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Compa Primo</v>
+        <v>Gecko (feat. Haley Bridge)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
+        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
       </c>
       <c r="D170" t="str">
         <v>2026-06-09</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Compa Primo - Single</v>
+        <v>How dare you tryna love me? - EP</v>
       </c>
       <c r="G170" t="str">
-        <v>3:12</v>
+        <v>2:46</v>
       </c>
       <c r="H170" t="str">
-        <v>Nueva H</v>
+        <v>Olga Myko</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
+        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
+        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
       </c>
       <c r="L170" t="str">
-        <v>Compa Primo - Nueva H</v>
+        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Parachute</v>
+        <v>Compa Primo</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/parachute/6768841410</v>
+        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
       </c>
       <c r="D171" t="str">
         <v>2026-06-09</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Parachute - Single</v>
+        <v>Compa Primo - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:11</v>
+        <v>3:12</v>
       </c>
       <c r="H171" t="str">
-        <v>Tyler James Bellinger</v>
+        <v>Nueva H</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
+        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/parachute/6768841409</v>
+        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
       </c>
       <c r="L171" t="str">
-        <v>Parachute - Tyler James Bellinger</v>
+        <v>Compa Primo - Nueva H</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Like a Bubble</v>
+        <v>Parachute</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
+        <v>https://music.apple.com/us/song/parachute/6768841410</v>
       </c>
       <c r="D172" t="str">
         <v>2026-06-09</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Imperfect-I'mperfect - EP</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:08</v>
+        <v>3:11</v>
       </c>
       <c r="H172" t="str">
-        <v>FIFTY FIFTY</v>
+        <v>Tyler James Bellinger</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
+        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
+        <v>https://music.apple.com/us/album/parachute/6768841409</v>
       </c>
       <c r="L172" t="str">
-        <v>Like a Bubble - FIFTY FIFTY</v>
+        <v>Parachute - Tyler James Bellinger</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Hustle and Opulence in America</v>
+        <v>Like a Bubble</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
+        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
       </c>
       <c r="D173" t="str">
         <v>2026-06-09</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>AK Cuts: Vol. 4 - EP</v>
+        <v>Imperfect-I'mperfect - EP</v>
       </c>
       <c r="G173" t="str">
-        <v>3:07</v>
+        <v>3:08</v>
       </c>
       <c r="H173" t="str">
-        <v>Anish Kumar</v>
+        <v>FIFTY FIFTY</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
+        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
       </c>
       <c r="L173" t="str">
-        <v>Hustle and Opulence in America - Anish Kumar</v>
+        <v>Like a Bubble - FIFTY FIFTY</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
+        <v>Hustle and Opulence in America</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
+        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
       </c>
       <c r="D174" t="str">
         <v>2026-06-09</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
+        <v>AK Cuts: Vol. 4 - EP</v>
       </c>
       <c r="G174" t="str">
-        <v>2:47</v>
+        <v>3:07</v>
       </c>
       <c r="H174" t="str">
-        <v>ivri</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
+        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
       </c>
       <c r="L174" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
+        <v>Hustle and Opulence in America - Anish Kumar</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>CLEAN SWEEP</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
+        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
       </c>
       <c r="D175" t="str">
         <v>2026-06-09</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>CLEAN SWEEP - Single</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:11</v>
+        <v>2:47</v>
       </c>
       <c r="H175" t="str">
-        <v>Storm Reid</v>
+        <v>ivri</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
+        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
       </c>
       <c r="L175" t="str">
-        <v>CLEAN SWEEP - Storm Reid</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>CANDYLAND!</v>
+        <v>CLEAN SWEEP</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/candyland/6766927008</v>
+        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
       </c>
       <c r="D176" t="str">
         <v>2026-06-09</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>CANDYLAND! - Single</v>
+        <v>CLEAN SWEEP - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:15</v>
+        <v>3:11</v>
       </c>
       <c r="H176" t="str">
-        <v>Natanya</v>
+        <v>Storm Reid</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
+        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/candyland/6766927000</v>
+        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
       </c>
       <c r="L176" t="str">
-        <v>CANDYLAND! - Natanya</v>
+        <v>CLEAN SWEEP - Storm Reid</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Double C</v>
+        <v>CANDYLAND!</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/double-c/6771836555</v>
+        <v>https://music.apple.com/us/song/candyland/6766927008</v>
       </c>
       <c r="D177" t="str">
         <v>2026-06-09</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Double C - Single</v>
+        <v>CANDYLAND! - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:21</v>
+        <v>3:15</v>
       </c>
       <c r="H177" t="str">
-        <v>Sk8star</v>
+        <v>Natanya</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
+        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/double-c/6771836554</v>
+        <v>https://music.apple.com/us/album/candyland/6766927000</v>
       </c>
       <c r="L177" t="str">
-        <v>Double C - Sk8star</v>
+        <v>CANDYLAND! - Natanya</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>madera</v>
+        <v>Double C</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/madera/6764638112</v>
+        <v>https://music.apple.com/us/song/double-c/6771836555</v>
       </c>
       <c r="D178" t="str">
         <v>2026-06-09</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>madera/un camino luminoso - Single</v>
+        <v>Double C - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>5:41</v>
+        <v>2:21</v>
       </c>
       <c r="H178" t="str">
-        <v>Lumtz</v>
+        <v>Sk8star</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
+        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/madera/6764638109</v>
+        <v>https://music.apple.com/us/album/double-c/6771836554</v>
       </c>
       <c r="L178" t="str">
-        <v>madera - Lumtz</v>
+        <v>Double C - Sk8star</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Slip the Noose</v>
+        <v>madera</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
+        <v>https://music.apple.com/us/song/madera/6764638112</v>
       </c>
       <c r="D179" t="str">
         <v>2026-06-09</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Hum of Hurt</v>
+        <v>madera/un camino luminoso - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>1:43</v>
+        <v>5:41</v>
       </c>
       <c r="H179" t="str">
-        <v>Converge</v>
+        <v>Lumtz</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
+        <v>https://music.apple.com/us/album/madera/6764638109</v>
       </c>
       <c r="L179" t="str">
-        <v>Slip the Noose - Converge</v>
+        <v>madera - Lumtz</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Crying Fire</v>
+        <v>Slip the Noose</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
+        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
       </c>
       <c r="D180" t="str">
         <v>2026-06-09</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Crying Fire - Single</v>
+        <v>Hum of Hurt</v>
       </c>
       <c r="G180" t="str">
-        <v>4:08</v>
+        <v>1:43</v>
       </c>
       <c r="H180" t="str">
-        <v>Avatar</v>
+        <v>Converge</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/avatar/187616241</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
+        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
       </c>
       <c r="L180" t="str">
-        <v>Crying Fire - Avatar</v>
+        <v>Slip the Noose - Converge</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>NI NA’</v>
+        <v>Crying Fire</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
+        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
       </c>
       <c r="D181" t="str">
         <v>2026-06-09</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>sorry si soy GRRRIS</v>
+        <v>Crying Fire - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:53</v>
+        <v>4:08</v>
       </c>
       <c r="H181" t="str">
-        <v>ROBI</v>
+        <v>Avatar</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/robi/1458047972</v>
+        <v>https://music.apple.com/us/artist/avatar/187616241</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
+        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
       </c>
       <c r="L181" t="str">
-        <v>NI NA’ - ROBI</v>
+        <v>Crying Fire - Avatar</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Holding Back</v>
+        <v>NI NA’</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
+        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
       </c>
       <c r="D182" t="str">
         <v>2026-06-09</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>AMA</v>
+        <v>sorry si soy GRRRIS</v>
       </c>
       <c r="G182" t="str">
-        <v>3:19</v>
+        <v>2:53</v>
       </c>
       <c r="H182" t="str">
-        <v>Ama</v>
+        <v>ROBI</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/robi/1458047972</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
+        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
       </c>
       <c r="L182" t="str">
-        <v>Holding Back - Ama</v>
+        <v>NI NA’ - ROBI</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>you're still mine</v>
+        <v>Holding Back</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
+        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
       </c>
       <c r="D183" t="str">
         <v>2026-06-09</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>you're still mine - Single</v>
+        <v>AMA</v>
       </c>
       <c r="G183" t="str">
         <v>3:19</v>
       </c>
       <c r="H183" t="str">
-        <v>Lexi Jayde</v>
+        <v>Ama</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
+        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
       </c>
       <c r="L183" t="str">
-        <v>you're still mine - Lexi Jayde</v>
+        <v>Holding Back - Ama</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>teksi</v>
+        <v>you're still mine</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/teksi/6769899742</v>
+        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
       </c>
       <c r="D184" t="str">
         <v>2026-06-09</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>pOCHO</v>
+        <v>you're still mine - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:48</v>
+        <v>3:19</v>
       </c>
       <c r="H184" t="str">
-        <v>8onthebeat</v>
+        <v>Lexi Jayde</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
+        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/teksi/6769899739</v>
+        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
       </c>
       <c r="L184" t="str">
-        <v>teksi - 8onthebeat</v>
+        <v>you're still mine - Lexi Jayde</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Let You Go</v>
+        <v>teksi</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
+        <v>https://music.apple.com/us/song/teksi/6769899742</v>
       </c>
       <c r="D185" t="str">
         <v>2026-06-09</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Let You Go - Single</v>
+        <v>pOCHO</v>
       </c>
       <c r="G185" t="str">
-        <v>1:37</v>
+        <v>2:48</v>
       </c>
       <c r="H185" t="str">
-        <v>Nate Sib</v>
+        <v>8onthebeat</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
+        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
+        <v>https://music.apple.com/us/album/teksi/6769899739</v>
       </c>
       <c r="L185" t="str">
-        <v>Let You Go - Nate Sib</v>
+        <v>teksi - 8onthebeat</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Dis-Moi</v>
+        <v>Let You Go</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
+        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
       </c>
       <c r="D186" t="str">
         <v>2026-06-09</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>CINNA</v>
+        <v>Let You Go - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:27</v>
+        <v>1:37</v>
       </c>
       <c r="H186" t="str">
-        <v>Cannelle</v>
+        <v>Nate Sib</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
+        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
+        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
       </c>
       <c r="L186" t="str">
-        <v>Dis-Moi - Cannelle</v>
+        <v>Let You Go - Nate Sib</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Leverage</v>
+        <v>Dis-Moi</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/leverage/6776432312</v>
+        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
       </c>
       <c r="D187" t="str">
         <v>2026-06-09</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Heaven on Mars</v>
+        <v>CINNA</v>
       </c>
       <c r="G187" t="str">
-        <v>3:04</v>
+        <v>2:27</v>
       </c>
       <c r="H187" t="str">
-        <v>NoCap</v>
+        <v>Cannelle</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
+        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/leverage/6776432217</v>
+        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
       </c>
       <c r="L187" t="str">
-        <v>Leverage - NoCap</v>
+        <v>Dis-Moi - Cannelle</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Kool Aid</v>
+        <v>Leverage</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
+        <v>https://music.apple.com/us/song/leverage/6776432312</v>
       </c>
       <c r="D188" t="str">
         <v>2026-06-09</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Where Have All The Good Men Gone? - EP</v>
+        <v>Heaven on Mars</v>
       </c>
       <c r="G188" t="str">
-        <v>3:40</v>
+        <v>3:04</v>
       </c>
       <c r="H188" t="str">
-        <v>Debbii Dawson</v>
+        <v>NoCap</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
+        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
+        <v>https://music.apple.com/us/album/leverage/6776432217</v>
       </c>
       <c r="L188" t="str">
-        <v>Kool Aid - Debbii Dawson</v>
+        <v>Leverage - NoCap</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Pieces</v>
+        <v>Kool Aid</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/pieces/6771861156</v>
+        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
       </c>
       <c r="D189" t="str">
         <v>2026-06-09</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Pieces - Single</v>
+        <v>Where Have All The Good Men Gone? - EP</v>
       </c>
       <c r="G189" t="str">
-        <v>2:19</v>
+        <v>3:40</v>
       </c>
       <c r="H189" t="str">
-        <v>Dom Innarella</v>
+        <v>Debbii Dawson</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
+        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/pieces/6771861155</v>
+        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
       </c>
       <c r="L189" t="str">
-        <v>Pieces - Dom Innarella</v>
+        <v>Kool Aid - Debbii Dawson</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Mesmerized</v>
+        <v>Pieces</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
+        <v>https://music.apple.com/us/song/pieces/6771861156</v>
       </c>
       <c r="D190" t="str">
         <v>2026-06-09</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Mesmerized - Single</v>
+        <v>Pieces - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:38</v>
+        <v>2:19</v>
       </c>
       <c r="H190" t="str">
-        <v>The Aces</v>
+        <v>Dom Innarella</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
+        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
+        <v>https://music.apple.com/us/album/pieces/6771861155</v>
       </c>
       <c r="L190" t="str">
-        <v>Mesmerized - The Aces</v>
+        <v>Pieces - Dom Innarella</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Perfect 10</v>
+        <v>Mesmerized</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
+        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
       </c>
       <c r="D191" t="str">
         <v>2026-06-09</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>No Hard Feelings (Deluxe)</v>
+        <v>Mesmerized - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:51</v>
+        <v>2:38</v>
       </c>
       <c r="H191" t="str">
-        <v>The Beaches</v>
+        <v>The Aces</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
+        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
+        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
       </c>
       <c r="L191" t="str">
-        <v>Perfect 10 - The Beaches</v>
+        <v>Mesmerized - The Aces</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Recognize</v>
+        <v>Perfect 10</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/recognize/6769164705</v>
+        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
       </c>
       <c r="D192" t="str">
         <v>2026-06-09</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Recognize - Single</v>
+        <v>No Hard Feelings (Deluxe)</v>
       </c>
       <c r="G192" t="str">
-        <v>2:05</v>
+        <v>2:51</v>
       </c>
       <c r="H192" t="str">
-        <v>Fana Hues</v>
+        <v>The Beaches</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
+        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/recognize/6769164704</v>
+        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
       </c>
       <c r="L192" t="str">
-        <v>Recognize - Fana Hues</v>
+        <v>Perfect 10 - The Beaches</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Feel The Vibe</v>
+        <v>Recognize</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
+        <v>https://music.apple.com/us/song/recognize/6769164705</v>
       </c>
       <c r="D193" t="str">
         <v>2026-06-09</v>
@@ -7709,68 +7709,106 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Feel The Vibe</v>
+        <v>Recognize - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:28</v>
+        <v>2:05</v>
       </c>
       <c r="H193" t="str">
-        <v>Above &amp; Beyond</v>
+        <v>Fana Hues</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
+        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
+        <v>https://music.apple.com/us/album/recognize/6769164704</v>
       </c>
       <c r="L193" t="str">
-        <v>Feel The Vibe - Above &amp; Beyond</v>
+        <v>Recognize - Fana Hues</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
+        <v>Feel The Vibe</v>
+      </c>
+      <c r="B194" t="str">
+        <v/>
+      </c>
+      <c r="C194" t="str">
+        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
+      </c>
+      <c r="D194" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E194" t="str">
+        <v/>
+      </c>
+      <c r="F194" t="str">
+        <v>Feel The Vibe</v>
+      </c>
+      <c r="G194" t="str">
+        <v>3:28</v>
+      </c>
+      <c r="H194" t="str">
+        <v>Above &amp; Beyond</v>
+      </c>
+      <c r="I194" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J194" t="str">
+        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
+      </c>
+      <c r="K194" t="str">
+        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
+      </c>
+      <c r="L194" t="str">
+        <v>Feel The Vibe - Above &amp; Beyond</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
         <v>I Never Knew</v>
       </c>
-      <c r="B194" t="str">
-        <v/>
-      </c>
-      <c r="C194" t="str">
+      <c r="B195" t="str">
+        <v/>
+      </c>
+      <c r="C195" t="str">
         <v>https://music.apple.com/us/song/i-never-knew/6764351468</v>
       </c>
-      <c r="D194" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E194" t="str">
-        <v/>
-      </c>
-      <c r="F194" t="str">
+      <c r="D195" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E195" t="str">
+        <v/>
+      </c>
+      <c r="F195" t="str">
         <v>I Never Knew - Single</v>
       </c>
-      <c r="G194" t="str">
+      <c r="G195" t="str">
         <v>3:51</v>
       </c>
-      <c r="H194" t="str">
+      <c r="H195" t="str">
         <v>Adam Ten</v>
       </c>
-      <c r="I194" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J194" t="str">
+      <c r="I195" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J195" t="str">
         <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
-      <c r="K194" t="str">
+      <c r="K195" t="str">
         <v>https://music.apple.com/us/album/i-never-knew/1895744479</v>
       </c>
-      <c r="L194" t="str">
+      <c r="L195" t="str">
         <v>I Never Knew - Adam Ten</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L194"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L195"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-06-week02/titles.xlsx
+++ b/data/global/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L195"/>
+  <dimension ref="A1:L194"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אנוש ilnka x – קרבית</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-09</v>
+        <v>23h ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%a0%d7%95%d7%a9-ilnka-x-%d7%a7%d7%a8%d7%91%d7%99%d7%aa/</v>
+        <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-09</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "קרבית" של אנוש צוברי (באירוח ilanka, המגולמת על ידי השחקן והרקדן אילן זכרוב) הוא אחת היצירות המטורללות, המבריקות והאמיצות ביותר שידע הפופ הים-תיכוני בישראל. קל לפטור את השיר כרצועת דאנס-חפלה מועדונים קלילה המיועדת להרמות. אולם, "קרבית" הוא למעשה שיר</v>
+        <v>23h ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Capital FM</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אנוש ilnka x – קרבית</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B3" t="str">
-        <v>19 hours ago</v>
+        <v>23h ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
+        <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-09</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>19 hours ago</v>
+        <v>23h ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B4" t="str">
-        <v>19 hours ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
+        <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-09</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>19 hours ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>19 hours ago</v>
+        <v>23h ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
+        <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
       </c>
       <c r="D5" t="str">
         <v>2026-06-09</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>19 hours ago</v>
+        <v>23h ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B6" t="str">
-        <v>19 hours ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
+        <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
       </c>
       <c r="D6" t="str">
         <v>2026-06-09</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>19 hours ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
+        <v>DEEP PURPLE - DIABLO (Official Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
+        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-09</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Capital FM</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video)</v>
+        <v>Reba McEntire - You Never Gave Up On Me</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
+        <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
       </c>
       <c r="D8" t="str">
         <v>2026-06-09</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Reba McEntire</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Reba McEntire - You Never Gave Up On Me - Reba McEntire</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Reba McEntire - You Never Gave Up On Me</v>
+        <v>elijah woods - Wonder (Official Lyric Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
+        <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-09</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Reba McEntire</v>
+        <v>elijah woods</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Reba McEntire - You Never Gave Up On Me - Reba McEntire</v>
+        <v>elijah woods - Wonder (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>elijah woods - Wonder (Official Lyric Video)</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
+        <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
       </c>
       <c r="D10" t="str">
         <v>2026-06-09</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>elijah woods</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>elijah woods - Wonder (Official Lyric Video) - elijah woods</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
+        <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
       </c>
       <c r="D11" t="str">
         <v>2026-06-09</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Capital FM and XG</v>
+        <v>Capital FM</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
+        <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
       </c>
       <c r="D12" t="str">
         <v>2026-06-09</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
+        <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
       </c>
       <c r="D13" t="str">
         <v>2026-06-09</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
+        <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
       </c>
       <c r="D14" t="str">
         <v>2026-06-09</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
+        <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
       </c>
       <c r="D15" t="str">
         <v>2026-06-09</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
+        <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
       </c>
       <c r="D16" t="str">
         <v>2026-06-09</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
+        <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
       </c>
       <c r="D17" t="str">
         <v>2026-06-09</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
+        <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
       </c>
       <c r="D18" t="str">
         <v>2026-06-09</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B19" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
+        <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
       </c>
       <c r="D19" t="str">
         <v>2026-06-09</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Capital FM and XG</v>
+        <v>Capital FM</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
+        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B20" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
+        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
       </c>
       <c r="D20" t="str">
         <v>2026-06-09</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B21" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
+        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
       </c>
       <c r="D21" t="str">
         <v>2026-06-09</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B22" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
+        <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
       </c>
       <c r="D22" t="str">
         <v>2026-06-09</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B23" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
+        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
       </c>
       <c r="D23" t="str">
         <v>2026-06-09</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
+        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
       </c>
       <c r="D24" t="str">
         <v>2026-06-09</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
+        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
       </c>
       <c r="D25" t="str">
         <v>2026-06-09</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
+        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
       </c>
       <c r="D26" t="str">
         <v>2026-06-09</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
+        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
+        <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
       </c>
       <c r="D27" t="str">
         <v>2026-06-09</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
+        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
       </c>
       <c r="D28" t="str">
         <v>2026-06-09</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
+        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
       </c>
       <c r="D29" t="str">
         <v>2026-06-09</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
+        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-06-09</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
+        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
       </c>
       <c r="D31" t="str">
         <v>2026-06-09</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
+        <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
       </c>
       <c r="D32" t="str">
         <v>2026-06-09</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
+        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
       </c>
       <c r="D33" t="str">
         <v>2026-06-09</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B34" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
+        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
       </c>
       <c r="D34" t="str">
         <v>2026-06-09</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B35" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
+        <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
       </c>
       <c r="D35" t="str">
         <v>2026-06-09</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
+        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
       </c>
       <c r="D36" t="str">
         <v>2026-06-09</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B37" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
+        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
       </c>
       <c r="D37" t="str">
         <v>2026-06-09</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
+        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
       </c>
       <c r="D38" t="str">
         <v>2026-06-09</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B39" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
+        <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
       </c>
       <c r="D39" t="str">
         <v>2026-06-09</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B40" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
+        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
       </c>
       <c r="D40" t="str">
         <v>2026-06-09</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
+        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
       </c>
       <c r="D41" t="str">
         <v>2026-06-09</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B42" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
+        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
       </c>
       <c r="D42" t="str">
         <v>2026-06-09</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
+        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
       </c>
       <c r="D43" t="str">
         <v>2026-06-09</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B44" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
+        <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
       </c>
       <c r="D44" t="str">
         <v>2026-06-09</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
       </c>
       <c r="B45" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
+        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
       </c>
       <c r="D45" t="str">
         <v>2026-06-09</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Capital FM</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
       </c>
       <c r="B46" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
+        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-06-09</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>TheCranberriesTV</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
+        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
       </c>
       <c r="D47" t="str">
         <v>2026-06-09</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>TheCranberriesTV</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
+        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
       </c>
       <c r="D48" t="str">
         <v>2026-06-09</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Jordana Bryant</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B49" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
+        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
       </c>
       <c r="D49" t="str">
         <v>2026-06-09</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Grace Enger</v>
+        <v>The Offspring</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
+        <v>Lola Young – From Down Here (From The Pool)</v>
       </c>
       <c r="B50" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
+        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
       </c>
       <c r="D50" t="str">
         <v>2026-06-09</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>The Offspring</v>
+        <v>Lola Young</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
+        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Lola Young – From Down Here (From The Pool)</v>
+        <v>CAIN - Living Water (Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
+        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
       </c>
       <c r="D51" t="str">
         <v>2026-06-09</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Lola Young</v>
+        <v>CAIN</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
+        <v>CAIN - Living Water (Music Video) - CAIN</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>CAIN - Living Water (Music Video)</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
+        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
       </c>
       <c r="D52" t="str">
         <v>2026-06-09</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>CAIN</v>
+        <v>Eric Clapton</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>CAIN - Living Water (Music Video) - CAIN</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
+        <v>Blu DeTiger - Whisper (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
+        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
       </c>
       <c r="D53" t="str">
         <v>2026-06-09</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Eric Clapton</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
+        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video)</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
+        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
       </c>
       <c r="D54" t="str">
         <v>2026-06-09</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Blu DeTiger</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
       </c>
       <c r="B55" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
+        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
       </c>
       <c r="D55" t="str">
         <v>2026-06-09</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Pink Floyd</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
+        <v>Holly Humberstone - it’s just White Noise</v>
       </c>
       <c r="B56" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
+        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
       </c>
       <c r="D56" t="str">
         <v>2026-06-09</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Pink Floyd</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
+        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Holly Humberstone - it’s just White Noise</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
+        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
       </c>
       <c r="D57" t="str">
         <v>2026-06-09</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Holly Humberstone</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
+        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
       </c>
       <c r="D58" t="str">
         <v>2026-06-09</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Freya Ridings</v>
+        <v>Muse</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
       </c>
       <c r="B59" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
+        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
       </c>
       <c r="D59" t="str">
         <v>2026-06-09</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Muse</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
+        <v>Evanescence - Sanctuary (Official Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
+        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
       </c>
       <c r="D60" t="str">
         <v>2026-06-09</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Ellie Goulding</v>
+        <v>Evanescence</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
+        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer)</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
       </c>
       <c r="B61" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
+        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
       </c>
       <c r="D61" t="str">
         <v>2026-06-09</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Evanescence</v>
+        <v>The Beaches</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
+        <v>Bella White - Stuff (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
+        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
       </c>
       <c r="D62" t="str">
         <v>2026-06-09</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>The Beaches</v>
+        <v>Bella White</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
+        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Bella White - Stuff (Official Music Video)</v>
+        <v>Meduza, Rani - Silence (Official Visualizer)</v>
       </c>
       <c r="B63" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
+        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
       </c>
       <c r="D63" t="str">
         <v>2026-06-09</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Bella White</v>
+        <v>Meduza and 2 more</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
+        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer)</v>
+        <v>CAIN - Living Water (Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
+        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
       </c>
       <c r="D64" t="str">
         <v>2026-06-09</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Meduza and 2 more</v>
+        <v>CAIN</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
+        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>CAIN - Living Water (Lyric Video)</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
+        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
       </c>
       <c r="D65" t="str">
         <v>2026-06-09</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>CAIN</v>
+        <v>Fitz and the Tantrums</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
+        <v>Jeremy Camp - Reflector (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
+        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
       </c>
       <c r="D66" t="str">
         <v>2026-06-09</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Fitz and the Tantrums</v>
+        <v>Jeremy Camp</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
+        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video)</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
+        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
       </c>
       <c r="D67" t="str">
         <v>2026-06-09</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Jeremy Camp</v>
+        <v>Alesso</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
       </c>
       <c r="B68" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
+        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
       </c>
       <c r="D68" t="str">
         <v>2026-06-09</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Alesso</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
+        <v>Isabel LaRosa - Every Life (Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
+        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
       </c>
       <c r="D69" t="str">
         <v>2026-06-09</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Malcolm Todd</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
+        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer)</v>
+        <v>Wyatt Flores - Half The Man (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
+        <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
       </c>
       <c r="D70" t="str">
         <v>2026-06-09</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
+        <v>Wyatt Flores - Half The Man (Official Music Video) - Wyatt Flores</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video)</v>
+        <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
+        <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
       </c>
       <c r="D71" t="str">
         <v>2026-06-09</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Wyatt Flores</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video) - Wyatt Flores</v>
+        <v>Mckenna Grace - Ugly and Rotten (Official Music Video) - Mckenna Grace</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
+        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B72" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
+        <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
       </c>
       <c r="D72" t="str">
         <v>2026-06-09</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Mckenna Grace</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video) - Mckenna Grace</v>
+        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>Boyzone - No Matter What (Live)</v>
       </c>
       <c r="B73" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
+        <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
       </c>
       <c r="D73" t="str">
         <v>2026-06-09</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Robert Grace</v>
+        <v>Boyzone</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>Boyzone - No Matter What (Live) - Boyzone</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Boyzone - No Matter What (Live)</v>
+        <v>Florrie - The Times (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
+        <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
       </c>
       <c r="D74" t="str">
         <v>2026-06-09</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Boyzone</v>
+        <v>florriemusic</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Boyzone - No Matter What (Live) - Boyzone</v>
+        <v>Florrie - The Times (Official Video) - florriemusic</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Florrie - The Times (Official Video)</v>
+        <v>Madonna - Love Sensation (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
+        <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
       </c>
       <c r="D75" t="str">
         <v>2026-06-09</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>florriemusic</v>
+        <v>Madonna</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Florrie - The Times (Official Video) - florriemusic</v>
+        <v>Madonna - Love Sensation (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer)</v>
+        <v>DMA'S - Hurracane (Official Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
+        <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
       </c>
       <c r="D76" t="str">
         <v>2026-06-09</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Madonna</v>
+        <v>DMA'S</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer) - Madonna</v>
+        <v>DMA'S - Hurracane (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>DMA'S - Hurracane (Official Video)</v>
+        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
       </c>
       <c r="B77" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
+        <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
       </c>
       <c r="D77" t="str">
         <v>2026-06-09</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>DMA'S</v>
+        <v>Lainey Wilson and John Mayer</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>DMA'S - Hurracane (Official Video) - DMA'S</v>
+        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio) - Lainey Wilson and John Mayer</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
+        <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
+        <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
       </c>
       <c r="D78" t="str">
         <v>2026-06-09</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Lainey Wilson and John Mayer</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio) - Lainey Wilson and John Mayer</v>
+        <v>ROLE MODEL - High Hopes 3000 (Official Music Video) - ROLE MODEL</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
+        <v>Shawn Mendes - Treat You Better (Live from New York)</v>
       </c>
       <c r="B79" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
+        <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-06-09</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>ROLE MODEL</v>
+        <v>Shawn Mendes</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video) - ROLE MODEL</v>
+        <v>Shawn Mendes - Treat You Better (Live from New York) - Shawn Mendes</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York)</v>
+        <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
+        <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
       </c>
       <c r="D80" t="str">
         <v>2026-06-09</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Shawn Mendes</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York) - Shawn Mendes</v>
+        <v>SIENNA SPIRO - The Visitor (Official Music Video) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
       </c>
       <c r="B81" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
+        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
       </c>
       <c r="D81" t="str">
         <v>2026-06-09</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video) - SIENNA SPIRO</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
+        <v>Europe - The Cult of Ignorance (Official Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
+        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
       </c>
       <c r="D82" t="str">
         <v>2026-06-09</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Europe</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video)</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
+        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
       </c>
       <c r="D83" t="str">
         <v>2026-06-09</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Europe</v>
+        <v>Air Supply</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
+        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
       </c>
       <c r="D84" t="str">
         <v>2026-06-09</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Air Supply</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
       </c>
       <c r="B85" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
+        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
       </c>
       <c r="D85" t="str">
         <v>2026-06-09</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Julia Cole Music</v>
+        <v>Allen Stone and Placeholder Sessions</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
       </c>
       <c r="B86" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
+        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
       </c>
       <c r="D86" t="str">
         <v>2026-06-09</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Allen Stone and Placeholder Sessions</v>
+        <v>Morgan Wallen</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
+        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
       </c>
       <c r="D87" t="str">
         <v>2026-06-09</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Morgan Wallen</v>
+        <v>Billy Idol</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
       </c>
       <c r="B88" t="str">
-        <v>6 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
+        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
       </c>
       <c r="D88" t="str">
         <v>2026-06-09</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>6 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Billy Idol</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>10 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
+        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
       </c>
       <c r="D89" t="str">
         <v>2026-06-09</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>10 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
+        <v>Hippo Campus - South</v>
       </c>
       <c r="B90" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
+        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
       </c>
       <c r="D90" t="str">
         <v>2026-06-09</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Icona Pop</v>
+        <v>Hippo Campus</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
+        <v>Hippo Campus - South - Hippo Campus</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Hippo Campus - South</v>
+        <v>elijah woods - Old (Treehouse Sessions)</v>
       </c>
       <c r="B91" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
+        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
       </c>
       <c r="D91" t="str">
         <v>2026-06-09</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Hippo Campus</v>
+        <v>elijah woods</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Hippo Campus - South - Hippo Campus</v>
+        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>elijah woods - Old (Treehouse Sessions)</v>
+        <v>Nothing But Thieves - Evolution (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
+        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
       </c>
       <c r="D92" t="str">
         <v>2026-06-09</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>elijah woods</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
+        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video)</v>
+        <v>Ariana Grande - hate that i made you love me (official music video)</v>
       </c>
       <c r="B93" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
+        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
       </c>
       <c r="D93" t="str">
         <v>2026-06-09</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
+        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video)</v>
+        <v>LAUREL - Fire Breather</v>
       </c>
       <c r="B94" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
+        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
       </c>
       <c r="D94" t="str">
         <v>2026-06-09</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Ariana Grande</v>
+        <v>LAUREL</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
+        <v>LAUREL - Fire Breather - LAUREL</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>LAUREL - Fire Breather</v>
+        <v>The Warning - Ego (Performance Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>7 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
+        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
       </c>
       <c r="D95" t="str">
         <v>2026-06-09</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>7 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>LAUREL</v>
+        <v>The Warning</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>LAUREL - Fire Breather - LAUREL</v>
+        <v>The Warning - Ego (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>The Warning - Ego (Performance Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
       </c>
       <c r="B96" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
+        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
       </c>
       <c r="D96" t="str">
         <v>2026-06-09</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>The Warning</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>The Warning - Ego (Performance Video) - The Warning</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B97" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
+        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
       </c>
       <c r="D97" t="str">
         <v>2026-06-09</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
       </c>
       <c r="B98" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
+        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
       </c>
       <c r="D98" t="str">
         <v>2026-06-09</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Armin van Buuren</v>
+        <v>Andrew Bird</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
+        <v>Danny Gokey - God's Not (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
+        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
       </c>
       <c r="D99" t="str">
         <v>2026-06-09</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Andrew Bird</v>
+        <v>Danny Gokey</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
+        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video)</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B100" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
+        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
       </c>
       <c r="D100" t="str">
         <v>2026-06-09</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Danny Gokey</v>
+        <v>Armik</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
       </c>
       <c r="B101" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
+        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
       </c>
       <c r="D101" t="str">
         <v>2026-06-09</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Armik</v>
+        <v>Holly Humberstone and Free People</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
+        <v>True Colors</v>
       </c>
       <c r="B102" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
+        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
       </c>
       <c r="D102" t="str">
         <v>2026-06-09</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>10 days ago</v>
+        <v>Thank You</v>
       </c>
       <c r="G102" t="str">
-        <v/>
+        <v>3:39</v>
       </c>
       <c r="H102" t="str">
-        <v>Holly Humberstone and Free People</v>
+        <v>Mike D</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
       </c>
       <c r="L102" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
+        <v>True Colors - Mike D</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>True Colors</v>
+        <v>Too Easy</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
+        <v>https://music.apple.com/us/song/too-easy/6774752170</v>
       </c>
       <c r="D103" t="str">
         <v>2026-06-09</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Thank You</v>
+        <v>Too Easy - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>3:39</v>
+        <v>1:54</v>
       </c>
       <c r="H103" t="str">
-        <v>Mike D</v>
+        <v>Tinashe</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
+        <v>https://music.apple.com/us/artist/tinashe/464835513</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
+        <v>https://music.apple.com/us/album/too-easy/6774752168</v>
       </c>
       <c r="L103" t="str">
-        <v>True Colors - Mike D</v>
+        <v>Too Easy - Tinashe</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Too Easy</v>
+        <v>I Knew It, I Knew You</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/too-easy/6774752170</v>
+        <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
       </c>
       <c r="D104" t="str">
         <v>2026-06-09</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Too Easy - Single</v>
+        <v>I Knew It, I Knew You - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>1:54</v>
+        <v>2:58</v>
       </c>
       <c r="H104" t="str">
-        <v>Tinashe</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/tinashe/464835513</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/too-easy/6774752168</v>
+        <v>https://music.apple.com/us/album/i-knew-it-i-knew-you/6775527442</v>
       </c>
       <c r="L104" t="str">
-        <v>Too Easy - Tinashe</v>
+        <v>I Knew It, I Knew You - Taylor Swift</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>I Knew It, I Knew You</v>
+        <v>Love Sensation</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
+        <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
       </c>
       <c r="D105" t="str">
         <v>2026-06-09</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>I Knew It, I Knew You - Single</v>
+        <v>Love Sensation - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:58</v>
+        <v>3:48</v>
       </c>
       <c r="H105" t="str">
-        <v>Taylor Swift</v>
+        <v>Madonna</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/i-knew-it-i-knew-you/6775527442</v>
+        <v>https://music.apple.com/us/album/love-sensation/6774810102</v>
       </c>
       <c r="L105" t="str">
-        <v>I Knew It, I Knew You - Taylor Swift</v>
+        <v>Love Sensation - Madonna</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Love Sensation</v>
+        <v>Mi Yo De Antes</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
+        <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
       </c>
       <c r="D106" t="str">
         <v>2026-06-09</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Love Sensation - Single</v>
+        <v>Mi Yo De Antes - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:48</v>
+        <v>3:04</v>
       </c>
       <c r="H106" t="str">
-        <v>Madonna</v>
+        <v>Ozuna</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/love-sensation/6774810102</v>
+        <v>https://music.apple.com/us/album/mi-yo-de-antes/6769193983</v>
       </c>
       <c r="L106" t="str">
-        <v>Love Sensation - Madonna</v>
+        <v>Mi Yo De Antes - Ozuna</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Mi Yo De Antes</v>
+        <v>Three Nations</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
+        <v>https://music.apple.com/us/song/three-nations/6776010602</v>
       </c>
       <c r="D107" t="str">
         <v>2026-06-09</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Mi Yo De Antes - Single</v>
+        <v>Official FIFA World Cup 2026™ Album</v>
       </c>
       <c r="G107" t="str">
-        <v>3:04</v>
+        <v>3:30</v>
       </c>
       <c r="H107" t="str">
-        <v>Ozuna</v>
+        <v>21 Savage</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v>https://music.apple.com/us/artist/21-savage/894820464</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/mi-yo-de-antes/6769193983</v>
+        <v>https://music.apple.com/us/album/three-nations/6776010591</v>
       </c>
       <c r="L107" t="str">
-        <v>Mi Yo De Antes - Ozuna</v>
+        <v>Three Nations - 21 Savage</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Three Nations</v>
+        <v>Champions (WC 26)</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/three-nations/6776010602</v>
+        <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
       </c>
       <c r="D108" t="str">
         <v>2026-06-09</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Official FIFA World Cup 2026™ Album</v>
+        <v>Champions (WC 26) - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:30</v>
+        <v>4:15</v>
       </c>
       <c r="H108" t="str">
-        <v>21 Savage</v>
+        <v>IShowSpeed</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/21-savage/894820464</v>
+        <v>https://music.apple.com/us/artist/ishowspeed/1574723975</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/three-nations/6776010591</v>
+        <v>https://music.apple.com/us/album/champions-wc-26/6775282246</v>
       </c>
       <c r="L108" t="str">
-        <v>Three Nations - 21 Savage</v>
+        <v>Champions (WC 26) - IShowSpeed</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Champions (WC 26)</v>
+        <v>ENCERRONES</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
+        <v>https://music.apple.com/us/song/encerrones/6771854522</v>
       </c>
       <c r="D109" t="str">
         <v>2026-06-09</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Champions (WC 26) - Single</v>
+        <v>TEOFANIA</v>
       </c>
       <c r="G109" t="str">
-        <v>4:15</v>
+        <v>2:23</v>
       </c>
       <c r="H109" t="str">
-        <v>IShowSpeed</v>
+        <v>LENCHO</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/ishowspeed/1574723975</v>
+        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/champions-wc-26/6775282246</v>
+        <v>https://music.apple.com/us/album/encerrones/6771854517</v>
       </c>
       <c r="L109" t="str">
-        <v>Champions (WC 26) - IShowSpeed</v>
+        <v>ENCERRONES - LENCHO</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>ENCERRONES</v>
+        <v>Cowgirl</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/encerrones/6771854522</v>
+        <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
       </c>
       <c r="D110" t="str">
         <v>2026-06-09</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>TEOFANIA</v>
+        <v>The Outlaw Cherie Lee &amp; Other Western Tales</v>
       </c>
       <c r="G110" t="str">
-        <v>2:23</v>
+        <v>2:56</v>
       </c>
       <c r="H110" t="str">
-        <v>LENCHO</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
+        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/encerrones/6771854517</v>
+        <v>https://music.apple.com/us/album/cowgirl/1894906682</v>
       </c>
       <c r="L110" t="str">
-        <v>ENCERRONES - LENCHO</v>
+        <v>Cowgirl - Shaboozey</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Cowgirl</v>
+        <v>PASSENGER</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
+        <v>https://music.apple.com/us/song/passenger/6773456081</v>
       </c>
       <c r="D111" t="str">
         <v>2026-06-09</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>The Outlaw Cherie Lee &amp; Other Western Tales</v>
+        <v>WILDCHILD</v>
       </c>
       <c r="G111" t="str">
-        <v>2:56</v>
+        <v>2:39</v>
       </c>
       <c r="H111" t="str">
-        <v>Shaboozey</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/cowgirl/1894906682</v>
+        <v>https://music.apple.com/us/album/passenger/6773456078</v>
       </c>
       <c r="L111" t="str">
-        <v>Cowgirl - Shaboozey</v>
+        <v>PASSENGER - Alex Warren</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>PASSENGER</v>
+        <v>Secret Language</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/passenger/6773456081</v>
+        <v>https://music.apple.com/us/song/secret-language/6774223667</v>
       </c>
       <c r="D112" t="str">
         <v>2026-06-09</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>WILDCHILD</v>
+        <v>Sweet Fortune</v>
       </c>
       <c r="G112" t="str">
-        <v>2:39</v>
+        <v>3:53</v>
       </c>
       <c r="H112" t="str">
-        <v>Alex Warren</v>
+        <v>Ryan Beatty</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/ryan-beatty/483234172</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/passenger/6773456078</v>
+        <v>https://music.apple.com/us/album/secret-language/6774223660</v>
       </c>
       <c r="L112" t="str">
-        <v>PASSENGER - Alex Warren</v>
+        <v>Secret Language - Ryan Beatty</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Secret Language</v>
+        <v>High Hopes 3000</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/secret-language/6774223667</v>
+        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
       </c>
       <c r="D113" t="str">
         <v>2026-06-09</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Sweet Fortune</v>
+        <v>Chuck Timely &amp; The Hourglass</v>
       </c>
       <c r="G113" t="str">
-        <v>3:53</v>
+        <v>4:05</v>
       </c>
       <c r="H113" t="str">
-        <v>Ryan Beatty</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/ryan-beatty/483234172</v>
+        <v>https://music.apple.com/us/artist/role-model/199215762</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/secret-language/6774223660</v>
+        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
       </c>
       <c r="L113" t="str">
-        <v>Secret Language - Ryan Beatty</v>
+        <v>High Hopes 3000 - ROLE MODEL</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>High Hopes 3000</v>
+        <v>Vertical</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
+        <v>https://music.apple.com/us/song/vertical/1892436336</v>
       </c>
       <c r="D114" t="str">
         <v>2026-06-09</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Chuck Timely &amp; The Hourglass</v>
+        <v>Emotional Junglist</v>
       </c>
       <c r="G114" t="str">
-        <v>4:05</v>
+        <v>2:36</v>
       </c>
       <c r="H114" t="str">
-        <v>ROLE MODEL</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/role-model/199215762</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
+        <v>https://music.apple.com/us/album/vertical/1892436329</v>
       </c>
       <c r="L114" t="str">
-        <v>High Hopes 3000 - ROLE MODEL</v>
+        <v>Vertical - Nia Archives</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Vertical</v>
+        <v>snake the drain</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/vertical/1892436336</v>
+        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
       </c>
       <c r="D115" t="str">
         <v>2026-06-09</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Emotional Junglist</v>
+        <v>this time it’s different / snake the drain - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>2:36</v>
+        <v>3:08</v>
       </c>
       <c r="H115" t="str">
-        <v>Nia Archives</v>
+        <v>Devon Again</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/vertical/1892436329</v>
+        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
       </c>
       <c r="L115" t="str">
-        <v>Vertical - Nia Archives</v>
+        <v>snake the drain - Devon Again</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>snake the drain</v>
+        <v>Every Single Weekend (feat. Jamie xx)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
+        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D116" t="str">
         <v>2026-06-09</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>this time it’s different / snake the drain - Single</v>
+        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:08</v>
+        <v>2:10</v>
       </c>
       <c r="H116" t="str">
-        <v>Devon Again</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
+        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
       </c>
       <c r="L116" t="str">
-        <v>snake the drain - Devon Again</v>
+        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Every Single Weekend (feat. Jamie xx)</v>
+        <v>Bluffin'</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
+        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
       </c>
       <c r="D117" t="str">
         <v>2026-06-09</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
+        <v>Piss In The Wind (Deluxe)</v>
       </c>
       <c r="G117" t="str">
-        <v>2:10</v>
+        <v>2:34</v>
       </c>
       <c r="H117" t="str">
-        <v>The Avalanches</v>
+        <v>Joji</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
+        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
       </c>
       <c r="L117" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
+        <v>Bluffin' - Joji</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Bluffin'</v>
+        <v>Dreams</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
+        <v>https://music.apple.com/us/song/dreams/1884731028</v>
       </c>
       <c r="D118" t="str">
         <v>2026-06-09</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Piss In The Wind (Deluxe)</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="G118" t="str">
-        <v>2:34</v>
+        <v>3:56</v>
       </c>
       <c r="H118" t="str">
-        <v>Joji</v>
+        <v>Prospa</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
+        <v>https://music.apple.com/us/album/dreams/1884730177</v>
       </c>
       <c r="L118" t="str">
-        <v>Bluffin' - Joji</v>
+        <v>Dreams - Prospa</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Dreams</v>
+        <v>Cotton</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/dreams/1884731028</v>
+        <v>https://music.apple.com/us/song/cotton/1887627941</v>
       </c>
       <c r="D119" t="str">
         <v>2026-06-09</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Free Your Mind</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G119" t="str">
-        <v>3:56</v>
+        <v>3:43</v>
       </c>
       <c r="H119" t="str">
-        <v>Prospa</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/dreams/1884730177</v>
+        <v>https://music.apple.com/us/album/cotton/1887627836</v>
       </c>
       <c r="L119" t="str">
-        <v>Dreams - Prospa</v>
+        <v>Cotton - Vince Staples</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Cotton</v>
+        <v>Black Prada Dress</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/cotton/1887627941</v>
+        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
       </c>
       <c r="D120" t="str">
         <v>2026-06-09</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Cry Baby</v>
+        <v>I Know Too Much</v>
       </c>
       <c r="G120" t="str">
-        <v>3:43</v>
+        <v>3:19</v>
       </c>
       <c r="H120" t="str">
-        <v>Vince Staples</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/cotton/1887627836</v>
+        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
       </c>
       <c r="L120" t="str">
-        <v>Cotton - Vince Staples</v>
+        <v>Black Prada Dress - Ellie Goulding</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Black Prada Dress</v>
+        <v>Don’t Break Her Heart</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
+        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
       </c>
       <c r="D121" t="str">
         <v>2026-06-09</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>I Know Too Much</v>
+        <v>THERAPY AT THE CLUB</v>
       </c>
       <c r="G121" t="str">
-        <v>3:19</v>
+        <v>3:44</v>
       </c>
       <c r="H121" t="str">
-        <v>Ellie Goulding</v>
+        <v>FLO</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
+        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
       </c>
       <c r="L121" t="str">
-        <v>Black Prada Dress - Ellie Goulding</v>
+        <v>Don’t Break Her Heart - FLO</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Don’t Break Her Heart</v>
+        <v>Sexy Ladies (feat. UCB)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
+        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
       </c>
       <c r="D122" t="str">
         <v>2026-06-09</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>THERAPY AT THE CLUB</v>
+        <v>BITCH</v>
       </c>
       <c r="G122" t="str">
-        <v>3:44</v>
+        <v>2:50</v>
       </c>
       <c r="H122" t="str">
-        <v>FLO</v>
+        <v>Lizzo</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
+        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
       </c>
       <c r="L122" t="str">
-        <v>Don’t Break Her Heart - FLO</v>
+        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Sexy Ladies (feat. UCB)</v>
+        <v>Noche Without You</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
+        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
       </c>
       <c r="D123" t="str">
         <v>2026-06-09</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>BITCH</v>
+        <v>SOMA</v>
       </c>
       <c r="G123" t="str">
-        <v>2:50</v>
+        <v>3:23</v>
       </c>
       <c r="H123" t="str">
-        <v>Lizzo</v>
+        <v>Skrillex</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
+        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
       </c>
       <c r="L123" t="str">
-        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
+        <v>Noche Without You - Skrillex</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Noche Without You</v>
+        <v>Difficult Love</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
+        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
       </c>
       <c r="D124" t="str">
         <v>2026-06-09</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>SOMA</v>
+        <v>Do That Again</v>
       </c>
       <c r="G124" t="str">
-        <v>3:23</v>
+        <v>2:33</v>
       </c>
       <c r="H124" t="str">
-        <v>Skrillex</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
+        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
       </c>
       <c r="L124" t="str">
-        <v>Noche Without You - Skrillex</v>
+        <v>Difficult Love - Malcolm Todd</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Difficult Love</v>
+        <v>Tastes So Good</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
+        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
       </c>
       <c r="D125" t="str">
         <v>2026-06-09</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Do That Again</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G125" t="str">
-        <v>2:33</v>
+        <v>3:05</v>
       </c>
       <c r="H125" t="str">
-        <v>Malcolm Todd</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
+        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
       </c>
       <c r="L125" t="str">
-        <v>Difficult Love - Malcolm Todd</v>
+        <v>Tastes So Good - Niall Horan</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Tastes So Good</v>
+        <v>Phone, Keys, Wallet</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
+        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
       </c>
       <c r="D126" t="str">
         <v>2026-06-09</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Dinner Party</v>
+        <v>Phone, Keys, Wallet - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:05</v>
+        <v>2:52</v>
       </c>
       <c r="H126" t="str">
-        <v>Niall Horan</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
+        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
       </c>
       <c r="L126" t="str">
-        <v>Tastes So Good - Niall Horan</v>
+        <v>Phone, Keys, Wallet - Lainey Wilson</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Phone, Keys, Wallet</v>
+        <v>Madrugada</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
+        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
       </c>
       <c r="D127" t="str">
         <v>2026-06-09</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Phone, Keys, Wallet - Single</v>
+        <v>Madrugada - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:52</v>
+        <v>2:58</v>
       </c>
       <c r="H127" t="str">
-        <v>Lainey Wilson</v>
+        <v>Chino Pacas</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
+        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
       </c>
       <c r="L127" t="str">
-        <v>Phone, Keys, Wallet - Lainey Wilson</v>
+        <v>Madrugada - Chino Pacas</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Madrugada</v>
+        <v>Oh Chet (feat. Travis Scott)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
+        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
       </c>
       <c r="D128" t="str">
         <v>2026-06-09</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Madrugada - Single</v>
+        <v>Oh Chet (feat. Travis Scott) - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:58</v>
+        <v>2:23</v>
       </c>
       <c r="H128" t="str">
-        <v>Chino Pacas</v>
+        <v>Jey One</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
+        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
+        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
       </c>
       <c r="L128" t="str">
-        <v>Madrugada - Chino Pacas</v>
+        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Oh Chet (feat. Travis Scott)</v>
+        <v>An Hour or So (Live at Apple Music Radio)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
+        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
       </c>
       <c r="D129" t="str">
         <v>2026-06-09</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Single</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G129" t="str">
-        <v>2:23</v>
+        <v>3:02</v>
       </c>
       <c r="H129" t="str">
-        <v>Jey One</v>
+        <v>Benny G</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
+        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
       </c>
       <c r="L129" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
+        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>An Hour or So (Live at Apple Music Radio)</v>
+        <v>it’s just White Noise</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
+        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
       </c>
       <c r="D130" t="str">
         <v>2026-06-09</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>it’s a real Cruel World - EP</v>
       </c>
       <c r="G130" t="str">
-        <v>3:02</v>
+        <v>3:57</v>
       </c>
       <c r="H130" t="str">
-        <v>Benny G</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
+        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
       </c>
       <c r="L130" t="str">
-        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
+        <v>it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>it’s just White Noise</v>
+        <v>the feeling</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
+        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
       </c>
       <c r="D131" t="str">
         <v>2026-06-09</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>it’s a real Cruel World - EP</v>
+        <v>Oh yeah?</v>
       </c>
       <c r="G131" t="str">
-        <v>3:57</v>
+        <v>4:35</v>
       </c>
       <c r="H131" t="str">
-        <v>Holly Humberstone</v>
+        <v>Steve Lacy</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
+        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
       </c>
       <c r="L131" t="str">
-        <v>it’s just White Noise - Holly Humberstone</v>
+        <v>the feeling - Steve Lacy</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>the feeling</v>
+        <v>baby (Live at Apple Music Radio)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
+        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
       </c>
       <c r="D132" t="str">
         <v>2026-06-09</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Oh yeah?</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G132" t="str">
-        <v>4:35</v>
+        <v>3:14</v>
       </c>
       <c r="H132" t="str">
-        <v>Steve Lacy</v>
+        <v>Gabriel Jacoby</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
+        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
+        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
       </c>
       <c r="L132" t="str">
-        <v>the feeling - Steve Lacy</v>
+        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>baby (Live at Apple Music Radio)</v>
+        <v>Drop The Lo</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
+        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
       </c>
       <c r="D133" t="str">
         <v>2026-06-09</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Drop The Lo - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:14</v>
+        <v>2:41</v>
       </c>
       <c r="H133" t="str">
-        <v>Gabriel Jacoby</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
+        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
       </c>
       <c r="L133" t="str">
-        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
+        <v>Drop The Lo - Bryson Tiller</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Drop The Lo</v>
+        <v>GANG BIZNESS feat paygotti</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
+        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
       </c>
       <c r="D134" t="str">
         <v>2026-06-09</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Drop The Lo - Single</v>
+        <v>GANG BIZNESS feat paygotti - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:41</v>
+        <v>2:47</v>
       </c>
       <c r="H134" t="str">
-        <v>Bryson Tiller</v>
+        <v>YG</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
+        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
       </c>
       <c r="L134" t="str">
-        <v>Drop The Lo - Bryson Tiller</v>
+        <v>GANG BIZNESS feat paygotti - YG</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>GANG BIZNESS feat paygotti</v>
+        <v>Lay It Down</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
+        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
       </c>
       <c r="D135" t="str">
         <v>2026-06-09</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>GANG BIZNESS feat paygotti - Single</v>
+        <v>Lay It Down - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:47</v>
+        <v>2:38</v>
       </c>
       <c r="H135" t="str">
-        <v>YG</v>
+        <v>FattMack</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
+        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
       </c>
       <c r="L135" t="str">
-        <v>GANG BIZNESS feat paygotti - YG</v>
+        <v>Lay It Down - FattMack</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Lay It Down</v>
+        <v>WAX PAPER</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
+        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
       </c>
       <c r="D136" t="str">
         <v>2026-06-09</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Lay It Down - Single</v>
+        <v>WHACK'S MUSEUM</v>
       </c>
       <c r="G136" t="str">
-        <v>2:38</v>
+        <v>2:43</v>
       </c>
       <c r="H136" t="str">
-        <v>FattMack</v>
+        <v>Tierra Whack</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
+        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
       </c>
       <c r="L136" t="str">
-        <v>Lay It Down - FattMack</v>
+        <v>WAX PAPER - Tierra Whack</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>WAX PAPER</v>
+        <v>abusadOra (tambores)</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
+        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
       </c>
       <c r="D137" t="str">
         <v>2026-06-09</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>WHACK'S MUSEUM</v>
+        <v>ANTES DE QUE SEA TARDE</v>
       </c>
       <c r="G137" t="str">
-        <v>2:43</v>
+        <v>3:11</v>
       </c>
       <c r="H137" t="str">
-        <v>Tierra Whack</v>
+        <v>Yorghaki</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
+        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
+        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
       </c>
       <c r="L137" t="str">
-        <v>WAX PAPER - Tierra Whack</v>
+        <v>abusadOra (tambores) - Yorghaki</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>abusadOra (tambores)</v>
+        <v>Ruin</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
+        <v>https://music.apple.com/us/song/ruin/6763176090</v>
       </c>
       <c r="D138" t="str">
         <v>2026-06-09</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>ANTES DE QUE SEA TARDE</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G138" t="str">
-        <v>3:11</v>
+        <v>3:19</v>
       </c>
       <c r="H138" t="str">
-        <v>Yorghaki</v>
+        <v>Blxst</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
+        <v>https://music.apple.com/us/album/ruin/1895199881</v>
       </c>
       <c r="L138" t="str">
-        <v>abusadOra (tambores) - Yorghaki</v>
+        <v>Ruin - Blxst</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Ruin</v>
+        <v>Do Today</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/ruin/6763176090</v>
+        <v>https://music.apple.com/us/song/do-today/1893402864</v>
       </c>
       <c r="D139" t="str">
         <v>2026-06-09</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Labor Of Love</v>
+        <v>Grateful</v>
       </c>
       <c r="G139" t="str">
-        <v>3:19</v>
+        <v>4:14</v>
       </c>
       <c r="H139" t="str">
-        <v>Blxst</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/ruin/1895199881</v>
+        <v>https://music.apple.com/us/album/do-today/1893402542</v>
       </c>
       <c r="L139" t="str">
-        <v>Ruin - Blxst</v>
+        <v>Do Today - The Red Clay Strays</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Do Today</v>
+        <v>Stone Over Water</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/do-today/1893402864</v>
+        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
       </c>
       <c r="D140" t="str">
         <v>2026-06-09</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Grateful</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G140" t="str">
-        <v>4:14</v>
+        <v>3:14</v>
       </c>
       <c r="H140" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/do-today/1893402542</v>
+        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
       </c>
       <c r="L140" t="str">
-        <v>Do Today - The Red Clay Strays</v>
+        <v>Stone Over Water - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Stone Over Water</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
+        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
       </c>
       <c r="D141" t="str">
         <v>2026-06-09</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>I Built You A Tower</v>
+        <v>Weezer</v>
       </c>
       <c r="G141" t="str">
-        <v>3:14</v>
+        <v>3:34</v>
       </c>
       <c r="H141" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Weezer</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/weezer/115234</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
+        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
       </c>
       <c r="L141" t="str">
-        <v>Stone Over Water - Death Cab for Cutie</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
+        <v>Tell Me When You've Had Enough</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
+        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
       </c>
       <c r="D142" t="str">
         <v>2026-06-09</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Weezer</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G142" t="str">
-        <v>3:34</v>
+        <v>3:19</v>
       </c>
       <c r="H142" t="str">
-        <v>Weezer</v>
+        <v>Evanescence</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/weezer/115234</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
+        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
       </c>
       <c r="L142" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
+        <v>Tell Me When You've Had Enough - Evanescence</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Tell Me When You've Had Enough</v>
+        <v>Your Ghost Again</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
+        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
       </c>
       <c r="D143" t="str">
         <v>2026-06-09</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Sanctuary</v>
+        <v>Your Ghost Again - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:19</v>
+        <v>4:35</v>
       </c>
       <c r="H143" t="str">
-        <v>Evanescence</v>
+        <v>Mastodon</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
+        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
       </c>
       <c r="L143" t="str">
-        <v>Tell Me When You've Had Enough - Evanescence</v>
+        <v>Your Ghost Again - Mastodon</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Your Ghost Again</v>
+        <v>Nightshift Superstar</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
+        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
       </c>
       <c r="D144" t="str">
         <v>2026-06-09</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Your Ghost Again - Single</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G144" t="str">
-        <v>4:35</v>
+        <v>4:07</v>
       </c>
       <c r="H144" t="str">
-        <v>Mastodon</v>
+        <v>Muse</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
+        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
       </c>
       <c r="L144" t="str">
-        <v>Your Ghost Again - Mastodon</v>
+        <v>Nightshift Superstar - Muse</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Nightshift Superstar</v>
+        <v>UNDER THE RHYTHM</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
+        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
       </c>
       <c r="D145" t="str">
         <v>2026-06-09</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>The Wow! Signal</v>
+        <v>ADAM</v>
       </c>
       <c r="G145" t="str">
-        <v>4:07</v>
+        <v>2:50</v>
       </c>
       <c r="H145" t="str">
-        <v>Muse</v>
+        <v>Adam Lambert</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
+        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
       </c>
       <c r="L145" t="str">
-        <v>Nightshift Superstar - Muse</v>
+        <v>UNDER THE RHYTHM - Adam Lambert</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>UNDER THE RHYTHM</v>
+        <v>You’re Mine</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
+        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
       </c>
       <c r="D146" t="str">
         <v>2026-06-09</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>ADAM</v>
+        <v>Papercut</v>
       </c>
       <c r="G146" t="str">
-        <v>2:50</v>
+        <v>4:25</v>
       </c>
       <c r="H146" t="str">
-        <v>Adam Lambert</v>
+        <v>Imani Imani</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
+        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
+        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
       </c>
       <c r="L146" t="str">
-        <v>UNDER THE RHYTHM - Adam Lambert</v>
+        <v>You’re Mine - Imani Imani</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>You’re Mine</v>
+        <v>point blank</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
+        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
       </c>
       <c r="D147" t="str">
         <v>2026-06-09</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Papercut</v>
+        <v>new avatar</v>
       </c>
       <c r="G147" t="str">
-        <v>4:25</v>
+        <v>4:26</v>
       </c>
       <c r="H147" t="str">
-        <v>Imani Imani</v>
+        <v>Kelela</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
+        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
       </c>
       <c r="L147" t="str">
-        <v>You’re Mine - Imani Imani</v>
+        <v>point blank - Kelela</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>point blank</v>
+        <v>that's my beach!</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
+        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
       </c>
       <c r="D148" t="str">
         <v>2026-06-09</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>new avatar</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G148" t="str">
-        <v>4:26</v>
+        <v>3:18</v>
       </c>
       <c r="H148" t="str">
-        <v>Kelela</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
+        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
       </c>
       <c r="L148" t="str">
-        <v>point blank - Kelela</v>
+        <v>that's my beach! - horsegiirL</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>that's my beach!</v>
+        <v>In Your Eyes</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
+        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
       </c>
       <c r="D149" t="str">
         <v>2026-06-09</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>In Your Eyes - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:18</v>
+        <v>3:36</v>
       </c>
       <c r="H149" t="str">
-        <v>horsegiirL</v>
+        <v>Alesso</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/alesso/432464201</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
+        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
       </c>
       <c r="L149" t="str">
-        <v>that's my beach! - horsegiirL</v>
+        <v>In Your Eyes - Alesso</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>In Your Eyes</v>
+        <v>ALL OR NOTHING</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
+        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
       </c>
       <c r="D150" t="str">
         <v>2026-06-09</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>In Your Eyes - Single</v>
+        <v>ALL OR NOTHING - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:36</v>
+        <v>3:17</v>
       </c>
       <c r="H150" t="str">
-        <v>Alesso</v>
+        <v>Tobe Nwigwe</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/alesso/432464201</v>
+        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
+        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
       </c>
       <c r="L150" t="str">
-        <v>In Your Eyes - Alesso</v>
+        <v>ALL OR NOTHING - Tobe Nwigwe</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>ALL OR NOTHING</v>
+        <v>IN MY HANDS</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
+        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
       </c>
       <c r="D151" t="str">
         <v>2026-06-09</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>ALL OR NOTHING - Single</v>
+        <v>IN MY HANDS - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:17</v>
+        <v>3:14</v>
       </c>
       <c r="H151" t="str">
-        <v>Tobe Nwigwe</v>
+        <v>Alessia Cara</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
+        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
+        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
       </c>
       <c r="L151" t="str">
-        <v>ALL OR NOTHING - Tobe Nwigwe</v>
+        <v>IN MY HANDS - Alessia Cara</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>IN MY HANDS</v>
+        <v>Life's a Dream</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
+        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
       </c>
       <c r="D152" t="str">
         <v>2026-06-09</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>IN MY HANDS - Single</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G152" t="str">
-        <v>3:14</v>
+        <v>5:31</v>
       </c>
       <c r="H152" t="str">
-        <v>Alessia Cara</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
+        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
       </c>
       <c r="L152" t="str">
-        <v>IN MY HANDS - Alessia Cara</v>
+        <v>Life's a Dream - Modest Mouse</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Life's a Dream</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
+        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
       </c>
       <c r="D153" t="str">
         <v>2026-06-09</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>Season of Surrender</v>
       </c>
       <c r="G153" t="str">
-        <v>5:31</v>
+        <v>4:47</v>
       </c>
       <c r="H153" t="str">
-        <v>Modest Mouse</v>
+        <v>August Burns Red</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
+        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
       </c>
       <c r="L153" t="str">
-        <v>Life's a Dream - Modest Mouse</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
+        <v>Shine</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
+        <v>https://music.apple.com/us/song/shine/6764654536</v>
       </c>
       <c r="D154" t="str">
         <v>2026-06-09</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Season of Surrender</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G154" t="str">
-        <v>4:47</v>
+        <v>2:27</v>
       </c>
       <c r="H154" t="str">
-        <v>August Burns Red</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
+        <v>https://music.apple.com/us/album/shine/1895866355</v>
       </c>
       <c r="L154" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
+        <v>Shine - Jon Batiste</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Shine</v>
+        <v>Half The Man</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/shine/6764654536</v>
+        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
       </c>
       <c r="D155" t="str">
         <v>2026-06-09</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Black Mozart</v>
+        <v>Scared of Heights</v>
       </c>
       <c r="G155" t="str">
-        <v>2:27</v>
+        <v>3:56</v>
       </c>
       <c r="H155" t="str">
-        <v>Jon Batiste</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/shine/1895866355</v>
+        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
       </c>
       <c r="L155" t="str">
-        <v>Shine - Jon Batiste</v>
+        <v>Half The Man - Wyatt Flores</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Half The Man</v>
+        <v>Preacher’s Kid</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
+        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
       </c>
       <c r="D156" t="str">
         <v>2026-06-09</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Scared of Heights</v>
+        <v>Preacher’s Kid - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:56</v>
+        <v>5:02</v>
       </c>
       <c r="H156" t="str">
-        <v>Wyatt Flores</v>
+        <v>Stephen Wilson Jr.</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
+        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
       </c>
       <c r="L156" t="str">
-        <v>Half The Man - Wyatt Flores</v>
+        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Preacher’s Kid</v>
+        <v>Weak</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
+        <v>https://music.apple.com/us/song/weak/6771151098</v>
       </c>
       <c r="D157" t="str">
         <v>2026-06-09</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Preacher’s Kid - Single</v>
+        <v>Weak - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>5:02</v>
+        <v>3:28</v>
       </c>
       <c r="H157" t="str">
-        <v>Stephen Wilson Jr.</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
+        <v>https://music.apple.com/us/album/weak/6771151088</v>
       </c>
       <c r="L157" t="str">
-        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
+        <v>Weak - Naomi Sharon</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Weak</v>
+        <v>ALL NIGHT LONG</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/weak/6771151098</v>
+        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
       </c>
       <c r="D158" t="str">
         <v>2026-06-09</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Weak - Single</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G158" t="str">
-        <v>3:28</v>
+        <v>2:28</v>
       </c>
       <c r="H158" t="str">
-        <v>Naomi Sharon</v>
+        <v>Pheelz</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/weak/6771151088</v>
+        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
       </c>
       <c r="L158" t="str">
-        <v>Weak - Naomi Sharon</v>
+        <v>ALL NIGHT LONG - Pheelz</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>ALL NIGHT LONG</v>
+        <v>Every Life</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
+        <v>https://music.apple.com/us/song/every-life/6764110978</v>
       </c>
       <c r="D159" t="str">
         <v>2026-06-09</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>A Rii Set</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G159" t="str">
-        <v>2:28</v>
+        <v>3:18</v>
       </c>
       <c r="H159" t="str">
-        <v>Pheelz</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
+        <v>https://music.apple.com/us/album/every-life/1895644574</v>
       </c>
       <c r="L159" t="str">
-        <v>ALL NIGHT LONG - Pheelz</v>
+        <v>Every Life - Isabel LaRosa</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Every Life</v>
+        <v>Home</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/every-life/6764110978</v>
+        <v>https://music.apple.com/us/song/home/6774718029</v>
       </c>
       <c r="D160" t="str">
         <v>2026-06-09</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>Good Grief</v>
       </c>
       <c r="G160" t="str">
-        <v>3:18</v>
+        <v>4:53</v>
       </c>
       <c r="H160" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Sara Bareilles</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/every-life/1895644574</v>
+        <v>https://music.apple.com/us/album/home/6774718027</v>
       </c>
       <c r="L160" t="str">
-        <v>Every Life - Isabel LaRosa</v>
+        <v>Home - Sara Bareilles</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Home</v>
+        <v>Satalanaaa</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/home/6774718029</v>
+        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
       </c>
       <c r="D161" t="str">
         <v>2026-06-09</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Good Grief</v>
+        <v>Satalanaaa - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>4:53</v>
+        <v>2:06</v>
       </c>
       <c r="H161" t="str">
-        <v>Sara Bareilles</v>
+        <v>Pitbull</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/home/6774718027</v>
+        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
       </c>
       <c r="L161" t="str">
-        <v>Home - Sara Bareilles</v>
+        <v>Satalanaaa - Pitbull</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Satalanaaa</v>
+        <v>Miss Me More</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
+        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
       </c>
       <c r="D162" t="str">
         <v>2026-06-09</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Satalanaaa - Single</v>
+        <v>Confessions of a Lonely Heart</v>
       </c>
       <c r="G162" t="str">
-        <v>2:06</v>
+        <v>2:43</v>
       </c>
       <c r="H162" t="str">
-        <v>Pitbull</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
+        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
       </c>
       <c r="L162" t="str">
-        <v>Satalanaaa - Pitbull</v>
+        <v>Miss Me More - Eric Nam</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Miss Me More</v>
+        <v>Rituals</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
+        <v>https://music.apple.com/us/song/rituals/6769628916</v>
       </c>
       <c r="D163" t="str">
         <v>2026-06-09</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Confessions of a Lonely Heart</v>
+        <v>Rituals - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:43</v>
+        <v>2:10</v>
       </c>
       <c r="H163" t="str">
-        <v>Eric Nam</v>
+        <v>Rico Nasty</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
+        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
+        <v>https://music.apple.com/us/album/rituals/6769628915</v>
       </c>
       <c r="L163" t="str">
-        <v>Miss Me More - Eric Nam</v>
+        <v>Rituals - Rico Nasty</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Rituals</v>
+        <v>Honeysuckle</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/rituals/6769628916</v>
+        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
       </c>
       <c r="D164" t="str">
         <v>2026-06-09</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Rituals - Single</v>
+        <v>Honeysuckle - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:10</v>
+        <v>3:15</v>
       </c>
       <c r="H164" t="str">
-        <v>Rico Nasty</v>
+        <v>Dylan Gossett</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
+        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/rituals/6769628915</v>
+        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
       </c>
       <c r="L164" t="str">
-        <v>Rituals - Rico Nasty</v>
+        <v>Honeysuckle - Dylan Gossett</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Honeysuckle</v>
+        <v>listen…</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
+        <v>https://music.apple.com/us/song/listen/6775576508</v>
       </c>
       <c r="D165" t="str">
         <v>2026-06-09</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Honeysuckle - Single</v>
+        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G165" t="str">
-        <v>3:15</v>
+        <v>4:08</v>
       </c>
       <c r="H165" t="str">
-        <v>Dylan Gossett</v>
+        <v>John Williams</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
+        <v>https://music.apple.com/us/artist/john-williams/63748</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
+        <v>https://music.apple.com/us/album/listen/6775576506</v>
       </c>
       <c r="L165" t="str">
-        <v>Honeysuckle - Dylan Gossett</v>
+        <v>listen… - John Williams</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>listen…</v>
+        <v>DEADMEAT</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/listen/6775576508</v>
+        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
       </c>
       <c r="D166" t="str">
         <v>2026-06-09</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
+        <v>DEADMEAT - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>4:08</v>
+        <v>2:52</v>
       </c>
       <c r="H166" t="str">
-        <v>John Williams</v>
+        <v>South Arcade</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/john-williams/63748</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/listen/6775576506</v>
+        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
       </c>
       <c r="L166" t="str">
-        <v>listen… - John Williams</v>
+        <v>DEADMEAT - South Arcade</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>DEADMEAT</v>
+        <v>Ugly and Rotten</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
+        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
       </c>
       <c r="D167" t="str">
         <v>2026-06-09</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>DEADMEAT - Single</v>
+        <v>Ugly and Rotten - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:52</v>
+        <v>2:49</v>
       </c>
       <c r="H167" t="str">
-        <v>South Arcade</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
+        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
       </c>
       <c r="L167" t="str">
-        <v>DEADMEAT - South Arcade</v>
+        <v>Ugly and Rotten - Mckenna Grace</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Ugly and Rotten</v>
+        <v>Whisper</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
+        <v>https://music.apple.com/us/song/whisper/6772254272</v>
       </c>
       <c r="D168" t="str">
         <v>2026-06-09</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Ugly and Rotten - Single</v>
+        <v>Whisper - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:49</v>
+        <v>2:47</v>
       </c>
       <c r="H168" t="str">
-        <v>Mckenna Grace</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
+        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
+        <v>https://music.apple.com/us/album/whisper/6772254268</v>
       </c>
       <c r="L168" t="str">
-        <v>Ugly and Rotten - Mckenna Grace</v>
+        <v>Whisper - Blu DeTiger</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Whisper</v>
+        <v>Gecko (feat. Haley Bridge)</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/whisper/6772254272</v>
+        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
       </c>
       <c r="D169" t="str">
         <v>2026-06-09</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Whisper - Single</v>
+        <v>How dare you tryna love me? - EP</v>
       </c>
       <c r="G169" t="str">
-        <v>2:47</v>
+        <v>2:46</v>
       </c>
       <c r="H169" t="str">
-        <v>Blu DeTiger</v>
+        <v>Olga Myko</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
+        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/whisper/6772254268</v>
+        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
       </c>
       <c r="L169" t="str">
-        <v>Whisper - Blu DeTiger</v>
+        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Gecko (feat. Haley Bridge)</v>
+        <v>Compa Primo</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
+        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
       </c>
       <c r="D170" t="str">
         <v>2026-06-09</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>How dare you tryna love me? - EP</v>
+        <v>Compa Primo - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>2:46</v>
+        <v>3:12</v>
       </c>
       <c r="H170" t="str">
-        <v>Olga Myko</v>
+        <v>Nueva H</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
+        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
+        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
       </c>
       <c r="L170" t="str">
-        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
+        <v>Compa Primo - Nueva H</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Compa Primo</v>
+        <v>Parachute</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
+        <v>https://music.apple.com/us/song/parachute/6768841410</v>
       </c>
       <c r="D171" t="str">
         <v>2026-06-09</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Compa Primo - Single</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:12</v>
+        <v>3:11</v>
       </c>
       <c r="H171" t="str">
-        <v>Nueva H</v>
+        <v>Tyler James Bellinger</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
+        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
+        <v>https://music.apple.com/us/album/parachute/6768841409</v>
       </c>
       <c r="L171" t="str">
-        <v>Compa Primo - Nueva H</v>
+        <v>Parachute - Tyler James Bellinger</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Parachute</v>
+        <v>Like a Bubble</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/parachute/6768841410</v>
+        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
       </c>
       <c r="D172" t="str">
         <v>2026-06-09</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Parachute - Single</v>
+        <v>Imperfect-I'mperfect - EP</v>
       </c>
       <c r="G172" t="str">
-        <v>3:11</v>
+        <v>3:08</v>
       </c>
       <c r="H172" t="str">
-        <v>Tyler James Bellinger</v>
+        <v>FIFTY FIFTY</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
+        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/parachute/6768841409</v>
+        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
       </c>
       <c r="L172" t="str">
-        <v>Parachute - Tyler James Bellinger</v>
+        <v>Like a Bubble - FIFTY FIFTY</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Like a Bubble</v>
+        <v>Hustle and Opulence in America</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
+        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
       </c>
       <c r="D173" t="str">
         <v>2026-06-09</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Imperfect-I'mperfect - EP</v>
+        <v>AK Cuts: Vol. 4 - EP</v>
       </c>
       <c r="G173" t="str">
-        <v>3:08</v>
+        <v>3:07</v>
       </c>
       <c r="H173" t="str">
-        <v>FIFTY FIFTY</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
+        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
       </c>
       <c r="L173" t="str">
-        <v>Like a Bubble - FIFTY FIFTY</v>
+        <v>Hustle and Opulence in America - Anish Kumar</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Hustle and Opulence in America</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
+        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
       </c>
       <c r="D174" t="str">
         <v>2026-06-09</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>AK Cuts: Vol. 4 - EP</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:07</v>
+        <v>2:47</v>
       </c>
       <c r="H174" t="str">
-        <v>Anish Kumar</v>
+        <v>ivri</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
+        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
       </c>
       <c r="L174" t="str">
-        <v>Hustle and Opulence in America - Anish Kumar</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
+        <v>CLEAN SWEEP</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
+        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
       </c>
       <c r="D175" t="str">
         <v>2026-06-09</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
+        <v>CLEAN SWEEP - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:47</v>
+        <v>3:11</v>
       </c>
       <c r="H175" t="str">
-        <v>ivri</v>
+        <v>Storm Reid</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
+        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
+        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
       </c>
       <c r="L175" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
+        <v>CLEAN SWEEP - Storm Reid</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>CLEAN SWEEP</v>
+        <v>CANDYLAND!</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
+        <v>https://music.apple.com/us/song/candyland/6766927008</v>
       </c>
       <c r="D176" t="str">
         <v>2026-06-09</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>CLEAN SWEEP - Single</v>
+        <v>CANDYLAND! - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:11</v>
+        <v>3:15</v>
       </c>
       <c r="H176" t="str">
-        <v>Storm Reid</v>
+        <v>Natanya</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
+        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
+        <v>https://music.apple.com/us/album/candyland/6766927000</v>
       </c>
       <c r="L176" t="str">
-        <v>CLEAN SWEEP - Storm Reid</v>
+        <v>CANDYLAND! - Natanya</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>CANDYLAND!</v>
+        <v>Double C</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/candyland/6766927008</v>
+        <v>https://music.apple.com/us/song/double-c/6771836555</v>
       </c>
       <c r="D177" t="str">
         <v>2026-06-09</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>CANDYLAND! - Single</v>
+        <v>Double C - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:15</v>
+        <v>2:21</v>
       </c>
       <c r="H177" t="str">
-        <v>Natanya</v>
+        <v>Sk8star</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
+        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/candyland/6766927000</v>
+        <v>https://music.apple.com/us/album/double-c/6771836554</v>
       </c>
       <c r="L177" t="str">
-        <v>CANDYLAND! - Natanya</v>
+        <v>Double C - Sk8star</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Double C</v>
+        <v>madera</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/double-c/6771836555</v>
+        <v>https://music.apple.com/us/song/madera/6764638112</v>
       </c>
       <c r="D178" t="str">
         <v>2026-06-09</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Double C - Single</v>
+        <v>madera/un camino luminoso - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:21</v>
+        <v>5:41</v>
       </c>
       <c r="H178" t="str">
-        <v>Sk8star</v>
+        <v>Lumtz</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
+        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/double-c/6771836554</v>
+        <v>https://music.apple.com/us/album/madera/6764638109</v>
       </c>
       <c r="L178" t="str">
-        <v>Double C - Sk8star</v>
+        <v>madera - Lumtz</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>madera</v>
+        <v>Slip the Noose</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/madera/6764638112</v>
+        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
       </c>
       <c r="D179" t="str">
         <v>2026-06-09</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>madera/un camino luminoso - Single</v>
+        <v>Hum of Hurt</v>
       </c>
       <c r="G179" t="str">
-        <v>5:41</v>
+        <v>1:43</v>
       </c>
       <c r="H179" t="str">
-        <v>Lumtz</v>
+        <v>Converge</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/madera/6764638109</v>
+        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
       </c>
       <c r="L179" t="str">
-        <v>madera - Lumtz</v>
+        <v>Slip the Noose - Converge</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Slip the Noose</v>
+        <v>Crying Fire</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
+        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
       </c>
       <c r="D180" t="str">
         <v>2026-06-09</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Hum of Hurt</v>
+        <v>Crying Fire - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>1:43</v>
+        <v>4:08</v>
       </c>
       <c r="H180" t="str">
-        <v>Converge</v>
+        <v>Avatar</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/avatar/187616241</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
+        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
       </c>
       <c r="L180" t="str">
-        <v>Slip the Noose - Converge</v>
+        <v>Crying Fire - Avatar</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Crying Fire</v>
+        <v>NI NA’</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
+        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
       </c>
       <c r="D181" t="str">
         <v>2026-06-09</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Crying Fire - Single</v>
+        <v>sorry si soy GRRRIS</v>
       </c>
       <c r="G181" t="str">
-        <v>4:08</v>
+        <v>2:53</v>
       </c>
       <c r="H181" t="str">
-        <v>Avatar</v>
+        <v>ROBI</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/avatar/187616241</v>
+        <v>https://music.apple.com/us/artist/robi/1458047972</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
+        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
       </c>
       <c r="L181" t="str">
-        <v>Crying Fire - Avatar</v>
+        <v>NI NA’ - ROBI</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>NI NA’</v>
+        <v>Holding Back</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
+        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
       </c>
       <c r="D182" t="str">
         <v>2026-06-09</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>sorry si soy GRRRIS</v>
+        <v>AMA</v>
       </c>
       <c r="G182" t="str">
-        <v>2:53</v>
+        <v>3:19</v>
       </c>
       <c r="H182" t="str">
-        <v>ROBI</v>
+        <v>Ama</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/robi/1458047972</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
+        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
       </c>
       <c r="L182" t="str">
-        <v>NI NA’ - ROBI</v>
+        <v>Holding Back - Ama</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Holding Back</v>
+        <v>you're still mine</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
+        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
       </c>
       <c r="D183" t="str">
         <v>2026-06-09</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>AMA</v>
+        <v>you're still mine - Single</v>
       </c>
       <c r="G183" t="str">
         <v>3:19</v>
       </c>
       <c r="H183" t="str">
-        <v>Ama</v>
+        <v>Lexi Jayde</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
+        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
       </c>
       <c r="L183" t="str">
-        <v>Holding Back - Ama</v>
+        <v>you're still mine - Lexi Jayde</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>you're still mine</v>
+        <v>teksi</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
+        <v>https://music.apple.com/us/song/teksi/6769899742</v>
       </c>
       <c r="D184" t="str">
         <v>2026-06-09</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>you're still mine - Single</v>
+        <v>pOCHO</v>
       </c>
       <c r="G184" t="str">
-        <v>3:19</v>
+        <v>2:48</v>
       </c>
       <c r="H184" t="str">
-        <v>Lexi Jayde</v>
+        <v>8onthebeat</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
+        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
+        <v>https://music.apple.com/us/album/teksi/6769899739</v>
       </c>
       <c r="L184" t="str">
-        <v>you're still mine - Lexi Jayde</v>
+        <v>teksi - 8onthebeat</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>teksi</v>
+        <v>Let You Go</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/teksi/6769899742</v>
+        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
       </c>
       <c r="D185" t="str">
         <v>2026-06-09</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>pOCHO</v>
+        <v>Let You Go - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:48</v>
+        <v>1:37</v>
       </c>
       <c r="H185" t="str">
-        <v>8onthebeat</v>
+        <v>Nate Sib</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
+        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/teksi/6769899739</v>
+        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
       </c>
       <c r="L185" t="str">
-        <v>teksi - 8onthebeat</v>
+        <v>Let You Go - Nate Sib</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Let You Go</v>
+        <v>Dis-Moi</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
+        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
       </c>
       <c r="D186" t="str">
         <v>2026-06-09</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Let You Go - Single</v>
+        <v>CINNA</v>
       </c>
       <c r="G186" t="str">
-        <v>1:37</v>
+        <v>2:27</v>
       </c>
       <c r="H186" t="str">
-        <v>Nate Sib</v>
+        <v>Cannelle</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
+        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
+        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
       </c>
       <c r="L186" t="str">
-        <v>Let You Go - Nate Sib</v>
+        <v>Dis-Moi - Cannelle</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Dis-Moi</v>
+        <v>Leverage</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
+        <v>https://music.apple.com/us/song/leverage/6776432312</v>
       </c>
       <c r="D187" t="str">
         <v>2026-06-09</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>CINNA</v>
+        <v>Heaven on Mars</v>
       </c>
       <c r="G187" t="str">
-        <v>2:27</v>
+        <v>3:04</v>
       </c>
       <c r="H187" t="str">
-        <v>Cannelle</v>
+        <v>NoCap</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
+        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
+        <v>https://music.apple.com/us/album/leverage/6776432217</v>
       </c>
       <c r="L187" t="str">
-        <v>Dis-Moi - Cannelle</v>
+        <v>Leverage - NoCap</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Leverage</v>
+        <v>Kool Aid</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/leverage/6776432312</v>
+        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
       </c>
       <c r="D188" t="str">
         <v>2026-06-09</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Heaven on Mars</v>
+        <v>Where Have All The Good Men Gone? - EP</v>
       </c>
       <c r="G188" t="str">
-        <v>3:04</v>
+        <v>3:40</v>
       </c>
       <c r="H188" t="str">
-        <v>NoCap</v>
+        <v>Debbii Dawson</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
+        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/leverage/6776432217</v>
+        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
       </c>
       <c r="L188" t="str">
-        <v>Leverage - NoCap</v>
+        <v>Kool Aid - Debbii Dawson</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Kool Aid</v>
+        <v>Pieces</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
+        <v>https://music.apple.com/us/song/pieces/6771861156</v>
       </c>
       <c r="D189" t="str">
         <v>2026-06-09</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Where Have All The Good Men Gone? - EP</v>
+        <v>Pieces - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:40</v>
+        <v>2:19</v>
       </c>
       <c r="H189" t="str">
-        <v>Debbii Dawson</v>
+        <v>Dom Innarella</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
+        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
+        <v>https://music.apple.com/us/album/pieces/6771861155</v>
       </c>
       <c r="L189" t="str">
-        <v>Kool Aid - Debbii Dawson</v>
+        <v>Pieces - Dom Innarella</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Pieces</v>
+        <v>Mesmerized</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/pieces/6771861156</v>
+        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
       </c>
       <c r="D190" t="str">
         <v>2026-06-09</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Pieces - Single</v>
+        <v>Mesmerized - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:19</v>
+        <v>2:38</v>
       </c>
       <c r="H190" t="str">
-        <v>Dom Innarella</v>
+        <v>The Aces</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
+        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/pieces/6771861155</v>
+        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
       </c>
       <c r="L190" t="str">
-        <v>Pieces - Dom Innarella</v>
+        <v>Mesmerized - The Aces</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Mesmerized</v>
+        <v>Perfect 10</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
+        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
       </c>
       <c r="D191" t="str">
         <v>2026-06-09</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Mesmerized - Single</v>
+        <v>No Hard Feelings (Deluxe)</v>
       </c>
       <c r="G191" t="str">
-        <v>2:38</v>
+        <v>2:51</v>
       </c>
       <c r="H191" t="str">
-        <v>The Aces</v>
+        <v>The Beaches</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
+        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
+        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
       </c>
       <c r="L191" t="str">
-        <v>Mesmerized - The Aces</v>
+        <v>Perfect 10 - The Beaches</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Perfect 10</v>
+        <v>Recognize</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
+        <v>https://music.apple.com/us/song/recognize/6769164705</v>
       </c>
       <c r="D192" t="str">
         <v>2026-06-09</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>No Hard Feelings (Deluxe)</v>
+        <v>Recognize - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:51</v>
+        <v>2:05</v>
       </c>
       <c r="H192" t="str">
-        <v>The Beaches</v>
+        <v>Fana Hues</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
+        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
+        <v>https://music.apple.com/us/album/recognize/6769164704</v>
       </c>
       <c r="L192" t="str">
-        <v>Perfect 10 - The Beaches</v>
+        <v>Recognize - Fana Hues</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Recognize</v>
+        <v>Feel The Vibe</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/recognize/6769164705</v>
+        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
       </c>
       <c r="D193" t="str">
         <v>2026-06-09</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Recognize - Single</v>
+        <v>Feel The Vibe</v>
       </c>
       <c r="G193" t="str">
-        <v>2:05</v>
+        <v>3:28</v>
       </c>
       <c r="H193" t="str">
-        <v>Fana Hues</v>
+        <v>Above &amp; Beyond</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
+        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/recognize/6769164704</v>
+        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
       </c>
       <c r="L193" t="str">
-        <v>Recognize - Fana Hues</v>
+        <v>Feel The Vibe - Above &amp; Beyond</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Feel The Vibe</v>
+        <v>I Never Knew</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
+        <v>https://music.apple.com/us/song/i-never-knew/6764351468</v>
       </c>
       <c r="D194" t="str">
         <v>2026-06-09</v>
@@ -7747,68 +7747,30 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Feel The Vibe</v>
+        <v>I Never Knew - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:28</v>
+        <v>3:51</v>
       </c>
       <c r="H194" t="str">
-        <v>Above &amp; Beyond</v>
+        <v>Adam Ten</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
+        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
+        <v>https://music.apple.com/us/album/i-never-knew/1895744479</v>
       </c>
       <c r="L194" t="str">
-        <v>Feel The Vibe - Above &amp; Beyond</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v>I Never Knew</v>
-      </c>
-      <c r="B195" t="str">
-        <v/>
-      </c>
-      <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/i-never-knew/6764351468</v>
-      </c>
-      <c r="D195" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E195" t="str">
-        <v/>
-      </c>
-      <c r="F195" t="str">
-        <v>I Never Knew - Single</v>
-      </c>
-      <c r="G195" t="str">
-        <v>3:51</v>
-      </c>
-      <c r="H195" t="str">
-        <v>Adam Ten</v>
-      </c>
-      <c r="I195" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
-      </c>
-      <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/i-never-knew/1895744479</v>
-      </c>
-      <c r="L195" t="str">
         <v>I Never Knew - Adam Ten</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L195"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L194"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-06-week02/titles.xlsx
+++ b/data/global/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L194"/>
+  <dimension ref="A1:L195"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
+        <v>עדן בן זקן וששון איפרם שאולוב מחול</v>
       </c>
       <c r="B2" t="str">
-        <v>23h ago</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
+        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%91%d7%9f-%d7%96%d7%a7%d7%9f-%d7%95%d7%a9%d7%a9%d7%95%d7%9f-%d7%90%d7%99%d7%a4%d7%a8%d7%9d-%d7%a9%d7%90%d7%95%d7%9c%d7%95%d7%91-%d7%9e%d7%97%d7%95%d7%9c/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-09</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>23h ago</v>
+        <v>הדואט "מחול" של עדן בן זקן וששון איפרם שאולוב מספק הצצה  למנגנון התעשייתי המשומן של המוזיקה הים-תיכונית העכשווית, ומציג את מה שניתן לכנות "נוסחת הזהב" של הפופ המקומי: טקסט פשטני, מנגינה מלנכולית ושירה מלודרמטית. הטקסט של השיר פונה למכנה המשותף</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>עדן בן זקן וששון איפרם שאולוב מחול</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B3" t="str">
-        <v>23h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
+        <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-09</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B4" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
+        <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-09</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>23h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
+        <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
       </c>
       <c r="D5" t="str">
         <v>2026-06-09</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>23h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B6" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
+        <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
       </c>
       <c r="D6" t="str">
         <v>2026-06-09</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video)</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B7" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
+        <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-09</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Capital FM</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Reba McEntire - You Never Gave Up On Me</v>
+        <v>DEEP PURPLE - DIABLO (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
+        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
       </c>
       <c r="D8" t="str">
         <v>2026-06-09</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Reba McEntire</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Reba McEntire - You Never Gave Up On Me - Reba McEntire</v>
+        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>elijah woods - Wonder (Official Lyric Video)</v>
+        <v>Reba McEntire - You Never Gave Up On Me</v>
       </c>
       <c r="B9" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
+        <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-09</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>elijah woods</v>
+        <v>Reba McEntire</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>elijah woods - Wonder (Official Lyric Video) - elijah woods</v>
+        <v>Reba McEntire - You Never Gave Up On Me - Reba McEntire</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>elijah woods - Wonder (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
+        <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
       </c>
       <c r="D10" t="str">
         <v>2026-06-09</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Capital FM and XG</v>
+        <v>elijah woods</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
+        <v>elijah woods - Wonder (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B11" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
+        <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
       </c>
       <c r="D11" t="str">
         <v>2026-06-09</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B12" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
+        <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
       </c>
       <c r="D12" t="str">
         <v>2026-06-09</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B13" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
+        <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
       </c>
       <c r="D13" t="str">
         <v>2026-06-09</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B14" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
+        <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
       </c>
       <c r="D14" t="str">
         <v>2026-06-09</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B15" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
+        <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
       </c>
       <c r="D15" t="str">
         <v>2026-06-09</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B16" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
+        <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
       </c>
       <c r="D16" t="str">
         <v>2026-06-09</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B17" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
+        <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
       </c>
       <c r="D17" t="str">
         <v>2026-06-09</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B18" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
+        <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
       </c>
       <c r="D18" t="str">
         <v>2026-06-09</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Capital FM and XG</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B19" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
+        <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
       </c>
       <c r="D19" t="str">
         <v>2026-06-09</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B20" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
+        <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
       </c>
       <c r="D20" t="str">
         <v>2026-06-09</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B21" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
+        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
       </c>
       <c r="D21" t="str">
         <v>2026-06-09</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B22" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
+        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
       </c>
       <c r="D22" t="str">
         <v>2026-06-09</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B23" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
+        <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
       </c>
       <c r="D23" t="str">
         <v>2026-06-09</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Capital FM and Take That</v>
+        <v>Capital FM</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
+        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B24" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
+        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
       </c>
       <c r="D24" t="str">
         <v>2026-06-09</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
+        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
       </c>
       <c r="D25" t="str">
         <v>2026-06-09</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Capital FM and Take That</v>
+        <v>Capital FM</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B26" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
+        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
       </c>
       <c r="D26" t="str">
         <v>2026-06-09</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
+        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
       </c>
       <c r="D27" t="str">
         <v>2026-06-09</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
+        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B28" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
+        <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
       </c>
       <c r="D28" t="str">
         <v>2026-06-09</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Capital FM and Take That</v>
+        <v>Capital FM</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
+        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B29" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
+        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
       </c>
       <c r="D29" t="str">
         <v>2026-06-09</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
+        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
       </c>
       <c r="D30" t="str">
         <v>2026-06-09</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B31" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
+        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
       </c>
       <c r="D31" t="str">
         <v>2026-06-09</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B32" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
+        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
       </c>
       <c r="D32" t="str">
         <v>2026-06-09</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
+        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B33" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
+        <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
       </c>
       <c r="D33" t="str">
         <v>2026-06-09</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B34" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
+        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
       </c>
       <c r="D34" t="str">
         <v>2026-06-09</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B35" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
+        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
       </c>
       <c r="D35" t="str">
         <v>2026-06-09</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
+        <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
       </c>
       <c r="D36" t="str">
         <v>2026-06-09</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B37" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
+        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
       </c>
       <c r="D37" t="str">
         <v>2026-06-09</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
+        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
       </c>
       <c r="D38" t="str">
         <v>2026-06-09</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B39" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
+        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
       </c>
       <c r="D39" t="str">
         <v>2026-06-09</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B40" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
+        <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
       </c>
       <c r="D40" t="str">
         <v>2026-06-09</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
+        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
       </c>
       <c r="D41" t="str">
         <v>2026-06-09</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B42" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
+        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
       </c>
       <c r="D42" t="str">
         <v>2026-06-09</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
+        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
       </c>
       <c r="D43" t="str">
         <v>2026-06-09</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B44" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
+        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
       </c>
       <c r="D44" t="str">
         <v>2026-06-09</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
+        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B45" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
+        <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
       </c>
       <c r="D45" t="str">
         <v>2026-06-09</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>3d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Capital FM</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
       </c>
       <c r="B46" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
+        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
       </c>
       <c r="D46" t="str">
         <v>2026-06-09</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>TheCranberriesTV</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
       </c>
       <c r="B47" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
+        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
       </c>
       <c r="D47" t="str">
         <v>2026-06-09</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Jordana Bryant</v>
+        <v>TheCranberriesTV</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
+        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
       </c>
       <c r="D48" t="str">
         <v>2026-06-09</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Grace Enger</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
+        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
       </c>
       <c r="D49" t="str">
         <v>2026-06-09</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>The Offspring</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Lola Young – From Down Here (From The Pool)</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B50" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
+        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
       </c>
       <c r="D50" t="str">
         <v>2026-06-09</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Lola Young</v>
+        <v>The Offspring</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>CAIN - Living Water (Music Video)</v>
+        <v>Lola Young – From Down Here (From The Pool)</v>
       </c>
       <c r="B51" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
+        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
       </c>
       <c r="D51" t="str">
         <v>2026-06-09</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>CAIN</v>
+        <v>Lola Young</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>CAIN - Living Water (Music Video) - CAIN</v>
+        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
+        <v>CAIN - Living Water (Music Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
+        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
       </c>
       <c r="D52" t="str">
         <v>2026-06-09</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Eric Clapton</v>
+        <v>CAIN</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
+        <v>CAIN - Living Water (Music Video) - CAIN</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video)</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
+        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
       </c>
       <c r="D53" t="str">
         <v>2026-06-09</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Blu DeTiger</v>
+        <v>Eric Clapton</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
+        <v>Blu DeTiger - Whisper (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
+        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
       </c>
       <c r="D54" t="str">
         <v>2026-06-09</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
+        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
       </c>
       <c r="D55" t="str">
         <v>2026-06-09</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Pink Floyd</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Holly Humberstone - it’s just White Noise</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
       </c>
       <c r="B56" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
+        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
       </c>
       <c r="D56" t="str">
         <v>2026-06-09</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Holly Humberstone</v>
+        <v>Pink Floyd</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
+        <v>Holly Humberstone - it’s just White Noise</v>
       </c>
       <c r="B57" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
+        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
       </c>
       <c r="D57" t="str">
         <v>2026-06-09</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Freya Ridings</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
+        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
+        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
       </c>
       <c r="D58" t="str">
         <v>2026-06-09</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Muse</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
+        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
       </c>
       <c r="D59" t="str">
         <v>2026-06-09</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Ellie Goulding</v>
+        <v>Muse</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer)</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
       </c>
       <c r="B60" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
+        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
       </c>
       <c r="D60" t="str">
         <v>2026-06-09</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Evanescence</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
+        <v>Evanescence - Sanctuary (Official Visualizer)</v>
       </c>
       <c r="B61" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
+        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
       </c>
       <c r="D61" t="str">
         <v>2026-06-09</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>The Beaches</v>
+        <v>Evanescence</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
+        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Bella White - Stuff (Official Music Video)</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
+        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
       </c>
       <c r="D62" t="str">
         <v>2026-06-09</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Bella White</v>
+        <v>The Beaches</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer)</v>
+        <v>Bella White - Stuff (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
+        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
       </c>
       <c r="D63" t="str">
         <v>2026-06-09</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Meduza and 2 more</v>
+        <v>Bella White</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
+        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>CAIN - Living Water (Lyric Video)</v>
+        <v>Meduza, Rani - Silence (Official Visualizer)</v>
       </c>
       <c r="B64" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
+        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
       </c>
       <c r="D64" t="str">
         <v>2026-06-09</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>CAIN</v>
+        <v>Meduza and 2 more</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
+        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
+        <v>CAIN - Living Water (Lyric Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
+        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
       </c>
       <c r="D65" t="str">
         <v>2026-06-09</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Fitz and the Tantrums</v>
+        <v>CAIN</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
+        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video)</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
+        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
       </c>
       <c r="D66" t="str">
         <v>2026-06-09</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Jeremy Camp</v>
+        <v>Fitz and the Tantrums</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
+        <v>Jeremy Camp - Reflector (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
+        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
       </c>
       <c r="D67" t="str">
         <v>2026-06-09</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Alesso</v>
+        <v>Jeremy Camp</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
+        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
       </c>
       <c r="B68" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
+        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
       </c>
       <c r="D68" t="str">
         <v>2026-06-09</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Malcolm Todd</v>
+        <v>Alesso</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer)</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
+        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
       </c>
       <c r="D69" t="str">
         <v>2026-06-09</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video)</v>
+        <v>Isabel LaRosa - Every Life (Visualizer)</v>
       </c>
       <c r="B70" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
+        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
       </c>
       <c r="D70" t="str">
         <v>2026-06-09</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Wyatt Flores</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video) - Wyatt Flores</v>
+        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
+        <v>Wyatt Flores - Half The Man (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
+        <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
       </c>
       <c r="D71" t="str">
         <v>2026-06-09</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Mckenna Grace</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video) - Mckenna Grace</v>
+        <v>Wyatt Flores - Half The Man (Official Music Video) - Wyatt Flores</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
+        <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
       </c>
       <c r="D72" t="str">
         <v>2026-06-09</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Robert Grace</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>Mckenna Grace - Ugly and Rotten (Official Music Video) - Mckenna Grace</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Boyzone - No Matter What (Live)</v>
+        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B73" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
+        <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
       </c>
       <c r="D73" t="str">
         <v>2026-06-09</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Boyzone</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Boyzone - No Matter What (Live) - Boyzone</v>
+        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Florrie - The Times (Official Video)</v>
+        <v>Boyzone - No Matter What (Live)</v>
       </c>
       <c r="B74" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
+        <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
       </c>
       <c r="D74" t="str">
         <v>2026-06-09</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>florriemusic</v>
+        <v>Boyzone</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Florrie - The Times (Official Video) - florriemusic</v>
+        <v>Boyzone - No Matter What (Live) - Boyzone</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer)</v>
+        <v>Florrie - The Times (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
+        <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
       </c>
       <c r="D75" t="str">
         <v>2026-06-09</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Madonna</v>
+        <v>florriemusic</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer) - Madonna</v>
+        <v>Florrie - The Times (Official Video) - florriemusic</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DMA'S - Hurracane (Official Video)</v>
+        <v>Madonna - Love Sensation (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
-        <v>5d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
+        <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
       </c>
       <c r="D76" t="str">
         <v>2026-06-09</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>5d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>DMA'S</v>
+        <v>Madonna</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>DMA'S - Hurracane (Official Video) - DMA'S</v>
+        <v>Madonna - Love Sensation (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
+        <v>DMA'S - Hurracane (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
+        <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
       </c>
       <c r="D77" t="str">
         <v>2026-06-09</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Lainey Wilson and John Mayer</v>
+        <v>DMA'S</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio) - Lainey Wilson and John Mayer</v>
+        <v>DMA'S - Hurracane (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
+        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
       </c>
       <c r="B78" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
+        <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
       </c>
       <c r="D78" t="str">
         <v>2026-06-09</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>ROLE MODEL</v>
+        <v>Lainey Wilson and John Mayer</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video) - ROLE MODEL</v>
+        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio) - Lainey Wilson and John Mayer</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York)</v>
+        <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
+        <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
       </c>
       <c r="D79" t="str">
         <v>2026-06-09</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Shawn Mendes</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York) - Shawn Mendes</v>
+        <v>ROLE MODEL - High Hopes 3000 (Official Music Video) - ROLE MODEL</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
+        <v>Shawn Mendes - Treat You Better (Live from New York)</v>
       </c>
       <c r="B80" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
+        <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
       </c>
       <c r="D80" t="str">
         <v>2026-06-09</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Shawn Mendes</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video) - SIENNA SPIRO</v>
+        <v>Shawn Mendes - Treat You Better (Live from New York) - Shawn Mendes</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
+        <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
+        <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
       </c>
       <c r="D81" t="str">
         <v>2026-06-09</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>SIENNA SPIRO - The Visitor (Official Music Video) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video)</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
       </c>
       <c r="B82" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
+        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
       </c>
       <c r="D82" t="str">
         <v>2026-06-09</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Europe</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
+        <v>Europe - The Cult of Ignorance (Official Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
+        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
       </c>
       <c r="D83" t="str">
         <v>2026-06-09</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Air Supply</v>
+        <v>Europe</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
+        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
+        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
       </c>
       <c r="D84" t="str">
         <v>2026-06-09</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Julia Cole Music</v>
+        <v>Air Supply</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
+        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
       </c>
       <c r="D85" t="str">
         <v>2026-06-09</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Allen Stone and Placeholder Sessions</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
       </c>
       <c r="B86" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
+        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
       </c>
       <c r="D86" t="str">
         <v>2026-06-09</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Morgan Wallen</v>
+        <v>Allen Stone and Placeholder Sessions</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
       </c>
       <c r="B87" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
+        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
       </c>
       <c r="D87" t="str">
         <v>2026-06-09</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Billy Idol</v>
+        <v>Morgan Wallen</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>10d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
+        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
       </c>
       <c r="D88" t="str">
         <v>2026-06-09</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>10d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Billy Idol</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
       </c>
       <c r="B89" t="str">
-        <v>6d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
+        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
       </c>
       <c r="D89" t="str">
         <v>2026-06-09</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>6d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Icona Pop</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Hippo Campus - South</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>7d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
+        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
       </c>
       <c r="D90" t="str">
         <v>2026-06-09</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>7d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Hippo Campus</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Hippo Campus - South - Hippo Campus</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>elijah woods - Old (Treehouse Sessions)</v>
+        <v>Hippo Campus - South</v>
       </c>
       <c r="B91" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
+        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
       </c>
       <c r="D91" t="str">
         <v>2026-06-09</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>elijah woods</v>
+        <v>Hippo Campus</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
+        <v>Hippo Campus - South - Hippo Campus</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video)</v>
+        <v>elijah woods - Old (Treehouse Sessions)</v>
       </c>
       <c r="B92" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
+        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
       </c>
       <c r="D92" t="str">
         <v>2026-06-09</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Nothing But Thieves</v>
+        <v>elijah woods</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
+        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video)</v>
+        <v>Nothing But Thieves - Evolution (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
+        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
       </c>
       <c r="D93" t="str">
         <v>2026-06-09</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Ariana Grande</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
+        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>LAUREL - Fire Breather</v>
+        <v>Ariana Grande - hate that i made you love me (official music video)</v>
       </c>
       <c r="B94" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
+        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
       </c>
       <c r="D94" t="str">
         <v>2026-06-09</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>LAUREL</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>LAUREL - Fire Breather - LAUREL</v>
+        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>The Warning - Ego (Performance Video)</v>
+        <v>LAUREL - Fire Breather</v>
       </c>
       <c r="B95" t="str">
-        <v>9d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
+        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
       </c>
       <c r="D95" t="str">
         <v>2026-06-09</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>9d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>The Warning</v>
+        <v>LAUREL</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>The Warning - Ego (Performance Video) - The Warning</v>
+        <v>LAUREL - Fire Breather - LAUREL</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
+        <v>The Warning - Ego (Performance Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
+        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
       </c>
       <c r="D96" t="str">
         <v>2026-06-09</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>The Warning</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
+        <v>The Warning - Ego (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
       </c>
       <c r="B97" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
+        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
       </c>
       <c r="D97" t="str">
         <v>2026-06-09</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Armin van Buuren</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B98" t="str">
-        <v>10d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
+        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
       </c>
       <c r="D98" t="str">
         <v>2026-06-09</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>10d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Andrew Bird</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video)</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
       </c>
       <c r="B99" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
+        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
       </c>
       <c r="D99" t="str">
         <v>2026-06-09</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Danny Gokey</v>
+        <v>Andrew Bird</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Danny Gokey - God's Not (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
+        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
       </c>
       <c r="D100" t="str">
         <v>2026-06-09</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Armik</v>
+        <v>Danny Gokey</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B101" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
+        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
       </c>
       <c r="D101" t="str">
         <v>2026-06-09</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Holly Humberstone and Free People</v>
+        <v>Armik</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>True Colors</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
+        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
       </c>
       <c r="D102" t="str">
         <v>2026-06-09</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Thank You</v>
+        <v>10 days ago</v>
       </c>
       <c r="G102" t="str">
-        <v>3:39</v>
+        <v/>
       </c>
       <c r="H102" t="str">
-        <v>Mike D</v>
+        <v>Holly Humberstone and Free People</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>True Colors - Mike D</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Too Easy</v>
+        <v>True Colors</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/too-easy/6774752170</v>
+        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
       </c>
       <c r="D103" t="str">
         <v>2026-06-09</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Too Easy - Single</v>
+        <v>Thank You</v>
       </c>
       <c r="G103" t="str">
-        <v>1:54</v>
+        <v>3:39</v>
       </c>
       <c r="H103" t="str">
-        <v>Tinashe</v>
+        <v>Mike D</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/tinashe/464835513</v>
+        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/too-easy/6774752168</v>
+        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
       </c>
       <c r="L103" t="str">
-        <v>Too Easy - Tinashe</v>
+        <v>True Colors - Mike D</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>I Knew It, I Knew You</v>
+        <v>Too Easy</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
+        <v>https://music.apple.com/us/song/too-easy/6774752170</v>
       </c>
       <c r="D104" t="str">
         <v>2026-06-09</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>I Knew It, I Knew You - Single</v>
+        <v>Too Easy - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>2:58</v>
+        <v>1:54</v>
       </c>
       <c r="H104" t="str">
-        <v>Taylor Swift</v>
+        <v>Tinashe</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/tinashe/464835513</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/i-knew-it-i-knew-you/6775527442</v>
+        <v>https://music.apple.com/us/album/too-easy/6774752168</v>
       </c>
       <c r="L104" t="str">
-        <v>I Knew It, I Knew You - Taylor Swift</v>
+        <v>Too Easy - Tinashe</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Love Sensation</v>
+        <v>I Knew It, I Knew You</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
+        <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
       </c>
       <c r="D105" t="str">
         <v>2026-06-09</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Love Sensation - Single</v>
+        <v>I Knew It, I Knew You - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:48</v>
+        <v>2:58</v>
       </c>
       <c r="H105" t="str">
-        <v>Madonna</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/love-sensation/6774810102</v>
+        <v>https://music.apple.com/us/album/i-knew-it-i-knew-you/6775527442</v>
       </c>
       <c r="L105" t="str">
-        <v>Love Sensation - Madonna</v>
+        <v>I Knew It, I Knew You - Taylor Swift</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Mi Yo De Antes</v>
+        <v>Love Sensation</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
+        <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
       </c>
       <c r="D106" t="str">
         <v>2026-06-09</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Mi Yo De Antes - Single</v>
+        <v>Love Sensation - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:04</v>
+        <v>3:48</v>
       </c>
       <c r="H106" t="str">
-        <v>Ozuna</v>
+        <v>Madonna</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/mi-yo-de-antes/6769193983</v>
+        <v>https://music.apple.com/us/album/love-sensation/6774810102</v>
       </c>
       <c r="L106" t="str">
-        <v>Mi Yo De Antes - Ozuna</v>
+        <v>Love Sensation - Madonna</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Three Nations</v>
+        <v>Mi Yo De Antes</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/three-nations/6776010602</v>
+        <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
       </c>
       <c r="D107" t="str">
         <v>2026-06-09</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Official FIFA World Cup 2026™ Album</v>
+        <v>Mi Yo De Antes - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:30</v>
+        <v>3:04</v>
       </c>
       <c r="H107" t="str">
-        <v>21 Savage</v>
+        <v>Ozuna</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/21-savage/894820464</v>
+        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/three-nations/6776010591</v>
+        <v>https://music.apple.com/us/album/mi-yo-de-antes/6769193983</v>
       </c>
       <c r="L107" t="str">
-        <v>Three Nations - 21 Savage</v>
+        <v>Mi Yo De Antes - Ozuna</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Champions (WC 26)</v>
+        <v>Three Nations</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
+        <v>https://music.apple.com/us/song/three-nations/6776010602</v>
       </c>
       <c r="D108" t="str">
         <v>2026-06-09</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Champions (WC 26) - Single</v>
+        <v>Official FIFA World Cup 2026™ Album</v>
       </c>
       <c r="G108" t="str">
-        <v>4:15</v>
+        <v>3:30</v>
       </c>
       <c r="H108" t="str">
-        <v>IShowSpeed</v>
+        <v>21 Savage</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/ishowspeed/1574723975</v>
+        <v>https://music.apple.com/us/artist/21-savage/894820464</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/champions-wc-26/6775282246</v>
+        <v>https://music.apple.com/us/album/three-nations/6776010591</v>
       </c>
       <c r="L108" t="str">
-        <v>Champions (WC 26) - IShowSpeed</v>
+        <v>Three Nations - 21 Savage</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>ENCERRONES</v>
+        <v>Champions (WC 26)</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/encerrones/6771854522</v>
+        <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
       </c>
       <c r="D109" t="str">
         <v>2026-06-09</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>TEOFANIA</v>
+        <v>Champions (WC 26) - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>2:23</v>
+        <v>4:15</v>
       </c>
       <c r="H109" t="str">
-        <v>LENCHO</v>
+        <v>IShowSpeed</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
+        <v>https://music.apple.com/us/artist/ishowspeed/1574723975</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/encerrones/6771854517</v>
+        <v>https://music.apple.com/us/album/champions-wc-26/6775282246</v>
       </c>
       <c r="L109" t="str">
-        <v>ENCERRONES - LENCHO</v>
+        <v>Champions (WC 26) - IShowSpeed</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Cowgirl</v>
+        <v>ENCERRONES</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
+        <v>https://music.apple.com/us/song/encerrones/6771854522</v>
       </c>
       <c r="D110" t="str">
         <v>2026-06-09</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>The Outlaw Cherie Lee &amp; Other Western Tales</v>
+        <v>TEOFANIA</v>
       </c>
       <c r="G110" t="str">
-        <v>2:56</v>
+        <v>2:23</v>
       </c>
       <c r="H110" t="str">
-        <v>Shaboozey</v>
+        <v>LENCHO</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
+        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/cowgirl/1894906682</v>
+        <v>https://music.apple.com/us/album/encerrones/6771854517</v>
       </c>
       <c r="L110" t="str">
-        <v>Cowgirl - Shaboozey</v>
+        <v>ENCERRONES - LENCHO</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>PASSENGER</v>
+        <v>Cowgirl</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/passenger/6773456081</v>
+        <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
       </c>
       <c r="D111" t="str">
         <v>2026-06-09</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>WILDCHILD</v>
+        <v>The Outlaw Cherie Lee &amp; Other Western Tales</v>
       </c>
       <c r="G111" t="str">
-        <v>2:39</v>
+        <v>2:56</v>
       </c>
       <c r="H111" t="str">
-        <v>Alex Warren</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/passenger/6773456078</v>
+        <v>https://music.apple.com/us/album/cowgirl/1894906682</v>
       </c>
       <c r="L111" t="str">
-        <v>PASSENGER - Alex Warren</v>
+        <v>Cowgirl - Shaboozey</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Secret Language</v>
+        <v>PASSENGER</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/secret-language/6774223667</v>
+        <v>https://music.apple.com/us/song/passenger/6773456081</v>
       </c>
       <c r="D112" t="str">
         <v>2026-06-09</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Sweet Fortune</v>
+        <v>WILDCHILD</v>
       </c>
       <c r="G112" t="str">
-        <v>3:53</v>
+        <v>2:39</v>
       </c>
       <c r="H112" t="str">
-        <v>Ryan Beatty</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/ryan-beatty/483234172</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/secret-language/6774223660</v>
+        <v>https://music.apple.com/us/album/passenger/6773456078</v>
       </c>
       <c r="L112" t="str">
-        <v>Secret Language - Ryan Beatty</v>
+        <v>PASSENGER - Alex Warren</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>High Hopes 3000</v>
+        <v>Secret Language</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
+        <v>https://music.apple.com/us/song/secret-language/6774223667</v>
       </c>
       <c r="D113" t="str">
         <v>2026-06-09</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Chuck Timely &amp; The Hourglass</v>
+        <v>Sweet Fortune</v>
       </c>
       <c r="G113" t="str">
-        <v>4:05</v>
+        <v>3:53</v>
       </c>
       <c r="H113" t="str">
-        <v>ROLE MODEL</v>
+        <v>Ryan Beatty</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/role-model/199215762</v>
+        <v>https://music.apple.com/us/artist/ryan-beatty/483234172</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
+        <v>https://music.apple.com/us/album/secret-language/6774223660</v>
       </c>
       <c r="L113" t="str">
-        <v>High Hopes 3000 - ROLE MODEL</v>
+        <v>Secret Language - Ryan Beatty</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Vertical</v>
+        <v>High Hopes 3000</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/vertical/1892436336</v>
+        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
       </c>
       <c r="D114" t="str">
         <v>2026-06-09</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Emotional Junglist</v>
+        <v>Chuck Timely &amp; The Hourglass</v>
       </c>
       <c r="G114" t="str">
-        <v>2:36</v>
+        <v>4:05</v>
       </c>
       <c r="H114" t="str">
-        <v>Nia Archives</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/role-model/199215762</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/vertical/1892436329</v>
+        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
       </c>
       <c r="L114" t="str">
-        <v>Vertical - Nia Archives</v>
+        <v>High Hopes 3000 - ROLE MODEL</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>snake the drain</v>
+        <v>Vertical</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
+        <v>https://music.apple.com/us/song/vertical/1892436336</v>
       </c>
       <c r="D115" t="str">
         <v>2026-06-09</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>this time it’s different / snake the drain - Single</v>
+        <v>Emotional Junglist</v>
       </c>
       <c r="G115" t="str">
-        <v>3:08</v>
+        <v>2:36</v>
       </c>
       <c r="H115" t="str">
-        <v>Devon Again</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
+        <v>https://music.apple.com/us/album/vertical/1892436329</v>
       </c>
       <c r="L115" t="str">
-        <v>snake the drain - Devon Again</v>
+        <v>Vertical - Nia Archives</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Every Single Weekend (feat. Jamie xx)</v>
+        <v>snake the drain</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
+        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
       </c>
       <c r="D116" t="str">
         <v>2026-06-09</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
+        <v>this time it’s different / snake the drain - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>2:10</v>
+        <v>3:08</v>
       </c>
       <c r="H116" t="str">
-        <v>The Avalanches</v>
+        <v>Devon Again</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
+        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
       </c>
       <c r="L116" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
+        <v>snake the drain - Devon Again</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Bluffin'</v>
+        <v>Every Single Weekend (feat. Jamie xx)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
+        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D117" t="str">
         <v>2026-06-09</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Piss In The Wind (Deluxe)</v>
+        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:34</v>
+        <v>2:10</v>
       </c>
       <c r="H117" t="str">
-        <v>Joji</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
+        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
       </c>
       <c r="L117" t="str">
-        <v>Bluffin' - Joji</v>
+        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Dreams</v>
+        <v>Bluffin'</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/dreams/1884731028</v>
+        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
       </c>
       <c r="D118" t="str">
         <v>2026-06-09</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Free Your Mind</v>
+        <v>Piss In The Wind (Deluxe)</v>
       </c>
       <c r="G118" t="str">
-        <v>3:56</v>
+        <v>2:34</v>
       </c>
       <c r="H118" t="str">
-        <v>Prospa</v>
+        <v>Joji</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/dreams/1884730177</v>
+        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
       </c>
       <c r="L118" t="str">
-        <v>Dreams - Prospa</v>
+        <v>Bluffin' - Joji</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Cotton</v>
+        <v>Dreams</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/cotton/1887627941</v>
+        <v>https://music.apple.com/us/song/dreams/1884731028</v>
       </c>
       <c r="D119" t="str">
         <v>2026-06-09</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Cry Baby</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="G119" t="str">
-        <v>3:43</v>
+        <v>3:56</v>
       </c>
       <c r="H119" t="str">
-        <v>Vince Staples</v>
+        <v>Prospa</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/cotton/1887627836</v>
+        <v>https://music.apple.com/us/album/dreams/1884730177</v>
       </c>
       <c r="L119" t="str">
-        <v>Cotton - Vince Staples</v>
+        <v>Dreams - Prospa</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Black Prada Dress</v>
+        <v>Cotton</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
+        <v>https://music.apple.com/us/song/cotton/1887627941</v>
       </c>
       <c r="D120" t="str">
         <v>2026-06-09</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>I Know Too Much</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G120" t="str">
-        <v>3:19</v>
+        <v>3:43</v>
       </c>
       <c r="H120" t="str">
-        <v>Ellie Goulding</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
+        <v>https://music.apple.com/us/album/cotton/1887627836</v>
       </c>
       <c r="L120" t="str">
-        <v>Black Prada Dress - Ellie Goulding</v>
+        <v>Cotton - Vince Staples</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Don’t Break Her Heart</v>
+        <v>Black Prada Dress</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
+        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
       </c>
       <c r="D121" t="str">
         <v>2026-06-09</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>THERAPY AT THE CLUB</v>
+        <v>I Know Too Much</v>
       </c>
       <c r="G121" t="str">
-        <v>3:44</v>
+        <v>3:19</v>
       </c>
       <c r="H121" t="str">
-        <v>FLO</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
+        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
       </c>
       <c r="L121" t="str">
-        <v>Don’t Break Her Heart - FLO</v>
+        <v>Black Prada Dress - Ellie Goulding</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Sexy Ladies (feat. UCB)</v>
+        <v>Don’t Break Her Heart</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
+        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
       </c>
       <c r="D122" t="str">
         <v>2026-06-09</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>BITCH</v>
+        <v>THERAPY AT THE CLUB</v>
       </c>
       <c r="G122" t="str">
-        <v>2:50</v>
+        <v>3:44</v>
       </c>
       <c r="H122" t="str">
-        <v>Lizzo</v>
+        <v>FLO</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
+        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
       </c>
       <c r="L122" t="str">
-        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
+        <v>Don’t Break Her Heart - FLO</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Noche Without You</v>
+        <v>Sexy Ladies (feat. UCB)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
+        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
       </c>
       <c r="D123" t="str">
         <v>2026-06-09</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>SOMA</v>
+        <v>BITCH</v>
       </c>
       <c r="G123" t="str">
-        <v>3:23</v>
+        <v>2:50</v>
       </c>
       <c r="H123" t="str">
-        <v>Skrillex</v>
+        <v>Lizzo</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
+        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
       </c>
       <c r="L123" t="str">
-        <v>Noche Without You - Skrillex</v>
+        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Difficult Love</v>
+        <v>Noche Without You</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
+        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
       </c>
       <c r="D124" t="str">
         <v>2026-06-09</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Do That Again</v>
+        <v>SOMA</v>
       </c>
       <c r="G124" t="str">
-        <v>2:33</v>
+        <v>3:23</v>
       </c>
       <c r="H124" t="str">
-        <v>Malcolm Todd</v>
+        <v>Skrillex</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
+        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
       </c>
       <c r="L124" t="str">
-        <v>Difficult Love - Malcolm Todd</v>
+        <v>Noche Without You - Skrillex</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Tastes So Good</v>
+        <v>Difficult Love</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
+        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
       </c>
       <c r="D125" t="str">
         <v>2026-06-09</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Dinner Party</v>
+        <v>Do That Again</v>
       </c>
       <c r="G125" t="str">
-        <v>3:05</v>
+        <v>2:33</v>
       </c>
       <c r="H125" t="str">
-        <v>Niall Horan</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
+        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
       </c>
       <c r="L125" t="str">
-        <v>Tastes So Good - Niall Horan</v>
+        <v>Difficult Love - Malcolm Todd</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Phone, Keys, Wallet</v>
+        <v>Tastes So Good</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
+        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
       </c>
       <c r="D126" t="str">
         <v>2026-06-09</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Phone, Keys, Wallet - Single</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G126" t="str">
-        <v>2:52</v>
+        <v>3:05</v>
       </c>
       <c r="H126" t="str">
-        <v>Lainey Wilson</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
+        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
       </c>
       <c r="L126" t="str">
-        <v>Phone, Keys, Wallet - Lainey Wilson</v>
+        <v>Tastes So Good - Niall Horan</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Madrugada</v>
+        <v>Phone, Keys, Wallet</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
+        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
       </c>
       <c r="D127" t="str">
         <v>2026-06-09</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Madrugada - Single</v>
+        <v>Phone, Keys, Wallet - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:58</v>
+        <v>2:52</v>
       </c>
       <c r="H127" t="str">
-        <v>Chino Pacas</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
+        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
       </c>
       <c r="L127" t="str">
-        <v>Madrugada - Chino Pacas</v>
+        <v>Phone, Keys, Wallet - Lainey Wilson</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Oh Chet (feat. Travis Scott)</v>
+        <v>Madrugada</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
+        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
       </c>
       <c r="D128" t="str">
         <v>2026-06-09</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Single</v>
+        <v>Madrugada - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:23</v>
+        <v>2:58</v>
       </c>
       <c r="H128" t="str">
-        <v>Jey One</v>
+        <v>Chino Pacas</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
+        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
+        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
       </c>
       <c r="L128" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
+        <v>Madrugada - Chino Pacas</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>An Hour or So (Live at Apple Music Radio)</v>
+        <v>Oh Chet (feat. Travis Scott)</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
+        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
       </c>
       <c r="D129" t="str">
         <v>2026-06-09</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Oh Chet (feat. Travis Scott) - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:02</v>
+        <v>2:23</v>
       </c>
       <c r="H129" t="str">
-        <v>Benny G</v>
+        <v>Jey One</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
+        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
       </c>
       <c r="L129" t="str">
-        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
+        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>it’s just White Noise</v>
+        <v>An Hour or So (Live at Apple Music Radio)</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
+        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
       </c>
       <c r="D130" t="str">
         <v>2026-06-09</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>it’s a real Cruel World - EP</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G130" t="str">
-        <v>3:57</v>
+        <v>3:02</v>
       </c>
       <c r="H130" t="str">
-        <v>Holly Humberstone</v>
+        <v>Benny G</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
+        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
       </c>
       <c r="L130" t="str">
-        <v>it’s just White Noise - Holly Humberstone</v>
+        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>the feeling</v>
+        <v>it’s just White Noise</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
+        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
       </c>
       <c r="D131" t="str">
         <v>2026-06-09</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Oh yeah?</v>
+        <v>it’s a real Cruel World - EP</v>
       </c>
       <c r="G131" t="str">
-        <v>4:35</v>
+        <v>3:57</v>
       </c>
       <c r="H131" t="str">
-        <v>Steve Lacy</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
+        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
       </c>
       <c r="L131" t="str">
-        <v>the feeling - Steve Lacy</v>
+        <v>it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>baby (Live at Apple Music Radio)</v>
+        <v>the feeling</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
+        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
       </c>
       <c r="D132" t="str">
         <v>2026-06-09</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Oh yeah?</v>
       </c>
       <c r="G132" t="str">
-        <v>3:14</v>
+        <v>4:35</v>
       </c>
       <c r="H132" t="str">
-        <v>Gabriel Jacoby</v>
+        <v>Steve Lacy</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
+        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
+        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
       </c>
       <c r="L132" t="str">
-        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
+        <v>the feeling - Steve Lacy</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Drop The Lo</v>
+        <v>baby (Live at Apple Music Radio)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
+        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
       </c>
       <c r="D133" t="str">
         <v>2026-06-09</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Drop The Lo - Single</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G133" t="str">
-        <v>2:41</v>
+        <v>3:14</v>
       </c>
       <c r="H133" t="str">
-        <v>Bryson Tiller</v>
+        <v>Gabriel Jacoby</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
+        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
       </c>
       <c r="L133" t="str">
-        <v>Drop The Lo - Bryson Tiller</v>
+        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>GANG BIZNESS feat paygotti</v>
+        <v>Drop The Lo</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
+        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
       </c>
       <c r="D134" t="str">
         <v>2026-06-09</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>GANG BIZNESS feat paygotti - Single</v>
+        <v>Drop The Lo - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:47</v>
+        <v>2:41</v>
       </c>
       <c r="H134" t="str">
-        <v>YG</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
+        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
       </c>
       <c r="L134" t="str">
-        <v>GANG BIZNESS feat paygotti - YG</v>
+        <v>Drop The Lo - Bryson Tiller</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Lay It Down</v>
+        <v>GANG BIZNESS feat paygotti</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
+        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
       </c>
       <c r="D135" t="str">
         <v>2026-06-09</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Lay It Down - Single</v>
+        <v>GANG BIZNESS feat paygotti - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:38</v>
+        <v>2:47</v>
       </c>
       <c r="H135" t="str">
-        <v>FattMack</v>
+        <v>YG</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
+        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
       </c>
       <c r="L135" t="str">
-        <v>Lay It Down - FattMack</v>
+        <v>GANG BIZNESS feat paygotti - YG</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>WAX PAPER</v>
+        <v>Lay It Down</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
+        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
       </c>
       <c r="D136" t="str">
         <v>2026-06-09</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>WHACK'S MUSEUM</v>
+        <v>Lay It Down - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:43</v>
+        <v>2:38</v>
       </c>
       <c r="H136" t="str">
-        <v>Tierra Whack</v>
+        <v>FattMack</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
+        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
       </c>
       <c r="L136" t="str">
-        <v>WAX PAPER - Tierra Whack</v>
+        <v>Lay It Down - FattMack</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>abusadOra (tambores)</v>
+        <v>WAX PAPER</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
+        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
       </c>
       <c r="D137" t="str">
         <v>2026-06-09</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>ANTES DE QUE SEA TARDE</v>
+        <v>WHACK'S MUSEUM</v>
       </c>
       <c r="G137" t="str">
-        <v>3:11</v>
+        <v>2:43</v>
       </c>
       <c r="H137" t="str">
-        <v>Yorghaki</v>
+        <v>Tierra Whack</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
+        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
+        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
       </c>
       <c r="L137" t="str">
-        <v>abusadOra (tambores) - Yorghaki</v>
+        <v>WAX PAPER - Tierra Whack</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Ruin</v>
+        <v>abusadOra (tambores)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/ruin/6763176090</v>
+        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
       </c>
       <c r="D138" t="str">
         <v>2026-06-09</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Labor Of Love</v>
+        <v>ANTES DE QUE SEA TARDE</v>
       </c>
       <c r="G138" t="str">
-        <v>3:19</v>
+        <v>3:11</v>
       </c>
       <c r="H138" t="str">
-        <v>Blxst</v>
+        <v>Yorghaki</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/ruin/1895199881</v>
+        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
       </c>
       <c r="L138" t="str">
-        <v>Ruin - Blxst</v>
+        <v>abusadOra (tambores) - Yorghaki</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Do Today</v>
+        <v>Ruin</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/do-today/1893402864</v>
+        <v>https://music.apple.com/us/song/ruin/6763176090</v>
       </c>
       <c r="D139" t="str">
         <v>2026-06-09</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Grateful</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G139" t="str">
-        <v>4:14</v>
+        <v>3:19</v>
       </c>
       <c r="H139" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Blxst</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/do-today/1893402542</v>
+        <v>https://music.apple.com/us/album/ruin/1895199881</v>
       </c>
       <c r="L139" t="str">
-        <v>Do Today - The Red Clay Strays</v>
+        <v>Ruin - Blxst</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Stone Over Water</v>
+        <v>Do Today</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
+        <v>https://music.apple.com/us/song/do-today/1893402864</v>
       </c>
       <c r="D140" t="str">
         <v>2026-06-09</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>I Built You A Tower</v>
+        <v>Grateful</v>
       </c>
       <c r="G140" t="str">
-        <v>3:14</v>
+        <v>4:14</v>
       </c>
       <c r="H140" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
+        <v>https://music.apple.com/us/album/do-today/1893402542</v>
       </c>
       <c r="L140" t="str">
-        <v>Stone Over Water - Death Cab for Cutie</v>
+        <v>Do Today - The Red Clay Strays</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
+        <v>Stone Over Water</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
+        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
       </c>
       <c r="D141" t="str">
         <v>2026-06-09</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Weezer</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G141" t="str">
-        <v>3:34</v>
+        <v>3:14</v>
       </c>
       <c r="H141" t="str">
-        <v>Weezer</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/weezer/115234</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
+        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
       </c>
       <c r="L141" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
+        <v>Stone Over Water - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Tell Me When You've Had Enough</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
+        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
       </c>
       <c r="D142" t="str">
         <v>2026-06-09</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Sanctuary</v>
+        <v>Weezer</v>
       </c>
       <c r="G142" t="str">
-        <v>3:19</v>
+        <v>3:34</v>
       </c>
       <c r="H142" t="str">
-        <v>Evanescence</v>
+        <v>Weezer</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/weezer/115234</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
+        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
       </c>
       <c r="L142" t="str">
-        <v>Tell Me When You've Had Enough - Evanescence</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Your Ghost Again</v>
+        <v>Tell Me When You've Had Enough</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
+        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
       </c>
       <c r="D143" t="str">
         <v>2026-06-09</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Your Ghost Again - Single</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G143" t="str">
-        <v>4:35</v>
+        <v>3:19</v>
       </c>
       <c r="H143" t="str">
-        <v>Mastodon</v>
+        <v>Evanescence</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
+        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
       </c>
       <c r="L143" t="str">
-        <v>Your Ghost Again - Mastodon</v>
+        <v>Tell Me When You've Had Enough - Evanescence</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Nightshift Superstar</v>
+        <v>Your Ghost Again</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
+        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
       </c>
       <c r="D144" t="str">
         <v>2026-06-09</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>The Wow! Signal</v>
+        <v>Your Ghost Again - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>4:07</v>
+        <v>4:35</v>
       </c>
       <c r="H144" t="str">
-        <v>Muse</v>
+        <v>Mastodon</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
+        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
       </c>
       <c r="L144" t="str">
-        <v>Nightshift Superstar - Muse</v>
+        <v>Your Ghost Again - Mastodon</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>UNDER THE RHYTHM</v>
+        <v>Nightshift Superstar</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
+        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
       </c>
       <c r="D145" t="str">
         <v>2026-06-09</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>ADAM</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G145" t="str">
-        <v>2:50</v>
+        <v>4:07</v>
       </c>
       <c r="H145" t="str">
-        <v>Adam Lambert</v>
+        <v>Muse</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
+        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
       </c>
       <c r="L145" t="str">
-        <v>UNDER THE RHYTHM - Adam Lambert</v>
+        <v>Nightshift Superstar - Muse</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>You’re Mine</v>
+        <v>UNDER THE RHYTHM</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
+        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
       </c>
       <c r="D146" t="str">
         <v>2026-06-09</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Papercut</v>
+        <v>ADAM</v>
       </c>
       <c r="G146" t="str">
-        <v>4:25</v>
+        <v>2:50</v>
       </c>
       <c r="H146" t="str">
-        <v>Imani Imani</v>
+        <v>Adam Lambert</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
+        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
+        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
       </c>
       <c r="L146" t="str">
-        <v>You’re Mine - Imani Imani</v>
+        <v>UNDER THE RHYTHM - Adam Lambert</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>point blank</v>
+        <v>You’re Mine</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
+        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
       </c>
       <c r="D147" t="str">
         <v>2026-06-09</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>new avatar</v>
+        <v>Papercut</v>
       </c>
       <c r="G147" t="str">
-        <v>4:26</v>
+        <v>4:25</v>
       </c>
       <c r="H147" t="str">
-        <v>Kelela</v>
+        <v>Imani Imani</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
+        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
       </c>
       <c r="L147" t="str">
-        <v>point blank - Kelela</v>
+        <v>You’re Mine - Imani Imani</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>that's my beach!</v>
+        <v>point blank</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
+        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
       </c>
       <c r="D148" t="str">
         <v>2026-06-09</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>new avatar</v>
       </c>
       <c r="G148" t="str">
-        <v>3:18</v>
+        <v>4:26</v>
       </c>
       <c r="H148" t="str">
-        <v>horsegiirL</v>
+        <v>Kelela</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
+        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
       </c>
       <c r="L148" t="str">
-        <v>that's my beach! - horsegiirL</v>
+        <v>point blank - Kelela</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>In Your Eyes</v>
+        <v>that's my beach!</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
+        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
       </c>
       <c r="D149" t="str">
         <v>2026-06-09</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>In Your Eyes - Single</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G149" t="str">
-        <v>3:36</v>
+        <v>3:18</v>
       </c>
       <c r="H149" t="str">
-        <v>Alesso</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/alesso/432464201</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
+        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
       </c>
       <c r="L149" t="str">
-        <v>In Your Eyes - Alesso</v>
+        <v>that's my beach! - horsegiirL</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>ALL OR NOTHING</v>
+        <v>In Your Eyes</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
+        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
       </c>
       <c r="D150" t="str">
         <v>2026-06-09</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>ALL OR NOTHING - Single</v>
+        <v>In Your Eyes - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:17</v>
+        <v>3:36</v>
       </c>
       <c r="H150" t="str">
-        <v>Tobe Nwigwe</v>
+        <v>Alesso</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
+        <v>https://music.apple.com/us/artist/alesso/432464201</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
+        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
       </c>
       <c r="L150" t="str">
-        <v>ALL OR NOTHING - Tobe Nwigwe</v>
+        <v>In Your Eyes - Alesso</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>IN MY HANDS</v>
+        <v>ALL OR NOTHING</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
+        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
       </c>
       <c r="D151" t="str">
         <v>2026-06-09</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>IN MY HANDS - Single</v>
+        <v>ALL OR NOTHING - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:14</v>
+        <v>3:17</v>
       </c>
       <c r="H151" t="str">
-        <v>Alessia Cara</v>
+        <v>Tobe Nwigwe</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
+        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
+        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
       </c>
       <c r="L151" t="str">
-        <v>IN MY HANDS - Alessia Cara</v>
+        <v>ALL OR NOTHING - Tobe Nwigwe</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Life's a Dream</v>
+        <v>IN MY HANDS</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
+        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
       </c>
       <c r="D152" t="str">
         <v>2026-06-09</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>IN MY HANDS - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>5:31</v>
+        <v>3:14</v>
       </c>
       <c r="H152" t="str">
-        <v>Modest Mouse</v>
+        <v>Alessia Cara</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
+        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
       </c>
       <c r="L152" t="str">
-        <v>Life's a Dream - Modest Mouse</v>
+        <v>IN MY HANDS - Alessia Cara</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
+        <v>Life's a Dream</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
+        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
       </c>
       <c r="D153" t="str">
         <v>2026-06-09</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Season of Surrender</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G153" t="str">
-        <v>4:47</v>
+        <v>5:31</v>
       </c>
       <c r="H153" t="str">
-        <v>August Burns Red</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
+        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
       </c>
       <c r="L153" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
+        <v>Life's a Dream - Modest Mouse</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Shine</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/shine/6764654536</v>
+        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
       </c>
       <c r="D154" t="str">
         <v>2026-06-09</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Black Mozart</v>
+        <v>Season of Surrender</v>
       </c>
       <c r="G154" t="str">
-        <v>2:27</v>
+        <v>4:47</v>
       </c>
       <c r="H154" t="str">
-        <v>Jon Batiste</v>
+        <v>August Burns Red</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/shine/1895866355</v>
+        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
       </c>
       <c r="L154" t="str">
-        <v>Shine - Jon Batiste</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Half The Man</v>
+        <v>Shine</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
+        <v>https://music.apple.com/us/song/shine/6764654536</v>
       </c>
       <c r="D155" t="str">
         <v>2026-06-09</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Scared of Heights</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G155" t="str">
-        <v>3:56</v>
+        <v>2:27</v>
       </c>
       <c r="H155" t="str">
-        <v>Wyatt Flores</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
+        <v>https://music.apple.com/us/album/shine/1895866355</v>
       </c>
       <c r="L155" t="str">
-        <v>Half The Man - Wyatt Flores</v>
+        <v>Shine - Jon Batiste</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Preacher’s Kid</v>
+        <v>Half The Man</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
+        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
       </c>
       <c r="D156" t="str">
         <v>2026-06-09</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Preacher’s Kid - Single</v>
+        <v>Scared of Heights</v>
       </c>
       <c r="G156" t="str">
-        <v>5:02</v>
+        <v>3:56</v>
       </c>
       <c r="H156" t="str">
-        <v>Stephen Wilson Jr.</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
+        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
       </c>
       <c r="L156" t="str">
-        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
+        <v>Half The Man - Wyatt Flores</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Weak</v>
+        <v>Preacher’s Kid</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/weak/6771151098</v>
+        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
       </c>
       <c r="D157" t="str">
         <v>2026-06-09</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Weak - Single</v>
+        <v>Preacher’s Kid - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:28</v>
+        <v>5:02</v>
       </c>
       <c r="H157" t="str">
-        <v>Naomi Sharon</v>
+        <v>Stephen Wilson Jr.</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/weak/6771151088</v>
+        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
       </c>
       <c r="L157" t="str">
-        <v>Weak - Naomi Sharon</v>
+        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>ALL NIGHT LONG</v>
+        <v>Weak</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
+        <v>https://music.apple.com/us/song/weak/6771151098</v>
       </c>
       <c r="D158" t="str">
         <v>2026-06-09</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>A Rii Set</v>
+        <v>Weak - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:28</v>
+        <v>3:28</v>
       </c>
       <c r="H158" t="str">
-        <v>Pheelz</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
+        <v>https://music.apple.com/us/album/weak/6771151088</v>
       </c>
       <c r="L158" t="str">
-        <v>ALL NIGHT LONG - Pheelz</v>
+        <v>Weak - Naomi Sharon</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Every Life</v>
+        <v>ALL NIGHT LONG</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/every-life/6764110978</v>
+        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
       </c>
       <c r="D159" t="str">
         <v>2026-06-09</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G159" t="str">
-        <v>3:18</v>
+        <v>2:28</v>
       </c>
       <c r="H159" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Pheelz</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/every-life/1895644574</v>
+        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
       </c>
       <c r="L159" t="str">
-        <v>Every Life - Isabel LaRosa</v>
+        <v>ALL NIGHT LONG - Pheelz</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Home</v>
+        <v>Every Life</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/home/6774718029</v>
+        <v>https://music.apple.com/us/song/every-life/6764110978</v>
       </c>
       <c r="D160" t="str">
         <v>2026-06-09</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Good Grief</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G160" t="str">
-        <v>4:53</v>
+        <v>3:18</v>
       </c>
       <c r="H160" t="str">
-        <v>Sara Bareilles</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/home/6774718027</v>
+        <v>https://music.apple.com/us/album/every-life/1895644574</v>
       </c>
       <c r="L160" t="str">
-        <v>Home - Sara Bareilles</v>
+        <v>Every Life - Isabel LaRosa</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Satalanaaa</v>
+        <v>Home</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
+        <v>https://music.apple.com/us/song/home/6774718029</v>
       </c>
       <c r="D161" t="str">
         <v>2026-06-09</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Satalanaaa - Single</v>
+        <v>Good Grief</v>
       </c>
       <c r="G161" t="str">
-        <v>2:06</v>
+        <v>4:53</v>
       </c>
       <c r="H161" t="str">
-        <v>Pitbull</v>
+        <v>Sara Bareilles</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
+        <v>https://music.apple.com/us/album/home/6774718027</v>
       </c>
       <c r="L161" t="str">
-        <v>Satalanaaa - Pitbull</v>
+        <v>Home - Sara Bareilles</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Miss Me More</v>
+        <v>Satalanaaa</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
+        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
       </c>
       <c r="D162" t="str">
         <v>2026-06-09</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Confessions of a Lonely Heart</v>
+        <v>Satalanaaa - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:43</v>
+        <v>2:06</v>
       </c>
       <c r="H162" t="str">
-        <v>Eric Nam</v>
+        <v>Pitbull</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
+        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
       </c>
       <c r="L162" t="str">
-        <v>Miss Me More - Eric Nam</v>
+        <v>Satalanaaa - Pitbull</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Rituals</v>
+        <v>Miss Me More</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/rituals/6769628916</v>
+        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
       </c>
       <c r="D163" t="str">
         <v>2026-06-09</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Rituals - Single</v>
+        <v>Confessions of a Lonely Heart</v>
       </c>
       <c r="G163" t="str">
-        <v>2:10</v>
+        <v>2:43</v>
       </c>
       <c r="H163" t="str">
-        <v>Rico Nasty</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/rituals/6769628915</v>
+        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
       </c>
       <c r="L163" t="str">
-        <v>Rituals - Rico Nasty</v>
+        <v>Miss Me More - Eric Nam</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Honeysuckle</v>
+        <v>Rituals</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
+        <v>https://music.apple.com/us/song/rituals/6769628916</v>
       </c>
       <c r="D164" t="str">
         <v>2026-06-09</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Honeysuckle - Single</v>
+        <v>Rituals - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:15</v>
+        <v>2:10</v>
       </c>
       <c r="H164" t="str">
-        <v>Dylan Gossett</v>
+        <v>Rico Nasty</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
+        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
+        <v>https://music.apple.com/us/album/rituals/6769628915</v>
       </c>
       <c r="L164" t="str">
-        <v>Honeysuckle - Dylan Gossett</v>
+        <v>Rituals - Rico Nasty</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>listen…</v>
+        <v>Honeysuckle</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/listen/6775576508</v>
+        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
       </c>
       <c r="D165" t="str">
         <v>2026-06-09</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
+        <v>Honeysuckle - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>4:08</v>
+        <v>3:15</v>
       </c>
       <c r="H165" t="str">
-        <v>John Williams</v>
+        <v>Dylan Gossett</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/john-williams/63748</v>
+        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/listen/6775576506</v>
+        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
       </c>
       <c r="L165" t="str">
-        <v>listen… - John Williams</v>
+        <v>Honeysuckle - Dylan Gossett</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>DEADMEAT</v>
+        <v>listen…</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
+        <v>https://music.apple.com/us/song/listen/6775576508</v>
       </c>
       <c r="D166" t="str">
         <v>2026-06-09</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>DEADMEAT - Single</v>
+        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G166" t="str">
-        <v>2:52</v>
+        <v>4:08</v>
       </c>
       <c r="H166" t="str">
-        <v>South Arcade</v>
+        <v>John Williams</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/john-williams/63748</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
+        <v>https://music.apple.com/us/album/listen/6775576506</v>
       </c>
       <c r="L166" t="str">
-        <v>DEADMEAT - South Arcade</v>
+        <v>listen… - John Williams</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Ugly and Rotten</v>
+        <v>DEADMEAT</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
+        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
       </c>
       <c r="D167" t="str">
         <v>2026-06-09</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Ugly and Rotten - Single</v>
+        <v>DEADMEAT - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:49</v>
+        <v>2:52</v>
       </c>
       <c r="H167" t="str">
-        <v>Mckenna Grace</v>
+        <v>South Arcade</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
+        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
       </c>
       <c r="L167" t="str">
-        <v>Ugly and Rotten - Mckenna Grace</v>
+        <v>DEADMEAT - South Arcade</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Whisper</v>
+        <v>Ugly and Rotten</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/whisper/6772254272</v>
+        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
       </c>
       <c r="D168" t="str">
         <v>2026-06-09</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Whisper - Single</v>
+        <v>Ugly and Rotten - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:47</v>
+        <v>2:49</v>
       </c>
       <c r="H168" t="str">
-        <v>Blu DeTiger</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
+        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/whisper/6772254268</v>
+        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
       </c>
       <c r="L168" t="str">
-        <v>Whisper - Blu DeTiger</v>
+        <v>Ugly and Rotten - Mckenna Grace</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Gecko (feat. Haley Bridge)</v>
+        <v>Whisper</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
+        <v>https://music.apple.com/us/song/whisper/6772254272</v>
       </c>
       <c r="D169" t="str">
         <v>2026-06-09</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>How dare you tryna love me? - EP</v>
+        <v>Whisper - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:46</v>
+        <v>2:47</v>
       </c>
       <c r="H169" t="str">
-        <v>Olga Myko</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
+        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
+        <v>https://music.apple.com/us/album/whisper/6772254268</v>
       </c>
       <c r="L169" t="str">
-        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
+        <v>Whisper - Blu DeTiger</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Compa Primo</v>
+        <v>Gecko (feat. Haley Bridge)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
+        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
       </c>
       <c r="D170" t="str">
         <v>2026-06-09</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Compa Primo - Single</v>
+        <v>How dare you tryna love me? - EP</v>
       </c>
       <c r="G170" t="str">
-        <v>3:12</v>
+        <v>2:46</v>
       </c>
       <c r="H170" t="str">
-        <v>Nueva H</v>
+        <v>Olga Myko</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
+        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
+        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
       </c>
       <c r="L170" t="str">
-        <v>Compa Primo - Nueva H</v>
+        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Parachute</v>
+        <v>Compa Primo</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/parachute/6768841410</v>
+        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
       </c>
       <c r="D171" t="str">
         <v>2026-06-09</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Parachute - Single</v>
+        <v>Compa Primo - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:11</v>
+        <v>3:12</v>
       </c>
       <c r="H171" t="str">
-        <v>Tyler James Bellinger</v>
+        <v>Nueva H</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
+        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/parachute/6768841409</v>
+        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
       </c>
       <c r="L171" t="str">
-        <v>Parachute - Tyler James Bellinger</v>
+        <v>Compa Primo - Nueva H</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Like a Bubble</v>
+        <v>Parachute</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
+        <v>https://music.apple.com/us/song/parachute/6768841410</v>
       </c>
       <c r="D172" t="str">
         <v>2026-06-09</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Imperfect-I'mperfect - EP</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:08</v>
+        <v>3:11</v>
       </c>
       <c r="H172" t="str">
-        <v>FIFTY FIFTY</v>
+        <v>Tyler James Bellinger</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
+        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
+        <v>https://music.apple.com/us/album/parachute/6768841409</v>
       </c>
       <c r="L172" t="str">
-        <v>Like a Bubble - FIFTY FIFTY</v>
+        <v>Parachute - Tyler James Bellinger</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Hustle and Opulence in America</v>
+        <v>Like a Bubble</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
+        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
       </c>
       <c r="D173" t="str">
         <v>2026-06-09</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>AK Cuts: Vol. 4 - EP</v>
+        <v>Imperfect-I'mperfect - EP</v>
       </c>
       <c r="G173" t="str">
-        <v>3:07</v>
+        <v>3:08</v>
       </c>
       <c r="H173" t="str">
-        <v>Anish Kumar</v>
+        <v>FIFTY FIFTY</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
+        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
       </c>
       <c r="L173" t="str">
-        <v>Hustle and Opulence in America - Anish Kumar</v>
+        <v>Like a Bubble - FIFTY FIFTY</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
+        <v>Hustle and Opulence in America</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
+        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
       </c>
       <c r="D174" t="str">
         <v>2026-06-09</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
+        <v>AK Cuts: Vol. 4 - EP</v>
       </c>
       <c r="G174" t="str">
-        <v>2:47</v>
+        <v>3:07</v>
       </c>
       <c r="H174" t="str">
-        <v>ivri</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
+        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
       </c>
       <c r="L174" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
+        <v>Hustle and Opulence in America - Anish Kumar</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>CLEAN SWEEP</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
+        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
       </c>
       <c r="D175" t="str">
         <v>2026-06-09</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>CLEAN SWEEP - Single</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:11</v>
+        <v>2:47</v>
       </c>
       <c r="H175" t="str">
-        <v>Storm Reid</v>
+        <v>ivri</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
+        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
       </c>
       <c r="L175" t="str">
-        <v>CLEAN SWEEP - Storm Reid</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>CANDYLAND!</v>
+        <v>CLEAN SWEEP</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/candyland/6766927008</v>
+        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
       </c>
       <c r="D176" t="str">
         <v>2026-06-09</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>CANDYLAND! - Single</v>
+        <v>CLEAN SWEEP - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:15</v>
+        <v>3:11</v>
       </c>
       <c r="H176" t="str">
-        <v>Natanya</v>
+        <v>Storm Reid</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
+        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/candyland/6766927000</v>
+        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
       </c>
       <c r="L176" t="str">
-        <v>CANDYLAND! - Natanya</v>
+        <v>CLEAN SWEEP - Storm Reid</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Double C</v>
+        <v>CANDYLAND!</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/double-c/6771836555</v>
+        <v>https://music.apple.com/us/song/candyland/6766927008</v>
       </c>
       <c r="D177" t="str">
         <v>2026-06-09</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Double C - Single</v>
+        <v>CANDYLAND! - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:21</v>
+        <v>3:15</v>
       </c>
       <c r="H177" t="str">
-        <v>Sk8star</v>
+        <v>Natanya</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
+        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/double-c/6771836554</v>
+        <v>https://music.apple.com/us/album/candyland/6766927000</v>
       </c>
       <c r="L177" t="str">
-        <v>Double C - Sk8star</v>
+        <v>CANDYLAND! - Natanya</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>madera</v>
+        <v>Double C</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/madera/6764638112</v>
+        <v>https://music.apple.com/us/song/double-c/6771836555</v>
       </c>
       <c r="D178" t="str">
         <v>2026-06-09</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>madera/un camino luminoso - Single</v>
+        <v>Double C - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>5:41</v>
+        <v>2:21</v>
       </c>
       <c r="H178" t="str">
-        <v>Lumtz</v>
+        <v>Sk8star</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
+        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/madera/6764638109</v>
+        <v>https://music.apple.com/us/album/double-c/6771836554</v>
       </c>
       <c r="L178" t="str">
-        <v>madera - Lumtz</v>
+        <v>Double C - Sk8star</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Slip the Noose</v>
+        <v>madera</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
+        <v>https://music.apple.com/us/song/madera/6764638112</v>
       </c>
       <c r="D179" t="str">
         <v>2026-06-09</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Hum of Hurt</v>
+        <v>madera/un camino luminoso - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>1:43</v>
+        <v>5:41</v>
       </c>
       <c r="H179" t="str">
-        <v>Converge</v>
+        <v>Lumtz</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
+        <v>https://music.apple.com/us/album/madera/6764638109</v>
       </c>
       <c r="L179" t="str">
-        <v>Slip the Noose - Converge</v>
+        <v>madera - Lumtz</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Crying Fire</v>
+        <v>Slip the Noose</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
+        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
       </c>
       <c r="D180" t="str">
         <v>2026-06-09</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Crying Fire - Single</v>
+        <v>Hum of Hurt</v>
       </c>
       <c r="G180" t="str">
-        <v>4:08</v>
+        <v>1:43</v>
       </c>
       <c r="H180" t="str">
-        <v>Avatar</v>
+        <v>Converge</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/avatar/187616241</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
+        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
       </c>
       <c r="L180" t="str">
-        <v>Crying Fire - Avatar</v>
+        <v>Slip the Noose - Converge</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>NI NA’</v>
+        <v>Crying Fire</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
+        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
       </c>
       <c r="D181" t="str">
         <v>2026-06-09</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>sorry si soy GRRRIS</v>
+        <v>Crying Fire - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:53</v>
+        <v>4:08</v>
       </c>
       <c r="H181" t="str">
-        <v>ROBI</v>
+        <v>Avatar</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/robi/1458047972</v>
+        <v>https://music.apple.com/us/artist/avatar/187616241</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
+        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
       </c>
       <c r="L181" t="str">
-        <v>NI NA’ - ROBI</v>
+        <v>Crying Fire - Avatar</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Holding Back</v>
+        <v>NI NA’</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
+        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
       </c>
       <c r="D182" t="str">
         <v>2026-06-09</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>AMA</v>
+        <v>sorry si soy GRRRIS</v>
       </c>
       <c r="G182" t="str">
-        <v>3:19</v>
+        <v>2:53</v>
       </c>
       <c r="H182" t="str">
-        <v>Ama</v>
+        <v>ROBI</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/robi/1458047972</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
+        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
       </c>
       <c r="L182" t="str">
-        <v>Holding Back - Ama</v>
+        <v>NI NA’ - ROBI</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>you're still mine</v>
+        <v>Holding Back</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
+        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
       </c>
       <c r="D183" t="str">
         <v>2026-06-09</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>you're still mine - Single</v>
+        <v>AMA</v>
       </c>
       <c r="G183" t="str">
         <v>3:19</v>
       </c>
       <c r="H183" t="str">
-        <v>Lexi Jayde</v>
+        <v>Ama</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
+        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
       </c>
       <c r="L183" t="str">
-        <v>you're still mine - Lexi Jayde</v>
+        <v>Holding Back - Ama</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>teksi</v>
+        <v>you're still mine</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/teksi/6769899742</v>
+        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
       </c>
       <c r="D184" t="str">
         <v>2026-06-09</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>pOCHO</v>
+        <v>you're still mine - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:48</v>
+        <v>3:19</v>
       </c>
       <c r="H184" t="str">
-        <v>8onthebeat</v>
+        <v>Lexi Jayde</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
+        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/teksi/6769899739</v>
+        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
       </c>
       <c r="L184" t="str">
-        <v>teksi - 8onthebeat</v>
+        <v>you're still mine - Lexi Jayde</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Let You Go</v>
+        <v>teksi</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
+        <v>https://music.apple.com/us/song/teksi/6769899742</v>
       </c>
       <c r="D185" t="str">
         <v>2026-06-09</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Let You Go - Single</v>
+        <v>pOCHO</v>
       </c>
       <c r="G185" t="str">
-        <v>1:37</v>
+        <v>2:48</v>
       </c>
       <c r="H185" t="str">
-        <v>Nate Sib</v>
+        <v>8onthebeat</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
+        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
+        <v>https://music.apple.com/us/album/teksi/6769899739</v>
       </c>
       <c r="L185" t="str">
-        <v>Let You Go - Nate Sib</v>
+        <v>teksi - 8onthebeat</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Dis-Moi</v>
+        <v>Let You Go</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
+        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
       </c>
       <c r="D186" t="str">
         <v>2026-06-09</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>CINNA</v>
+        <v>Let You Go - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:27</v>
+        <v>1:37</v>
       </c>
       <c r="H186" t="str">
-        <v>Cannelle</v>
+        <v>Nate Sib</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
+        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
+        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
       </c>
       <c r="L186" t="str">
-        <v>Dis-Moi - Cannelle</v>
+        <v>Let You Go - Nate Sib</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Leverage</v>
+        <v>Dis-Moi</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/leverage/6776432312</v>
+        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
       </c>
       <c r="D187" t="str">
         <v>2026-06-09</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Heaven on Mars</v>
+        <v>CINNA</v>
       </c>
       <c r="G187" t="str">
-        <v>3:04</v>
+        <v>2:27</v>
       </c>
       <c r="H187" t="str">
-        <v>NoCap</v>
+        <v>Cannelle</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
+        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/leverage/6776432217</v>
+        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
       </c>
       <c r="L187" t="str">
-        <v>Leverage - NoCap</v>
+        <v>Dis-Moi - Cannelle</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Kool Aid</v>
+        <v>Leverage</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
+        <v>https://music.apple.com/us/song/leverage/6776432312</v>
       </c>
       <c r="D188" t="str">
         <v>2026-06-09</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Where Have All The Good Men Gone? - EP</v>
+        <v>Heaven on Mars</v>
       </c>
       <c r="G188" t="str">
-        <v>3:40</v>
+        <v>3:04</v>
       </c>
       <c r="H188" t="str">
-        <v>Debbii Dawson</v>
+        <v>NoCap</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
+        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
+        <v>https://music.apple.com/us/album/leverage/6776432217</v>
       </c>
       <c r="L188" t="str">
-        <v>Kool Aid - Debbii Dawson</v>
+        <v>Leverage - NoCap</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Pieces</v>
+        <v>Kool Aid</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/pieces/6771861156</v>
+        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
       </c>
       <c r="D189" t="str">
         <v>2026-06-09</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Pieces - Single</v>
+        <v>Where Have All The Good Men Gone? - EP</v>
       </c>
       <c r="G189" t="str">
-        <v>2:19</v>
+        <v>3:40</v>
       </c>
       <c r="H189" t="str">
-        <v>Dom Innarella</v>
+        <v>Debbii Dawson</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
+        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/pieces/6771861155</v>
+        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
       </c>
       <c r="L189" t="str">
-        <v>Pieces - Dom Innarella</v>
+        <v>Kool Aid - Debbii Dawson</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Mesmerized</v>
+        <v>Pieces</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
+        <v>https://music.apple.com/us/song/pieces/6771861156</v>
       </c>
       <c r="D190" t="str">
         <v>2026-06-09</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Mesmerized - Single</v>
+        <v>Pieces - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:38</v>
+        <v>2:19</v>
       </c>
       <c r="H190" t="str">
-        <v>The Aces</v>
+        <v>Dom Innarella</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
+        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
+        <v>https://music.apple.com/us/album/pieces/6771861155</v>
       </c>
       <c r="L190" t="str">
-        <v>Mesmerized - The Aces</v>
+        <v>Pieces - Dom Innarella</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Perfect 10</v>
+        <v>Mesmerized</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
+        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
       </c>
       <c r="D191" t="str">
         <v>2026-06-09</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>No Hard Feelings (Deluxe)</v>
+        <v>Mesmerized - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:51</v>
+        <v>2:38</v>
       </c>
       <c r="H191" t="str">
-        <v>The Beaches</v>
+        <v>The Aces</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
+        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
+        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
       </c>
       <c r="L191" t="str">
-        <v>Perfect 10 - The Beaches</v>
+        <v>Mesmerized - The Aces</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Recognize</v>
+        <v>Perfect 10</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/recognize/6769164705</v>
+        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
       </c>
       <c r="D192" t="str">
         <v>2026-06-09</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Recognize - Single</v>
+        <v>No Hard Feelings (Deluxe)</v>
       </c>
       <c r="G192" t="str">
-        <v>2:05</v>
+        <v>2:51</v>
       </c>
       <c r="H192" t="str">
-        <v>Fana Hues</v>
+        <v>The Beaches</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
+        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/recognize/6769164704</v>
+        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
       </c>
       <c r="L192" t="str">
-        <v>Recognize - Fana Hues</v>
+        <v>Perfect 10 - The Beaches</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Feel The Vibe</v>
+        <v>Recognize</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
+        <v>https://music.apple.com/us/song/recognize/6769164705</v>
       </c>
       <c r="D193" t="str">
         <v>2026-06-09</v>
@@ -7709,68 +7709,106 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Feel The Vibe</v>
+        <v>Recognize - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:28</v>
+        <v>2:05</v>
       </c>
       <c r="H193" t="str">
-        <v>Above &amp; Beyond</v>
+        <v>Fana Hues</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
+        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
+        <v>https://music.apple.com/us/album/recognize/6769164704</v>
       </c>
       <c r="L193" t="str">
-        <v>Feel The Vibe - Above &amp; Beyond</v>
+        <v>Recognize - Fana Hues</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
+        <v>Feel The Vibe</v>
+      </c>
+      <c r="B194" t="str">
+        <v/>
+      </c>
+      <c r="C194" t="str">
+        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
+      </c>
+      <c r="D194" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E194" t="str">
+        <v/>
+      </c>
+      <c r="F194" t="str">
+        <v>Feel The Vibe</v>
+      </c>
+      <c r="G194" t="str">
+        <v>3:28</v>
+      </c>
+      <c r="H194" t="str">
+        <v>Above &amp; Beyond</v>
+      </c>
+      <c r="I194" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J194" t="str">
+        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
+      </c>
+      <c r="K194" t="str">
+        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
+      </c>
+      <c r="L194" t="str">
+        <v>Feel The Vibe - Above &amp; Beyond</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
         <v>I Never Knew</v>
       </c>
-      <c r="B194" t="str">
-        <v/>
-      </c>
-      <c r="C194" t="str">
+      <c r="B195" t="str">
+        <v/>
+      </c>
+      <c r="C195" t="str">
         <v>https://music.apple.com/us/song/i-never-knew/6764351468</v>
       </c>
-      <c r="D194" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E194" t="str">
-        <v/>
-      </c>
-      <c r="F194" t="str">
+      <c r="D195" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E195" t="str">
+        <v/>
+      </c>
+      <c r="F195" t="str">
         <v>I Never Knew - Single</v>
       </c>
-      <c r="G194" t="str">
+      <c r="G195" t="str">
         <v>3:51</v>
       </c>
-      <c r="H194" t="str">
+      <c r="H195" t="str">
         <v>Adam Ten</v>
       </c>
-      <c r="I194" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J194" t="str">
+      <c r="I195" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J195" t="str">
         <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
-      <c r="K194" t="str">
+      <c r="K195" t="str">
         <v>https://music.apple.com/us/album/i-never-knew/1895744479</v>
       </c>
-      <c r="L194" t="str">
+      <c r="L195" t="str">
         <v>I Never Knew - Adam Ten</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L194"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L195"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-06-week02/titles.xlsx
+++ b/data/global/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L195"/>
+  <dimension ref="A1:L209"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עדן בן זקן וששון איפרם שאולוב מחול</v>
+        <v>תמר ריילי - מרים לי ברמות</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%91%d7%9f-%d7%96%d7%a7%d7%9f-%d7%95%d7%a9%d7%a9%d7%95%d7%9f-%d7%90%d7%99%d7%a4%d7%a8%d7%9d-%d7%a9%d7%90%d7%95%d7%9c%d7%95%d7%91-%d7%9e%d7%97%d7%95%d7%9c/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411289&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-09</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הדואט "מחול" של עדן בן זקן וששון איפרם שאולוב מספק הצצה  למנגנון התעשייתי המשומן של המוזיקה הים-תיכונית העכשווית, ומציג את מה שניתן לכנות "נוסחת הזהב" של הפופ המקומי: טקסט פשטני, מנגינה מלנכולית ושירה מלודרמטית. הטקסט של השיר פונה למכנה המשותף</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עדן בן זקן וששון איפרם שאולוב מחול</v>
+        <v>תמר ריילי - מרים לי ברמות</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
+        <v>תמיר גל - דם זה לא מים</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411288&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-09</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>תמיר גל - דם זה לא מים</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>שניר עוקשי - הבטחות גדולות</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411287&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-09</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
+        <v>שניר עוקשי - הבטחות גדולות</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
+        <v>שירי מימון &amp; עופר ניסים - תסתכל לי בעיניים</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411286&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
       </c>
       <c r="D5" t="str">
         <v>2026-06-09</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>שירי מימון &amp; עופר ניסים - תסתכל לי בעיניים</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>שירז אברהם - את כל הזמן בוכה</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411285&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
       </c>
       <c r="D6" t="str">
         <v>2026-06-09</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>שירז אברהם - את כל הזמן בוכה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
+        <v>רועי לביא - פשוט יודע</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411284&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-09</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>רועי לביא - פשוט יודע</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video)</v>
+        <v>עדן בן זקן &amp; ששון שאולוב - מחול</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411283&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
       </c>
       <c r="D8" t="str">
         <v>2026-06-09</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>עדן בן זקן &amp; ששון שאולוב - מחול</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Reba McEntire - You Never Gave Up On Me</v>
+        <v>הראל מויאל - גיבור מנייר</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411282&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-09</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Reba McEntire</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Reba McEntire - You Never Gave Up On Me - Reba McEntire</v>
+        <v>הראל מויאל - גיבור מנייר</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>elijah woods - Wonder (Official Lyric Video)</v>
+        <v>אלדד ישעיהו - חי את החיים</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411281&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
       </c>
       <c r="D10" t="str">
         <v>2026-06-09</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>elijah woods</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>elijah woods - Wonder (Official Lyric Video) - elijah woods</v>
+        <v>אלדד ישעיהו - חי את החיים</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>אינו - מועדון הלבבות השבורים</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411280&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
       </c>
       <c r="D11" t="str">
         <v>2026-06-09</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Capital FM and XG</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
+        <v>אינו - מועדון הלבבות השבורים</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
+        <v>אוהד שרגאי - נערי שובה אליי קאבר</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411279&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
       </c>
       <c r="D12" t="str">
         <v>2026-06-09</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>אוהד שרגאי - נערי שובה אליי קאבר</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>אוהב חממה - אהבת חינם</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411278&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
       </c>
       <c r="D13" t="str">
         <v>2026-06-09</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>אוהב חממה - אהבת חינם</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
+        <v>עדן בן זקן וששון איפרם שאולוב – מחול</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
+        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%91%d7%9f-%d7%96%d7%a7%d7%9f-%d7%95%d7%a9%d7%a9%d7%95%d7%9f-%d7%90%d7%99%d7%a4%d7%a8%d7%9d-%d7%a9%d7%90%d7%95%d7%9c%d7%95%d7%91-%d7%9e%d7%97%d7%95%d7%9c/</v>
       </c>
       <c r="D14" t="str">
         <v>2026-06-09</v>
@@ -907,16 +907,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>הדואט "מחול" של עדן בן זקן וששון איפרם שאולוב מספק הצצה  למנגנון התעשייתי המשומן של המוזיקה הים-תיכונית העכשווית, ומציג את מה שניתן לכנות "נוסחת הזהב" של הפופ המקומי: טקסט פשטני, מנגינה מלנכולית ושירה מלודרמטית. הטקסט של השיר פונה למכנה המשותף</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>עדן בן זקן וששון איפרם שאולוב – מחול</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>יובל דיין - יובל דיין לייב</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>2026-06-09</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24475&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D15" t="str">
         <v>2026-06-09</v>
@@ -945,16 +945,16 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>20:02</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Capital FM</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
+        <v>יובל דיין - יובל דיין לייב</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
+        <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
       </c>
       <c r="D16" t="str">
         <v>2026-06-09</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
+        <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
       </c>
       <c r="D17" t="str">
         <v>2026-06-09</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
+        <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
       </c>
       <c r="D18" t="str">
         <v>2026-06-09</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B19" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
+        <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
       </c>
       <c r="D19" t="str">
         <v>2026-06-09</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Capital FM and XG</v>
+        <v>Capital FM</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
+        <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
       </c>
       <c r="D20" t="str">
         <v>2026-06-09</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
+        <v>DEEP PURPLE - DIABLO (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
+        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
       </c>
       <c r="D21" t="str">
         <v>2026-06-09</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Capital FM</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
+        <v>Reba McEntire - You Never Gave Up On Me</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
+        <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
       </c>
       <c r="D22" t="str">
         <v>2026-06-09</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Capital FM</v>
+        <v>Reba McEntire</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Reba McEntire - You Never Gave Up On Me - Reba McEntire</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
+        <v>elijah woods - Wonder (Official Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
+        <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
       </c>
       <c r="D23" t="str">
         <v>2026-06-09</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Capital FM</v>
+        <v>elijah woods</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>elijah woods - Wonder (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
+        <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
       </c>
       <c r="D24" t="str">
         <v>2026-06-09</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Capital FM and Take That</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
+        <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
       </c>
       <c r="D25" t="str">
         <v>2026-06-09</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
+        <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
       </c>
       <c r="D26" t="str">
         <v>2026-06-09</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Capital FM and Take That</v>
+        <v>Capital FM</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
+        <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
       </c>
       <c r="D27" t="str">
         <v>2026-06-09</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
+        <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
       </c>
       <c r="D28" t="str">
         <v>2026-06-09</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
+        <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
       </c>
       <c r="D29" t="str">
         <v>2026-06-09</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Capital FM and Take That</v>
+        <v>Capital FM</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
+        <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
       </c>
       <c r="D30" t="str">
         <v>2026-06-09</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
+        <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
       </c>
       <c r="D31" t="str">
         <v>2026-06-09</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
+        <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
       </c>
       <c r="D32" t="str">
         <v>2026-06-09</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
+        <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
       </c>
       <c r="D33" t="str">
         <v>2026-06-09</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B34" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
+        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
       </c>
       <c r="D34" t="str">
         <v>2026-06-09</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B35" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
+        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
       </c>
       <c r="D35" t="str">
         <v>2026-06-09</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
+        <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
       </c>
       <c r="D36" t="str">
         <v>2026-06-09</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B37" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
+        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
       </c>
       <c r="D37" t="str">
         <v>2026-06-09</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
+        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
       </c>
       <c r="D38" t="str">
         <v>2026-06-09</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B39" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
+        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
       </c>
       <c r="D39" t="str">
         <v>2026-06-09</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B40" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
+        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
       </c>
       <c r="D40" t="str">
         <v>2026-06-09</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
+        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
+        <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
       </c>
       <c r="D41" t="str">
         <v>2026-06-09</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B42" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
+        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
       </c>
       <c r="D42" t="str">
         <v>2026-06-09</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
+        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
       </c>
       <c r="D43" t="str">
         <v>2026-06-09</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B44" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
+        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
       </c>
       <c r="D44" t="str">
         <v>2026-06-09</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B45" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
+        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
       </c>
       <c r="D45" t="str">
         <v>2026-06-09</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
+        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B46" t="str">
-        <v>4 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
+        <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
       </c>
       <c r="D46" t="str">
         <v>2026-06-09</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>4 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Capital FM</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B47" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
+        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
       </c>
       <c r="D47" t="str">
         <v>2026-06-09</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>TheCranberriesTV</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B48" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
+        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
       </c>
       <c r="D48" t="str">
         <v>2026-06-09</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Jordana Bryant</v>
+        <v>Capital FM</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
+        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B49" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
+        <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
       </c>
       <c r="D49" t="str">
         <v>2026-06-09</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>3 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Grace Enger</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
+        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B50" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
+        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
       </c>
       <c r="D50" t="str">
         <v>2026-06-09</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>The Offspring</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Lola Young – From Down Here (From The Pool)</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B51" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
+        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
       </c>
       <c r="D51" t="str">
         <v>2026-06-09</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>CAIN - Living Water (Music Video)</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B52" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
+        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
       </c>
       <c r="D52" t="str">
         <v>2026-06-09</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>CAIN</v>
+        <v>Capital FM</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>CAIN - Living Water (Music Video) - CAIN</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
+        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B53" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
+        <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
       </c>
       <c r="D53" t="str">
         <v>2026-06-09</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Eric Clapton</v>
+        <v>Capital FM</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
+        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video)</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B54" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
+        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
       </c>
       <c r="D54" t="str">
         <v>2026-06-09</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Blu DeTiger</v>
+        <v>Capital FM</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B55" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
+        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
       </c>
       <c r="D55" t="str">
         <v>2026-06-09</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Capital FM</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B56" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
+        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
       </c>
       <c r="D56" t="str">
         <v>2026-06-09</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Pink Floyd</v>
+        <v>Capital FM</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Holly Humberstone - it’s just White Noise</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B57" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
+        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
       </c>
       <c r="D57" t="str">
         <v>2026-06-09</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Holly Humberstone</v>
+        <v>Capital FM</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
+        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B58" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
+        <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
       </c>
       <c r="D58" t="str">
         <v>2026-06-09</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Freya Ridings</v>
+        <v>Capital FM</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
+        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
       </c>
       <c r="B59" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
+        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
       </c>
       <c r="D59" t="str">
         <v>2026-06-09</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Muse</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
       </c>
       <c r="B60" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
+        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
       </c>
       <c r="D60" t="str">
         <v>2026-06-09</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Ellie Goulding</v>
+        <v>TheCranberriesTV</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer)</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
+        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
       </c>
       <c r="D61" t="str">
         <v>2026-06-09</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Evanescence</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
+        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
       </c>
       <c r="D62" t="str">
         <v>2026-06-09</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>The Beaches</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Bella White - Stuff (Official Music Video)</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B63" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
+        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
       </c>
       <c r="D63" t="str">
         <v>2026-06-09</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Bella White</v>
+        <v>The Offspring</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer)</v>
+        <v>Lola Young – From Down Here (From The Pool)</v>
       </c>
       <c r="B64" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
+        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
       </c>
       <c r="D64" t="str">
         <v>2026-06-09</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Meduza and 2 more</v>
+        <v>Lola Young</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
+        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>CAIN - Living Water (Lyric Video)</v>
+        <v>CAIN - Living Water (Music Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
+        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
       </c>
       <c r="D65" t="str">
         <v>2026-06-09</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
+        <v>CAIN - Living Water (Music Video) - CAIN</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
+        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
       </c>
       <c r="D66" t="str">
         <v>2026-06-09</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Fitz and the Tantrums</v>
+        <v>Eric Clapton</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video)</v>
+        <v>Blu DeTiger - Whisper (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
+        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
       </c>
       <c r="D67" t="str">
         <v>2026-06-09</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Jeremy Camp</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
+        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
+        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
       </c>
       <c r="D68" t="str">
         <v>2026-06-09</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Alesso</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
+        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
       </c>
       <c r="D69" t="str">
         <v>2026-06-09</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Malcolm Todd</v>
+        <v>Pink Floyd</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer)</v>
+        <v>Holly Humberstone - it’s just White Noise</v>
       </c>
       <c r="B70" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
+        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
       </c>
       <c r="D70" t="str">
         <v>2026-06-09</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
+        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video)</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
+        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
       </c>
       <c r="D71" t="str">
         <v>2026-06-09</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Wyatt Flores</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video) - Wyatt Flores</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
+        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
       </c>
       <c r="D72" t="str">
         <v>2026-06-09</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Mckenna Grace</v>
+        <v>Muse</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video) - Mckenna Grace</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
       </c>
       <c r="B73" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
+        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
       </c>
       <c r="D73" t="str">
         <v>2026-06-09</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Robert Grace</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Boyzone - No Matter What (Live)</v>
+        <v>Evanescence - Sanctuary (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
+        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
       </c>
       <c r="D74" t="str">
         <v>2026-06-09</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Boyzone</v>
+        <v>Evanescence</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Boyzone - No Matter What (Live) - Boyzone</v>
+        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Florrie - The Times (Official Video)</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
+        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
       </c>
       <c r="D75" t="str">
         <v>2026-06-09</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>florriemusic</v>
+        <v>The Beaches</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Florrie - The Times (Official Video) - florriemusic</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer)</v>
+        <v>Bella White - Stuff (Official Music Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
+        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
       </c>
       <c r="D76" t="str">
         <v>2026-06-09</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Madonna</v>
+        <v>Bella White</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer) - Madonna</v>
+        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>DMA'S - Hurracane (Official Video)</v>
+        <v>Meduza, Rani - Silence (Official Visualizer)</v>
       </c>
       <c r="B77" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
+        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
       </c>
       <c r="D77" t="str">
         <v>2026-06-09</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>DMA'S</v>
+        <v>Meduza and 2 more</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>DMA'S - Hurracane (Official Video) - DMA'S</v>
+        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
+        <v>CAIN - Living Water (Lyric Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
+        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
       </c>
       <c r="D78" t="str">
         <v>2026-06-09</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Lainey Wilson and John Mayer</v>
+        <v>CAIN</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio) - Lainey Wilson and John Mayer</v>
+        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
       </c>
       <c r="B79" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
+        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
       </c>
       <c r="D79" t="str">
         <v>2026-06-09</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>ROLE MODEL</v>
+        <v>Fitz and the Tantrums</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video) - ROLE MODEL</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York)</v>
+        <v>Jeremy Camp - Reflector (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
+        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
       </c>
       <c r="D80" t="str">
         <v>2026-06-09</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Shawn Mendes</v>
+        <v>Jeremy Camp</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York) - Shawn Mendes</v>
+        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
       </c>
       <c r="B81" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
+        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
       </c>
       <c r="D81" t="str">
         <v>2026-06-09</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Alesso</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video) - SIENNA SPIRO</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
       </c>
       <c r="B82" t="str">
-        <v>6 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
+        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
       </c>
       <c r="D82" t="str">
         <v>2026-06-09</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>6 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video)</v>
+        <v>Isabel LaRosa - Every Life (Visualizer)</v>
       </c>
       <c r="B83" t="str">
-        <v>6 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
+        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
       </c>
       <c r="D83" t="str">
         <v>2026-06-09</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>6 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Europe</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
+        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
+        <v>Wyatt Flores - Half The Man (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>6 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
+        <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
       </c>
       <c r="D84" t="str">
         <v>2026-06-09</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>6 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Air Supply</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
+        <v>Wyatt Flores - Half The Man (Official Music Video) - Wyatt Flores</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
+        <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>6 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
+        <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
       </c>
       <c r="D85" t="str">
         <v>2026-06-09</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>6 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Julia Cole Music</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
+        <v>Mckenna Grace - Ugly and Rotten (Official Music Video) - Mckenna Grace</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
+        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B86" t="str">
-        <v>6 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
+        <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
       </c>
       <c r="D86" t="str">
         <v>2026-06-09</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>6 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Allen Stone and Placeholder Sessions</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
+        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
+        <v>Boyzone - No Matter What (Live)</v>
       </c>
       <c r="B87" t="str">
-        <v>6 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
+        <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
       </c>
       <c r="D87" t="str">
         <v>2026-06-09</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>6 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Morgan Wallen</v>
+        <v>Boyzone</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
+        <v>Boyzone - No Matter What (Live) - Boyzone</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
+        <v>Florrie - The Times (Official Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>6 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
+        <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
       </c>
       <c r="D88" t="str">
         <v>2026-06-09</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>6 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Billy Idol</v>
+        <v>florriemusic</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
+        <v>Florrie - The Times (Official Video) - florriemusic</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
+        <v>Madonna - Love Sensation (Official Visualizer)</v>
       </c>
       <c r="B89" t="str">
-        <v>11 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
+        <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
       </c>
       <c r="D89" t="str">
         <v>2026-06-09</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>11 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Madonna</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Madonna - Love Sensation (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
+        <v>DMA'S - Hurracane (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
+        <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
       </c>
       <c r="D90" t="str">
         <v>2026-06-09</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Icona Pop</v>
+        <v>DMA'S</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
+        <v>DMA'S - Hurracane (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Hippo Campus - South</v>
+        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
       </c>
       <c r="B91" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
+        <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
       </c>
       <c r="D91" t="str">
         <v>2026-06-09</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>7 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Hippo Campus</v>
+        <v>Lainey Wilson and John Mayer</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Hippo Campus - South - Hippo Campus</v>
+        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio) - Lainey Wilson and John Mayer</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>elijah woods - Old (Treehouse Sessions)</v>
+        <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
+        <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
       </c>
       <c r="D92" t="str">
         <v>2026-06-09</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>elijah woods</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
+        <v>ROLE MODEL - High Hopes 3000 (Official Music Video) - ROLE MODEL</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video)</v>
+        <v>Shawn Mendes - Treat You Better (Live from New York)</v>
       </c>
       <c r="B93" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
+        <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
       </c>
       <c r="D93" t="str">
         <v>2026-06-09</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Shawn Mendes</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
+        <v>Shawn Mendes - Treat You Better (Live from New York) - Shawn Mendes</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video)</v>
+        <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
+        <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
       </c>
       <c r="D94" t="str">
         <v>2026-06-09</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Ariana Grande</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
+        <v>SIENNA SPIRO - The Visitor (Official Music Video) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>LAUREL - Fire Breather</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
       </c>
       <c r="B95" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
+        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
       </c>
       <c r="D95" t="str">
         <v>2026-06-09</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>8 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>LAUREL</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>LAUREL - Fire Breather - LAUREL</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>The Warning - Ego (Performance Video)</v>
+        <v>Europe - The Cult of Ignorance (Official Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>9 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
+        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
       </c>
       <c r="D96" t="str">
         <v>2026-06-09</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>9 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>The Warning</v>
+        <v>Europe</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>The Warning - Ego (Performance Video) - The Warning</v>
+        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>9 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
+        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
       </c>
       <c r="D97" t="str">
         <v>2026-06-09</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>9 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Air Supply</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>9 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
+        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
       </c>
       <c r="D98" t="str">
         <v>2026-06-09</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>9 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Armin van Buuren</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
       </c>
       <c r="B99" t="str">
-        <v>10 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
+        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
       </c>
       <c r="D99" t="str">
         <v>2026-06-09</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>10 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Andrew Bird</v>
+        <v>Allen Stone and Placeholder Sessions</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video)</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
       </c>
       <c r="B100" t="str">
-        <v>10 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
+        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
       </c>
       <c r="D100" t="str">
         <v>2026-06-09</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>10 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Danny Gokey</v>
+        <v>Morgan Wallen</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>10 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
+        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
       </c>
       <c r="D101" t="str">
         <v>2026-06-09</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>10 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Armik</v>
+        <v>Billy Idol</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
       </c>
       <c r="B102" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
+        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
       </c>
       <c r="D102" t="str">
         <v>2026-06-09</v>
@@ -4251,13 +4251,13 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G102" t="str">
         <v/>
       </c>
       <c r="H102" t="str">
-        <v>Holly Humberstone and Free People</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,18 +4269,18 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>True Colors</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>7d ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
+        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
       </c>
       <c r="D103" t="str">
         <v>2026-06-09</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Thank You</v>
+        <v>7d ago</v>
       </c>
       <c r="G103" t="str">
-        <v>3:39</v>
+        <v/>
       </c>
       <c r="H103" t="str">
-        <v>Mike D</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>True Colors - Mike D</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Too Easy</v>
+        <v>Hippo Campus - South</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>8d ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/too-easy/6774752170</v>
+        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
       </c>
       <c r="D104" t="str">
         <v>2026-06-09</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Too Easy - Single</v>
+        <v>8d ago</v>
       </c>
       <c r="G104" t="str">
-        <v>1:54</v>
+        <v/>
       </c>
       <c r="H104" t="str">
-        <v>Tinashe</v>
+        <v>Hippo Campus</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/tinashe/464835513</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/too-easy/6774752168</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>Too Easy - Tinashe</v>
+        <v>Hippo Campus - South - Hippo Campus</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>I Knew It, I Knew You</v>
+        <v>elijah woods - Old (Treehouse Sessions)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>8d ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
+        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
       </c>
       <c r="D105" t="str">
         <v>2026-06-09</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>I Knew It, I Knew You - Single</v>
+        <v>8d ago</v>
       </c>
       <c r="G105" t="str">
-        <v>2:58</v>
+        <v/>
       </c>
       <c r="H105" t="str">
-        <v>Taylor Swift</v>
+        <v>elijah woods</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/i-knew-it-i-knew-you/6775527442</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>I Knew It, I Knew You - Taylor Swift</v>
+        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Love Sensation</v>
+        <v>Nothing But Thieves - Evolution (Official Video)</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>8d ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
+        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
       </c>
       <c r="D106" t="str">
         <v>2026-06-09</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Love Sensation - Single</v>
+        <v>8d ago</v>
       </c>
       <c r="G106" t="str">
-        <v>3:48</v>
+        <v/>
       </c>
       <c r="H106" t="str">
-        <v>Madonna</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/love-sensation/6774810102</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>Love Sensation - Madonna</v>
+        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Mi Yo De Antes</v>
+        <v>Ariana Grande - hate that i made you love me (official music video)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>8d ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
+        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
       </c>
       <c r="D107" t="str">
         <v>2026-06-09</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Mi Yo De Antes - Single</v>
+        <v>8d ago</v>
       </c>
       <c r="G107" t="str">
-        <v>3:04</v>
+        <v/>
       </c>
       <c r="H107" t="str">
-        <v>Ozuna</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/mi-yo-de-antes/6769193983</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>Mi Yo De Antes - Ozuna</v>
+        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Three Nations</v>
+        <v>LAUREL - Fire Breather</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>8d ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/three-nations/6776010602</v>
+        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
       </c>
       <c r="D108" t="str">
         <v>2026-06-09</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Official FIFA World Cup 2026™ Album</v>
+        <v>8d ago</v>
       </c>
       <c r="G108" t="str">
-        <v>3:30</v>
+        <v/>
       </c>
       <c r="H108" t="str">
-        <v>21 Savage</v>
+        <v>LAUREL</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/21-savage/894820464</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/three-nations/6776010591</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>Three Nations - 21 Savage</v>
+        <v>LAUREL - Fire Breather - LAUREL</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Champions (WC 26)</v>
+        <v>The Warning - Ego (Performance Video)</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>9d ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
+        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
       </c>
       <c r="D109" t="str">
         <v>2026-06-09</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Champions (WC 26) - Single</v>
+        <v>9d ago</v>
       </c>
       <c r="G109" t="str">
-        <v>4:15</v>
+        <v/>
       </c>
       <c r="H109" t="str">
-        <v>IShowSpeed</v>
+        <v>The Warning</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/ishowspeed/1574723975</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/champions-wc-26/6775282246</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>Champions (WC 26) - IShowSpeed</v>
+        <v>The Warning - Ego (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>ENCERRONES</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>10d ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/encerrones/6771854522</v>
+        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
       </c>
       <c r="D110" t="str">
         <v>2026-06-09</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>TEOFANIA</v>
+        <v>10d ago</v>
       </c>
       <c r="G110" t="str">
-        <v>2:23</v>
+        <v/>
       </c>
       <c r="H110" t="str">
-        <v>LENCHO</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/encerrones/6771854517</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>ENCERRONES - LENCHO</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Cowgirl</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>10d ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
+        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
       </c>
       <c r="D111" t="str">
         <v>2026-06-09</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>The Outlaw Cherie Lee &amp; Other Western Tales</v>
+        <v>10d ago</v>
       </c>
       <c r="G111" t="str">
-        <v>2:56</v>
+        <v/>
       </c>
       <c r="H111" t="str">
-        <v>Shaboozey</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/cowgirl/1894906682</v>
+        <v/>
       </c>
       <c r="L111" t="str">
-        <v>Cowgirl - Shaboozey</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>PASSENGER</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>11d ago</v>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/passenger/6773456081</v>
+        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
       </c>
       <c r="D112" t="str">
         <v>2026-06-09</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>WILDCHILD</v>
+        <v>11d ago</v>
       </c>
       <c r="G112" t="str">
-        <v>2:39</v>
+        <v/>
       </c>
       <c r="H112" t="str">
-        <v>Alex Warren</v>
+        <v>Andrew Bird</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v/>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/passenger/6773456078</v>
+        <v/>
       </c>
       <c r="L112" t="str">
-        <v>PASSENGER - Alex Warren</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Secret Language</v>
+        <v>Danny Gokey - God's Not (Official Music Video)</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>11d ago</v>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/secret-language/6774223667</v>
+        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
       </c>
       <c r="D113" t="str">
         <v>2026-06-09</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Sweet Fortune</v>
+        <v>11d ago</v>
       </c>
       <c r="G113" t="str">
-        <v>3:53</v>
+        <v/>
       </c>
       <c r="H113" t="str">
-        <v>Ryan Beatty</v>
+        <v>Danny Gokey</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/ryan-beatty/483234172</v>
+        <v/>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/secret-language/6774223660</v>
+        <v/>
       </c>
       <c r="L113" t="str">
-        <v>Secret Language - Ryan Beatty</v>
+        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>High Hopes 3000</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B114" t="str">
-        <v/>
+        <v>11d ago</v>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
+        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
       </c>
       <c r="D114" t="str">
         <v>2026-06-09</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Chuck Timely &amp; The Hourglass</v>
+        <v>11d ago</v>
       </c>
       <c r="G114" t="str">
-        <v>4:05</v>
+        <v/>
       </c>
       <c r="H114" t="str">
-        <v>ROLE MODEL</v>
+        <v>Armik</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/role-model/199215762</v>
+        <v/>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
+        <v/>
       </c>
       <c r="L114" t="str">
-        <v>High Hopes 3000 - ROLE MODEL</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Vertical</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
       </c>
       <c r="B115" t="str">
-        <v/>
+        <v>11d ago</v>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/vertical/1892436336</v>
+        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
       </c>
       <c r="D115" t="str">
         <v>2026-06-09</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Emotional Junglist</v>
+        <v>11d ago</v>
       </c>
       <c r="G115" t="str">
-        <v>2:36</v>
+        <v/>
       </c>
       <c r="H115" t="str">
-        <v>Nia Archives</v>
+        <v>Holly Humberstone and Free People</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v/>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/vertical/1892436329</v>
+        <v/>
       </c>
       <c r="L115" t="str">
-        <v>Vertical - Nia Archives</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>snake the drain</v>
+        <v>Eat For Peace</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
+        <v>https://music.apple.com/us/song/eat-for-peace/1891187413</v>
       </c>
       <c r="D116" t="str">
         <v>2026-06-09</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>this time it’s different / snake the drain - Single</v>
+        <v>Alone Together</v>
       </c>
       <c r="G116" t="str">
-        <v>3:08</v>
+        <v>3:18</v>
       </c>
       <c r="H116" t="str">
-        <v>Devon Again</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
+        <v>https://music.apple.com/us/album/eat-for-peace/1891187411</v>
       </c>
       <c r="L116" t="str">
-        <v>snake the drain - Devon Again</v>
+        <v>Eat For Peace - Show Me the Body</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Every Single Weekend (feat. Jamie xx)</v>
+        <v>Too Easy</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
+        <v>https://music.apple.com/us/song/too-easy/6774752170</v>
       </c>
       <c r="D117" t="str">
         <v>2026-06-09</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
+        <v>Too Easy - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:10</v>
+        <v>1:54</v>
       </c>
       <c r="H117" t="str">
-        <v>The Avalanches</v>
+        <v>Tinashe</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/tinashe/464835513</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
+        <v>https://music.apple.com/us/album/too-easy/6774752168</v>
       </c>
       <c r="L117" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
+        <v>Too Easy - Tinashe</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Bluffin'</v>
+        <v>I Knew It, I Knew You</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
+        <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
       </c>
       <c r="D118" t="str">
         <v>2026-06-09</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Piss In The Wind (Deluxe)</v>
+        <v>I Knew It, I Knew You - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:34</v>
+        <v>2:58</v>
       </c>
       <c r="H118" t="str">
-        <v>Joji</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
+        <v>https://music.apple.com/us/album/i-knew-it-i-knew-you/6775527442</v>
       </c>
       <c r="L118" t="str">
-        <v>Bluffin' - Joji</v>
+        <v>I Knew It, I Knew You - Taylor Swift</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Dreams</v>
+        <v>Love Sensation</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/dreams/1884731028</v>
+        <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
       </c>
       <c r="D119" t="str">
         <v>2026-06-09</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Free Your Mind</v>
+        <v>Love Sensation - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:56</v>
+        <v>3:48</v>
       </c>
       <c r="H119" t="str">
-        <v>Prospa</v>
+        <v>Madonna</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/dreams/1884730177</v>
+        <v>https://music.apple.com/us/album/love-sensation/6774810102</v>
       </c>
       <c r="L119" t="str">
-        <v>Dreams - Prospa</v>
+        <v>Love Sensation - Madonna</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Cotton</v>
+        <v>Mi Yo De Antes</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/cotton/1887627941</v>
+        <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
       </c>
       <c r="D120" t="str">
         <v>2026-06-09</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Cry Baby</v>
+        <v>Mi Yo De Antes - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:43</v>
+        <v>3:04</v>
       </c>
       <c r="H120" t="str">
-        <v>Vince Staples</v>
+        <v>Ozuna</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/cotton/1887627836</v>
+        <v>https://music.apple.com/us/album/mi-yo-de-antes/6769193983</v>
       </c>
       <c r="L120" t="str">
-        <v>Cotton - Vince Staples</v>
+        <v>Mi Yo De Antes - Ozuna</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Black Prada Dress</v>
+        <v>Three Nations</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
+        <v>https://music.apple.com/us/song/three-nations/6776010602</v>
       </c>
       <c r="D121" t="str">
         <v>2026-06-09</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>I Know Too Much</v>
+        <v>Official FIFA World Cup 2026™ Album</v>
       </c>
       <c r="G121" t="str">
-        <v>3:19</v>
+        <v>3:30</v>
       </c>
       <c r="H121" t="str">
-        <v>Ellie Goulding</v>
+        <v>21 Savage</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
+        <v>https://music.apple.com/us/artist/21-savage/894820464</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
+        <v>https://music.apple.com/us/album/three-nations/6776010591</v>
       </c>
       <c r="L121" t="str">
-        <v>Black Prada Dress - Ellie Goulding</v>
+        <v>Three Nations - 21 Savage</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Don’t Break Her Heart</v>
+        <v>Champions (WC 26)</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
+        <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
       </c>
       <c r="D122" t="str">
         <v>2026-06-09</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>THERAPY AT THE CLUB</v>
+        <v>Champions (WC 26) - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:44</v>
+        <v>4:15</v>
       </c>
       <c r="H122" t="str">
-        <v>FLO</v>
+        <v>IShowSpeed</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/ishowspeed/1574723975</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
+        <v>https://music.apple.com/us/album/champions-wc-26/6775282246</v>
       </c>
       <c r="L122" t="str">
-        <v>Don’t Break Her Heart - FLO</v>
+        <v>Champions (WC 26) - IShowSpeed</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Sexy Ladies (feat. UCB)</v>
+        <v>ENCERRONES</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
+        <v>https://music.apple.com/us/song/encerrones/6771854522</v>
       </c>
       <c r="D123" t="str">
         <v>2026-06-09</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>BITCH</v>
+        <v>TEOFANIA</v>
       </c>
       <c r="G123" t="str">
-        <v>2:50</v>
+        <v>2:23</v>
       </c>
       <c r="H123" t="str">
-        <v>Lizzo</v>
+        <v>LENCHO</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
+        <v>https://music.apple.com/us/album/encerrones/6771854517</v>
       </c>
       <c r="L123" t="str">
-        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
+        <v>ENCERRONES - LENCHO</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Noche Without You</v>
+        <v>Cowgirl</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
+        <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
       </c>
       <c r="D124" t="str">
         <v>2026-06-09</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>SOMA</v>
+        <v>The Outlaw Cherie Lee &amp; Other Western Tales</v>
       </c>
       <c r="G124" t="str">
-        <v>3:23</v>
+        <v>2:56</v>
       </c>
       <c r="H124" t="str">
-        <v>Skrillex</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
+        <v>https://music.apple.com/us/album/cowgirl/1894906682</v>
       </c>
       <c r="L124" t="str">
-        <v>Noche Without You - Skrillex</v>
+        <v>Cowgirl - Shaboozey</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Difficult Love</v>
+        <v>PASSENGER</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
+        <v>https://music.apple.com/us/song/passenger/6773456081</v>
       </c>
       <c r="D125" t="str">
         <v>2026-06-09</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Do That Again</v>
+        <v>WILDCHILD</v>
       </c>
       <c r="G125" t="str">
-        <v>2:33</v>
+        <v>2:39</v>
       </c>
       <c r="H125" t="str">
-        <v>Malcolm Todd</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
+        <v>https://music.apple.com/us/album/passenger/6773456078</v>
       </c>
       <c r="L125" t="str">
-        <v>Difficult Love - Malcolm Todd</v>
+        <v>PASSENGER - Alex Warren</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Tastes So Good</v>
+        <v>Secret Language</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
+        <v>https://music.apple.com/us/song/secret-language/6774223667</v>
       </c>
       <c r="D126" t="str">
         <v>2026-06-09</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Dinner Party</v>
+        <v>Sweet Fortune</v>
       </c>
       <c r="G126" t="str">
-        <v>3:05</v>
+        <v>3:53</v>
       </c>
       <c r="H126" t="str">
-        <v>Niall Horan</v>
+        <v>Ryan Beatty</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/ryan-beatty/483234172</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
+        <v>https://music.apple.com/us/album/secret-language/6774223660</v>
       </c>
       <c r="L126" t="str">
-        <v>Tastes So Good - Niall Horan</v>
+        <v>Secret Language - Ryan Beatty</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Phone, Keys, Wallet</v>
+        <v>True Colors</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
+        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
       </c>
       <c r="D127" t="str">
         <v>2026-06-09</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Phone, Keys, Wallet - Single</v>
+        <v>Thank You</v>
       </c>
       <c r="G127" t="str">
-        <v>2:52</v>
+        <v>3:39</v>
       </c>
       <c r="H127" t="str">
-        <v>Lainey Wilson</v>
+        <v>Mike D</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
+        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
       </c>
       <c r="L127" t="str">
-        <v>Phone, Keys, Wallet - Lainey Wilson</v>
+        <v>True Colors - Mike D</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Madrugada</v>
+        <v>High Hopes 3000</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
+        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
       </c>
       <c r="D128" t="str">
         <v>2026-06-09</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Madrugada - Single</v>
+        <v>Chuck Timely &amp; The Hourglass</v>
       </c>
       <c r="G128" t="str">
-        <v>2:58</v>
+        <v>4:05</v>
       </c>
       <c r="H128" t="str">
-        <v>Chino Pacas</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
+        <v>https://music.apple.com/us/artist/role-model/199215762</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
+        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
       </c>
       <c r="L128" t="str">
-        <v>Madrugada - Chino Pacas</v>
+        <v>High Hopes 3000 - ROLE MODEL</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Oh Chet (feat. Travis Scott)</v>
+        <v>Vertical</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
+        <v>https://music.apple.com/us/song/vertical/1892436336</v>
       </c>
       <c r="D129" t="str">
         <v>2026-06-09</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Single</v>
+        <v>Emotional Junglist</v>
       </c>
       <c r="G129" t="str">
-        <v>2:23</v>
+        <v>2:36</v>
       </c>
       <c r="H129" t="str">
-        <v>Jey One</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
+        <v>https://music.apple.com/us/album/vertical/1892436329</v>
       </c>
       <c r="L129" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
+        <v>Vertical - Nia Archives</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>An Hour or So (Live at Apple Music Radio)</v>
+        <v>snake the drain</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
+        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
       </c>
       <c r="D130" t="str">
         <v>2026-06-09</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>this time it’s different / snake the drain - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:02</v>
+        <v>3:08</v>
       </c>
       <c r="H130" t="str">
-        <v>Benny G</v>
+        <v>Devon Again</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
+        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
       </c>
       <c r="L130" t="str">
-        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
+        <v>snake the drain - Devon Again</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>it’s just White Noise</v>
+        <v>Every Single Weekend (feat. Jamie xx)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
+        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D131" t="str">
         <v>2026-06-09</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>it’s a real Cruel World - EP</v>
+        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:57</v>
+        <v>2:10</v>
       </c>
       <c r="H131" t="str">
-        <v>Holly Humberstone</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
+        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
       </c>
       <c r="L131" t="str">
-        <v>it’s just White Noise - Holly Humberstone</v>
+        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>the feeling</v>
+        <v>Bluffin'</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
+        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
       </c>
       <c r="D132" t="str">
         <v>2026-06-09</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Oh yeah?</v>
+        <v>Piss In The Wind (Deluxe)</v>
       </c>
       <c r="G132" t="str">
-        <v>4:35</v>
+        <v>2:34</v>
       </c>
       <c r="H132" t="str">
-        <v>Steve Lacy</v>
+        <v>Joji</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
+        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
       </c>
       <c r="L132" t="str">
-        <v>the feeling - Steve Lacy</v>
+        <v>Bluffin' - Joji</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>baby (Live at Apple Music Radio)</v>
+        <v>Dreams</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
+        <v>https://music.apple.com/us/song/dreams/1884731028</v>
       </c>
       <c r="D133" t="str">
         <v>2026-06-09</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="G133" t="str">
-        <v>3:14</v>
+        <v>3:56</v>
       </c>
       <c r="H133" t="str">
-        <v>Gabriel Jacoby</v>
+        <v>Prospa</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
+        <v>https://music.apple.com/us/album/dreams/1884730177</v>
       </c>
       <c r="L133" t="str">
-        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
+        <v>Dreams - Prospa</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Drop The Lo</v>
+        <v>Cotton</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
+        <v>https://music.apple.com/us/song/cotton/1887627941</v>
       </c>
       <c r="D134" t="str">
         <v>2026-06-09</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Drop The Lo - Single</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G134" t="str">
-        <v>2:41</v>
+        <v>3:43</v>
       </c>
       <c r="H134" t="str">
-        <v>Bryson Tiller</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
+        <v>https://music.apple.com/us/album/cotton/1887627836</v>
       </c>
       <c r="L134" t="str">
-        <v>Drop The Lo - Bryson Tiller</v>
+        <v>Cotton - Vince Staples</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>GANG BIZNESS feat paygotti</v>
+        <v>Black Prada Dress</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
+        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
       </c>
       <c r="D135" t="str">
         <v>2026-06-09</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>GANG BIZNESS feat paygotti - Single</v>
+        <v>I Know Too Much</v>
       </c>
       <c r="G135" t="str">
-        <v>2:47</v>
+        <v>3:19</v>
       </c>
       <c r="H135" t="str">
-        <v>YG</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
+        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
       </c>
       <c r="L135" t="str">
-        <v>GANG BIZNESS feat paygotti - YG</v>
+        <v>Black Prada Dress - Ellie Goulding</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Lay It Down</v>
+        <v>Don’t Break Her Heart</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
+        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
       </c>
       <c r="D136" t="str">
         <v>2026-06-09</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Lay It Down - Single</v>
+        <v>THERAPY AT THE CLUB</v>
       </c>
       <c r="G136" t="str">
-        <v>2:38</v>
+        <v>3:44</v>
       </c>
       <c r="H136" t="str">
-        <v>FattMack</v>
+        <v>FLO</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
+        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
       </c>
       <c r="L136" t="str">
-        <v>Lay It Down - FattMack</v>
+        <v>Don’t Break Her Heart - FLO</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>WAX PAPER</v>
+        <v>Sexy Ladies (feat. UCB)</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
+        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
       </c>
       <c r="D137" t="str">
         <v>2026-06-09</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>WHACK'S MUSEUM</v>
+        <v>BITCH</v>
       </c>
       <c r="G137" t="str">
-        <v>2:43</v>
+        <v>2:50</v>
       </c>
       <c r="H137" t="str">
-        <v>Tierra Whack</v>
+        <v>Lizzo</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
+        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
       </c>
       <c r="L137" t="str">
-        <v>WAX PAPER - Tierra Whack</v>
+        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>abusadOra (tambores)</v>
+        <v>Noche Without You</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
+        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
       </c>
       <c r="D138" t="str">
         <v>2026-06-09</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>ANTES DE QUE SEA TARDE</v>
+        <v>SOMA</v>
       </c>
       <c r="G138" t="str">
-        <v>3:11</v>
+        <v>3:23</v>
       </c>
       <c r="H138" t="str">
-        <v>Yorghaki</v>
+        <v>Skrillex</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
+        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
       </c>
       <c r="L138" t="str">
-        <v>abusadOra (tambores) - Yorghaki</v>
+        <v>Noche Without You - Skrillex</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Ruin</v>
+        <v>Difficult Love</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/ruin/6763176090</v>
+        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
       </c>
       <c r="D139" t="str">
         <v>2026-06-09</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Labor Of Love</v>
+        <v>Do That Again</v>
       </c>
       <c r="G139" t="str">
-        <v>3:19</v>
+        <v>2:33</v>
       </c>
       <c r="H139" t="str">
-        <v>Blxst</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/ruin/1895199881</v>
+        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
       </c>
       <c r="L139" t="str">
-        <v>Ruin - Blxst</v>
+        <v>Difficult Love - Malcolm Todd</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Do Today</v>
+        <v>Tastes So Good</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/do-today/1893402864</v>
+        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
       </c>
       <c r="D140" t="str">
         <v>2026-06-09</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Grateful</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G140" t="str">
-        <v>4:14</v>
+        <v>3:05</v>
       </c>
       <c r="H140" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/do-today/1893402542</v>
+        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
       </c>
       <c r="L140" t="str">
-        <v>Do Today - The Red Clay Strays</v>
+        <v>Tastes So Good - Niall Horan</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Stone Over Water</v>
+        <v>Phone, Keys, Wallet</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
+        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
       </c>
       <c r="D141" t="str">
         <v>2026-06-09</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>I Built You A Tower</v>
+        <v>Phone, Keys, Wallet - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:14</v>
+        <v>2:52</v>
       </c>
       <c r="H141" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
+        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
       </c>
       <c r="L141" t="str">
-        <v>Stone Over Water - Death Cab for Cutie</v>
+        <v>Phone, Keys, Wallet - Lainey Wilson</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
+        <v>Madrugada</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
+        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
       </c>
       <c r="D142" t="str">
         <v>2026-06-09</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Weezer</v>
+        <v>Madrugada - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:34</v>
+        <v>2:58</v>
       </c>
       <c r="H142" t="str">
-        <v>Weezer</v>
+        <v>Chino Pacas</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/weezer/115234</v>
+        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
+        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
       </c>
       <c r="L142" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
+        <v>Madrugada - Chino Pacas</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Tell Me When You've Had Enough</v>
+        <v>Oh Chet (feat. Travis Scott)</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
+        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
       </c>
       <c r="D143" t="str">
         <v>2026-06-09</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Sanctuary</v>
+        <v>Oh Chet (feat. Travis Scott) - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:19</v>
+        <v>2:23</v>
       </c>
       <c r="H143" t="str">
-        <v>Evanescence</v>
+        <v>Jey One</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
+        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
       </c>
       <c r="L143" t="str">
-        <v>Tell Me When You've Had Enough - Evanescence</v>
+        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Your Ghost Again</v>
+        <v>An Hour or So (Live at Apple Music Radio)</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
+        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
       </c>
       <c r="D144" t="str">
         <v>2026-06-09</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Your Ghost Again - Single</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G144" t="str">
-        <v>4:35</v>
+        <v>3:02</v>
       </c>
       <c r="H144" t="str">
-        <v>Mastodon</v>
+        <v>Benny G</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
+        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
       </c>
       <c r="L144" t="str">
-        <v>Your Ghost Again - Mastodon</v>
+        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Nightshift Superstar</v>
+        <v>it’s just White Noise</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
+        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
       </c>
       <c r="D145" t="str">
         <v>2026-06-09</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>The Wow! Signal</v>
+        <v>it’s a real Cruel World - EP</v>
       </c>
       <c r="G145" t="str">
-        <v>4:07</v>
+        <v>3:57</v>
       </c>
       <c r="H145" t="str">
-        <v>Muse</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
+        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
       </c>
       <c r="L145" t="str">
-        <v>Nightshift Superstar - Muse</v>
+        <v>it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>UNDER THE RHYTHM</v>
+        <v>the feeling</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
+        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
       </c>
       <c r="D146" t="str">
         <v>2026-06-09</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>ADAM</v>
+        <v>Oh yeah?</v>
       </c>
       <c r="G146" t="str">
-        <v>2:50</v>
+        <v>4:35</v>
       </c>
       <c r="H146" t="str">
-        <v>Adam Lambert</v>
+        <v>Steve Lacy</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
+        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
+        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
       </c>
       <c r="L146" t="str">
-        <v>UNDER THE RHYTHM - Adam Lambert</v>
+        <v>the feeling - Steve Lacy</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>You’re Mine</v>
+        <v>baby (Live at Apple Music Radio)</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
+        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
       </c>
       <c r="D147" t="str">
         <v>2026-06-09</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Papercut</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G147" t="str">
-        <v>4:25</v>
+        <v>3:14</v>
       </c>
       <c r="H147" t="str">
-        <v>Imani Imani</v>
+        <v>Gabriel Jacoby</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
+        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
+        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
       </c>
       <c r="L147" t="str">
-        <v>You’re Mine - Imani Imani</v>
+        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>point blank</v>
+        <v>Drop The Lo</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
+        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
       </c>
       <c r="D148" t="str">
         <v>2026-06-09</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>new avatar</v>
+        <v>Drop The Lo - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>4:26</v>
+        <v>2:41</v>
       </c>
       <c r="H148" t="str">
-        <v>Kelela</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
+        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
       </c>
       <c r="L148" t="str">
-        <v>point blank - Kelela</v>
+        <v>Drop The Lo - Bryson Tiller</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>that's my beach!</v>
+        <v>GANG BIZNESS feat paygotti</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
+        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
       </c>
       <c r="D149" t="str">
         <v>2026-06-09</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>GANG BIZNESS feat paygotti - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:18</v>
+        <v>2:47</v>
       </c>
       <c r="H149" t="str">
-        <v>horsegiirL</v>
+        <v>YG</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
+        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
       </c>
       <c r="L149" t="str">
-        <v>that's my beach! - horsegiirL</v>
+        <v>GANG BIZNESS feat paygotti - YG</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>In Your Eyes</v>
+        <v>Lay It Down</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
+        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
       </c>
       <c r="D150" t="str">
         <v>2026-06-09</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>In Your Eyes - Single</v>
+        <v>Lay It Down - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>3:36</v>
+        <v>2:38</v>
       </c>
       <c r="H150" t="str">
-        <v>Alesso</v>
+        <v>FattMack</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/alesso/432464201</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
+        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
       </c>
       <c r="L150" t="str">
-        <v>In Your Eyes - Alesso</v>
+        <v>Lay It Down - FattMack</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>ALL OR NOTHING</v>
+        <v>WAX PAPER</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
+        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
       </c>
       <c r="D151" t="str">
         <v>2026-06-09</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>ALL OR NOTHING - Single</v>
+        <v>WHACK'S MUSEUM</v>
       </c>
       <c r="G151" t="str">
-        <v>3:17</v>
+        <v>2:43</v>
       </c>
       <c r="H151" t="str">
-        <v>Tobe Nwigwe</v>
+        <v>Tierra Whack</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
+        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
+        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
       </c>
       <c r="L151" t="str">
-        <v>ALL OR NOTHING - Tobe Nwigwe</v>
+        <v>WAX PAPER - Tierra Whack</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>IN MY HANDS</v>
+        <v>abusadOra (tambores)</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
+        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
       </c>
       <c r="D152" t="str">
         <v>2026-06-09</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>IN MY HANDS - Single</v>
+        <v>ANTES DE QUE SEA TARDE</v>
       </c>
       <c r="G152" t="str">
-        <v>3:14</v>
+        <v>3:11</v>
       </c>
       <c r="H152" t="str">
-        <v>Alessia Cara</v>
+        <v>Yorghaki</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
+        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
+        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
       </c>
       <c r="L152" t="str">
-        <v>IN MY HANDS - Alessia Cara</v>
+        <v>abusadOra (tambores) - Yorghaki</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Life's a Dream</v>
+        <v>Ruin</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
+        <v>https://music.apple.com/us/song/ruin/6763176090</v>
       </c>
       <c r="D153" t="str">
         <v>2026-06-09</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G153" t="str">
-        <v>5:31</v>
+        <v>3:19</v>
       </c>
       <c r="H153" t="str">
-        <v>Modest Mouse</v>
+        <v>Blxst</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
+        <v>https://music.apple.com/us/album/ruin/1895199881</v>
       </c>
       <c r="L153" t="str">
-        <v>Life's a Dream - Modest Mouse</v>
+        <v>Ruin - Blxst</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
+        <v>Do Today</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
+        <v>https://music.apple.com/us/song/do-today/1893402864</v>
       </c>
       <c r="D154" t="str">
         <v>2026-06-09</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Season of Surrender</v>
+        <v>Grateful</v>
       </c>
       <c r="G154" t="str">
-        <v>4:47</v>
+        <v>4:14</v>
       </c>
       <c r="H154" t="str">
-        <v>August Burns Red</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
+        <v>https://music.apple.com/us/album/do-today/1893402542</v>
       </c>
       <c r="L154" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
+        <v>Do Today - The Red Clay Strays</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Shine</v>
+        <v>Stone Over Water</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/shine/6764654536</v>
+        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
       </c>
       <c r="D155" t="str">
         <v>2026-06-09</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Black Mozart</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G155" t="str">
-        <v>2:27</v>
+        <v>3:14</v>
       </c>
       <c r="H155" t="str">
-        <v>Jon Batiste</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/shine/1895866355</v>
+        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
       </c>
       <c r="L155" t="str">
-        <v>Shine - Jon Batiste</v>
+        <v>Stone Over Water - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Half The Man</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
+        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
       </c>
       <c r="D156" t="str">
         <v>2026-06-09</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Scared of Heights</v>
+        <v>Weezer</v>
       </c>
       <c r="G156" t="str">
-        <v>3:56</v>
+        <v>3:34</v>
       </c>
       <c r="H156" t="str">
-        <v>Wyatt Flores</v>
+        <v>Weezer</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/weezer/115234</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
+        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
       </c>
       <c r="L156" t="str">
-        <v>Half The Man - Wyatt Flores</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Preacher’s Kid</v>
+        <v>Tell Me When You've Had Enough</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
+        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
       </c>
       <c r="D157" t="str">
         <v>2026-06-09</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Preacher’s Kid - Single</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G157" t="str">
-        <v>5:02</v>
+        <v>3:19</v>
       </c>
       <c r="H157" t="str">
-        <v>Stephen Wilson Jr.</v>
+        <v>Evanescence</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
+        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
       </c>
       <c r="L157" t="str">
-        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
+        <v>Tell Me When You've Had Enough - Evanescence</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Weak</v>
+        <v>Your Ghost Again</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/weak/6771151098</v>
+        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
       </c>
       <c r="D158" t="str">
         <v>2026-06-09</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Weak - Single</v>
+        <v>Your Ghost Again - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:28</v>
+        <v>4:35</v>
       </c>
       <c r="H158" t="str">
-        <v>Naomi Sharon</v>
+        <v>Mastodon</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/weak/6771151088</v>
+        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
       </c>
       <c r="L158" t="str">
-        <v>Weak - Naomi Sharon</v>
+        <v>Your Ghost Again - Mastodon</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>ALL NIGHT LONG</v>
+        <v>Nightshift Superstar</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
+        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
       </c>
       <c r="D159" t="str">
         <v>2026-06-09</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>A Rii Set</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G159" t="str">
-        <v>2:28</v>
+        <v>4:07</v>
       </c>
       <c r="H159" t="str">
-        <v>Pheelz</v>
+        <v>Muse</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
+        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
       </c>
       <c r="L159" t="str">
-        <v>ALL NIGHT LONG - Pheelz</v>
+        <v>Nightshift Superstar - Muse</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Every Life</v>
+        <v>UNDER THE RHYTHM</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/every-life/6764110978</v>
+        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
       </c>
       <c r="D160" t="str">
         <v>2026-06-09</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>ADAM</v>
       </c>
       <c r="G160" t="str">
-        <v>3:18</v>
+        <v>2:50</v>
       </c>
       <c r="H160" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Adam Lambert</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/every-life/1895644574</v>
+        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
       </c>
       <c r="L160" t="str">
-        <v>Every Life - Isabel LaRosa</v>
+        <v>UNDER THE RHYTHM - Adam Lambert</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Home</v>
+        <v>You’re Mine</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/home/6774718029</v>
+        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
       </c>
       <c r="D161" t="str">
         <v>2026-06-09</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Good Grief</v>
+        <v>Papercut</v>
       </c>
       <c r="G161" t="str">
-        <v>4:53</v>
+        <v>4:25</v>
       </c>
       <c r="H161" t="str">
-        <v>Sara Bareilles</v>
+        <v>Imani Imani</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
+        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/home/6774718027</v>
+        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
       </c>
       <c r="L161" t="str">
-        <v>Home - Sara Bareilles</v>
+        <v>You’re Mine - Imani Imani</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Satalanaaa</v>
+        <v>point blank</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
+        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
       </c>
       <c r="D162" t="str">
         <v>2026-06-09</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Satalanaaa - Single</v>
+        <v>new avatar</v>
       </c>
       <c r="G162" t="str">
-        <v>2:06</v>
+        <v>4:26</v>
       </c>
       <c r="H162" t="str">
-        <v>Pitbull</v>
+        <v>Kelela</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
+        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
       </c>
       <c r="L162" t="str">
-        <v>Satalanaaa - Pitbull</v>
+        <v>point blank - Kelela</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Miss Me More</v>
+        <v>that's my beach!</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
+        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
       </c>
       <c r="D163" t="str">
         <v>2026-06-09</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Confessions of a Lonely Heart</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G163" t="str">
-        <v>2:43</v>
+        <v>3:18</v>
       </c>
       <c r="H163" t="str">
-        <v>Eric Nam</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
+        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
       </c>
       <c r="L163" t="str">
-        <v>Miss Me More - Eric Nam</v>
+        <v>that's my beach! - horsegiirL</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Rituals</v>
+        <v>In Your Eyes</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/rituals/6769628916</v>
+        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
       </c>
       <c r="D164" t="str">
         <v>2026-06-09</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Rituals - Single</v>
+        <v>In Your Eyes - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:10</v>
+        <v>3:36</v>
       </c>
       <c r="H164" t="str">
-        <v>Rico Nasty</v>
+        <v>Alesso</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
+        <v>https://music.apple.com/us/artist/alesso/432464201</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/rituals/6769628915</v>
+        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
       </c>
       <c r="L164" t="str">
-        <v>Rituals - Rico Nasty</v>
+        <v>In Your Eyes - Alesso</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Honeysuckle</v>
+        <v>ALL OR NOTHING</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
+        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
       </c>
       <c r="D165" t="str">
         <v>2026-06-09</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Honeysuckle - Single</v>
+        <v>ALL OR NOTHING - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:15</v>
+        <v>3:17</v>
       </c>
       <c r="H165" t="str">
-        <v>Dylan Gossett</v>
+        <v>Tobe Nwigwe</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
+        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
+        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
       </c>
       <c r="L165" t="str">
-        <v>Honeysuckle - Dylan Gossett</v>
+        <v>ALL OR NOTHING - Tobe Nwigwe</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>listen…</v>
+        <v>IN MY HANDS</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/listen/6775576508</v>
+        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
       </c>
       <c r="D166" t="str">
         <v>2026-06-09</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
+        <v>IN MY HANDS - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>4:08</v>
+        <v>3:14</v>
       </c>
       <c r="H166" t="str">
-        <v>John Williams</v>
+        <v>Alessia Cara</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/john-williams/63748</v>
+        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/listen/6775576506</v>
+        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
       </c>
       <c r="L166" t="str">
-        <v>listen… - John Williams</v>
+        <v>IN MY HANDS - Alessia Cara</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>DEADMEAT</v>
+        <v>Life's a Dream</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
+        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
       </c>
       <c r="D167" t="str">
         <v>2026-06-09</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>DEADMEAT - Single</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G167" t="str">
-        <v>2:52</v>
+        <v>5:31</v>
       </c>
       <c r="H167" t="str">
-        <v>South Arcade</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
+        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
       </c>
       <c r="L167" t="str">
-        <v>DEADMEAT - South Arcade</v>
+        <v>Life's a Dream - Modest Mouse</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Ugly and Rotten</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
+        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
       </c>
       <c r="D168" t="str">
         <v>2026-06-09</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Ugly and Rotten - Single</v>
+        <v>Season of Surrender</v>
       </c>
       <c r="G168" t="str">
-        <v>2:49</v>
+        <v>4:47</v>
       </c>
       <c r="H168" t="str">
-        <v>Mckenna Grace</v>
+        <v>August Burns Red</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
+        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
+        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
       </c>
       <c r="L168" t="str">
-        <v>Ugly and Rotten - Mckenna Grace</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Whisper</v>
+        <v>Shine</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/whisper/6772254272</v>
+        <v>https://music.apple.com/us/song/shine/6764654536</v>
       </c>
       <c r="D169" t="str">
         <v>2026-06-09</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Whisper - Single</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G169" t="str">
-        <v>2:47</v>
+        <v>2:27</v>
       </c>
       <c r="H169" t="str">
-        <v>Blu DeTiger</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/whisper/6772254268</v>
+        <v>https://music.apple.com/us/album/shine/1895866355</v>
       </c>
       <c r="L169" t="str">
-        <v>Whisper - Blu DeTiger</v>
+        <v>Shine - Jon Batiste</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Gecko (feat. Haley Bridge)</v>
+        <v>Half The Man</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
+        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
       </c>
       <c r="D170" t="str">
         <v>2026-06-09</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>How dare you tryna love me? - EP</v>
+        <v>Scared of Heights</v>
       </c>
       <c r="G170" t="str">
-        <v>2:46</v>
+        <v>3:56</v>
       </c>
       <c r="H170" t="str">
-        <v>Olga Myko</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
+        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
       </c>
       <c r="L170" t="str">
-        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
+        <v>Half The Man - Wyatt Flores</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Compa Primo</v>
+        <v>Preacher’s Kid</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
+        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
       </c>
       <c r="D171" t="str">
         <v>2026-06-09</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Compa Primo - Single</v>
+        <v>Preacher’s Kid - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:12</v>
+        <v>5:02</v>
       </c>
       <c r="H171" t="str">
-        <v>Nueva H</v>
+        <v>Stephen Wilson Jr.</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
+        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
+        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
       </c>
       <c r="L171" t="str">
-        <v>Compa Primo - Nueva H</v>
+        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Parachute</v>
+        <v>Weak</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/parachute/6768841410</v>
+        <v>https://music.apple.com/us/song/weak/6771151098</v>
       </c>
       <c r="D172" t="str">
         <v>2026-06-09</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Parachute - Single</v>
+        <v>Weak - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:11</v>
+        <v>3:28</v>
       </c>
       <c r="H172" t="str">
-        <v>Tyler James Bellinger</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/parachute/6768841409</v>
+        <v>https://music.apple.com/us/album/weak/6771151088</v>
       </c>
       <c r="L172" t="str">
-        <v>Parachute - Tyler James Bellinger</v>
+        <v>Weak - Naomi Sharon</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Like a Bubble</v>
+        <v>ALL NIGHT LONG</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
+        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
       </c>
       <c r="D173" t="str">
         <v>2026-06-09</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Imperfect-I'mperfect - EP</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G173" t="str">
-        <v>3:08</v>
+        <v>2:28</v>
       </c>
       <c r="H173" t="str">
-        <v>FIFTY FIFTY</v>
+        <v>Pheelz</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
+        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
       </c>
       <c r="L173" t="str">
-        <v>Like a Bubble - FIFTY FIFTY</v>
+        <v>ALL NIGHT LONG - Pheelz</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Hustle and Opulence in America</v>
+        <v>Every Life</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
+        <v>https://music.apple.com/us/song/every-life/6764110978</v>
       </c>
       <c r="D174" t="str">
         <v>2026-06-09</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>AK Cuts: Vol. 4 - EP</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G174" t="str">
-        <v>3:07</v>
+        <v>3:18</v>
       </c>
       <c r="H174" t="str">
-        <v>Anish Kumar</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
+        <v>https://music.apple.com/us/album/every-life/1895644574</v>
       </c>
       <c r="L174" t="str">
-        <v>Hustle and Opulence in America - Anish Kumar</v>
+        <v>Every Life - Isabel LaRosa</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
+        <v>Home</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
+        <v>https://music.apple.com/us/song/home/6774718029</v>
       </c>
       <c r="D175" t="str">
         <v>2026-06-09</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
+        <v>Good Grief</v>
       </c>
       <c r="G175" t="str">
-        <v>2:47</v>
+        <v>4:53</v>
       </c>
       <c r="H175" t="str">
-        <v>ivri</v>
+        <v>Sara Bareilles</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
+        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
+        <v>https://music.apple.com/us/album/home/6774718027</v>
       </c>
       <c r="L175" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
+        <v>Home - Sara Bareilles</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>CLEAN SWEEP</v>
+        <v>Satalanaaa</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
+        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
       </c>
       <c r="D176" t="str">
         <v>2026-06-09</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>CLEAN SWEEP - Single</v>
+        <v>Satalanaaa - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:11</v>
+        <v>2:06</v>
       </c>
       <c r="H176" t="str">
-        <v>Storm Reid</v>
+        <v>Pitbull</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
+        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
       </c>
       <c r="L176" t="str">
-        <v>CLEAN SWEEP - Storm Reid</v>
+        <v>Satalanaaa - Pitbull</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>CANDYLAND!</v>
+        <v>Miss Me More</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/candyland/6766927008</v>
+        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
       </c>
       <c r="D177" t="str">
         <v>2026-06-09</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>CANDYLAND! - Single</v>
+        <v>Confessions of a Lonely Heart</v>
       </c>
       <c r="G177" t="str">
-        <v>3:15</v>
+        <v>2:43</v>
       </c>
       <c r="H177" t="str">
-        <v>Natanya</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/candyland/6766927000</v>
+        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
       </c>
       <c r="L177" t="str">
-        <v>CANDYLAND! - Natanya</v>
+        <v>Miss Me More - Eric Nam</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Double C</v>
+        <v>Rituals</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/double-c/6771836555</v>
+        <v>https://music.apple.com/us/song/rituals/6769628916</v>
       </c>
       <c r="D178" t="str">
         <v>2026-06-09</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Double C - Single</v>
+        <v>Rituals - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:21</v>
+        <v>2:10</v>
       </c>
       <c r="H178" t="str">
-        <v>Sk8star</v>
+        <v>Rico Nasty</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
+        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/double-c/6771836554</v>
+        <v>https://music.apple.com/us/album/rituals/6769628915</v>
       </c>
       <c r="L178" t="str">
-        <v>Double C - Sk8star</v>
+        <v>Rituals - Rico Nasty</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>madera</v>
+        <v>Honeysuckle</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/madera/6764638112</v>
+        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
       </c>
       <c r="D179" t="str">
         <v>2026-06-09</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>madera/un camino luminoso - Single</v>
+        <v>Honeysuckle - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>5:41</v>
+        <v>3:15</v>
       </c>
       <c r="H179" t="str">
-        <v>Lumtz</v>
+        <v>Dylan Gossett</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
+        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/madera/6764638109</v>
+        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
       </c>
       <c r="L179" t="str">
-        <v>madera - Lumtz</v>
+        <v>Honeysuckle - Dylan Gossett</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Slip the Noose</v>
+        <v>listen…</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
+        <v>https://music.apple.com/us/song/listen/6775576508</v>
       </c>
       <c r="D180" t="str">
         <v>2026-06-09</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Hum of Hurt</v>
+        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G180" t="str">
-        <v>1:43</v>
+        <v>4:08</v>
       </c>
       <c r="H180" t="str">
-        <v>Converge</v>
+        <v>John Williams</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/john-williams/63748</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
+        <v>https://music.apple.com/us/album/listen/6775576506</v>
       </c>
       <c r="L180" t="str">
-        <v>Slip the Noose - Converge</v>
+        <v>listen… - John Williams</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Crying Fire</v>
+        <v>DEADMEAT</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
+        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
       </c>
       <c r="D181" t="str">
         <v>2026-06-09</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Crying Fire - Single</v>
+        <v>DEADMEAT - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>4:08</v>
+        <v>2:52</v>
       </c>
       <c r="H181" t="str">
-        <v>Avatar</v>
+        <v>South Arcade</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/avatar/187616241</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
+        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
       </c>
       <c r="L181" t="str">
-        <v>Crying Fire - Avatar</v>
+        <v>DEADMEAT - South Arcade</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>NI NA’</v>
+        <v>Ugly and Rotten</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
+        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
       </c>
       <c r="D182" t="str">
         <v>2026-06-09</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>sorry si soy GRRRIS</v>
+        <v>Ugly and Rotten - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:53</v>
+        <v>2:49</v>
       </c>
       <c r="H182" t="str">
-        <v>ROBI</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/robi/1458047972</v>
+        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
+        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
       </c>
       <c r="L182" t="str">
-        <v>NI NA’ - ROBI</v>
+        <v>Ugly and Rotten - Mckenna Grace</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Holding Back</v>
+        <v>Whisper</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
+        <v>https://music.apple.com/us/song/whisper/6772254272</v>
       </c>
       <c r="D183" t="str">
         <v>2026-06-09</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>AMA</v>
+        <v>Whisper - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:19</v>
+        <v>2:47</v>
       </c>
       <c r="H183" t="str">
-        <v>Ama</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
+        <v>https://music.apple.com/us/album/whisper/6772254268</v>
       </c>
       <c r="L183" t="str">
-        <v>Holding Back - Ama</v>
+        <v>Whisper - Blu DeTiger</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>you're still mine</v>
+        <v>Gecko (feat. Haley Bridge)</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
+        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
       </c>
       <c r="D184" t="str">
         <v>2026-06-09</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>you're still mine - Single</v>
+        <v>How dare you tryna love me? - EP</v>
       </c>
       <c r="G184" t="str">
-        <v>3:19</v>
+        <v>2:46</v>
       </c>
       <c r="H184" t="str">
-        <v>Lexi Jayde</v>
+        <v>Olga Myko</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
+        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
+        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
       </c>
       <c r="L184" t="str">
-        <v>you're still mine - Lexi Jayde</v>
+        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>teksi</v>
+        <v>Compa Primo</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/teksi/6769899742</v>
+        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
       </c>
       <c r="D185" t="str">
         <v>2026-06-09</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>pOCHO</v>
+        <v>Compa Primo - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:48</v>
+        <v>3:12</v>
       </c>
       <c r="H185" t="str">
-        <v>8onthebeat</v>
+        <v>Nueva H</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
+        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/teksi/6769899739</v>
+        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
       </c>
       <c r="L185" t="str">
-        <v>teksi - 8onthebeat</v>
+        <v>Compa Primo - Nueva H</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Let You Go</v>
+        <v>Parachute</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
+        <v>https://music.apple.com/us/song/parachute/6768841410</v>
       </c>
       <c r="D186" t="str">
         <v>2026-06-09</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Let You Go - Single</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>1:37</v>
+        <v>3:11</v>
       </c>
       <c r="H186" t="str">
-        <v>Nate Sib</v>
+        <v>Tyler James Bellinger</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
+        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
+        <v>https://music.apple.com/us/album/parachute/6768841409</v>
       </c>
       <c r="L186" t="str">
-        <v>Let You Go - Nate Sib</v>
+        <v>Parachute - Tyler James Bellinger</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Dis-Moi</v>
+        <v>Like a Bubble</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
+        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
       </c>
       <c r="D187" t="str">
         <v>2026-06-09</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>CINNA</v>
+        <v>Imperfect-I'mperfect - EP</v>
       </c>
       <c r="G187" t="str">
-        <v>2:27</v>
+        <v>3:08</v>
       </c>
       <c r="H187" t="str">
-        <v>Cannelle</v>
+        <v>FIFTY FIFTY</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
+        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
+        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
       </c>
       <c r="L187" t="str">
-        <v>Dis-Moi - Cannelle</v>
+        <v>Like a Bubble - FIFTY FIFTY</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Leverage</v>
+        <v>Hustle and Opulence in America</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/leverage/6776432312</v>
+        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
       </c>
       <c r="D188" t="str">
         <v>2026-06-09</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Heaven on Mars</v>
+        <v>AK Cuts: Vol. 4 - EP</v>
       </c>
       <c r="G188" t="str">
-        <v>3:04</v>
+        <v>3:07</v>
       </c>
       <c r="H188" t="str">
-        <v>NoCap</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/leverage/6776432217</v>
+        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
       </c>
       <c r="L188" t="str">
-        <v>Leverage - NoCap</v>
+        <v>Hustle and Opulence in America - Anish Kumar</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Kool Aid</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
+        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
       </c>
       <c r="D189" t="str">
         <v>2026-06-09</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Where Have All The Good Men Gone? - EP</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:40</v>
+        <v>2:47</v>
       </c>
       <c r="H189" t="str">
-        <v>Debbii Dawson</v>
+        <v>ivri</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
+        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
       </c>
       <c r="L189" t="str">
-        <v>Kool Aid - Debbii Dawson</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Pieces</v>
+        <v>CLEAN SWEEP</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/pieces/6771861156</v>
+        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
       </c>
       <c r="D190" t="str">
         <v>2026-06-09</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Pieces - Single</v>
+        <v>CLEAN SWEEP - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:19</v>
+        <v>3:11</v>
       </c>
       <c r="H190" t="str">
-        <v>Dom Innarella</v>
+        <v>Storm Reid</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
+        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/pieces/6771861155</v>
+        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
       </c>
       <c r="L190" t="str">
-        <v>Pieces - Dom Innarella</v>
+        <v>CLEAN SWEEP - Storm Reid</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Mesmerized</v>
+        <v>CANDYLAND!</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
+        <v>https://music.apple.com/us/song/candyland/6766927008</v>
       </c>
       <c r="D191" t="str">
         <v>2026-06-09</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Mesmerized - Single</v>
+        <v>CANDYLAND! - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:38</v>
+        <v>3:15</v>
       </c>
       <c r="H191" t="str">
-        <v>The Aces</v>
+        <v>Natanya</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
+        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
+        <v>https://music.apple.com/us/album/candyland/6766927000</v>
       </c>
       <c r="L191" t="str">
-        <v>Mesmerized - The Aces</v>
+        <v>CANDYLAND! - Natanya</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Perfect 10</v>
+        <v>Double C</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
+        <v>https://music.apple.com/us/song/double-c/6771836555</v>
       </c>
       <c r="D192" t="str">
         <v>2026-06-09</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>No Hard Feelings (Deluxe)</v>
+        <v>Double C - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:51</v>
+        <v>2:21</v>
       </c>
       <c r="H192" t="str">
-        <v>The Beaches</v>
+        <v>Sk8star</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
+        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
+        <v>https://music.apple.com/us/album/double-c/6771836554</v>
       </c>
       <c r="L192" t="str">
-        <v>Perfect 10 - The Beaches</v>
+        <v>Double C - Sk8star</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Recognize</v>
+        <v>madera</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/recognize/6769164705</v>
+        <v>https://music.apple.com/us/song/madera/6764638112</v>
       </c>
       <c r="D193" t="str">
         <v>2026-06-09</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Recognize - Single</v>
+        <v>madera/un camino luminoso - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>2:05</v>
+        <v>5:41</v>
       </c>
       <c r="H193" t="str">
-        <v>Fana Hues</v>
+        <v>Lumtz</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
+        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/recognize/6769164704</v>
+        <v>https://music.apple.com/us/album/madera/6764638109</v>
       </c>
       <c r="L193" t="str">
-        <v>Recognize - Fana Hues</v>
+        <v>madera - Lumtz</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Feel The Vibe</v>
+        <v>Slip the Noose</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
+        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
       </c>
       <c r="D194" t="str">
         <v>2026-06-09</v>
@@ -7747,68 +7747,600 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Feel The Vibe</v>
+        <v>Hum of Hurt</v>
       </c>
       <c r="G194" t="str">
-        <v>3:28</v>
+        <v>1:43</v>
       </c>
       <c r="H194" t="str">
-        <v>Above &amp; Beyond</v>
+        <v>Converge</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
+        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
       </c>
       <c r="L194" t="str">
-        <v>Feel The Vibe - Above &amp; Beyond</v>
+        <v>Slip the Noose - Converge</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
+        <v>Crying Fire</v>
+      </c>
+      <c r="B195" t="str">
+        <v/>
+      </c>
+      <c r="C195" t="str">
+        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
+      </c>
+      <c r="D195" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E195" t="str">
+        <v/>
+      </c>
+      <c r="F195" t="str">
+        <v>Crying Fire - Single</v>
+      </c>
+      <c r="G195" t="str">
+        <v>4:08</v>
+      </c>
+      <c r="H195" t="str">
+        <v>Avatar</v>
+      </c>
+      <c r="I195" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J195" t="str">
+        <v>https://music.apple.com/us/artist/avatar/187616241</v>
+      </c>
+      <c r="K195" t="str">
+        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
+      </c>
+      <c r="L195" t="str">
+        <v>Crying Fire - Avatar</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>NI NA’</v>
+      </c>
+      <c r="B196" t="str">
+        <v/>
+      </c>
+      <c r="C196" t="str">
+        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
+      </c>
+      <c r="D196" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E196" t="str">
+        <v/>
+      </c>
+      <c r="F196" t="str">
+        <v>sorry si soy GRRRIS</v>
+      </c>
+      <c r="G196" t="str">
+        <v>2:53</v>
+      </c>
+      <c r="H196" t="str">
+        <v>ROBI</v>
+      </c>
+      <c r="I196" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J196" t="str">
+        <v>https://music.apple.com/us/artist/robi/1458047972</v>
+      </c>
+      <c r="K196" t="str">
+        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
+      </c>
+      <c r="L196" t="str">
+        <v>NI NA’ - ROBI</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>Holding Back</v>
+      </c>
+      <c r="B197" t="str">
+        <v/>
+      </c>
+      <c r="C197" t="str">
+        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
+      </c>
+      <c r="D197" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E197" t="str">
+        <v/>
+      </c>
+      <c r="F197" t="str">
+        <v>AMA</v>
+      </c>
+      <c r="G197" t="str">
+        <v>3:19</v>
+      </c>
+      <c r="H197" t="str">
+        <v>Ama</v>
+      </c>
+      <c r="I197" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J197" t="str">
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+      </c>
+      <c r="K197" t="str">
+        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
+      </c>
+      <c r="L197" t="str">
+        <v>Holding Back - Ama</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>you're still mine</v>
+      </c>
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
+        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v>you're still mine - Single</v>
+      </c>
+      <c r="G198" t="str">
+        <v>3:19</v>
+      </c>
+      <c r="H198" t="str">
+        <v>Lexi Jayde</v>
+      </c>
+      <c r="I198" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J198" t="str">
+        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
+      </c>
+      <c r="K198" t="str">
+        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
+      </c>
+      <c r="L198" t="str">
+        <v>you're still mine - Lexi Jayde</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>teksi</v>
+      </c>
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
+        <v>https://music.apple.com/us/song/teksi/6769899742</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v>pOCHO</v>
+      </c>
+      <c r="G199" t="str">
+        <v>2:48</v>
+      </c>
+      <c r="H199" t="str">
+        <v>8onthebeat</v>
+      </c>
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
+        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
+      </c>
+      <c r="K199" t="str">
+        <v>https://music.apple.com/us/album/teksi/6769899739</v>
+      </c>
+      <c r="L199" t="str">
+        <v>teksi - 8onthebeat</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>Let You Go</v>
+      </c>
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
+        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
+      </c>
+      <c r="D200" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v>Let You Go - Single</v>
+      </c>
+      <c r="G200" t="str">
+        <v>1:37</v>
+      </c>
+      <c r="H200" t="str">
+        <v>Nate Sib</v>
+      </c>
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
+        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
+      </c>
+      <c r="K200" t="str">
+        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
+      </c>
+      <c r="L200" t="str">
+        <v>Let You Go - Nate Sib</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Dis-Moi</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>CINNA</v>
+      </c>
+      <c r="G201" t="str">
+        <v>2:27</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Cannelle</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Dis-Moi - Cannelle</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>Leverage</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/leverage/6776432312</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>Heaven on Mars</v>
+      </c>
+      <c r="G202" t="str">
+        <v>3:04</v>
+      </c>
+      <c r="H202" t="str">
+        <v>NoCap</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/leverage/6776432217</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Leverage - NoCap</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Kool Aid</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v>Where Have All The Good Men Gone? - EP</v>
+      </c>
+      <c r="G203" t="str">
+        <v>3:40</v>
+      </c>
+      <c r="H203" t="str">
+        <v>Debbii Dawson</v>
+      </c>
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
+      </c>
+      <c r="K203" t="str">
+        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Kool Aid - Debbii Dawson</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Pieces</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/pieces/6771861156</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>Pieces - Single</v>
+      </c>
+      <c r="G204" t="str">
+        <v>2:19</v>
+      </c>
+      <c r="H204" t="str">
+        <v>Dom Innarella</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/pieces/6771861155</v>
+      </c>
+      <c r="L204" t="str">
+        <v>Pieces - Dom Innarella</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>Mesmerized</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v>Mesmerized - Single</v>
+      </c>
+      <c r="G205" t="str">
+        <v>2:38</v>
+      </c>
+      <c r="H205" t="str">
+        <v>The Aces</v>
+      </c>
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
+      </c>
+      <c r="K205" t="str">
+        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
+      </c>
+      <c r="L205" t="str">
+        <v>Mesmerized - The Aces</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Perfect 10</v>
+      </c>
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
+        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v>No Hard Feelings (Deluxe)</v>
+      </c>
+      <c r="G206" t="str">
+        <v>2:51</v>
+      </c>
+      <c r="H206" t="str">
+        <v>The Beaches</v>
+      </c>
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
+      </c>
+      <c r="K206" t="str">
+        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
+      </c>
+      <c r="L206" t="str">
+        <v>Perfect 10 - The Beaches</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Recognize</v>
+      </c>
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
+        <v>https://music.apple.com/us/song/recognize/6769164705</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v>Recognize - Single</v>
+      </c>
+      <c r="G207" t="str">
+        <v>2:05</v>
+      </c>
+      <c r="H207" t="str">
+        <v>Fana Hues</v>
+      </c>
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
+        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
+      </c>
+      <c r="K207" t="str">
+        <v>https://music.apple.com/us/album/recognize/6769164704</v>
+      </c>
+      <c r="L207" t="str">
+        <v>Recognize - Fana Hues</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Feel The Vibe</v>
+      </c>
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
+        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
+      </c>
+      <c r="D208" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
+        <v>Feel The Vibe</v>
+      </c>
+      <c r="G208" t="str">
+        <v>3:28</v>
+      </c>
+      <c r="H208" t="str">
+        <v>Above &amp; Beyond</v>
+      </c>
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
+        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
+      </c>
+      <c r="K208" t="str">
+        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
+      </c>
+      <c r="L208" t="str">
+        <v>Feel The Vibe - Above &amp; Beyond</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
         <v>I Never Knew</v>
       </c>
-      <c r="B195" t="str">
-        <v/>
-      </c>
-      <c r="C195" t="str">
+      <c r="B209" t="str">
+        <v/>
+      </c>
+      <c r="C209" t="str">
         <v>https://music.apple.com/us/song/i-never-knew/6764351468</v>
       </c>
-      <c r="D195" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E195" t="str">
-        <v/>
-      </c>
-      <c r="F195" t="str">
+      <c r="D209" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
         <v>I Never Knew - Single</v>
       </c>
-      <c r="G195" t="str">
+      <c r="G209" t="str">
         <v>3:51</v>
       </c>
-      <c r="H195" t="str">
+      <c r="H209" t="str">
         <v>Adam Ten</v>
       </c>
-      <c r="I195" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J195" t="str">
+      <c r="I209" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J209" t="str">
         <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
-      <c r="K195" t="str">
+      <c r="K209" t="str">
         <v>https://music.apple.com/us/album/i-never-knew/1895744479</v>
       </c>
-      <c r="L195" t="str">
+      <c r="L209" t="str">
         <v>I Never Knew - Adam Ten</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L195"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L209"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-06-week02/titles.xlsx
+++ b/data/global/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L209"/>
+  <dimension ref="A1:L203"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תמר ריילי - מרים לי ברמות</v>
+        <v>מוטי כרמל &amp; אביה שרמן - קרוב אליך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411289&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411297&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-09</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תמר ריילי - מרים לי ברמות</v>
+        <v>מוטי כרמל &amp; אביה שרמן - קרוב אליך</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>תמיר גל - דם זה לא מים</v>
+        <v>ליאור מיארה - מחרוזת שבוי לאהבה 2026</v>
       </c>
       <c r="B3" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411288&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411296&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-09</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>תמיר גל - דם זה לא מים</v>
+        <v>ליאור מיארה - מחרוזת שבוי לאהבה 2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שניר עוקשי - הבטחות גדולות</v>
+        <v>ליאור מיארה - מחרוזת נשיקה 2026</v>
       </c>
       <c r="B4" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411287&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411295&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-09</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שניר עוקשי - הבטחות גדולות</v>
+        <v>ליאור מיארה - מחרוזת נשיקה 2026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שירי מימון &amp; עופר ניסים - תסתכל לי בעיניים</v>
+        <v>יאיר בן טוב - מנסה</v>
       </c>
       <c r="B5" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411286&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411294&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D5" t="str">
         <v>2026-06-09</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שירי מימון &amp; עופר ניסים - תסתכל לי בעיניים</v>
+        <v>יאיר בן טוב - מנסה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>שירז אברהם - את כל הזמן בוכה</v>
+        <v>גוסטו - רוב הזמן את אשתי</v>
       </c>
       <c r="B6" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411285&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411293&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D6" t="str">
         <v>2026-06-09</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>שירז אברהם - את כל הזמן בוכה</v>
+        <v>גוסטו - רוב הזמן את אשתי</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>רועי לביא - פשוט יודע</v>
+        <v>אמיר שוהר - מסיבה של השמחות</v>
       </c>
       <c r="B7" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411284&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411292&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-09</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>רועי לביא - פשוט יודע</v>
+        <v>אמיר שוהר - מסיבה של השמחות</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>עדן בן זקן &amp; ששון שאולוב - מחול</v>
+        <v>אוהד חסקי &amp; אליף יילדיז - את בגדת בי</v>
       </c>
       <c r="B8" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411283&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411291&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D8" t="str">
         <v>2026-06-09</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>עדן בן זקן &amp; ששון שאולוב - מחול</v>
+        <v>אוהד חסקי &amp; אליף יילדיז - את בגדת בי</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>הראל מויאל - גיבור מנייר</v>
+        <v>אביתר גואטה - החטא שלי</v>
       </c>
       <c r="B9" t="str">
         <v>2026-06-09</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411282&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411290&amp;sid=55390b5eabec38928044626c162bd3cb</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-09</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>הראל מויאל - גיבור מנייר</v>
+        <v>אביתר גואטה - החטא שלי</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אלדד ישעיהו - חי את החיים</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-06-09</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411281&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
       </c>
       <c r="D10" t="str">
         <v>2026-06-09</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Capital FM</v>
       </c>
       <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אלדד ישעיהו - חי את החיים</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אינו - מועדון הלבבות השבורים</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-06-09</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411280&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
       </c>
       <c r="D11" t="str">
         <v>2026-06-09</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>Capital FM</v>
       </c>
       <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אינו - מועדון הלבבות השבורים</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>אוהד שרגאי - נערי שובה אליי קאבר</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-06-09</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411279&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
       </c>
       <c r="D12" t="str">
         <v>2026-06-09</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>Capital FM</v>
       </c>
       <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>אוהד שרגאי - נערי שובה אליי קאבר</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>אוהב חממה - אהבת חינם</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-06-09</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411278&amp;sid=ea3a31cb60e3660af5e84eef462556aa</v>
+        <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
       </c>
       <c r="D13" t="str">
         <v>2026-06-09</v>
@@ -869,16 +869,16 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>Capital FM</v>
       </c>
       <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>אוהב חממה - אהבת חינם</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>עדן בן זקן וששון איפרם שאולוב – מחול</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-06-09</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%91%d7%9f-%d7%96%d7%a7%d7%9f-%d7%95%d7%a9%d7%a9%d7%95%d7%9f-%d7%90%d7%99%d7%a4%d7%a8%d7%9d-%d7%a9%d7%90%d7%95%d7%9c%d7%95%d7%91-%d7%9e%d7%97%d7%95%d7%9c/</v>
+        <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
       </c>
       <c r="D14" t="str">
         <v>2026-06-09</v>
@@ -907,16 +907,16 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>הדואט "מחול" של עדן בן זקן וששון איפרם שאולוב מספק הצצה  למנגנון התעשייתי המשומן של המוזיקה הים-תיכונית העכשווית, ומציג את מה שניתן לכנות "נוסחת הזהב" של הפופ המקומי: טקסט פשטני, מנגינה מלנכולית ושירה מלודרמטית. הטקסט של השיר פונה למכנה המשותף</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>Capital FM</v>
       </c>
       <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>עדן בן זקן וששון איפרם שאולוב – מחול</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>יובל דיין - יובל דיין לייב</v>
+        <v>DEEP PURPLE - DIABLO (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-06-09</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24475&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
       </c>
       <c r="D15" t="str">
         <v>2026-06-09</v>
@@ -945,16 +945,16 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>20:02</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I15" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>יובל דיין - יובל דיין לייב</v>
+        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
+        <v>Reba McEntire - You Never Gave Up On Me</v>
       </c>
       <c r="B16" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
+        <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
       </c>
       <c r="D16" t="str">
         <v>2026-06-09</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Capital FM</v>
+        <v>Reba McEntire</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Reba McEntire - You Never Gave Up On Me - Reba McEntire</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>elijah woods - Wonder (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
+        <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
       </c>
       <c r="D17" t="str">
         <v>2026-06-09</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Capital FM</v>
+        <v>elijah woods</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
+        <v>elijah woods - Wonder (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B18" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
+        <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
       </c>
       <c r="D18" t="str">
         <v>2026-06-09</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B19" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
+        <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
       </c>
       <c r="D19" t="str">
         <v>2026-06-09</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B20" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
+        <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
       </c>
       <c r="D20" t="str">
         <v>2026-06-09</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video)</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B21" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
+        <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
       </c>
       <c r="D21" t="str">
         <v>2026-06-09</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Capital FM</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Reba McEntire - You Never Gave Up On Me</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B22" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
+        <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
       </c>
       <c r="D22" t="str">
         <v>2026-06-09</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Reba McEntire</v>
+        <v>Capital FM</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Reba McEntire - You Never Gave Up On Me - Reba McEntire</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>elijah woods - Wonder (Official Lyric Video)</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B23" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
+        <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
       </c>
       <c r="D23" t="str">
         <v>2026-06-09</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>elijah woods</v>
+        <v>Capital FM</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>elijah woods - Wonder (Official Lyric Video) - elijah woods</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B24" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
+        <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
       </c>
       <c r="D24" t="str">
         <v>2026-06-09</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Capital FM and XG</v>
+        <v>Capital FM</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
+        <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
       </c>
       <c r="D25" t="str">
         <v>2026-06-09</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B26" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
+        <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
       </c>
       <c r="D26" t="str">
         <v>2026-06-09</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
+        <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
       </c>
       <c r="D27" t="str">
         <v>2026-06-09</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B28" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
+        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
       </c>
       <c r="D28" t="str">
         <v>2026-06-09</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B29" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
+        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
       </c>
       <c r="D29" t="str">
         <v>2026-06-09</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
+        <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
       </c>
       <c r="D30" t="str">
         <v>2026-06-09</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B31" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
+        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
       </c>
       <c r="D31" t="str">
         <v>2026-06-09</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B32" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
+        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
       </c>
       <c r="D32" t="str">
         <v>2026-06-09</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Capital FM and XG</v>
+        <v>Capital FM</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B33" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
+        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
       </c>
       <c r="D33" t="str">
         <v>2026-06-09</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B34" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
+        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
       </c>
       <c r="D34" t="str">
         <v>2026-06-09</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
+        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B35" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
+        <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
       </c>
       <c r="D35" t="str">
         <v>2026-06-09</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
+        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
       </c>
       <c r="D36" t="str">
         <v>2026-06-09</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B37" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
+        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
       </c>
       <c r="D37" t="str">
         <v>2026-06-09</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Capital FM and Take That</v>
+        <v>Capital FM</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
+        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
       </c>
       <c r="D38" t="str">
         <v>2026-06-09</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B39" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
+        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
       </c>
       <c r="D39" t="str">
         <v>2026-06-09</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Capital FM and Take That</v>
+        <v>Capital FM</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
+        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B40" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
+        <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
       </c>
       <c r="D40" t="str">
         <v>2026-06-09</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B41" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
+        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
       </c>
       <c r="D41" t="str">
         <v>2026-06-09</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B42" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
+        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
       </c>
       <c r="D42" t="str">
         <v>2026-06-09</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Capital FM and Take That</v>
+        <v>Capital FM</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
+        <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
       </c>
       <c r="D43" t="str">
         <v>2026-06-09</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B44" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
+        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
       </c>
       <c r="D44" t="str">
         <v>2026-06-09</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B45" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
+        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
       </c>
       <c r="D45" t="str">
         <v>2026-06-09</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B46" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
+        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
       </c>
       <c r="D46" t="str">
         <v>2026-06-09</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B47" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
+        <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
       </c>
       <c r="D47" t="str">
         <v>2026-06-09</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B48" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
+        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
       </c>
       <c r="D48" t="str">
         <v>2026-06-09</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B49" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
+        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
       </c>
       <c r="D49" t="str">
         <v>2026-06-09</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B50" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
+        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
       </c>
       <c r="D50" t="str">
         <v>2026-06-09</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B51" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
+        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
       </c>
       <c r="D51" t="str">
         <v>2026-06-09</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B52" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
+        <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
       </c>
       <c r="D52" t="str">
         <v>2026-06-09</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
       </c>
       <c r="B53" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
+        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
       </c>
       <c r="D53" t="str">
         <v>2026-06-09</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Capital FM</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
       </c>
       <c r="B54" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
+        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
       </c>
       <c r="D54" t="str">
         <v>2026-06-09</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Capital FM</v>
+        <v>TheCranberriesTV</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
+        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
       </c>
       <c r="D55" t="str">
         <v>2026-06-09</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Capital FM</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
+        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
       </c>
       <c r="D56" t="str">
         <v>2026-06-09</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Capital FM</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B57" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
+        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
       </c>
       <c r="D57" t="str">
         <v>2026-06-09</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Capital FM</v>
+        <v>The Offspring</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young – From Down Here (From The Pool)</v>
       </c>
       <c r="B58" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
+        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
       </c>
       <c r="D58" t="str">
         <v>2026-06-09</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Capital FM</v>
+        <v>Lola Young</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
+        <v>CAIN - Living Water (Music Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
+        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
       </c>
       <c r="D59" t="str">
         <v>2026-06-09</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>CAIN</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>CAIN - Living Water (Music Video) - CAIN</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
+        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
       </c>
       <c r="D60" t="str">
         <v>2026-06-09</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>TheCranberriesTV</v>
+        <v>Eric Clapton</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
+        <v>Blu DeTiger - Whisper (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
+        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
       </c>
       <c r="D61" t="str">
         <v>2026-06-09</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Jordana Bryant</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
+        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
+        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
       </c>
       <c r="D62" t="str">
         <v>2026-06-09</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Grace Enger</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
       </c>
       <c r="B63" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
+        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
       </c>
       <c r="D63" t="str">
         <v>2026-06-09</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>The Offspring</v>
+        <v>Pink Floyd</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Lola Young – From Down Here (From The Pool)</v>
+        <v>Holly Humberstone - it’s just White Noise</v>
       </c>
       <c r="B64" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
+        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
       </c>
       <c r="D64" t="str">
         <v>2026-06-09</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Lola Young</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
+        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>CAIN - Living Water (Music Video)</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
+        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
       </c>
       <c r="D65" t="str">
         <v>2026-06-09</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>CAIN</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>CAIN - Living Water (Music Video) - CAIN</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
+        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
       </c>
       <c r="D66" t="str">
         <v>2026-06-09</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Eric Clapton</v>
+        <v>Muse</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video)</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
       </c>
       <c r="B67" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
+        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
       </c>
       <c r="D67" t="str">
         <v>2026-06-09</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Blu DeTiger</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
+        <v>Evanescence - Sanctuary (Official Visualizer)</v>
       </c>
       <c r="B68" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
+        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
       </c>
       <c r="D68" t="str">
         <v>2026-06-09</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Evanescence</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
+        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
       </c>
       <c r="D69" t="str">
         <v>2026-06-09</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Pink Floyd</v>
+        <v>The Beaches</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Holly Humberstone - it’s just White Noise</v>
+        <v>Bella White - Stuff (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
+        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
       </c>
       <c r="D70" t="str">
         <v>2026-06-09</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Holly Humberstone</v>
+        <v>Bella White</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
+        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
+        <v>Meduza, Rani - Silence (Official Visualizer)</v>
       </c>
       <c r="B71" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
+        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
       </c>
       <c r="D71" t="str">
         <v>2026-06-09</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Freya Ridings</v>
+        <v>Meduza and 2 more</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
+        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
+        <v>CAIN - Living Water (Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
+        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
       </c>
       <c r="D72" t="str">
         <v>2026-06-09</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Muse</v>
+        <v>CAIN</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
+        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
       </c>
       <c r="B73" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
+        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
       </c>
       <c r="D73" t="str">
         <v>2026-06-09</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Ellie Goulding</v>
+        <v>Fitz and the Tantrums</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer)</v>
+        <v>Jeremy Camp - Reflector (Official Music Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
+        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
       </c>
       <c r="D74" t="str">
         <v>2026-06-09</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Evanescence</v>
+        <v>Jeremy Camp</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
+        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
+        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
       </c>
       <c r="D75" t="str">
         <v>2026-06-09</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>The Beaches</v>
+        <v>Alesso</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Bella White - Stuff (Official Music Video)</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
+        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
       </c>
       <c r="D76" t="str">
         <v>2026-06-09</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Bella White</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer)</v>
+        <v>Isabel LaRosa - Every Life (Visualizer)</v>
       </c>
       <c r="B77" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
+        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
       </c>
       <c r="D77" t="str">
         <v>2026-06-09</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Meduza and 2 more</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
+        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>CAIN - Living Water (Lyric Video)</v>
+        <v>Wyatt Flores - Half The Man (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
+        <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
       </c>
       <c r="D78" t="str">
         <v>2026-06-09</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>CAIN</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
+        <v>Wyatt Flores - Half The Man (Official Music Video) - Wyatt Flores</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
+        <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
+        <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
       </c>
       <c r="D79" t="str">
         <v>2026-06-09</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Fitz and the Tantrums</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
+        <v>Mckenna Grace - Ugly and Rotten (Official Music Video) - Mckenna Grace</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video)</v>
+        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B80" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
+        <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
       </c>
       <c r="D80" t="str">
         <v>2026-06-09</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Jeremy Camp</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
+        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
+        <v>Boyzone - No Matter What (Live)</v>
       </c>
       <c r="B81" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
+        <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
       </c>
       <c r="D81" t="str">
         <v>2026-06-09</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Alesso</v>
+        <v>Boyzone</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
+        <v>Boyzone - No Matter What (Live) - Boyzone</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
+        <v>Florrie - The Times (Official Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
+        <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
       </c>
       <c r="D82" t="str">
         <v>2026-06-09</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Malcolm Todd</v>
+        <v>florriemusic</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
+        <v>Florrie - The Times (Official Video) - florriemusic</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer)</v>
+        <v>Madonna - Love Sensation (Official Visualizer)</v>
       </c>
       <c r="B83" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
+        <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
       </c>
       <c r="D83" t="str">
         <v>2026-06-09</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Madonna</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
+        <v>Madonna - Love Sensation (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video)</v>
+        <v>DMA'S - Hurracane (Official Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
+        <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
       </c>
       <c r="D84" t="str">
         <v>2026-06-09</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Wyatt Flores</v>
+        <v>DMA'S</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video) - Wyatt Flores</v>
+        <v>DMA'S - Hurracane (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
+        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
       </c>
       <c r="B85" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
+        <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
       </c>
       <c r="D85" t="str">
         <v>2026-06-09</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Mckenna Grace</v>
+        <v>Lainey Wilson and John Mayer</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video) - Mckenna Grace</v>
+        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio) - Lainey Wilson and John Mayer</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>4d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
+        <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
       </c>
       <c r="D86" t="str">
         <v>2026-06-09</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>4d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Robert Grace</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>ROLE MODEL - High Hopes 3000 (Official Music Video) - ROLE MODEL</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Boyzone - No Matter What (Live)</v>
+        <v>Shawn Mendes - Treat You Better (Live from New York)</v>
       </c>
       <c r="B87" t="str">
-        <v>4d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
+        <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
       </c>
       <c r="D87" t="str">
         <v>2026-06-09</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>4d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Boyzone</v>
+        <v>Shawn Mendes</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Boyzone - No Matter What (Live) - Boyzone</v>
+        <v>Shawn Mendes - Treat You Better (Live from New York) - Shawn Mendes</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Florrie - The Times (Official Video)</v>
+        <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>4d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
+        <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
       </c>
       <c r="D88" t="str">
         <v>2026-06-09</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>4d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>florriemusic</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Florrie - The Times (Official Video) - florriemusic</v>
+        <v>SIENNA SPIRO - The Visitor (Official Music Video) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer)</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
       </c>
       <c r="B89" t="str">
-        <v>4d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
+        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
       </c>
       <c r="D89" t="str">
         <v>2026-06-09</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>4d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Madonna</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer) - Madonna</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>DMA'S - Hurracane (Official Video)</v>
+        <v>Europe - The Cult of Ignorance (Official Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
+        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
       </c>
       <c r="D90" t="str">
         <v>2026-06-09</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>DMA'S</v>
+        <v>Europe</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>DMA'S - Hurracane (Official Video) - DMA'S</v>
+        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
+        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
       </c>
       <c r="D91" t="str">
         <v>2026-06-09</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Lainey Wilson and John Mayer</v>
+        <v>Air Supply</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio) - Lainey Wilson and John Mayer</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
+        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
       </c>
       <c r="D92" t="str">
         <v>2026-06-09</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>ROLE MODEL</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video) - ROLE MODEL</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York)</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
       </c>
       <c r="B93" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
+        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
       </c>
       <c r="D93" t="str">
         <v>2026-06-09</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Shawn Mendes</v>
+        <v>Allen Stone and Placeholder Sessions</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York) - Shawn Mendes</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
       </c>
       <c r="B94" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
+        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
       </c>
       <c r="D94" t="str">
         <v>2026-06-09</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Morgan Wallen</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video) - SIENNA SPIRO</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
+        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
       </c>
       <c r="D95" t="str">
         <v>2026-06-09</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Billy Idol</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video)</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
       </c>
       <c r="B96" t="str">
-        <v>6d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
+        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
       </c>
       <c r="D96" t="str">
         <v>2026-06-09</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>6d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Europe</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
+        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
       </c>
       <c r="D97" t="str">
         <v>2026-06-09</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Air Supply</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
+        <v>Hippo Campus - South</v>
       </c>
       <c r="B98" t="str">
-        <v>6d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
+        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
       </c>
       <c r="D98" t="str">
         <v>2026-06-09</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>6d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Julia Cole Music</v>
+        <v>Hippo Campus</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
+        <v>Hippo Campus - South - Hippo Campus</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
+        <v>elijah woods - Old (Treehouse Sessions)</v>
       </c>
       <c r="B99" t="str">
-        <v>6d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
+        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
       </c>
       <c r="D99" t="str">
         <v>2026-06-09</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>6d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Allen Stone and Placeholder Sessions</v>
+        <v>elijah woods</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
+        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
+        <v>Nothing But Thieves - Evolution (Official Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
+        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
       </c>
       <c r="D100" t="str">
         <v>2026-06-09</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Morgan Wallen</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
+        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
+        <v>Ariana Grande - hate that i made you love me (official music video)</v>
       </c>
       <c r="B101" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
+        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
       </c>
       <c r="D101" t="str">
         <v>2026-06-09</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Billy Idol</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
+        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
+        <v>LAUREL - Fire Breather</v>
       </c>
       <c r="B102" t="str">
-        <v>11d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
+        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
       </c>
       <c r="D102" t="str">
         <v>2026-06-09</v>
@@ -4251,13 +4251,13 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>11d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G102" t="str">
         <v/>
       </c>
       <c r="H102" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>LAUREL</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,18 +4269,18 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>LAUREL - Fire Breather - LAUREL</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
+        <v>The Warning - Ego (Performance Video)</v>
       </c>
       <c r="B103" t="str">
-        <v>7d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
+        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
       </c>
       <c r="D103" t="str">
         <v>2026-06-09</v>
@@ -4289,13 +4289,13 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>7d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G103" t="str">
         <v/>
       </c>
       <c r="H103" t="str">
-        <v>Icona Pop</v>
+        <v>The Warning</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4307,18 +4307,18 @@
         <v/>
       </c>
       <c r="L103" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
+        <v>The Warning - Ego (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Hippo Campus - South</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
       </c>
       <c r="B104" t="str">
-        <v>8d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
+        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
       </c>
       <c r="D104" t="str">
         <v>2026-06-09</v>
@@ -4327,13 +4327,13 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>8d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G104" t="str">
         <v/>
       </c>
       <c r="H104" t="str">
-        <v>Hippo Campus</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4345,18 +4345,18 @@
         <v/>
       </c>
       <c r="L104" t="str">
-        <v>Hippo Campus - South - Hippo Campus</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>elijah woods - Old (Treehouse Sessions)</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B105" t="str">
-        <v>8d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
+        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
       </c>
       <c r="D105" t="str">
         <v>2026-06-09</v>
@@ -4365,13 +4365,13 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>8d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G105" t="str">
         <v/>
       </c>
       <c r="H105" t="str">
-        <v>elijah woods</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4383,18 +4383,18 @@
         <v/>
       </c>
       <c r="L105" t="str">
-        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video)</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
       </c>
       <c r="B106" t="str">
-        <v>8d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
+        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
       </c>
       <c r="D106" t="str">
         <v>2026-06-09</v>
@@ -4403,13 +4403,13 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>8d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G106" t="str">
         <v/>
       </c>
       <c r="H106" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Andrew Bird</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4421,18 +4421,18 @@
         <v/>
       </c>
       <c r="L106" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video)</v>
+        <v>Danny Gokey - God's Not (Official Music Video)</v>
       </c>
       <c r="B107" t="str">
-        <v>8d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
+        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
       </c>
       <c r="D107" t="str">
         <v>2026-06-09</v>
@@ -4441,13 +4441,13 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>8d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G107" t="str">
         <v/>
       </c>
       <c r="H107" t="str">
-        <v>Ariana Grande</v>
+        <v>Danny Gokey</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4459,18 +4459,18 @@
         <v/>
       </c>
       <c r="L107" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
+        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>LAUREL - Fire Breather</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B108" t="str">
-        <v>8d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
+        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
       </c>
       <c r="D108" t="str">
         <v>2026-06-09</v>
@@ -4479,13 +4479,13 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>8d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G108" t="str">
         <v/>
       </c>
       <c r="H108" t="str">
-        <v>LAUREL</v>
+        <v>Armik</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4497,18 +4497,18 @@
         <v/>
       </c>
       <c r="L108" t="str">
-        <v>LAUREL - Fire Breather - LAUREL</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>The Warning - Ego (Performance Video)</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
       </c>
       <c r="B109" t="str">
-        <v>9d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
+        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
       </c>
       <c r="D109" t="str">
         <v>2026-06-09</v>
@@ -4517,13 +4517,13 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>9d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G109" t="str">
         <v/>
       </c>
       <c r="H109" t="str">
-        <v>The Warning</v>
+        <v>Holly Humberstone and Free People</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4535,18 +4535,18 @@
         <v/>
       </c>
       <c r="L109" t="str">
-        <v>The Warning - Ego (Performance Video) - The Warning</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
+        <v>Eat For Peace</v>
       </c>
       <c r="B110" t="str">
-        <v>10d ago</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
+        <v>https://music.apple.com/us/song/eat-for-peace/1891187413</v>
       </c>
       <c r="D110" t="str">
         <v>2026-06-09</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>10d ago</v>
+        <v>Alone Together</v>
       </c>
       <c r="G110" t="str">
-        <v/>
+        <v>3:18</v>
       </c>
       <c r="H110" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/eat-for-peace/1891187411</v>
       </c>
       <c r="L110" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
+        <v>Eat For Peace - Show Me the Body</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
+        <v>Too Easy</v>
       </c>
       <c r="B111" t="str">
-        <v>10d ago</v>
+        <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
+        <v>https://music.apple.com/us/song/too-easy/6774752170</v>
       </c>
       <c r="D111" t="str">
         <v>2026-06-09</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>10d ago</v>
+        <v>Too Easy - Single</v>
       </c>
       <c r="G111" t="str">
-        <v/>
+        <v>1:54</v>
       </c>
       <c r="H111" t="str">
-        <v>Armin van Buuren</v>
+        <v>Tinashe</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/tinashe/464835513</v>
       </c>
       <c r="K111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/too-easy/6774752168</v>
       </c>
       <c r="L111" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Too Easy - Tinashe</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
+        <v>I Knew It, I Knew You</v>
       </c>
       <c r="B112" t="str">
-        <v>11d ago</v>
+        <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
+        <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
       </c>
       <c r="D112" t="str">
         <v>2026-06-09</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>11d ago</v>
+        <v>I Knew It, I Knew You - Single</v>
       </c>
       <c r="G112" t="str">
-        <v/>
+        <v>2:58</v>
       </c>
       <c r="H112" t="str">
-        <v>Andrew Bird</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/i-knew-it-i-knew-you/6775527442</v>
       </c>
       <c r="L112" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
+        <v>I Knew It, I Knew You - Taylor Swift</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video)</v>
+        <v>Love Sensation</v>
       </c>
       <c r="B113" t="str">
-        <v>11d ago</v>
+        <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
+        <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
       </c>
       <c r="D113" t="str">
         <v>2026-06-09</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>11d ago</v>
+        <v>Love Sensation - Single</v>
       </c>
       <c r="G113" t="str">
-        <v/>
+        <v>3:48</v>
       </c>
       <c r="H113" t="str">
-        <v>Danny Gokey</v>
+        <v>Madonna</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K113" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/love-sensation/6774810102</v>
       </c>
       <c r="L113" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
+        <v>Love Sensation - Madonna</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Mi Yo De Antes</v>
       </c>
       <c r="B114" t="str">
-        <v>11d ago</v>
+        <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
+        <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
       </c>
       <c r="D114" t="str">
         <v>2026-06-09</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>11d ago</v>
+        <v>Mi Yo De Antes - Single</v>
       </c>
       <c r="G114" t="str">
-        <v/>
+        <v>3:04</v>
       </c>
       <c r="H114" t="str">
-        <v>Armik</v>
+        <v>Ozuna</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
       </c>
       <c r="K114" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/mi-yo-de-antes/6769193983</v>
       </c>
       <c r="L114" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Mi Yo De Antes - Ozuna</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
+        <v>Three Nations</v>
       </c>
       <c r="B115" t="str">
-        <v>11d ago</v>
+        <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
+        <v>https://music.apple.com/us/song/three-nations/6776010602</v>
       </c>
       <c r="D115" t="str">
         <v>2026-06-09</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>11d ago</v>
+        <v>Official FIFA World Cup 2026™ Album</v>
       </c>
       <c r="G115" t="str">
-        <v/>
+        <v>3:30</v>
       </c>
       <c r="H115" t="str">
-        <v>Holly Humberstone and Free People</v>
+        <v>21 Savage</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/21-savage/894820464</v>
       </c>
       <c r="K115" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/three-nations/6776010591</v>
       </c>
       <c r="L115" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
+        <v>Three Nations - 21 Savage</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Eat For Peace</v>
+        <v>Champions (WC 26)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/eat-for-peace/1891187413</v>
+        <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
       </c>
       <c r="D116" t="str">
         <v>2026-06-09</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Alone Together</v>
+        <v>Champions (WC 26) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:18</v>
+        <v>4:15</v>
       </c>
       <c r="H116" t="str">
-        <v>Show Me the Body</v>
+        <v>IShowSpeed</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
+        <v>https://music.apple.com/us/artist/ishowspeed/1574723975</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/eat-for-peace/1891187411</v>
+        <v>https://music.apple.com/us/album/champions-wc-26/6775282246</v>
       </c>
       <c r="L116" t="str">
-        <v>Eat For Peace - Show Me the Body</v>
+        <v>Champions (WC 26) - IShowSpeed</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Too Easy</v>
+        <v>ENCERRONES</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/too-easy/6774752170</v>
+        <v>https://music.apple.com/us/song/encerrones/6771854522</v>
       </c>
       <c r="D117" t="str">
         <v>2026-06-09</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Too Easy - Single</v>
+        <v>TEOFANIA</v>
       </c>
       <c r="G117" t="str">
-        <v>1:54</v>
+        <v>2:23</v>
       </c>
       <c r="H117" t="str">
-        <v>Tinashe</v>
+        <v>LENCHO</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/tinashe/464835513</v>
+        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/too-easy/6774752168</v>
+        <v>https://music.apple.com/us/album/encerrones/6771854517</v>
       </c>
       <c r="L117" t="str">
-        <v>Too Easy - Tinashe</v>
+        <v>ENCERRONES - LENCHO</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>I Knew It, I Knew You</v>
+        <v>Cowgirl</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
+        <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
       </c>
       <c r="D118" t="str">
         <v>2026-06-09</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>I Knew It, I Knew You - Single</v>
+        <v>The Outlaw Cherie Lee &amp; Other Western Tales</v>
       </c>
       <c r="G118" t="str">
-        <v>2:58</v>
+        <v>2:56</v>
       </c>
       <c r="H118" t="str">
-        <v>Taylor Swift</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/i-knew-it-i-knew-you/6775527442</v>
+        <v>https://music.apple.com/us/album/cowgirl/1894906682</v>
       </c>
       <c r="L118" t="str">
-        <v>I Knew It, I Knew You - Taylor Swift</v>
+        <v>Cowgirl - Shaboozey</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Love Sensation</v>
+        <v>PASSENGER</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
+        <v>https://music.apple.com/us/song/passenger/6773456081</v>
       </c>
       <c r="D119" t="str">
         <v>2026-06-09</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Love Sensation - Single</v>
+        <v>WILDCHILD</v>
       </c>
       <c r="G119" t="str">
-        <v>3:48</v>
+        <v>2:39</v>
       </c>
       <c r="H119" t="str">
-        <v>Madonna</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/love-sensation/6774810102</v>
+        <v>https://music.apple.com/us/album/passenger/6773456078</v>
       </c>
       <c r="L119" t="str">
-        <v>Love Sensation - Madonna</v>
+        <v>PASSENGER - Alex Warren</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Mi Yo De Antes</v>
+        <v>Secret Language</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
+        <v>https://music.apple.com/us/song/secret-language/6774223667</v>
       </c>
       <c r="D120" t="str">
         <v>2026-06-09</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Mi Yo De Antes - Single</v>
+        <v>Sweet Fortune</v>
       </c>
       <c r="G120" t="str">
-        <v>3:04</v>
+        <v>3:53</v>
       </c>
       <c r="H120" t="str">
-        <v>Ozuna</v>
+        <v>Ryan Beatty</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v>https://music.apple.com/us/artist/ryan-beatty/483234172</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/mi-yo-de-antes/6769193983</v>
+        <v>https://music.apple.com/us/album/secret-language/6774223660</v>
       </c>
       <c r="L120" t="str">
-        <v>Mi Yo De Antes - Ozuna</v>
+        <v>Secret Language - Ryan Beatty</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Three Nations</v>
+        <v>True Colors</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/three-nations/6776010602</v>
+        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
       </c>
       <c r="D121" t="str">
         <v>2026-06-09</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Official FIFA World Cup 2026™ Album</v>
+        <v>Thank You</v>
       </c>
       <c r="G121" t="str">
-        <v>3:30</v>
+        <v>3:39</v>
       </c>
       <c r="H121" t="str">
-        <v>21 Savage</v>
+        <v>Mike D</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/21-savage/894820464</v>
+        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/three-nations/6776010591</v>
+        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
       </c>
       <c r="L121" t="str">
-        <v>Three Nations - 21 Savage</v>
+        <v>True Colors - Mike D</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Champions (WC 26)</v>
+        <v>High Hopes 3000</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
+        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
       </c>
       <c r="D122" t="str">
         <v>2026-06-09</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Champions (WC 26) - Single</v>
+        <v>Chuck Timely &amp; The Hourglass</v>
       </c>
       <c r="G122" t="str">
-        <v>4:15</v>
+        <v>4:05</v>
       </c>
       <c r="H122" t="str">
-        <v>IShowSpeed</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/ishowspeed/1574723975</v>
+        <v>https://music.apple.com/us/artist/role-model/199215762</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/champions-wc-26/6775282246</v>
+        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
       </c>
       <c r="L122" t="str">
-        <v>Champions (WC 26) - IShowSpeed</v>
+        <v>High Hopes 3000 - ROLE MODEL</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>ENCERRONES</v>
+        <v>Vertical</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/encerrones/6771854522</v>
+        <v>https://music.apple.com/us/song/vertical/1892436336</v>
       </c>
       <c r="D123" t="str">
         <v>2026-06-09</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>TEOFANIA</v>
+        <v>Emotional Junglist</v>
       </c>
       <c r="G123" t="str">
-        <v>2:23</v>
+        <v>2:36</v>
       </c>
       <c r="H123" t="str">
-        <v>LENCHO</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/encerrones/6771854517</v>
+        <v>https://music.apple.com/us/album/vertical/1892436329</v>
       </c>
       <c r="L123" t="str">
-        <v>ENCERRONES - LENCHO</v>
+        <v>Vertical - Nia Archives</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Cowgirl</v>
+        <v>snake the drain</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
+        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
       </c>
       <c r="D124" t="str">
         <v>2026-06-09</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>The Outlaw Cherie Lee &amp; Other Western Tales</v>
+        <v>this time it’s different / snake the drain - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:56</v>
+        <v>3:08</v>
       </c>
       <c r="H124" t="str">
-        <v>Shaboozey</v>
+        <v>Devon Again</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
+        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/cowgirl/1894906682</v>
+        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
       </c>
       <c r="L124" t="str">
-        <v>Cowgirl - Shaboozey</v>
+        <v>snake the drain - Devon Again</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>PASSENGER</v>
+        <v>Every Single Weekend (feat. Jamie xx)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/passenger/6773456081</v>
+        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D125" t="str">
         <v>2026-06-09</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>WILDCHILD</v>
+        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:39</v>
+        <v>2:10</v>
       </c>
       <c r="H125" t="str">
-        <v>Alex Warren</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/passenger/6773456078</v>
+        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
       </c>
       <c r="L125" t="str">
-        <v>PASSENGER - Alex Warren</v>
+        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Secret Language</v>
+        <v>Bluffin'</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/secret-language/6774223667</v>
+        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
       </c>
       <c r="D126" t="str">
         <v>2026-06-09</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Sweet Fortune</v>
+        <v>Piss In The Wind (Deluxe)</v>
       </c>
       <c r="G126" t="str">
-        <v>3:53</v>
+        <v>2:34</v>
       </c>
       <c r="H126" t="str">
-        <v>Ryan Beatty</v>
+        <v>Joji</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/ryan-beatty/483234172</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/secret-language/6774223660</v>
+        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
       </c>
       <c r="L126" t="str">
-        <v>Secret Language - Ryan Beatty</v>
+        <v>Bluffin' - Joji</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>True Colors</v>
+        <v>Dreams</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
+        <v>https://music.apple.com/us/song/dreams/1884731028</v>
       </c>
       <c r="D127" t="str">
         <v>2026-06-09</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Thank You</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="G127" t="str">
-        <v>3:39</v>
+        <v>3:56</v>
       </c>
       <c r="H127" t="str">
-        <v>Mike D</v>
+        <v>Prospa</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
+        <v>https://music.apple.com/us/album/dreams/1884730177</v>
       </c>
       <c r="L127" t="str">
-        <v>True Colors - Mike D</v>
+        <v>Dreams - Prospa</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>High Hopes 3000</v>
+        <v>Cotton</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
+        <v>https://music.apple.com/us/song/cotton/1887627941</v>
       </c>
       <c r="D128" t="str">
         <v>2026-06-09</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Chuck Timely &amp; The Hourglass</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G128" t="str">
-        <v>4:05</v>
+        <v>3:43</v>
       </c>
       <c r="H128" t="str">
-        <v>ROLE MODEL</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/role-model/199215762</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
+        <v>https://music.apple.com/us/album/cotton/1887627836</v>
       </c>
       <c r="L128" t="str">
-        <v>High Hopes 3000 - ROLE MODEL</v>
+        <v>Cotton - Vince Staples</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Vertical</v>
+        <v>Black Prada Dress</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/vertical/1892436336</v>
+        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
       </c>
       <c r="D129" t="str">
         <v>2026-06-09</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Emotional Junglist</v>
+        <v>I Know Too Much</v>
       </c>
       <c r="G129" t="str">
-        <v>2:36</v>
+        <v>3:19</v>
       </c>
       <c r="H129" t="str">
-        <v>Nia Archives</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/vertical/1892436329</v>
+        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
       </c>
       <c r="L129" t="str">
-        <v>Vertical - Nia Archives</v>
+        <v>Black Prada Dress - Ellie Goulding</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>snake the drain</v>
+        <v>Don’t Break Her Heart</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
+        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
       </c>
       <c r="D130" t="str">
         <v>2026-06-09</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>this time it’s different / snake the drain - Single</v>
+        <v>THERAPY AT THE CLUB</v>
       </c>
       <c r="G130" t="str">
-        <v>3:08</v>
+        <v>3:44</v>
       </c>
       <c r="H130" t="str">
-        <v>Devon Again</v>
+        <v>FLO</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
+        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
       </c>
       <c r="L130" t="str">
-        <v>snake the drain - Devon Again</v>
+        <v>Don’t Break Her Heart - FLO</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Every Single Weekend (feat. Jamie xx)</v>
+        <v>Sexy Ladies (feat. UCB)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
+        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
       </c>
       <c r="D131" t="str">
         <v>2026-06-09</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
+        <v>BITCH</v>
       </c>
       <c r="G131" t="str">
-        <v>2:10</v>
+        <v>2:50</v>
       </c>
       <c r="H131" t="str">
-        <v>The Avalanches</v>
+        <v>Lizzo</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
+        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
       </c>
       <c r="L131" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
+        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Bluffin'</v>
+        <v>Noche Without You</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
+        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
       </c>
       <c r="D132" t="str">
         <v>2026-06-09</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Piss In The Wind (Deluxe)</v>
+        <v>SOMA</v>
       </c>
       <c r="G132" t="str">
-        <v>2:34</v>
+        <v>3:23</v>
       </c>
       <c r="H132" t="str">
-        <v>Joji</v>
+        <v>Skrillex</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
+        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
       </c>
       <c r="L132" t="str">
-        <v>Bluffin' - Joji</v>
+        <v>Noche Without You - Skrillex</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Dreams</v>
+        <v>Difficult Love</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/dreams/1884731028</v>
+        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
       </c>
       <c r="D133" t="str">
         <v>2026-06-09</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Free Your Mind</v>
+        <v>Do That Again</v>
       </c>
       <c r="G133" t="str">
-        <v>3:56</v>
+        <v>2:33</v>
       </c>
       <c r="H133" t="str">
-        <v>Prospa</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/dreams/1884730177</v>
+        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
       </c>
       <c r="L133" t="str">
-        <v>Dreams - Prospa</v>
+        <v>Difficult Love - Malcolm Todd</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Cotton</v>
+        <v>Tastes So Good</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/cotton/1887627941</v>
+        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
       </c>
       <c r="D134" t="str">
         <v>2026-06-09</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Cry Baby</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G134" t="str">
-        <v>3:43</v>
+        <v>3:05</v>
       </c>
       <c r="H134" t="str">
-        <v>Vince Staples</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/cotton/1887627836</v>
+        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
       </c>
       <c r="L134" t="str">
-        <v>Cotton - Vince Staples</v>
+        <v>Tastes So Good - Niall Horan</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Black Prada Dress</v>
+        <v>Phone, Keys, Wallet</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
+        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
       </c>
       <c r="D135" t="str">
         <v>2026-06-09</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>I Know Too Much</v>
+        <v>Phone, Keys, Wallet - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:19</v>
+        <v>2:52</v>
       </c>
       <c r="H135" t="str">
-        <v>Ellie Goulding</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
+        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
       </c>
       <c r="L135" t="str">
-        <v>Black Prada Dress - Ellie Goulding</v>
+        <v>Phone, Keys, Wallet - Lainey Wilson</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Don’t Break Her Heart</v>
+        <v>Madrugada</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
+        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
       </c>
       <c r="D136" t="str">
         <v>2026-06-09</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>THERAPY AT THE CLUB</v>
+        <v>Madrugada - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:44</v>
+        <v>2:58</v>
       </c>
       <c r="H136" t="str">
-        <v>FLO</v>
+        <v>Chino Pacas</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
+        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
       </c>
       <c r="L136" t="str">
-        <v>Don’t Break Her Heart - FLO</v>
+        <v>Madrugada - Chino Pacas</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Sexy Ladies (feat. UCB)</v>
+        <v>Oh Chet (feat. Travis Scott)</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
+        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
       </c>
       <c r="D137" t="str">
         <v>2026-06-09</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>BITCH</v>
+        <v>Oh Chet (feat. Travis Scott) - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:50</v>
+        <v>2:23</v>
       </c>
       <c r="H137" t="str">
-        <v>Lizzo</v>
+        <v>Jey One</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
+        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
       </c>
       <c r="L137" t="str">
-        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
+        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Noche Without You</v>
+        <v>An Hour or So (Live at Apple Music Radio)</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
+        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
       </c>
       <c r="D138" t="str">
         <v>2026-06-09</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>SOMA</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G138" t="str">
-        <v>3:23</v>
+        <v>3:02</v>
       </c>
       <c r="H138" t="str">
-        <v>Skrillex</v>
+        <v>Benny G</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
+        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
       </c>
       <c r="L138" t="str">
-        <v>Noche Without You - Skrillex</v>
+        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Difficult Love</v>
+        <v>it’s just White Noise</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
+        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
       </c>
       <c r="D139" t="str">
         <v>2026-06-09</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Do That Again</v>
+        <v>it’s a real Cruel World - EP</v>
       </c>
       <c r="G139" t="str">
-        <v>2:33</v>
+        <v>3:57</v>
       </c>
       <c r="H139" t="str">
-        <v>Malcolm Todd</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
+        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
       </c>
       <c r="L139" t="str">
-        <v>Difficult Love - Malcolm Todd</v>
+        <v>it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Tastes So Good</v>
+        <v>the feeling</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
+        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
       </c>
       <c r="D140" t="str">
         <v>2026-06-09</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Dinner Party</v>
+        <v>Oh yeah?</v>
       </c>
       <c r="G140" t="str">
-        <v>3:05</v>
+        <v>4:35</v>
       </c>
       <c r="H140" t="str">
-        <v>Niall Horan</v>
+        <v>Steve Lacy</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
+        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
       </c>
       <c r="L140" t="str">
-        <v>Tastes So Good - Niall Horan</v>
+        <v>the feeling - Steve Lacy</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Phone, Keys, Wallet</v>
+        <v>baby (Live at Apple Music Radio)</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
+        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
       </c>
       <c r="D141" t="str">
         <v>2026-06-09</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Phone, Keys, Wallet - Single</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G141" t="str">
-        <v>2:52</v>
+        <v>3:14</v>
       </c>
       <c r="H141" t="str">
-        <v>Lainey Wilson</v>
+        <v>Gabriel Jacoby</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
+        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
       </c>
       <c r="L141" t="str">
-        <v>Phone, Keys, Wallet - Lainey Wilson</v>
+        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Madrugada</v>
+        <v>Drop The Lo</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
+        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
       </c>
       <c r="D142" t="str">
         <v>2026-06-09</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Madrugada - Single</v>
+        <v>Drop The Lo - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:58</v>
+        <v>2:41</v>
       </c>
       <c r="H142" t="str">
-        <v>Chino Pacas</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
+        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
       </c>
       <c r="L142" t="str">
-        <v>Madrugada - Chino Pacas</v>
+        <v>Drop The Lo - Bryson Tiller</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Oh Chet (feat. Travis Scott)</v>
+        <v>GANG BIZNESS feat paygotti</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
+        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
       </c>
       <c r="D143" t="str">
         <v>2026-06-09</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Single</v>
+        <v>GANG BIZNESS feat paygotti - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:23</v>
+        <v>2:47</v>
       </c>
       <c r="H143" t="str">
-        <v>Jey One</v>
+        <v>YG</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
+        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
       </c>
       <c r="L143" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
+        <v>GANG BIZNESS feat paygotti - YG</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>An Hour or So (Live at Apple Music Radio)</v>
+        <v>Lay It Down</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
+        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
       </c>
       <c r="D144" t="str">
         <v>2026-06-09</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Lay It Down - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:02</v>
+        <v>2:38</v>
       </c>
       <c r="H144" t="str">
-        <v>Benny G</v>
+        <v>FattMack</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
+        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
       </c>
       <c r="L144" t="str">
-        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
+        <v>Lay It Down - FattMack</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>it’s just White Noise</v>
+        <v>WAX PAPER</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
+        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
       </c>
       <c r="D145" t="str">
         <v>2026-06-09</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>it’s a real Cruel World - EP</v>
+        <v>WHACK'S MUSEUM</v>
       </c>
       <c r="G145" t="str">
-        <v>3:57</v>
+        <v>2:43</v>
       </c>
       <c r="H145" t="str">
-        <v>Holly Humberstone</v>
+        <v>Tierra Whack</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
+        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
       </c>
       <c r="L145" t="str">
-        <v>it’s just White Noise - Holly Humberstone</v>
+        <v>WAX PAPER - Tierra Whack</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>the feeling</v>
+        <v>abusadOra (tambores)</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
+        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
       </c>
       <c r="D146" t="str">
         <v>2026-06-09</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Oh yeah?</v>
+        <v>ANTES DE QUE SEA TARDE</v>
       </c>
       <c r="G146" t="str">
-        <v>4:35</v>
+        <v>3:11</v>
       </c>
       <c r="H146" t="str">
-        <v>Steve Lacy</v>
+        <v>Yorghaki</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
+        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
+        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
       </c>
       <c r="L146" t="str">
-        <v>the feeling - Steve Lacy</v>
+        <v>abusadOra (tambores) - Yorghaki</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>baby (Live at Apple Music Radio)</v>
+        <v>Ruin</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
+        <v>https://music.apple.com/us/song/ruin/6763176090</v>
       </c>
       <c r="D147" t="str">
         <v>2026-06-09</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G147" t="str">
-        <v>3:14</v>
+        <v>3:19</v>
       </c>
       <c r="H147" t="str">
-        <v>Gabriel Jacoby</v>
+        <v>Blxst</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
+        <v>https://music.apple.com/us/album/ruin/1895199881</v>
       </c>
       <c r="L147" t="str">
-        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
+        <v>Ruin - Blxst</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drop The Lo</v>
+        <v>Do Today</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
+        <v>https://music.apple.com/us/song/do-today/1893402864</v>
       </c>
       <c r="D148" t="str">
         <v>2026-06-09</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Drop The Lo - Single</v>
+        <v>Grateful</v>
       </c>
       <c r="G148" t="str">
-        <v>2:41</v>
+        <v>4:14</v>
       </c>
       <c r="H148" t="str">
-        <v>Bryson Tiller</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
+        <v>https://music.apple.com/us/album/do-today/1893402542</v>
       </c>
       <c r="L148" t="str">
-        <v>Drop The Lo - Bryson Tiller</v>
+        <v>Do Today - The Red Clay Strays</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>GANG BIZNESS feat paygotti</v>
+        <v>Stone Over Water</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
+        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
       </c>
       <c r="D149" t="str">
         <v>2026-06-09</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>GANG BIZNESS feat paygotti - Single</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G149" t="str">
-        <v>2:47</v>
+        <v>3:14</v>
       </c>
       <c r="H149" t="str">
-        <v>YG</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
+        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
       </c>
       <c r="L149" t="str">
-        <v>GANG BIZNESS feat paygotti - YG</v>
+        <v>Stone Over Water - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Lay It Down</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
+        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
       </c>
       <c r="D150" t="str">
         <v>2026-06-09</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Lay It Down - Single</v>
+        <v>Weezer</v>
       </c>
       <c r="G150" t="str">
-        <v>2:38</v>
+        <v>3:34</v>
       </c>
       <c r="H150" t="str">
-        <v>FattMack</v>
+        <v>Weezer</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/weezer/115234</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
+        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
       </c>
       <c r="L150" t="str">
-        <v>Lay It Down - FattMack</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>WAX PAPER</v>
+        <v>Tell Me When You've Had Enough</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
+        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
       </c>
       <c r="D151" t="str">
         <v>2026-06-09</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>WHACK'S MUSEUM</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G151" t="str">
-        <v>2:43</v>
+        <v>3:19</v>
       </c>
       <c r="H151" t="str">
-        <v>Tierra Whack</v>
+        <v>Evanescence</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
+        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
       </c>
       <c r="L151" t="str">
-        <v>WAX PAPER - Tierra Whack</v>
+        <v>Tell Me When You've Had Enough - Evanescence</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>abusadOra (tambores)</v>
+        <v>Your Ghost Again</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
+        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
       </c>
       <c r="D152" t="str">
         <v>2026-06-09</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>ANTES DE QUE SEA TARDE</v>
+        <v>Your Ghost Again - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:11</v>
+        <v>4:35</v>
       </c>
       <c r="H152" t="str">
-        <v>Yorghaki</v>
+        <v>Mastodon</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
+        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
+        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
       </c>
       <c r="L152" t="str">
-        <v>abusadOra (tambores) - Yorghaki</v>
+        <v>Your Ghost Again - Mastodon</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ruin</v>
+        <v>Nightshift Superstar</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/ruin/6763176090</v>
+        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
       </c>
       <c r="D153" t="str">
         <v>2026-06-09</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Labor Of Love</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G153" t="str">
-        <v>3:19</v>
+        <v>4:07</v>
       </c>
       <c r="H153" t="str">
-        <v>Blxst</v>
+        <v>Muse</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/ruin/1895199881</v>
+        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
       </c>
       <c r="L153" t="str">
-        <v>Ruin - Blxst</v>
+        <v>Nightshift Superstar - Muse</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Do Today</v>
+        <v>UNDER THE RHYTHM</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/do-today/1893402864</v>
+        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
       </c>
       <c r="D154" t="str">
         <v>2026-06-09</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Grateful</v>
+        <v>ADAM</v>
       </c>
       <c r="G154" t="str">
-        <v>4:14</v>
+        <v>2:50</v>
       </c>
       <c r="H154" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Adam Lambert</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/do-today/1893402542</v>
+        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
       </c>
       <c r="L154" t="str">
-        <v>Do Today - The Red Clay Strays</v>
+        <v>UNDER THE RHYTHM - Adam Lambert</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Stone Over Water</v>
+        <v>You’re Mine</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
+        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
       </c>
       <c r="D155" t="str">
         <v>2026-06-09</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>I Built You A Tower</v>
+        <v>Papercut</v>
       </c>
       <c r="G155" t="str">
-        <v>3:14</v>
+        <v>4:25</v>
       </c>
       <c r="H155" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Imani Imani</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
+        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
       </c>
       <c r="L155" t="str">
-        <v>Stone Over Water - Death Cab for Cutie</v>
+        <v>You’re Mine - Imani Imani</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
+        <v>point blank</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
+        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
       </c>
       <c r="D156" t="str">
         <v>2026-06-09</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Weezer</v>
+        <v>new avatar</v>
       </c>
       <c r="G156" t="str">
-        <v>3:34</v>
+        <v>4:26</v>
       </c>
       <c r="H156" t="str">
-        <v>Weezer</v>
+        <v>Kelela</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/weezer/115234</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
+        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
       </c>
       <c r="L156" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
+        <v>point blank - Kelela</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Tell Me When You've Had Enough</v>
+        <v>that's my beach!</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
+        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
       </c>
       <c r="D157" t="str">
         <v>2026-06-09</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Sanctuary</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G157" t="str">
-        <v>3:19</v>
+        <v>3:18</v>
       </c>
       <c r="H157" t="str">
-        <v>Evanescence</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
+        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
       </c>
       <c r="L157" t="str">
-        <v>Tell Me When You've Had Enough - Evanescence</v>
+        <v>that's my beach! - horsegiirL</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Your Ghost Again</v>
+        <v>In Your Eyes</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
+        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
       </c>
       <c r="D158" t="str">
         <v>2026-06-09</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Your Ghost Again - Single</v>
+        <v>In Your Eyes - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>4:35</v>
+        <v>3:36</v>
       </c>
       <c r="H158" t="str">
-        <v>Mastodon</v>
+        <v>Alesso</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
+        <v>https://music.apple.com/us/artist/alesso/432464201</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
+        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
       </c>
       <c r="L158" t="str">
-        <v>Your Ghost Again - Mastodon</v>
+        <v>In Your Eyes - Alesso</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Nightshift Superstar</v>
+        <v>ALL OR NOTHING</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
+        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
       </c>
       <c r="D159" t="str">
         <v>2026-06-09</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>The Wow! Signal</v>
+        <v>ALL OR NOTHING - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>4:07</v>
+        <v>3:17</v>
       </c>
       <c r="H159" t="str">
-        <v>Muse</v>
+        <v>Tobe Nwigwe</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
+        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
       </c>
       <c r="L159" t="str">
-        <v>Nightshift Superstar - Muse</v>
+        <v>ALL OR NOTHING - Tobe Nwigwe</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>UNDER THE RHYTHM</v>
+        <v>IN MY HANDS</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
+        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
       </c>
       <c r="D160" t="str">
         <v>2026-06-09</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>ADAM</v>
+        <v>IN MY HANDS - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:50</v>
+        <v>3:14</v>
       </c>
       <c r="H160" t="str">
-        <v>Adam Lambert</v>
+        <v>Alessia Cara</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
+        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
+        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
       </c>
       <c r="L160" t="str">
-        <v>UNDER THE RHYTHM - Adam Lambert</v>
+        <v>IN MY HANDS - Alessia Cara</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>You’re Mine</v>
+        <v>Life's a Dream</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
+        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
       </c>
       <c r="D161" t="str">
         <v>2026-06-09</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Papercut</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G161" t="str">
-        <v>4:25</v>
+        <v>5:31</v>
       </c>
       <c r="H161" t="str">
-        <v>Imani Imani</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
+        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
       </c>
       <c r="L161" t="str">
-        <v>You’re Mine - Imani Imani</v>
+        <v>Life's a Dream - Modest Mouse</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>point blank</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
+        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
       </c>
       <c r="D162" t="str">
         <v>2026-06-09</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>new avatar</v>
+        <v>Season of Surrender</v>
       </c>
       <c r="G162" t="str">
-        <v>4:26</v>
+        <v>4:47</v>
       </c>
       <c r="H162" t="str">
-        <v>Kelela</v>
+        <v>August Burns Red</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
+        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
       </c>
       <c r="L162" t="str">
-        <v>point blank - Kelela</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>that's my beach!</v>
+        <v>Shine</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
+        <v>https://music.apple.com/us/song/shine/6764654536</v>
       </c>
       <c r="D163" t="str">
         <v>2026-06-09</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G163" t="str">
-        <v>3:18</v>
+        <v>2:27</v>
       </c>
       <c r="H163" t="str">
-        <v>horsegiirL</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
+        <v>https://music.apple.com/us/album/shine/1895866355</v>
       </c>
       <c r="L163" t="str">
-        <v>that's my beach! - horsegiirL</v>
+        <v>Shine - Jon Batiste</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>In Your Eyes</v>
+        <v>Half The Man</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
+        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
       </c>
       <c r="D164" t="str">
         <v>2026-06-09</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>In Your Eyes - Single</v>
+        <v>Scared of Heights</v>
       </c>
       <c r="G164" t="str">
-        <v>3:36</v>
+        <v>3:56</v>
       </c>
       <c r="H164" t="str">
-        <v>Alesso</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/alesso/432464201</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
+        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
       </c>
       <c r="L164" t="str">
-        <v>In Your Eyes - Alesso</v>
+        <v>Half The Man - Wyatt Flores</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>ALL OR NOTHING</v>
+        <v>Preacher’s Kid</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
+        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
       </c>
       <c r="D165" t="str">
         <v>2026-06-09</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>ALL OR NOTHING - Single</v>
+        <v>Preacher’s Kid - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:17</v>
+        <v>5:02</v>
       </c>
       <c r="H165" t="str">
-        <v>Tobe Nwigwe</v>
+        <v>Stephen Wilson Jr.</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
+        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
+        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
       </c>
       <c r="L165" t="str">
-        <v>ALL OR NOTHING - Tobe Nwigwe</v>
+        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>IN MY HANDS</v>
+        <v>Weak</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
+        <v>https://music.apple.com/us/song/weak/6771151098</v>
       </c>
       <c r="D166" t="str">
         <v>2026-06-09</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>IN MY HANDS - Single</v>
+        <v>Weak - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:14</v>
+        <v>3:28</v>
       </c>
       <c r="H166" t="str">
-        <v>Alessia Cara</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
+        <v>https://music.apple.com/us/album/weak/6771151088</v>
       </c>
       <c r="L166" t="str">
-        <v>IN MY HANDS - Alessia Cara</v>
+        <v>Weak - Naomi Sharon</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Life's a Dream</v>
+        <v>ALL NIGHT LONG</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
+        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
       </c>
       <c r="D167" t="str">
         <v>2026-06-09</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G167" t="str">
-        <v>5:31</v>
+        <v>2:28</v>
       </c>
       <c r="H167" t="str">
-        <v>Modest Mouse</v>
+        <v>Pheelz</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
+        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
       </c>
       <c r="L167" t="str">
-        <v>Life's a Dream - Modest Mouse</v>
+        <v>ALL NIGHT LONG - Pheelz</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
+        <v>Every Life</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
+        <v>https://music.apple.com/us/song/every-life/6764110978</v>
       </c>
       <c r="D168" t="str">
         <v>2026-06-09</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Season of Surrender</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G168" t="str">
-        <v>4:47</v>
+        <v>3:18</v>
       </c>
       <c r="H168" t="str">
-        <v>August Burns Red</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
+        <v>https://music.apple.com/us/album/every-life/1895644574</v>
       </c>
       <c r="L168" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
+        <v>Every Life - Isabel LaRosa</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Shine</v>
+        <v>Home</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/shine/6764654536</v>
+        <v>https://music.apple.com/us/song/home/6774718029</v>
       </c>
       <c r="D169" t="str">
         <v>2026-06-09</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Black Mozart</v>
+        <v>Good Grief</v>
       </c>
       <c r="G169" t="str">
-        <v>2:27</v>
+        <v>4:53</v>
       </c>
       <c r="H169" t="str">
-        <v>Jon Batiste</v>
+        <v>Sara Bareilles</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/shine/1895866355</v>
+        <v>https://music.apple.com/us/album/home/6774718027</v>
       </c>
       <c r="L169" t="str">
-        <v>Shine - Jon Batiste</v>
+        <v>Home - Sara Bareilles</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Half The Man</v>
+        <v>Satalanaaa</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
+        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
       </c>
       <c r="D170" t="str">
         <v>2026-06-09</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Scared of Heights</v>
+        <v>Satalanaaa - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:56</v>
+        <v>2:06</v>
       </c>
       <c r="H170" t="str">
-        <v>Wyatt Flores</v>
+        <v>Pitbull</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
+        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
       </c>
       <c r="L170" t="str">
-        <v>Half The Man - Wyatt Flores</v>
+        <v>Satalanaaa - Pitbull</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Preacher’s Kid</v>
+        <v>Miss Me More</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
+        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
       </c>
       <c r="D171" t="str">
         <v>2026-06-09</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Preacher’s Kid - Single</v>
+        <v>Confessions of a Lonely Heart</v>
       </c>
       <c r="G171" t="str">
-        <v>5:02</v>
+        <v>2:43</v>
       </c>
       <c r="H171" t="str">
-        <v>Stephen Wilson Jr.</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
+        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
       </c>
       <c r="L171" t="str">
-        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
+        <v>Miss Me More - Eric Nam</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Weak</v>
+        <v>Rituals</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/weak/6771151098</v>
+        <v>https://music.apple.com/us/song/rituals/6769628916</v>
       </c>
       <c r="D172" t="str">
         <v>2026-06-09</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Weak - Single</v>
+        <v>Rituals - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:28</v>
+        <v>2:10</v>
       </c>
       <c r="H172" t="str">
-        <v>Naomi Sharon</v>
+        <v>Rico Nasty</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/weak/6771151088</v>
+        <v>https://music.apple.com/us/album/rituals/6769628915</v>
       </c>
       <c r="L172" t="str">
-        <v>Weak - Naomi Sharon</v>
+        <v>Rituals - Rico Nasty</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>ALL NIGHT LONG</v>
+        <v>Honeysuckle</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
+        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
       </c>
       <c r="D173" t="str">
         <v>2026-06-09</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>A Rii Set</v>
+        <v>Honeysuckle - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:28</v>
+        <v>3:15</v>
       </c>
       <c r="H173" t="str">
-        <v>Pheelz</v>
+        <v>Dylan Gossett</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
+        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
       </c>
       <c r="L173" t="str">
-        <v>ALL NIGHT LONG - Pheelz</v>
+        <v>Honeysuckle - Dylan Gossett</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Every Life</v>
+        <v>listen…</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/every-life/6764110978</v>
+        <v>https://music.apple.com/us/song/listen/6775576508</v>
       </c>
       <c r="D174" t="str">
         <v>2026-06-09</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G174" t="str">
-        <v>3:18</v>
+        <v>4:08</v>
       </c>
       <c r="H174" t="str">
-        <v>Isabel LaRosa</v>
+        <v>John Williams</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/john-williams/63748</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/every-life/1895644574</v>
+        <v>https://music.apple.com/us/album/listen/6775576506</v>
       </c>
       <c r="L174" t="str">
-        <v>Every Life - Isabel LaRosa</v>
+        <v>listen… - John Williams</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Home</v>
+        <v>DEADMEAT</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/home/6774718029</v>
+        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
       </c>
       <c r="D175" t="str">
         <v>2026-06-09</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Good Grief</v>
+        <v>DEADMEAT - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>4:53</v>
+        <v>2:52</v>
       </c>
       <c r="H175" t="str">
-        <v>Sara Bareilles</v>
+        <v>South Arcade</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/home/6774718027</v>
+        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
       </c>
       <c r="L175" t="str">
-        <v>Home - Sara Bareilles</v>
+        <v>DEADMEAT - South Arcade</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Satalanaaa</v>
+        <v>Ugly and Rotten</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
+        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
       </c>
       <c r="D176" t="str">
         <v>2026-06-09</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Satalanaaa - Single</v>
+        <v>Ugly and Rotten - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:06</v>
+        <v>2:49</v>
       </c>
       <c r="H176" t="str">
-        <v>Pitbull</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
+        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
       </c>
       <c r="L176" t="str">
-        <v>Satalanaaa - Pitbull</v>
+        <v>Ugly and Rotten - Mckenna Grace</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Miss Me More</v>
+        <v>Whisper</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
+        <v>https://music.apple.com/us/song/whisper/6772254272</v>
       </c>
       <c r="D177" t="str">
         <v>2026-06-09</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Confessions of a Lonely Heart</v>
+        <v>Whisper - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:43</v>
+        <v>2:47</v>
       </c>
       <c r="H177" t="str">
-        <v>Eric Nam</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
+        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
+        <v>https://music.apple.com/us/album/whisper/6772254268</v>
       </c>
       <c r="L177" t="str">
-        <v>Miss Me More - Eric Nam</v>
+        <v>Whisper - Blu DeTiger</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Rituals</v>
+        <v>Gecko (feat. Haley Bridge)</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/rituals/6769628916</v>
+        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
       </c>
       <c r="D178" t="str">
         <v>2026-06-09</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Rituals - Single</v>
+        <v>How dare you tryna love me? - EP</v>
       </c>
       <c r="G178" t="str">
-        <v>2:10</v>
+        <v>2:46</v>
       </c>
       <c r="H178" t="str">
-        <v>Rico Nasty</v>
+        <v>Olga Myko</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
+        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/rituals/6769628915</v>
+        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
       </c>
       <c r="L178" t="str">
-        <v>Rituals - Rico Nasty</v>
+        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Honeysuckle</v>
+        <v>Compa Primo</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
+        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
       </c>
       <c r="D179" t="str">
         <v>2026-06-09</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Honeysuckle - Single</v>
+        <v>Compa Primo - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:15</v>
+        <v>3:12</v>
       </c>
       <c r="H179" t="str">
-        <v>Dylan Gossett</v>
+        <v>Nueva H</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
+        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
+        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
       </c>
       <c r="L179" t="str">
-        <v>Honeysuckle - Dylan Gossett</v>
+        <v>Compa Primo - Nueva H</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>listen…</v>
+        <v>Parachute</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/listen/6775576508</v>
+        <v>https://music.apple.com/us/song/parachute/6768841410</v>
       </c>
       <c r="D180" t="str">
         <v>2026-06-09</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>4:08</v>
+        <v>3:11</v>
       </c>
       <c r="H180" t="str">
-        <v>John Williams</v>
+        <v>Tyler James Bellinger</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/john-williams/63748</v>
+        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/listen/6775576506</v>
+        <v>https://music.apple.com/us/album/parachute/6768841409</v>
       </c>
       <c r="L180" t="str">
-        <v>listen… - John Williams</v>
+        <v>Parachute - Tyler James Bellinger</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>DEADMEAT</v>
+        <v>Like a Bubble</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
+        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
       </c>
       <c r="D181" t="str">
         <v>2026-06-09</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>DEADMEAT - Single</v>
+        <v>Imperfect-I'mperfect - EP</v>
       </c>
       <c r="G181" t="str">
-        <v>2:52</v>
+        <v>3:08</v>
       </c>
       <c r="H181" t="str">
-        <v>South Arcade</v>
+        <v>FIFTY FIFTY</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
+        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
       </c>
       <c r="L181" t="str">
-        <v>DEADMEAT - South Arcade</v>
+        <v>Like a Bubble - FIFTY FIFTY</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Ugly and Rotten</v>
+        <v>Hustle and Opulence in America</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
+        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
       </c>
       <c r="D182" t="str">
         <v>2026-06-09</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Ugly and Rotten - Single</v>
+        <v>AK Cuts: Vol. 4 - EP</v>
       </c>
       <c r="G182" t="str">
-        <v>2:49</v>
+        <v>3:07</v>
       </c>
       <c r="H182" t="str">
-        <v>Mckenna Grace</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
+        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
       </c>
       <c r="L182" t="str">
-        <v>Ugly and Rotten - Mckenna Grace</v>
+        <v>Hustle and Opulence in America - Anish Kumar</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Whisper</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/whisper/6772254272</v>
+        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
       </c>
       <c r="D183" t="str">
         <v>2026-06-09</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Whisper - Single</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
       </c>
       <c r="G183" t="str">
         <v>2:47</v>
       </c>
       <c r="H183" t="str">
-        <v>Blu DeTiger</v>
+        <v>ivri</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/whisper/6772254268</v>
+        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
       </c>
       <c r="L183" t="str">
-        <v>Whisper - Blu DeTiger</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Gecko (feat. Haley Bridge)</v>
+        <v>CLEAN SWEEP</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
+        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
       </c>
       <c r="D184" t="str">
         <v>2026-06-09</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>How dare you tryna love me? - EP</v>
+        <v>CLEAN SWEEP - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:46</v>
+        <v>3:11</v>
       </c>
       <c r="H184" t="str">
-        <v>Olga Myko</v>
+        <v>Storm Reid</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
+        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
+        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
       </c>
       <c r="L184" t="str">
-        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
+        <v>CLEAN SWEEP - Storm Reid</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Compa Primo</v>
+        <v>CANDYLAND!</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
+        <v>https://music.apple.com/us/song/candyland/6766927008</v>
       </c>
       <c r="D185" t="str">
         <v>2026-06-09</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Compa Primo - Single</v>
+        <v>CANDYLAND! - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:12</v>
+        <v>3:15</v>
       </c>
       <c r="H185" t="str">
-        <v>Nueva H</v>
+        <v>Natanya</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
+        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
+        <v>https://music.apple.com/us/album/candyland/6766927000</v>
       </c>
       <c r="L185" t="str">
-        <v>Compa Primo - Nueva H</v>
+        <v>CANDYLAND! - Natanya</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Parachute</v>
+        <v>Double C</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/parachute/6768841410</v>
+        <v>https://music.apple.com/us/song/double-c/6771836555</v>
       </c>
       <c r="D186" t="str">
         <v>2026-06-09</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Parachute - Single</v>
+        <v>Double C - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:11</v>
+        <v>2:21</v>
       </c>
       <c r="H186" t="str">
-        <v>Tyler James Bellinger</v>
+        <v>Sk8star</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
+        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/parachute/6768841409</v>
+        <v>https://music.apple.com/us/album/double-c/6771836554</v>
       </c>
       <c r="L186" t="str">
-        <v>Parachute - Tyler James Bellinger</v>
+        <v>Double C - Sk8star</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Like a Bubble</v>
+        <v>madera</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
+        <v>https://music.apple.com/us/song/madera/6764638112</v>
       </c>
       <c r="D187" t="str">
         <v>2026-06-09</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Imperfect-I'mperfect - EP</v>
+        <v>madera/un camino luminoso - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:08</v>
+        <v>5:41</v>
       </c>
       <c r="H187" t="str">
-        <v>FIFTY FIFTY</v>
+        <v>Lumtz</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
+        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
+        <v>https://music.apple.com/us/album/madera/6764638109</v>
       </c>
       <c r="L187" t="str">
-        <v>Like a Bubble - FIFTY FIFTY</v>
+        <v>madera - Lumtz</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Hustle and Opulence in America</v>
+        <v>Slip the Noose</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
+        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
       </c>
       <c r="D188" t="str">
         <v>2026-06-09</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>AK Cuts: Vol. 4 - EP</v>
+        <v>Hum of Hurt</v>
       </c>
       <c r="G188" t="str">
-        <v>3:07</v>
+        <v>1:43</v>
       </c>
       <c r="H188" t="str">
-        <v>Anish Kumar</v>
+        <v>Converge</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
+        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
       </c>
       <c r="L188" t="str">
-        <v>Hustle and Opulence in America - Anish Kumar</v>
+        <v>Slip the Noose - Converge</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
+        <v>Crying Fire</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
+        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
       </c>
       <c r="D189" t="str">
         <v>2026-06-09</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
+        <v>Crying Fire - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:47</v>
+        <v>4:08</v>
       </c>
       <c r="H189" t="str">
-        <v>ivri</v>
+        <v>Avatar</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
+        <v>https://music.apple.com/us/artist/avatar/187616241</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
+        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
       </c>
       <c r="L189" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
+        <v>Crying Fire - Avatar</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>CLEAN SWEEP</v>
+        <v>NI NA’</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
+        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
       </c>
       <c r="D190" t="str">
         <v>2026-06-09</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>CLEAN SWEEP - Single</v>
+        <v>sorry si soy GRRRIS</v>
       </c>
       <c r="G190" t="str">
-        <v>3:11</v>
+        <v>2:53</v>
       </c>
       <c r="H190" t="str">
-        <v>Storm Reid</v>
+        <v>ROBI</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
+        <v>https://music.apple.com/us/artist/robi/1458047972</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
+        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
       </c>
       <c r="L190" t="str">
-        <v>CLEAN SWEEP - Storm Reid</v>
+        <v>NI NA’ - ROBI</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>CANDYLAND!</v>
+        <v>Holding Back</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/candyland/6766927008</v>
+        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
       </c>
       <c r="D191" t="str">
         <v>2026-06-09</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>CANDYLAND! - Single</v>
+        <v>AMA</v>
       </c>
       <c r="G191" t="str">
-        <v>3:15</v>
+        <v>3:19</v>
       </c>
       <c r="H191" t="str">
-        <v>Natanya</v>
+        <v>Ama</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/candyland/6766927000</v>
+        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
       </c>
       <c r="L191" t="str">
-        <v>CANDYLAND! - Natanya</v>
+        <v>Holding Back - Ama</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Double C</v>
+        <v>you're still mine</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/double-c/6771836555</v>
+        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
       </c>
       <c r="D192" t="str">
         <v>2026-06-09</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Double C - Single</v>
+        <v>you're still mine - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:21</v>
+        <v>3:19</v>
       </c>
       <c r="H192" t="str">
-        <v>Sk8star</v>
+        <v>Lexi Jayde</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
+        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/double-c/6771836554</v>
+        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
       </c>
       <c r="L192" t="str">
-        <v>Double C - Sk8star</v>
+        <v>you're still mine - Lexi Jayde</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>madera</v>
+        <v>teksi</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/madera/6764638112</v>
+        <v>https://music.apple.com/us/song/teksi/6769899742</v>
       </c>
       <c r="D193" t="str">
         <v>2026-06-09</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>madera/un camino luminoso - Single</v>
+        <v>pOCHO</v>
       </c>
       <c r="G193" t="str">
-        <v>5:41</v>
+        <v>2:48</v>
       </c>
       <c r="H193" t="str">
-        <v>Lumtz</v>
+        <v>8onthebeat</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
+        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/madera/6764638109</v>
+        <v>https://music.apple.com/us/album/teksi/6769899739</v>
       </c>
       <c r="L193" t="str">
-        <v>madera - Lumtz</v>
+        <v>teksi - 8onthebeat</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Slip the Noose</v>
+        <v>Let You Go</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
+        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
       </c>
       <c r="D194" t="str">
         <v>2026-06-09</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Hum of Hurt</v>
+        <v>Let You Go - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>1:43</v>
+        <v>1:37</v>
       </c>
       <c r="H194" t="str">
-        <v>Converge</v>
+        <v>Nate Sib</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
+        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
       </c>
       <c r="L194" t="str">
-        <v>Slip the Noose - Converge</v>
+        <v>Let You Go - Nate Sib</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Crying Fire</v>
+        <v>Dis-Moi</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
+        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
       </c>
       <c r="D195" t="str">
         <v>2026-06-09</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Crying Fire - Single</v>
+        <v>CINNA</v>
       </c>
       <c r="G195" t="str">
-        <v>4:08</v>
+        <v>2:27</v>
       </c>
       <c r="H195" t="str">
-        <v>Avatar</v>
+        <v>Cannelle</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/avatar/187616241</v>
+        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
+        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
       </c>
       <c r="L195" t="str">
-        <v>Crying Fire - Avatar</v>
+        <v>Dis-Moi - Cannelle</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>NI NA’</v>
+        <v>Leverage</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
+        <v>https://music.apple.com/us/song/leverage/6776432312</v>
       </c>
       <c r="D196" t="str">
         <v>2026-06-09</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>sorry si soy GRRRIS</v>
+        <v>Heaven on Mars</v>
       </c>
       <c r="G196" t="str">
-        <v>2:53</v>
+        <v>3:04</v>
       </c>
       <c r="H196" t="str">
-        <v>ROBI</v>
+        <v>NoCap</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/robi/1458047972</v>
+        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
+        <v>https://music.apple.com/us/album/leverage/6776432217</v>
       </c>
       <c r="L196" t="str">
-        <v>NI NA’ - ROBI</v>
+        <v>Leverage - NoCap</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Holding Back</v>
+        <v>Kool Aid</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
+        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
       </c>
       <c r="D197" t="str">
         <v>2026-06-09</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>AMA</v>
+        <v>Where Have All The Good Men Gone? - EP</v>
       </c>
       <c r="G197" t="str">
-        <v>3:19</v>
+        <v>3:40</v>
       </c>
       <c r="H197" t="str">
-        <v>Ama</v>
+        <v>Debbii Dawson</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
+        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
       </c>
       <c r="L197" t="str">
-        <v>Holding Back - Ama</v>
+        <v>Kool Aid - Debbii Dawson</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>you're still mine</v>
+        <v>Pieces</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
+        <v>https://music.apple.com/us/song/pieces/6771861156</v>
       </c>
       <c r="D198" t="str">
         <v>2026-06-09</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>you're still mine - Single</v>
+        <v>Pieces - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:19</v>
+        <v>2:19</v>
       </c>
       <c r="H198" t="str">
-        <v>Lexi Jayde</v>
+        <v>Dom Innarella</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
+        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
+        <v>https://music.apple.com/us/album/pieces/6771861155</v>
       </c>
       <c r="L198" t="str">
-        <v>you're still mine - Lexi Jayde</v>
+        <v>Pieces - Dom Innarella</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>teksi</v>
+        <v>Mesmerized</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/teksi/6769899742</v>
+        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
       </c>
       <c r="D199" t="str">
         <v>2026-06-09</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>pOCHO</v>
+        <v>Mesmerized - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:48</v>
+        <v>2:38</v>
       </c>
       <c r="H199" t="str">
-        <v>8onthebeat</v>
+        <v>The Aces</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
+        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/teksi/6769899739</v>
+        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
       </c>
       <c r="L199" t="str">
-        <v>teksi - 8onthebeat</v>
+        <v>Mesmerized - The Aces</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Let You Go</v>
+        <v>Perfect 10</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
+        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
       </c>
       <c r="D200" t="str">
         <v>2026-06-09</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Let You Go - Single</v>
+        <v>No Hard Feelings (Deluxe)</v>
       </c>
       <c r="G200" t="str">
-        <v>1:37</v>
+        <v>2:51</v>
       </c>
       <c r="H200" t="str">
-        <v>Nate Sib</v>
+        <v>The Beaches</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
+        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
+        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
       </c>
       <c r="L200" t="str">
-        <v>Let You Go - Nate Sib</v>
+        <v>Perfect 10 - The Beaches</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Dis-Moi</v>
+        <v>Recognize</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
+        <v>https://music.apple.com/us/song/recognize/6769164705</v>
       </c>
       <c r="D201" t="str">
         <v>2026-06-09</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>CINNA</v>
+        <v>Recognize - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>2:27</v>
+        <v>2:05</v>
       </c>
       <c r="H201" t="str">
-        <v>Cannelle</v>
+        <v>Fana Hues</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
+        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
+        <v>https://music.apple.com/us/album/recognize/6769164704</v>
       </c>
       <c r="L201" t="str">
-        <v>Dis-Moi - Cannelle</v>
+        <v>Recognize - Fana Hues</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Leverage</v>
+        <v>Feel The Vibe</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/leverage/6776432312</v>
+        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
       </c>
       <c r="D202" t="str">
         <v>2026-06-09</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Heaven on Mars</v>
+        <v>Feel The Vibe</v>
       </c>
       <c r="G202" t="str">
-        <v>3:04</v>
+        <v>3:28</v>
       </c>
       <c r="H202" t="str">
-        <v>NoCap</v>
+        <v>Above &amp; Beyond</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
+        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/leverage/6776432217</v>
+        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
       </c>
       <c r="L202" t="str">
-        <v>Leverage - NoCap</v>
+        <v>Feel The Vibe - Above &amp; Beyond</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Kool Aid</v>
+        <v>I Never Knew</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
+        <v>https://music.apple.com/us/song/i-never-knew/6764351468</v>
       </c>
       <c r="D203" t="str">
         <v>2026-06-09</v>
@@ -8089,258 +8089,30 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Where Have All The Good Men Gone? - EP</v>
+        <v>I Never Knew - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>3:40</v>
+        <v>3:51</v>
       </c>
       <c r="H203" t="str">
-        <v>Debbii Dawson</v>
+        <v>Adam Ten</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
+        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
+        <v>https://music.apple.com/us/album/i-never-knew/1895744479</v>
       </c>
       <c r="L203" t="str">
-        <v>Kool Aid - Debbii Dawson</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>Pieces</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/pieces/6771861156</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>Pieces - Single</v>
-      </c>
-      <c r="G204" t="str">
-        <v>2:19</v>
-      </c>
-      <c r="H204" t="str">
-        <v>Dom Innarella</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/pieces/6771861155</v>
-      </c>
-      <c r="L204" t="str">
-        <v>Pieces - Dom Innarella</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>Mesmerized</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>Mesmerized - Single</v>
-      </c>
-      <c r="G205" t="str">
-        <v>2:38</v>
-      </c>
-      <c r="H205" t="str">
-        <v>The Aces</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
-      </c>
-      <c r="L205" t="str">
-        <v>Mesmerized - The Aces</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>Perfect 10</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
-      </c>
-      <c r="D206" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>No Hard Feelings (Deluxe)</v>
-      </c>
-      <c r="G206" t="str">
-        <v>2:51</v>
-      </c>
-      <c r="H206" t="str">
-        <v>The Beaches</v>
-      </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
-      </c>
-      <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
-      </c>
-      <c r="L206" t="str">
-        <v>Perfect 10 - The Beaches</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>Recognize</v>
-      </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/recognize/6769164705</v>
-      </c>
-      <c r="D207" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v>Recognize - Single</v>
-      </c>
-      <c r="G207" t="str">
-        <v>2:05</v>
-      </c>
-      <c r="H207" t="str">
-        <v>Fana Hues</v>
-      </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
-      </c>
-      <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/recognize/6769164704</v>
-      </c>
-      <c r="L207" t="str">
-        <v>Recognize - Fana Hues</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>Feel The Vibe</v>
-      </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
-      </c>
-      <c r="D208" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v>Feel The Vibe</v>
-      </c>
-      <c r="G208" t="str">
-        <v>3:28</v>
-      </c>
-      <c r="H208" t="str">
-        <v>Above &amp; Beyond</v>
-      </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
-      </c>
-      <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
-      </c>
-      <c r="L208" t="str">
-        <v>Feel The Vibe - Above &amp; Beyond</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>I Never Knew</v>
-      </c>
-      <c r="B209" t="str">
-        <v/>
-      </c>
-      <c r="C209" t="str">
-        <v>https://music.apple.com/us/song/i-never-knew/6764351468</v>
-      </c>
-      <c r="D209" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="E209" t="str">
-        <v/>
-      </c>
-      <c r="F209" t="str">
-        <v>I Never Knew - Single</v>
-      </c>
-      <c r="G209" t="str">
-        <v>3:51</v>
-      </c>
-      <c r="H209" t="str">
-        <v>Adam Ten</v>
-      </c>
-      <c r="I209" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J209" t="str">
-        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
-      </c>
-      <c r="K209" t="str">
-        <v>https://music.apple.com/us/album/i-never-knew/1895744479</v>
-      </c>
-      <c r="L209" t="str">
         <v>I Never Knew - Adam Ten</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L209"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L203"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-06-week02/titles.xlsx
+++ b/data/global/2026-06-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L203"/>
+  <dimension ref="A1:L199"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מוטי כרמל &amp; אביה שרמן - קרוב אליך</v>
+        <v>התקווה וסבא אורי (תמיר בר) 6 – מכת זקנה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411297&amp;sid=55390b5eabec38928044626c162bd3cb</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-%d7%95%d7%a1%d7%91%d7%90-%d7%90%d7%95%d7%a8%d7%99-%d7%aa%d7%9e%d7%99%d7%a8-%d7%91%d7%a8-6-%d7%9e%d7%9b%d7%aa-%d7%96%d7%a7%d7%a0%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>הניסיון לחבר בין מוזיקת הרגאיי הקלילה והקצבית של להקת "התקווה 6" לבין ההומור הנונסנסי והדמות האייקונית של "סבא אורי" (בגילומו של תמיר בר) מתגלה כפספוס. השיר אמנם מנסה להצחיק ולייצר מניפסט משעשע על משבר גיל ה-40 והזקנה, אך הוא נופל</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,27 +469,27 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מוטי כרמל &amp; אביה שרמן - קרוב אליך</v>
+        <v>התקווה וסבא אורי (תמיר בר) 6 – מכת זקנה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ליאור מיארה - מחרוזת שבוי לאהבה 2026</v>
+        <v>נס X סטילה – מי כמוני</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411296&amp;sid=55390b5eabec38928044626c162bd3cb</v>
+        <v>https://yosmusic.com/%d7%a0%d7%a1-x-%d7%a1%d7%98%d7%99%d7%9c%d7%94-%d7%9e%d7%99-%d7%9b%d7%9e%d7%95%d7%a0%d7%99/</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>"מי כמוני" הוא יריית פתיחה לקראת הפרויקט החדש של הצמד נס וסטילה. השיר מביא את כל מה שהפך אותם לאחד הצמדים המסקרנים והמזוהים ביותר בהיפ־הופ הישראלי של השנים האחרונות: ביטים קופצניים, הומור פרוע, ביטחון עצמי מוגזם במכוון, ושפה שמרגישה כאילו</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,27 +507,27 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>ליאור מיארה - מחרוזת שבוי לאהבה 2026</v>
+        <v>נס X סטילה – מי כמוני</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ליאור מיארה - מחרוזת נשיקה 2026</v>
+        <v>מיוז Nightshift Superstar</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411295&amp;sid=55390b5eabec38928044626c162bd3cb</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%95%d7%96-nightshift-superstar/</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>"Nightshift Superstar" הוא אחד השירים המפתיעים ביותר של Muse בשנים האחרונות. בעוד שהלהקה מזוהה בדרך כלל עם רוק חללי, פרוגרסיבי ודרמטי, כאן היא פונה לטריטוריה הרבה יותר רקידה: שילוב של French House, דיסקו מודרני, פאנק אלקטרוני ורוק אצטדיונים. השיר הוא</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -545,36 +545,36 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ליאור מיארה - מחרוזת נשיקה 2026</v>
+        <v>מיוז Nightshift Superstar</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יאיר בן טוב - מנסה</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-06-09</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411294&amp;sid=55390b5eabec38928044626c162bd3cb</v>
+        <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Capital FM</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,36 +583,36 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יאיר בן טוב - מנסה</v>
+        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>גוסטו - רוב הזמן את אשתי</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-06-09</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411293&amp;sid=55390b5eabec38928044626c162bd3cb</v>
+        <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Capital FM</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,36 +621,36 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>גוסטו - רוב הזמן את אשתי</v>
+        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אמיר שוהר - מסיבה של השמחות</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-06-09</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411292&amp;sid=55390b5eabec38928044626c162bd3cb</v>
+        <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Capital FM</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,36 +659,36 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אמיר שוהר - מסיבה של השמחות</v>
+        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אוהד חסקי &amp; אליף יילדיז - את בגדת בי</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-06-09</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411291&amp;sid=55390b5eabec38928044626c162bd3cb</v>
+        <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Capital FM</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,36 +697,36 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אוהד חסקי &amp; אליף יילדיז - את בגדת בי</v>
+        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אביתר גואטה - החטא שלי</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-06-09</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411290&amp;sid=55390b5eabec38928044626c162bd3cb</v>
+        <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>Capital FM</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,33 +735,33 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אביתר גואטה - החטא שלי</v>
+        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026)</v>
+        <v>DEEP PURPLE - DIABLO (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=ym-h0EIlL3A</v>
+        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Capital FM</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,33 +773,33 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Jason Derulo - The Other Side (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>Reba McEntire - You Never Gave Up On Me</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=bIwcNmu-rAg</v>
+        <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Capital FM</v>
+        <v>Reba McEntire</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,33 +811,33 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Stephen Sanchez - Be More (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
+        <v>Reba McEntire - You Never Gave Up On Me - Reba McEntire</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026)</v>
+        <v>elijah woods - Wonder (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=oLzj8E8fHRQ</v>
+        <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Capital FM</v>
+        <v>elijah woods</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,33 +849,33 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Jason Derulo - Take You Dancing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>elijah woods - Wonder (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=YIy2g4enMiY</v>
+        <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,21 +887,21 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Sekou - Someone Like You (Adele Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026)</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=NhuPT6MR2XU</v>
+        <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -925,21 +925,21 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Sienna Spiro - He's Not My Baby, I'm His (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video)</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=Z4RpBEg5uis</v>
+        <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -951,7 +951,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Capital FM</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,33 +963,33 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>DEEP PURPLE - DIABLO (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Reba McEntire - You Never Gave Up On Me</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=AUCRUStLmJM</v>
+        <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Reba McEntire</v>
+        <v>Capital FM</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,21 +1001,21 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Reba McEntire - You Never Gave Up On Me - Reba McEntire</v>
+        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>elijah woods - Wonder (Official Lyric Video)</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=sDDbD4R-xD4</v>
+        <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1027,7 +1027,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>elijah woods</v>
+        <v>Capital FM</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,21 +1039,21 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>elijah woods - Wonder (Official Lyric Video) - elijah woods</v>
+        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=MxJQoyKh8TQ</v>
+        <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Capital FM and XG</v>
+        <v>Capital FM</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,21 +1077,21 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>XG - Flowers (Sweet Female Attitude Cover) (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
+        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026)</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=-UIkkGxMQG8</v>
+        <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1115,21 +1115,21 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Niall Horan - Nice To Meet Ya (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=b_uO5ROpk_0</v>
+        <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,21 +1153,21 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Niall Horan - Steal My Girl (One Direction cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026)</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=hSJfAFpdllk</v>
+        <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and XG</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,27 +1191,27 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Niall Horan - Dinner Party (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital</v>
+        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=vdMK2DvnWJI</v>
+        <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1229,27 +1229,27 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Niall Horan - Slow Hands (Live at Capital's Summertime Ball 2026) | Capital - Capital FM</v>
+        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=5gvhRAGaOUo</v>
+        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1267,27 +1267,27 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>RAYE - Joy (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=2AIMnAPxqfw</v>
+        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1305,33 +1305,33 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Myles Smith - Stargazing (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026)</v>
+        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=UD7HkkAbnVA</v>
+        <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,33 +1343,33 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Lola Young - From Down Here (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=c5u3ur4vLo0</v>
+        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Capital FM and XG</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,27 +1381,27 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>XG - Hypnotize (Live at Capital's Summertime Ball 2026) - Capital FM and XG</v>
+        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026)</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=MibVDrnrQ10</v>
+        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1419,33 +1419,33 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Sienna Spiro - The Visitor (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=UhWumamExiI</v>
+        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Take That</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,27 +1457,27 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Sienna Spiro - Die On This Hill (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026)</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=Z_HR2ZYY1VA</v>
+        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1495,27 +1495,27 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>RAYE - Where Is My Husband? (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026)</v>
+        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=ywplqaIeHeQ</v>
+        <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1533,27 +1533,27 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>RAYE - Escapism (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=9S61JkOZLe8</v>
+        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1571,27 +1571,27 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Take That - Never Forget (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
+        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026)</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=_4SfgNPngbo</v>
+        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1609,33 +1609,33 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Robyn - Dancing On My Own (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026)</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=_I9qIxmrDuI</v>
+        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Capital FM and Take That</v>
+        <v>Capital FM</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,27 +1647,27 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Take That - Patience (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
+        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026)</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=5AyQM_coDb8</v>
+        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1685,27 +1685,27 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Mis-Teeq - Full Set (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026)</v>
+        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=2ekY7Cb7CKs</v>
+        <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1723,33 +1723,33 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Myles Smith - Stay (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=0nc-qdhh6eU</v>
+        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Capital FM and Take That</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,27 +1761,27 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Take That - Rule The World (Live at Capital's Summertime Ball 2026) - Capital FM and Take That</v>
+        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026)</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B37" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=dZjAtTc9DBQ</v>
+        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1799,33 +1799,33 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Sienna Spiro - Material Lover (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=T6TmxqOGIf0</v>
+        <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Take That - Shine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026)</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B39" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=4jnM--XhsC0</v>
+        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Capital FM</v>
+        <v>Capital FM and Lola Young</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,27 +1875,27 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>MEEK - Dracula (Tame Impala Cover) (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B40" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=kKSlraqNMhI</v>
+        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1913,21 +1913,21 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>MEEK - Fabulous (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026)</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B41" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=cUvsaKkjHYQ</v>
+        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1939,7 +1939,7 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,21 +1951,21 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Lola Young - Messy (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B42" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=oKKNK0OCpQk</v>
+        <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1989,21 +1989,21 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Stephen Sanchez - Until I Found You (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B43" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=ymvr4RCN-WE</v>
+        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,21 +2027,21 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Lola Young - D£aler (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B44" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=nhL2l4HCiRg</v>
+        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2053,7 +2053,7 @@
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Capital FM and Lola Young</v>
+        <v>Capital FM</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,21 +2065,21 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Lola Young - One Thing (Live at Capital's Summertime Ball 2026) - Capital FM and Lola Young</v>
+        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B45" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=e0PkSQNMcGs</v>
+        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2103,21 +2103,21 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Bebe Rexha - Sad Girls (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B46" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=-7mPIus0U5Y</v>
+        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2141,21 +2141,21 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Robyn - Dopamine (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026)</v>
+        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
       </c>
       <c r="B47" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=G6jhovaAz3U</v>
+        <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2179,33 +2179,33 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Jason Derulo - Ridin' Solo (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026) - Capital FM</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026)</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
       </c>
       <c r="B48" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=QkCKENp-4Rs</v>
+        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Capital FM</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,33 +2217,33 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Jason Derulo - Trumpets (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026)</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
       </c>
       <c r="B49" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=jsFekVlEaSA</v>
+        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Capital FM</v>
+        <v>TheCranberriesTV</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,33 +2255,33 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Jason Derulo - Whatcha Say (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026)</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=nfDKQ09bY_w</v>
+        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Capital FM</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,33 +2293,33 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Bebe Rexha - New Religion (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026)</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=eqceDkaK3PU</v>
+        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Capital FM</v>
+        <v>Grace Enger</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,33 +2331,33 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Bebe Rexha - I'm Good (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026)</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
       </c>
       <c r="B52" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=UlP9zTLUeLw</v>
+        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Capital FM</v>
+        <v>The Offspring</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,21 +2369,21 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Bebe Rexha - In The Name Of Love (Live at Capital's Summertime Ball 2026) - Capital FM</v>
+        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K</v>
+        <v>Lola Young – From Down Here (From The Pool)</v>
       </c>
       <c r="B53" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=QCNwFDTkfYU</v>
+        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2395,7 +2395,7 @@
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Lola Young</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,33 +2407,33 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Strange Surreal AI - In Here - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel)</v>
+        <v>CAIN - Living Water (Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=5-peG8H-lqE</v>
+        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>TheCranberriesTV</v>
+        <v>CAIN</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,21 +2445,21 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>The Cranberries - Scenes From 'Linger' (The Only Color Reel) - TheCranberriesTV</v>
+        <v>CAIN - Living Water (Music Video) - CAIN</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video)</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=P26-NjdBmbU</v>
+        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2471,7 +2471,7 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Jordana Bryant</v>
+        <v>Eric Clapton</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,21 +2483,21 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Jordana Bryant - Too Little Too Late (Official Lyric Video) - Jordana Bryant</v>
+        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video)</v>
+        <v>Blu DeTiger - Whisper (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=BON1BSWLntE</v>
+        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Grace Enger</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,21 +2521,21 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Grace Enger - "Running Back To You" (Official Music Video) - Grace Enger</v>
+        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
       </c>
       <c r="B57" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=UTw106Ivz8o</v>
+        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>The Offspring</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,21 +2559,21 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>The Offspring - Gone Away | Live at BeachLife Festival 2026 - The Offspring</v>
+        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Lola Young – From Down Here (From The Pool)</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
       </c>
       <c r="B58" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=YFhpMpONGUY</v>
+        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2585,7 +2585,7 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Lola Young</v>
+        <v>Pink Floyd</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,21 +2597,21 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Lola Young – From Down Here (From The Pool) - Lola Young</v>
+        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>CAIN - Living Water (Music Video)</v>
+        <v>Holly Humberstone - it’s just White Noise</v>
       </c>
       <c r="B59" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=WrsXAfnTAdA</v>
+        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>CAIN</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,33 +2635,33 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>CAIN - Living Water (Music Video) - CAIN</v>
+        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video)</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=L7Ls8ceHxhc</v>
+        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Eric Clapton</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,33 +2673,33 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>B.B. King &amp; Eric Clapton - Riding With The King (Official Music Video) - Eric Clapton</v>
+        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video)</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=OfcBfPnskG4</v>
+        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Blu DeTiger</v>
+        <v>Muse</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,33 +2711,33 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Blu DeTiger - Whisper (Official Music Video) - Blu DeTiger</v>
+        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video)</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
       </c>
       <c r="B62" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=-uvNvVtUidc</v>
+        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,33 +2749,33 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Romeo Santos, Prince Royce - Ay! San Miguel (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio)</v>
+        <v>Evanescence - Sanctuary (Official Visualizer)</v>
       </c>
       <c r="B63" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=WZUKJ90i6Tw</v>
+        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Pink Floyd</v>
+        <v>Evanescence</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,33 +2787,33 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Pink Floyd - Pigs on the Wing (8-Track Version - Official Audio) - Pink Floyd</v>
+        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Holly Humberstone - it’s just White Noise</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
       </c>
       <c r="B64" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=KeRZtPUjl8g</v>
+        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Holly Humberstone</v>
+        <v>The Beaches</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,33 +2825,33 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Holly Humberstone - it’s just White Noise - Holly Humberstone</v>
+        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video)</v>
+        <v>Bella White - Stuff (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=So5gx12fCsA</v>
+        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Freya Ridings</v>
+        <v>Bella White</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,33 +2863,33 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Freya Ridings - Mother Of Pearl (Official Video) - Freya Ridings</v>
+        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video)</v>
+        <v>Meduza, Rani - Silence (Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=p--xk9n1eIM</v>
+        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Muse</v>
+        <v>Meduza and 2 more</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,33 +2901,33 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>MUSE - Nightshift Superstar (Official Music Video) - Muse</v>
+        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser)</v>
+        <v>CAIN - Living Water (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=zr9CYpgPueI</v>
+        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Ellie Goulding</v>
+        <v>CAIN</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,33 +2939,33 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Ellie Goulding - Black Prada Dress (Visualiser) - Ellie Goulding</v>
+        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer)</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
       </c>
       <c r="B68" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=E64jOWeVfpg</v>
+        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Evanescence</v>
+        <v>Fitz and the Tantrums</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,33 +2977,33 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Evanescence - Sanctuary (Official Visualizer) - Evanescence</v>
+        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer)</v>
+        <v>Jeremy Camp - Reflector (Official Music Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=N7TOR_l-CM8</v>
+        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>The Beaches</v>
+        <v>Jeremy Camp</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,33 +3015,33 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>The Beaches - Perfect 10 (Official Visualizer) - The Beaches</v>
+        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Bella White - Stuff (Official Music Video)</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
       </c>
       <c r="B70" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=7QZtxsGBTks</v>
+        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Bella White</v>
+        <v>Alesso</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,33 +3053,33 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Bella White - Stuff (Official Music Video) - Bella White</v>
+        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer)</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
       </c>
       <c r="B71" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=cIdqz-WMod4</v>
+        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Meduza and 2 more</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,33 +3091,33 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Meduza, Rani - Silence (Official Visualizer) - Meduza and 2 more</v>
+        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>CAIN - Living Water (Lyric Video)</v>
+        <v>Isabel LaRosa - Every Life (Visualizer)</v>
       </c>
       <c r="B72" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=Hv-8CM5NIPM</v>
+        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>CAIN</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,33 +3129,33 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>CAIN - Living Water (Lyric Video) - CAIN</v>
+        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer)</v>
+        <v>Wyatt Flores - Half The Man (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=Zx-ZPBbcA58</v>
+        <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Fitz and the Tantrums</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,33 +3167,33 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Fitz and the Tantrums - Greenlight (Official Visualizer) - Fitz and the Tantrums</v>
+        <v>Wyatt Flores - Half The Man (Official Music Video) - Wyatt Flores</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video)</v>
+        <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=SR-4q1yiYNA</v>
+        <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Jeremy Camp</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,33 +3205,33 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Jeremy Camp - Reflector (Official Music Video) - Jeremy Camp</v>
+        <v>Mckenna Grace - Ugly and Rotten (Official Music Video) - Mckenna Grace</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer)</v>
+        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
       </c>
       <c r="B75" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=bS9C1ipyMy8</v>
+        <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Alesso</v>
+        <v>Robert Grace</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,33 +3243,33 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Alesso, OneRepublic - In Your Eyes (Visualizer) - Alesso</v>
+        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer)</v>
+        <v>Boyzone - No Matter What (Live)</v>
       </c>
       <c r="B76" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=wBBQptUsOhw</v>
+        <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Malcolm Todd</v>
+        <v>Boyzone</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,33 +3281,33 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Malcolm Todd - Free.99 (Official Visualizer) - Malcolm Todd</v>
+        <v>Boyzone - No Matter What (Live) - Boyzone</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer)</v>
+        <v>Florrie - The Times (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=tIQDAtwNAY4</v>
+        <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Isabel LaRosa</v>
+        <v>florriemusic</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,33 +3319,33 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Isabel LaRosa - Every Life (Visualizer) - Isabel LaRosa</v>
+        <v>Florrie - The Times (Official Video) - florriemusic</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video)</v>
+        <v>Madonna - Love Sensation (Official Visualizer)</v>
       </c>
       <c r="B78" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=2ChzcWHryFM</v>
+        <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Wyatt Flores</v>
+        <v>Madonna</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,33 +3357,33 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Wyatt Flores - Half The Man (Official Music Video) - Wyatt Flores</v>
+        <v>Madonna - Love Sensation (Official Visualizer) - Madonna</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video)</v>
+        <v>DMA'S - Hurracane (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=4yXFVgy7laM</v>
+        <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Mckenna Grace</v>
+        <v>DMA'S</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,33 +3395,33 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Mckenna Grace - Ugly and Rotten (Official Music Video) - Mckenna Grace</v>
+        <v>DMA'S - Hurracane (Official Video) - DMA'S</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO)</v>
+        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
       </c>
       <c r="B80" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=fbpQjMi3Hco</v>
+        <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Robert Grace</v>
+        <v>Lainey Wilson and John Mayer</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,33 +3433,33 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Robert Grace - If You Were Gone ft. Bob Grace (OFFICIAL LYRIC VIDEO) - Robert Grace</v>
+        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio) - Lainey Wilson and John Mayer</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Boyzone - No Matter What (Live)</v>
+        <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=CEy96_jHw-Q</v>
+        <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Boyzone</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,33 +3471,33 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Boyzone - No Matter What (Live) - Boyzone</v>
+        <v>ROLE MODEL - High Hopes 3000 (Official Music Video) - ROLE MODEL</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Florrie - The Times (Official Video)</v>
+        <v>Shawn Mendes - Treat You Better (Live from New York)</v>
       </c>
       <c r="B82" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=6yBlNUaW7r4</v>
+        <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>florriemusic</v>
+        <v>Shawn Mendes</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,33 +3509,33 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Florrie - The Times (Official Video) - florriemusic</v>
+        <v>Shawn Mendes - Treat You Better (Live from New York) - Shawn Mendes</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer)</v>
+        <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=88fD-UtG_yo</v>
+        <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Madonna</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,33 +3547,33 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Madonna - Love Sensation (Official Visualizer) - Madonna</v>
+        <v>SIENNA SPIRO - The Visitor (Official Music Video) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>DMA'S - Hurracane (Official Video)</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
       </c>
       <c r="B84" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=-zTB57LiXPk</v>
+        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>DMA'S</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,33 +3585,33 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>DMA'S - Hurracane (Official Video) - DMA'S</v>
+        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio)</v>
+        <v>Europe - The Cult of Ignorance (Official Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=JzW6RnzeF9A</v>
+        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Lainey Wilson and John Mayer</v>
+        <v>Europe</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,33 +3623,33 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Lainey Wilson and John Mayer - Phone, Keys, Wallet (Official Audio) - Lainey Wilson and John Mayer</v>
+        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video)</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=D_KTG0BzRiI</v>
+        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>ROLE MODEL</v>
+        <v>Air Supply</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,33 +3661,33 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>ROLE MODEL - High Hopes 3000 (Official Music Video) - ROLE MODEL</v>
+        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York)</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=29bfaHc1XiY</v>
+        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Shawn Mendes</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,33 +3699,33 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Shawn Mendes - Treat You Better (Live from New York) - Shawn Mendes</v>
+        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video)</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
       </c>
       <c r="B88" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=LiYb4WGbp5Y</v>
+        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Allen Stone and Placeholder Sessions</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,33 +3737,33 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>SIENNA SPIRO - The Visitor (Official Music Video) - SIENNA SPIRO</v>
+        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
       </c>
       <c r="B89" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=lC14fuU8aPc</v>
+        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Morgan Wallen</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,33 +3775,33 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Just Slide Official Music Video | Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video)</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
       </c>
       <c r="B90" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=p-IOsjOJpnA</v>
+        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Europe</v>
+        <v>Billy Idol</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,33 +3813,33 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Europe - The Cult of Ignorance (Official Video) - Europe</v>
+        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video)</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
       </c>
       <c r="B91" t="str">
-        <v>6 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=axiK2vYjXio</v>
+        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>6 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Air Supply</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,33 +3851,33 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Air Supply - Sweet Dreams (Official Lyric Video) - Air Supply</v>
+        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video)</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=TS2Mgp5F0cs</v>
+        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Julia Cole Music</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,33 +3889,33 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Julia Cole - Treat Me Like Dirt (Official Lyric Video) - Julia Cole Music</v>
+        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions</v>
+        <v>Hippo Campus - South</v>
       </c>
       <c r="B93" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=JPetpt4QMPE</v>
+        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>6 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Allen Stone and Placeholder Sessions</v>
+        <v>Hippo Campus</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,33 +3927,33 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Allen Stone - A Fathers Song - Placeholder Sessions - Allen Stone and Placeholder Sessions</v>
+        <v>Hippo Campus - South - Hippo Campus</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa)</v>
+        <v>elijah woods - Old (Treehouse Sessions)</v>
       </c>
       <c r="B94" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=qhmWM3uXPAU</v>
+        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Morgan Wallen</v>
+        <v>elijah woods</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,33 +3965,33 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Morgan Wallen - Don't We (Live From Tuscaloosa) - Morgan Wallen</v>
+        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video)</v>
+        <v>Nothing But Thieves - Evolution (Official Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=47LNk7oiTVI</v>
+        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Billy Idol</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,33 +4003,33 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Billy Idol - John Wayne feat. Alison Mosshart (Official Music Video) - Billy Idol</v>
+        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K</v>
+        <v>Ariana Grande - hate that i made you love me (official music video)</v>
       </c>
       <c r="B96" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=Ru3fB2l1RSo</v>
+        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>11 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Kelly Boesch AI Art</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,33 +4041,33 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>'It's Unusual' Official Music Video - Kelly Boesch | 4K - Kelly Boesch AI Art</v>
+        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video)</v>
+        <v>LAUREL - Fire Breather</v>
       </c>
       <c r="B97" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=AMW1Zq9RbIU</v>
+        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Icona Pop</v>
+        <v>LAUREL</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,33 +4079,33 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Video) - Icona Pop</v>
+        <v>LAUREL - Fire Breather - LAUREL</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Hippo Campus - South</v>
+        <v>The Warning - Ego (Performance Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=FYOmFfV7Ojo</v>
+        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Hippo Campus</v>
+        <v>The Warning</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,33 +4117,33 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Hippo Campus - South - Hippo Campus</v>
+        <v>The Warning - Ego (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>elijah woods - Old (Treehouse Sessions)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
       </c>
       <c r="B99" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=yDlkPdR_6zM</v>
+        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>elijah woods</v>
+        <v>David Guetta and Jennifer Lopez</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,33 +4155,33 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>elijah woods - Old (Treehouse Sessions) - elijah woods</v>
+        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video)</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B100" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=hmjfuuuRRYU</v>
+        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,33 +4193,33 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Nothing But Thieves - Evolution (Official Video) - Nothing But Thieves</v>
+        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video)</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
       </c>
       <c r="B101" t="str">
-        <v>8 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=82-jTNka3uc</v>
+        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>8 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Ariana Grande</v>
+        <v>Andrew Bird</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,33 +4231,33 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Ariana Grande - hate that i made you love me (official music video) - Ariana Grande</v>
+        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>LAUREL - Fire Breather</v>
+        <v>Danny Gokey - God's Not (Official Music Video)</v>
       </c>
       <c r="B102" t="str">
-        <v>8 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=rtyavLIJjy0</v>
+        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>8 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G102" t="str">
         <v/>
       </c>
       <c r="H102" t="str">
-        <v>LAUREL</v>
+        <v>Danny Gokey</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,33 +4269,33 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>LAUREL - Fire Breather - LAUREL</v>
+        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>The Warning - Ego (Performance Video)</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
       </c>
       <c r="B103" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=7PApWObImjo</v>
+        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E103" t="str">
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G103" t="str">
         <v/>
       </c>
       <c r="H103" t="str">
-        <v>The Warning</v>
+        <v>Armik</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4307,33 +4307,33 @@
         <v/>
       </c>
       <c r="L103" t="str">
-        <v>The Warning - Ego (Performance Video) - The Warning</v>
+        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video]</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
       </c>
       <c r="B104" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=vruZSAYJBe4</v>
+        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E104" t="str">
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G104" t="str">
         <v/>
       </c>
       <c r="H104" t="str">
-        <v>David Guetta and Jennifer Lopez</v>
+        <v>Holly Humberstone and Free People</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4345,3774 +4345,3622 @@
         <v/>
       </c>
       <c r="L104" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Salvame Hoy (feat. Gabito Ballesteros) [Official Lyric Video] - David Guetta and Jennifer Lopez</v>
+        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video]</v>
+        <v>Eat For Peace</v>
       </c>
       <c r="B105" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=k93t10R-Qrg</v>
+        <v>https://music.apple.com/us/song/eat-for-peace/1891187413</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E105" t="str">
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>10 days ago</v>
+        <v>Alone Together</v>
       </c>
       <c r="G105" t="str">
-        <v/>
+        <v>3:18</v>
       </c>
       <c r="H105" t="str">
-        <v>Armin van Buuren</v>
+        <v>Show Me the Body</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/eat-for-peace/1891187411</v>
       </c>
       <c r="L105" t="str">
-        <v>Armin van Buuren - Equanimity (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Eat For Peace - Show Me the Body</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill)</v>
+        <v>Too Easy</v>
       </c>
       <c r="B106" t="str">
-        <v>11 days ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=XyRgdfXo2nI</v>
+        <v>https://music.apple.com/us/song/too-easy/6774752170</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E106" t="str">
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>11 days ago</v>
+        <v>Too Easy - Single</v>
       </c>
       <c r="G106" t="str">
-        <v/>
+        <v>1:54</v>
       </c>
       <c r="H106" t="str">
-        <v>Andrew Bird</v>
+        <v>Tinashe</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/tinashe/464835513</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/too-easy/6774752168</v>
       </c>
       <c r="L106" t="str">
-        <v>“I Didn’t Know What Time It Was” - Andrew Bird Jazz Trio (Live from The Green Mill) - Andrew Bird</v>
+        <v>Too Easy - Tinashe</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video)</v>
+        <v>I Knew It, I Knew You</v>
       </c>
       <c r="B107" t="str">
-        <v>11 days ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=oGpKqX6ftcU</v>
+        <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E107" t="str">
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>11 days ago</v>
+        <v>I Knew It, I Knew You - Single</v>
       </c>
       <c r="G107" t="str">
-        <v/>
+        <v>2:58</v>
       </c>
       <c r="H107" t="str">
-        <v>Danny Gokey</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/i-knew-it-i-knew-you/6775527442</v>
       </c>
       <c r="L107" t="str">
-        <v>Danny Gokey - God's Not (Official Music Video) - Danny Gokey</v>
+        <v>I Knew It, I Knew You - Taylor Swift</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar)</v>
+        <v>Love Sensation</v>
       </c>
       <c r="B108" t="str">
-        <v>11 days ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=51Zu2iU2z2Q</v>
+        <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E108" t="str">
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>11 days ago</v>
+        <v>Love Sensation - Single</v>
       </c>
       <c r="G108" t="str">
-        <v/>
+        <v>3:48</v>
       </c>
       <c r="H108" t="str">
-        <v>Armik</v>
+        <v>Madonna</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/love-sensation/6774810102</v>
       </c>
       <c r="L108" t="str">
-        <v>Armik - Brisas (2026 Remaster/Remix) (Exciting Rumba Flamenco, Spanish Guitar) - Armik</v>
+        <v>Love Sensation - Madonna</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions)</v>
+        <v>Mi Yo De Antes</v>
       </c>
       <c r="B109" t="str">
-        <v>11 days ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=c1GR2TTs9W8</v>
+        <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E109" t="str">
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>11 days ago</v>
+        <v>Mi Yo De Antes - Single</v>
       </c>
       <c r="G109" t="str">
-        <v/>
+        <v>3:04</v>
       </c>
       <c r="H109" t="str">
-        <v>Holly Humberstone and Free People</v>
+        <v>Ozuna</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/mi-yo-de-antes/6769193983</v>
       </c>
       <c r="L109" t="str">
-        <v>Holly Humberstone - Lucy (Free People Sessions) - Holly Humberstone and Free People</v>
+        <v>Mi Yo De Antes - Ozuna</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Eat For Peace</v>
+        <v>Three Nations</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/eat-for-peace/1891187413</v>
+        <v>https://music.apple.com/us/song/three-nations/6776010602</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E110" t="str">
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Alone Together</v>
+        <v>Official FIFA World Cup 2026™ Album</v>
       </c>
       <c r="G110" t="str">
-        <v>3:18</v>
+        <v>3:30</v>
       </c>
       <c r="H110" t="str">
-        <v>Show Me the Body</v>
+        <v>21 Savage</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/show-me-the-body/982959371</v>
+        <v>https://music.apple.com/us/artist/21-savage/894820464</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/eat-for-peace/1891187411</v>
+        <v>https://music.apple.com/us/album/three-nations/6776010591</v>
       </c>
       <c r="L110" t="str">
-        <v>Eat For Peace - Show Me the Body</v>
+        <v>Three Nations - 21 Savage</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Too Easy</v>
+        <v>Champions (WC 26)</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/too-easy/6774752170</v>
+        <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E111" t="str">
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Too Easy - Single</v>
+        <v>Champions (WC 26) - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>1:54</v>
+        <v>4:15</v>
       </c>
       <c r="H111" t="str">
-        <v>Tinashe</v>
+        <v>IShowSpeed</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/tinashe/464835513</v>
+        <v>https://music.apple.com/us/artist/ishowspeed/1574723975</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/too-easy/6774752168</v>
+        <v>https://music.apple.com/us/album/champions-wc-26/6775282246</v>
       </c>
       <c r="L111" t="str">
-        <v>Too Easy - Tinashe</v>
+        <v>Champions (WC 26) - IShowSpeed</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>I Knew It, I Knew You</v>
+        <v>ENCERRONES</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/i-knew-it-i-knew-you/6775527443</v>
+        <v>https://music.apple.com/us/song/encerrones/6771854522</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E112" t="str">
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>I Knew It, I Knew You - Single</v>
+        <v>TEOFANIA</v>
       </c>
       <c r="G112" t="str">
-        <v>2:58</v>
+        <v>2:23</v>
       </c>
       <c r="H112" t="str">
-        <v>Taylor Swift</v>
+        <v>LENCHO</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/i-knew-it-i-knew-you/6775527442</v>
+        <v>https://music.apple.com/us/album/encerrones/6771854517</v>
       </c>
       <c r="L112" t="str">
-        <v>I Knew It, I Knew You - Taylor Swift</v>
+        <v>ENCERRONES - LENCHO</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Love Sensation</v>
+        <v>Cowgirl</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/love-sensation/6774810627</v>
+        <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E113" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Love Sensation - Single</v>
+        <v>The Outlaw Cherie Lee &amp; Other Western Tales</v>
       </c>
       <c r="G113" t="str">
-        <v>3:48</v>
+        <v>2:56</v>
       </c>
       <c r="H113" t="str">
-        <v>Madonna</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/love-sensation/6774810102</v>
+        <v>https://music.apple.com/us/album/cowgirl/1894906682</v>
       </c>
       <c r="L113" t="str">
-        <v>Love Sensation - Madonna</v>
+        <v>Cowgirl - Shaboozey</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Mi Yo De Antes</v>
+        <v>PASSENGER</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/mi-yo-de-antes/6769194234</v>
+        <v>https://music.apple.com/us/song/passenger/6773456081</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E114" t="str">
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Mi Yo De Antes - Single</v>
+        <v>WILDCHILD</v>
       </c>
       <c r="G114" t="str">
-        <v>3:04</v>
+        <v>2:39</v>
       </c>
       <c r="H114" t="str">
-        <v>Ozuna</v>
+        <v>Alex Warren</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/ozuna/283578837</v>
+        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/mi-yo-de-antes/6769193983</v>
+        <v>https://music.apple.com/us/album/passenger/6773456078</v>
       </c>
       <c r="L114" t="str">
-        <v>Mi Yo De Antes - Ozuna</v>
+        <v>PASSENGER - Alex Warren</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Three Nations</v>
+        <v>Secret Language</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/three-nations/6776010602</v>
+        <v>https://music.apple.com/us/song/secret-language/6774223667</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E115" t="str">
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Official FIFA World Cup 2026™ Album</v>
+        <v>Sweet Fortune</v>
       </c>
       <c r="G115" t="str">
-        <v>3:30</v>
+        <v>3:53</v>
       </c>
       <c r="H115" t="str">
-        <v>21 Savage</v>
+        <v>Ryan Beatty</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/21-savage/894820464</v>
+        <v>https://music.apple.com/us/artist/ryan-beatty/483234172</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/three-nations/6776010591</v>
+        <v>https://music.apple.com/us/album/secret-language/6774223660</v>
       </c>
       <c r="L115" t="str">
-        <v>Three Nations - 21 Savage</v>
+        <v>Secret Language - Ryan Beatty</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Champions (WC 26)</v>
+        <v>True Colors</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/champions-wc-26/6775282247</v>
+        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E116" t="str">
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Champions (WC 26) - Single</v>
+        <v>Thank You</v>
       </c>
       <c r="G116" t="str">
-        <v>4:15</v>
+        <v>3:39</v>
       </c>
       <c r="H116" t="str">
-        <v>IShowSpeed</v>
+        <v>Mike D</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/ishowspeed/1574723975</v>
+        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/champions-wc-26/6775282246</v>
+        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
       </c>
       <c r="L116" t="str">
-        <v>Champions (WC 26) - IShowSpeed</v>
+        <v>True Colors - Mike D</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>ENCERRONES</v>
+        <v>High Hopes 3000</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/encerrones/6771854522</v>
+        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E117" t="str">
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>TEOFANIA</v>
+        <v>Chuck Timely &amp; The Hourglass</v>
       </c>
       <c r="G117" t="str">
-        <v>2:23</v>
+        <v>4:05</v>
       </c>
       <c r="H117" t="str">
-        <v>LENCHO</v>
+        <v>ROLE MODEL</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/lencho/1854923384</v>
+        <v>https://music.apple.com/us/artist/role-model/199215762</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/encerrones/6771854517</v>
+        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
       </c>
       <c r="L117" t="str">
-        <v>ENCERRONES - LENCHO</v>
+        <v>High Hopes 3000 - ROLE MODEL</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Cowgirl</v>
+        <v>Vertical</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/cowgirl/1894906692</v>
+        <v>https://music.apple.com/us/song/vertical/1892436336</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E118" t="str">
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>The Outlaw Cherie Lee &amp; Other Western Tales</v>
+        <v>Emotional Junglist</v>
       </c>
       <c r="G118" t="str">
-        <v>2:56</v>
+        <v>2:36</v>
       </c>
       <c r="H118" t="str">
-        <v>Shaboozey</v>
+        <v>Nia Archives</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/shaboozey/914125510</v>
+        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/cowgirl/1894906682</v>
+        <v>https://music.apple.com/us/album/vertical/1892436329</v>
       </c>
       <c r="L118" t="str">
-        <v>Cowgirl - Shaboozey</v>
+        <v>Vertical - Nia Archives</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>PASSENGER</v>
+        <v>snake the drain</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/passenger/6773456081</v>
+        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E119" t="str">
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>WILDCHILD</v>
+        <v>this time it’s different / snake the drain - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:39</v>
+        <v>3:08</v>
       </c>
       <c r="H119" t="str">
-        <v>Alex Warren</v>
+        <v>Devon Again</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/alex-warren/1572671688</v>
+        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/passenger/6773456078</v>
+        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
       </c>
       <c r="L119" t="str">
-        <v>PASSENGER - Alex Warren</v>
+        <v>snake the drain - Devon Again</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Secret Language</v>
+        <v>Every Single Weekend (feat. Jamie xx)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/secret-language/6774223667</v>
+        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E120" t="str">
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Sweet Fortune</v>
+        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:53</v>
+        <v>2:10</v>
       </c>
       <c r="H120" t="str">
-        <v>Ryan Beatty</v>
+        <v>The Avalanches</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/ryan-beatty/483234172</v>
+        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/secret-language/6774223660</v>
+        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
       </c>
       <c r="L120" t="str">
-        <v>Secret Language - Ryan Beatty</v>
+        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>True Colors</v>
+        <v>Bluffin'</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/true-colors/6776032892</v>
+        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E121" t="str">
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Thank You</v>
+        <v>Piss In The Wind (Deluxe)</v>
       </c>
       <c r="G121" t="str">
-        <v>3:39</v>
+        <v>2:34</v>
       </c>
       <c r="H121" t="str">
-        <v>Mike D</v>
+        <v>Joji</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
+        <v>https://music.apple.com/us/artist/joji/1258279972</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/true-colors/6776032889</v>
+        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
       </c>
       <c r="L121" t="str">
-        <v>True Colors - Mike D</v>
+        <v>Bluffin' - Joji</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>High Hopes 3000</v>
+        <v>Dreams</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/high-hopes-3000/6772366438</v>
+        <v>https://music.apple.com/us/song/dreams/1884731028</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E122" t="str">
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Chuck Timely &amp; The Hourglass</v>
+        <v>Free Your Mind</v>
       </c>
       <c r="G122" t="str">
-        <v>4:05</v>
+        <v>3:56</v>
       </c>
       <c r="H122" t="str">
-        <v>ROLE MODEL</v>
+        <v>Prospa</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/role-model/199215762</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/high-hopes-3000/6772366436</v>
+        <v>https://music.apple.com/us/album/dreams/1884730177</v>
       </c>
       <c r="L122" t="str">
-        <v>High Hopes 3000 - ROLE MODEL</v>
+        <v>Dreams - Prospa</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Vertical</v>
+        <v>Cotton</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/vertical/1892436336</v>
+        <v>https://music.apple.com/us/song/cotton/1887627941</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E123" t="str">
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Emotional Junglist</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G123" t="str">
-        <v>2:36</v>
+        <v>3:43</v>
       </c>
       <c r="H123" t="str">
-        <v>Nia Archives</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/nia-archives/1515978311</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/vertical/1892436329</v>
+        <v>https://music.apple.com/us/album/cotton/1887627836</v>
       </c>
       <c r="L123" t="str">
-        <v>Vertical - Nia Archives</v>
+        <v>Cotton - Vince Staples</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>snake the drain</v>
+        <v>Black Prada Dress</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/snake-the-drain/6771506655</v>
+        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E124" t="str">
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>this time it’s different / snake the drain - Single</v>
+        <v>I Know Too Much</v>
       </c>
       <c r="G124" t="str">
-        <v>3:08</v>
+        <v>3:19</v>
       </c>
       <c r="H124" t="str">
-        <v>Devon Again</v>
+        <v>Ellie Goulding</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/devon-again/1574318250</v>
+        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/snake-the-drain/6771506650</v>
+        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
       </c>
       <c r="L124" t="str">
-        <v>snake the drain - Devon Again</v>
+        <v>Black Prada Dress - Ellie Goulding</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Every Single Weekend (feat. Jamie xx)</v>
+        <v>Don’t Break Her Heart</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/every-single-weekend-feat-jamie-xx/6770445933</v>
+        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E125" t="str">
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - Single</v>
+        <v>THERAPY AT THE CLUB</v>
       </c>
       <c r="G125" t="str">
-        <v>2:10</v>
+        <v>3:44</v>
       </c>
       <c r="H125" t="str">
-        <v>The Avalanches</v>
+        <v>FLO</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/the-avalanches/27524431</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/every-single-weekend-feat-jamie-xx/6770445752</v>
+        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
       </c>
       <c r="L125" t="str">
-        <v>Every Single Weekend (feat. Jamie xx) - The Avalanches</v>
+        <v>Don’t Break Her Heart - FLO</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Bluffin'</v>
+        <v>Sexy Ladies (feat. UCB)</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/bluffin/6772951032</v>
+        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E126" t="str">
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Piss In The Wind (Deluxe)</v>
+        <v>BITCH</v>
       </c>
       <c r="G126" t="str">
-        <v>2:34</v>
+        <v>2:50</v>
       </c>
       <c r="H126" t="str">
-        <v>Joji</v>
+        <v>Lizzo</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/joji/1258279972</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/bluffin/6772950585</v>
+        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
       </c>
       <c r="L126" t="str">
-        <v>Bluffin' - Joji</v>
+        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Dreams</v>
+        <v>Noche Without You</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/dreams/1884731028</v>
+        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E127" t="str">
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Free Your Mind</v>
+        <v>SOMA</v>
       </c>
       <c r="G127" t="str">
-        <v>3:56</v>
+        <v>3:23</v>
       </c>
       <c r="H127" t="str">
-        <v>Prospa</v>
+        <v>Skrillex</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/dreams/1884730177</v>
+        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
       </c>
       <c r="L127" t="str">
-        <v>Dreams - Prospa</v>
+        <v>Noche Without You - Skrillex</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Cotton</v>
+        <v>Difficult Love</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/cotton/1887627941</v>
+        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E128" t="str">
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Cry Baby</v>
+        <v>Do That Again</v>
       </c>
       <c r="G128" t="str">
-        <v>3:43</v>
+        <v>2:33</v>
       </c>
       <c r="H128" t="str">
-        <v>Vince Staples</v>
+        <v>Malcolm Todd</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/cotton/1887627836</v>
+        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
       </c>
       <c r="L128" t="str">
-        <v>Cotton - Vince Staples</v>
+        <v>Difficult Love - Malcolm Todd</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Black Prada Dress</v>
+        <v>Tastes So Good</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/black-prada-dress/6773855795</v>
+        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E129" t="str">
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>I Know Too Much</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G129" t="str">
-        <v>3:19</v>
+        <v>3:05</v>
       </c>
       <c r="H129" t="str">
-        <v>Ellie Goulding</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/ellie-goulding/338264227</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/black-prada-dress/6773855466</v>
+        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
       </c>
       <c r="L129" t="str">
-        <v>Black Prada Dress - Ellie Goulding</v>
+        <v>Tastes So Good - Niall Horan</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Don’t Break Her Heart</v>
+        <v>Phone, Keys, Wallet</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/dont-break-her-heart/6764050374</v>
+        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E130" t="str">
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>THERAPY AT THE CLUB</v>
+        <v>Phone, Keys, Wallet - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:44</v>
+        <v>2:52</v>
       </c>
       <c r="H130" t="str">
-        <v>FLO</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/dont-break-her-heart/1895613904</v>
+        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
       </c>
       <c r="L130" t="str">
-        <v>Don’t Break Her Heart - FLO</v>
+        <v>Phone, Keys, Wallet - Lainey Wilson</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Sexy Ladies (feat. UCB)</v>
+        <v>Madrugada</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/sexy-ladies-feat-ucb/6763622116</v>
+        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E131" t="str">
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>BITCH</v>
+        <v>Madrugada - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:50</v>
+        <v>2:58</v>
       </c>
       <c r="H131" t="str">
-        <v>Lizzo</v>
+        <v>Chino Pacas</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/sexy-ladies-feat-ucb/1895402771</v>
+        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
       </c>
       <c r="L131" t="str">
-        <v>Sexy Ladies (feat. UCB) - Lizzo</v>
+        <v>Madrugada - Chino Pacas</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Noche Without You</v>
+        <v>Oh Chet (feat. Travis Scott)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/noche-without-you/6776024792</v>
+        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E132" t="str">
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>SOMA</v>
+        <v>Oh Chet (feat. Travis Scott) - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:23</v>
+        <v>2:23</v>
       </c>
       <c r="H132" t="str">
-        <v>Skrillex</v>
+        <v>Jey One</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/skrillex/356545647</v>
+        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/noche-without-you/6776024723</v>
+        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
       </c>
       <c r="L132" t="str">
-        <v>Noche Without You - Skrillex</v>
+        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Difficult Love</v>
+        <v>An Hour or So (Live at Apple Music Radio)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/difficult-love/6762883069</v>
+        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E133" t="str">
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Do That Again</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G133" t="str">
-        <v>2:33</v>
+        <v>3:02</v>
       </c>
       <c r="H133" t="str">
-        <v>Malcolm Todd</v>
+        <v>Benny G</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/malcolm-todd/1624326848</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/difficult-love/1895057998</v>
+        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
       </c>
       <c r="L133" t="str">
-        <v>Difficult Love - Malcolm Todd</v>
+        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Tastes So Good</v>
+        <v>it’s just White Noise</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/tastes-so-good/6773550038</v>
+        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E134" t="str">
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Dinner Party</v>
+        <v>it’s a real Cruel World - EP</v>
       </c>
       <c r="G134" t="str">
-        <v>3:05</v>
+        <v>3:57</v>
       </c>
       <c r="H134" t="str">
-        <v>Niall Horan</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/tastes-so-good/6773550034</v>
+        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
       </c>
       <c r="L134" t="str">
-        <v>Tastes So Good - Niall Horan</v>
+        <v>it’s just White Noise - Holly Humberstone</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Phone, Keys, Wallet</v>
+        <v>the feeling</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/phone-keys-wallet/6770622562</v>
+        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E135" t="str">
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Phone, Keys, Wallet - Single</v>
+        <v>Oh yeah?</v>
       </c>
       <c r="G135" t="str">
-        <v>2:52</v>
+        <v>4:35</v>
       </c>
       <c r="H135" t="str">
-        <v>Lainey Wilson</v>
+        <v>Steve Lacy</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/lainey-wilson/907166363</v>
+        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/phone-keys-wallet/6770622560</v>
+        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
       </c>
       <c r="L135" t="str">
-        <v>Phone, Keys, Wallet - Lainey Wilson</v>
+        <v>the feeling - Steve Lacy</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Madrugada</v>
+        <v>baby (Live at Apple Music Radio)</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/madrugada/6773906244</v>
+        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E136" t="str">
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Madrugada - Single</v>
+        <v>Live at Apple Music Radio</v>
       </c>
       <c r="G136" t="str">
-        <v>2:58</v>
+        <v>3:14</v>
       </c>
       <c r="H136" t="str">
-        <v>Chino Pacas</v>
+        <v>Gabriel Jacoby</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/chino-pacas/1666295765</v>
+        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/madrugada/6773906243</v>
+        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
       </c>
       <c r="L136" t="str">
-        <v>Madrugada - Chino Pacas</v>
+        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Oh Chet (feat. Travis Scott)</v>
+        <v>Drop The Lo</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/oh-chet-feat-travis-scott/6776790203</v>
+        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E137" t="str">
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Single</v>
+        <v>Drop The Lo - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:23</v>
+        <v>2:41</v>
       </c>
       <c r="H137" t="str">
-        <v>Jey One</v>
+        <v>Bryson Tiller</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/jey-one/1534914623</v>
+        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/oh-chet-feat-travis-scott/6776790192</v>
+        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
       </c>
       <c r="L137" t="str">
-        <v>Oh Chet (feat. Travis Scott) - Jey One</v>
+        <v>Drop The Lo - Bryson Tiller</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>An Hour or So (Live at Apple Music Radio)</v>
+        <v>GANG BIZNESS feat paygotti</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/an-hour-or-so-live-at-apple-music-radio/6774347383</v>
+        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E138" t="str">
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>GANG BIZNESS feat paygotti - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:02</v>
+        <v>2:47</v>
       </c>
       <c r="H138" t="str">
-        <v>Benny G</v>
+        <v>YG</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/yg/189792075</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/an-hour-or-so-live-at-apple-music-radio/6774347373</v>
+        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
       </c>
       <c r="L138" t="str">
-        <v>An Hour or So (Live at Apple Music Radio) - Benny G</v>
+        <v>GANG BIZNESS feat paygotti - YG</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>it’s just White Noise</v>
+        <v>Lay It Down</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/its-just-white-noise/6775559037</v>
+        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E139" t="str">
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>it’s a real Cruel World - EP</v>
+        <v>Lay It Down - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:57</v>
+        <v>2:38</v>
       </c>
       <c r="H139" t="str">
-        <v>Holly Humberstone</v>
+        <v>FattMack</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/its-just-white-noise/6775559025</v>
+        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
       </c>
       <c r="L139" t="str">
-        <v>it’s just White Noise - Holly Humberstone</v>
+        <v>Lay It Down - FattMack</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>the feeling</v>
+        <v>WAX PAPER</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/the-feeling/6773775295</v>
+        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E140" t="str">
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Oh yeah?</v>
+        <v>WHACK'S MUSEUM</v>
       </c>
       <c r="G140" t="str">
-        <v>4:35</v>
+        <v>2:43</v>
       </c>
       <c r="H140" t="str">
-        <v>Steve Lacy</v>
+        <v>Tierra Whack</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/steve-lacy/1210275020</v>
+        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/the-feeling/6773775032</v>
+        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
       </c>
       <c r="L140" t="str">
-        <v>the feeling - Steve Lacy</v>
+        <v>WAX PAPER - Tierra Whack</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>baby (Live at Apple Music Radio)</v>
+        <v>abusadOra (tambores)</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/baby-live-at-apple-music-radio/6774268054</v>
+        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E141" t="str">
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Live at Apple Music Radio</v>
+        <v>ANTES DE QUE SEA TARDE</v>
       </c>
       <c r="G141" t="str">
-        <v>3:14</v>
+        <v>3:11</v>
       </c>
       <c r="H141" t="str">
-        <v>Gabriel Jacoby</v>
+        <v>Yorghaki</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/gabriel-jacoby/1610957262</v>
+        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/baby-live-at-apple-music-radio/6774268047</v>
+        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
       </c>
       <c r="L141" t="str">
-        <v>baby (Live at Apple Music Radio) - Gabriel Jacoby</v>
+        <v>abusadOra (tambores) - Yorghaki</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Drop The Lo</v>
+        <v>Ruin</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/drop-the-lo/6775562558</v>
+        <v>https://music.apple.com/us/song/ruin/6763176090</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E142" t="str">
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Drop The Lo - Single</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G142" t="str">
-        <v>2:41</v>
+        <v>3:19</v>
       </c>
       <c r="H142" t="str">
-        <v>Bryson Tiller</v>
+        <v>Blxst</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/bryson-tiller/642591128</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/drop-the-lo/6775562557</v>
+        <v>https://music.apple.com/us/album/ruin/1895199881</v>
       </c>
       <c r="L142" t="str">
-        <v>Drop The Lo - Bryson Tiller</v>
+        <v>Ruin - Blxst</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>GANG BIZNESS feat paygotti</v>
+        <v>Do Today</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/gang-bizness-feat-paygotti/6775052802</v>
+        <v>https://music.apple.com/us/song/do-today/1893402864</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E143" t="str">
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>GANG BIZNESS feat paygotti - Single</v>
+        <v>Grateful</v>
       </c>
       <c r="G143" t="str">
-        <v>2:47</v>
+        <v>4:14</v>
       </c>
       <c r="H143" t="str">
-        <v>YG</v>
+        <v>The Red Clay Strays</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/yg/189792075</v>
+        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/gang-bizness-feat-paygotti/6775052791</v>
+        <v>https://music.apple.com/us/album/do-today/1893402542</v>
       </c>
       <c r="L143" t="str">
-        <v>GANG BIZNESS feat paygotti - YG</v>
+        <v>Do Today - The Red Clay Strays</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Lay It Down</v>
+        <v>Stone Over Water</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/lay-it-down/6771479704</v>
+        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E144" t="str">
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Lay It Down - Single</v>
+        <v>I Built You A Tower</v>
       </c>
       <c r="G144" t="str">
-        <v>2:38</v>
+        <v>3:14</v>
       </c>
       <c r="H144" t="str">
-        <v>FattMack</v>
+        <v>Death Cab for Cutie</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/fattmack/1526850149</v>
+        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/lay-it-down/6771479698</v>
+        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
       </c>
       <c r="L144" t="str">
-        <v>Lay It Down - FattMack</v>
+        <v>Stone Over Water - Death Cab for Cutie</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>WAX PAPER</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/wax-paper/6773954513</v>
+        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E145" t="str">
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>WHACK'S MUSEUM</v>
+        <v>Weezer</v>
       </c>
       <c r="G145" t="str">
-        <v>2:43</v>
+        <v>3:34</v>
       </c>
       <c r="H145" t="str">
-        <v>Tierra Whack</v>
+        <v>Weezer</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/tierra-whack/1209032442</v>
+        <v>https://music.apple.com/us/artist/weezer/115234</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/wax-paper/6773954494</v>
+        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
       </c>
       <c r="L145" t="str">
-        <v>WAX PAPER - Tierra Whack</v>
+        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>abusadOra (tambores)</v>
+        <v>Tell Me When You've Had Enough</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/abusadora-tambores/6774274222</v>
+        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E146" t="str">
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>ANTES DE QUE SEA TARDE</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G146" t="str">
-        <v>3:11</v>
+        <v>3:19</v>
       </c>
       <c r="H146" t="str">
-        <v>Yorghaki</v>
+        <v>Evanescence</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/yorghaki/1280681802</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/abusadora-tambores/6774274214</v>
+        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
       </c>
       <c r="L146" t="str">
-        <v>abusadOra (tambores) - Yorghaki</v>
+        <v>Tell Me When You've Had Enough - Evanescence</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Ruin</v>
+        <v>Your Ghost Again</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/ruin/6763176090</v>
+        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E147" t="str">
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Labor Of Love</v>
+        <v>Your Ghost Again - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:19</v>
+        <v>4:35</v>
       </c>
       <c r="H147" t="str">
-        <v>Blxst</v>
+        <v>Mastodon</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/ruin/1895199881</v>
+        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
       </c>
       <c r="L147" t="str">
-        <v>Ruin - Blxst</v>
+        <v>Your Ghost Again - Mastodon</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Do Today</v>
+        <v>Nightshift Superstar</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/do-today/1893402864</v>
+        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E148" t="str">
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Grateful</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G148" t="str">
-        <v>4:14</v>
+        <v>4:07</v>
       </c>
       <c r="H148" t="str">
-        <v>The Red Clay Strays</v>
+        <v>Muse</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/the-red-clay-strays/1483812664</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/do-today/1893402542</v>
+        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
       </c>
       <c r="L148" t="str">
-        <v>Do Today - The Red Clay Strays</v>
+        <v>Nightshift Superstar - Muse</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Stone Over Water</v>
+        <v>UNDER THE RHYTHM</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/stone-over-water/1878362642</v>
+        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E149" t="str">
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>I Built You A Tower</v>
+        <v>ADAM</v>
       </c>
       <c r="G149" t="str">
-        <v>3:14</v>
+        <v>2:50</v>
       </c>
       <c r="H149" t="str">
-        <v>Death Cab for Cutie</v>
+        <v>Adam Lambert</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/death-cab-for-cutie/5448636</v>
+        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/stone-over-water/1878362451</v>
+        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
       </c>
       <c r="L149" t="str">
-        <v>Stone Over Water - Death Cab for Cutie</v>
+        <v>UNDER THE RHYTHM - Adam Lambert</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday)</v>
+        <v>You’re Mine</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/we-might-as-well-be-strangers-ft-wednesday/6772365051</v>
+        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E150" t="str">
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Weezer</v>
+        <v>Papercut</v>
       </c>
       <c r="G150" t="str">
-        <v>3:34</v>
+        <v>4:25</v>
       </c>
       <c r="H150" t="str">
-        <v>Weezer</v>
+        <v>Imani Imani</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/weezer/115234</v>
+        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/we-might-as-well-be-strangers-ft-wednesday/6772364953</v>
+        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
       </c>
       <c r="L150" t="str">
-        <v>We Might as Well Be Strangers (ft. Wednesday) - Weezer</v>
+        <v>You’re Mine - Imani Imani</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Tell Me When You've Had Enough</v>
+        <v>point blank</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/tell-me-when-youve-had-enough/1891104591</v>
+        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E151" t="str">
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Sanctuary</v>
+        <v>new avatar</v>
       </c>
       <c r="G151" t="str">
-        <v>3:19</v>
+        <v>4:26</v>
       </c>
       <c r="H151" t="str">
-        <v>Evanescence</v>
+        <v>Kelela</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/tell-me-when-youve-had-enough/1891104460</v>
+        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
       </c>
       <c r="L151" t="str">
-        <v>Tell Me When You've Had Enough - Evanescence</v>
+        <v>point blank - Kelela</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Your Ghost Again</v>
+        <v>that's my beach!</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/your-ghost-again/6767050811</v>
+        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E152" t="str">
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Your Ghost Again - Single</v>
+        <v>NATURE IS HEALING</v>
       </c>
       <c r="G152" t="str">
-        <v>4:35</v>
+        <v>3:18</v>
       </c>
       <c r="H152" t="str">
-        <v>Mastodon</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/mastodon/65922937</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/your-ghost-again/1896359084</v>
+        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
       </c>
       <c r="L152" t="str">
-        <v>Your Ghost Again - Mastodon</v>
+        <v>that's my beach! - horsegiirL</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Nightshift Superstar</v>
+        <v>In Your Eyes</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/nightshift-superstar/1885607719</v>
+        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E153" t="str">
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>The Wow! Signal</v>
+        <v>In Your Eyes - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>4:07</v>
+        <v>3:36</v>
       </c>
       <c r="H153" t="str">
-        <v>Muse</v>
+        <v>Alesso</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/alesso/432464201</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/nightshift-superstar/1885607338</v>
+        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
       </c>
       <c r="L153" t="str">
-        <v>Nightshift Superstar - Muse</v>
+        <v>In Your Eyes - Alesso</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>UNDER THE RHYTHM</v>
+        <v>ALL OR NOTHING</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/under-the-rhythm/6762153397</v>
+        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E154" t="str">
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>ADAM</v>
+        <v>ALL OR NOTHING - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:50</v>
+        <v>3:17</v>
       </c>
       <c r="H154" t="str">
-        <v>Adam Lambert</v>
+        <v>Tobe Nwigwe</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/adam-lambert/305371030</v>
+        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/under-the-rhythm/1893149385</v>
+        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
       </c>
       <c r="L154" t="str">
-        <v>UNDER THE RHYTHM - Adam Lambert</v>
+        <v>ALL OR NOTHING - Tobe Nwigwe</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>You’re Mine</v>
+        <v>IN MY HANDS</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/youre-mine/6774762159</v>
+        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Papercut</v>
+        <v>IN MY HANDS - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>4:25</v>
+        <v>3:14</v>
       </c>
       <c r="H155" t="str">
-        <v>Imani Imani</v>
+        <v>Alessia Cara</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/imani-imani/1671911720</v>
+        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/youre-mine/6774761870</v>
+        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
       </c>
       <c r="L155" t="str">
-        <v>You’re Mine - Imani Imani</v>
+        <v>IN MY HANDS - Alessia Cara</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>point blank</v>
+        <v>Life's a Dream</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/point-blank/1888561542</v>
+        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>new avatar</v>
+        <v>An Eraser And A Maze</v>
       </c>
       <c r="G156" t="str">
-        <v>4:26</v>
+        <v>5:31</v>
       </c>
       <c r="H156" t="str">
-        <v>Kelela</v>
+        <v>Modest Mouse</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/point-blank/1888561538</v>
+        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
       </c>
       <c r="L156" t="str">
-        <v>point blank - Kelela</v>
+        <v>Life's a Dream - Modest Mouse</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>that's my beach!</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/thats-my-beach/1893373637</v>
+        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>NATURE IS HEALING</v>
+        <v>Season of Surrender</v>
       </c>
       <c r="G157" t="str">
-        <v>3:18</v>
+        <v>4:47</v>
       </c>
       <c r="H157" t="str">
-        <v>horsegiirL</v>
+        <v>August Burns Red</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/thats-my-beach/1893373426</v>
+        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
       </c>
       <c r="L157" t="str">
-        <v>that's my beach! - horsegiirL</v>
+        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>In Your Eyes</v>
+        <v>Shine</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/in-your-eyes/6772624509</v>
+        <v>https://music.apple.com/us/song/shine/6764654536</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>In Your Eyes - Single</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G158" t="str">
-        <v>3:36</v>
+        <v>2:27</v>
       </c>
       <c r="H158" t="str">
-        <v>Alesso</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/alesso/432464201</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/in-your-eyes/6772624508</v>
+        <v>https://music.apple.com/us/album/shine/1895866355</v>
       </c>
       <c r="L158" t="str">
-        <v>In Your Eyes - Alesso</v>
+        <v>Shine - Jon Batiste</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>ALL OR NOTHING</v>
+        <v>Half The Man</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/all-or-nothing/6770629810</v>
+        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E159" t="str">
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>ALL OR NOTHING - Single</v>
+        <v>Scared of Heights</v>
       </c>
       <c r="G159" t="str">
-        <v>3:17</v>
+        <v>3:56</v>
       </c>
       <c r="H159" t="str">
-        <v>Tobe Nwigwe</v>
+        <v>Wyatt Flores</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/tobe-nwigwe/1124529007</v>
+        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/all-or-nothing/6770629415</v>
+        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
       </c>
       <c r="L159" t="str">
-        <v>ALL OR NOTHING - Tobe Nwigwe</v>
+        <v>Half The Man - Wyatt Flores</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>IN MY HANDS</v>
+        <v>Preacher’s Kid</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/in-my-hands/6772151843</v>
+        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>IN MY HANDS - Single</v>
+        <v>Preacher’s Kid - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:14</v>
+        <v>5:02</v>
       </c>
       <c r="H160" t="str">
-        <v>Alessia Cara</v>
+        <v>Stephen Wilson Jr.</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/alessia-cara/991444375</v>
+        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/in-my-hands/6772151360</v>
+        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
       </c>
       <c r="L160" t="str">
-        <v>IN MY HANDS - Alessia Cara</v>
+        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Life's a Dream</v>
+        <v>Weak</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/lifes-a-dream/1885992023</v>
+        <v>https://music.apple.com/us/song/weak/6771151098</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E161" t="str">
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>An Eraser And A Maze</v>
+        <v>Weak - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>5:31</v>
+        <v>3:28</v>
       </c>
       <c r="H161" t="str">
-        <v>Modest Mouse</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/modest-mouse/467112</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/lifes-a-dream/1885991734</v>
+        <v>https://music.apple.com/us/album/weak/6771151088</v>
       </c>
       <c r="L161" t="str">
-        <v>Life's a Dream - Modest Mouse</v>
+        <v>Weak - Naomi Sharon</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer)</v>
+        <v>ALL NIGHT LONG</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/cerebral-malfunction-feat-make-them-suffer/1879684335</v>
+        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E162" t="str">
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Season of Surrender</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G162" t="str">
-        <v>4:47</v>
+        <v>2:28</v>
       </c>
       <c r="H162" t="str">
-        <v>August Burns Red</v>
+        <v>Pheelz</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/august-burns-red/47796394</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/cerebral-malfunction-feat-make-them-suffer/1879684119</v>
+        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
       </c>
       <c r="L162" t="str">
-        <v>Cerebral Malfunction (feat. Make Them Suffer) - August Burns Red</v>
+        <v>ALL NIGHT LONG - Pheelz</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Shine</v>
+        <v>Every Life</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/shine/6764654536</v>
+        <v>https://music.apple.com/us/song/every-life/6764110978</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E163" t="str">
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Black Mozart</v>
+        <v>Promising Young Woman - EP</v>
       </c>
       <c r="G163" t="str">
-        <v>2:27</v>
+        <v>3:18</v>
       </c>
       <c r="H163" t="str">
-        <v>Jon Batiste</v>
+        <v>Isabel LaRosa</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/shine/1895866355</v>
+        <v>https://music.apple.com/us/album/every-life/1895644574</v>
       </c>
       <c r="L163" t="str">
-        <v>Shine - Jon Batiste</v>
+        <v>Every Life - Isabel LaRosa</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Half The Man</v>
+        <v>Home</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/half-the-man/6773435899</v>
+        <v>https://music.apple.com/us/song/home/6774718029</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E164" t="str">
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Scared of Heights</v>
+        <v>Good Grief</v>
       </c>
       <c r="G164" t="str">
-        <v>3:56</v>
+        <v>4:53</v>
       </c>
       <c r="H164" t="str">
-        <v>Wyatt Flores</v>
+        <v>Sara Bareilles</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/wyatt-flores/1563146833</v>
+        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/half-the-man/6773435890</v>
+        <v>https://music.apple.com/us/album/home/6774718027</v>
       </c>
       <c r="L164" t="str">
-        <v>Half The Man - Wyatt Flores</v>
+        <v>Home - Sara Bareilles</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Preacher’s Kid</v>
+        <v>Satalanaaa</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/preachers-kid/6770632867</v>
+        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E165" t="str">
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Preacher’s Kid - Single</v>
+        <v>Satalanaaa - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>5:02</v>
+        <v>2:06</v>
       </c>
       <c r="H165" t="str">
-        <v>Stephen Wilson Jr.</v>
+        <v>Pitbull</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/stephen-wilson-jr/1456928834</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/preachers-kid/6770632865</v>
+        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
       </c>
       <c r="L165" t="str">
-        <v>Preacher’s Kid - Stephen Wilson Jr.</v>
+        <v>Satalanaaa - Pitbull</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Weak</v>
+        <v>Year of the Horse</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/weak/6771151098</v>
+        <v>https://music.apple.com/us/song/year-of-the-horse/6770590158</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E166" t="str">
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Weak - Single</v>
+        <v>Year of the Horse - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:28</v>
+        <v>4:16</v>
       </c>
       <c r="H166" t="str">
-        <v>Naomi Sharon</v>
+        <v>Aly &amp; AJ</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/aly-aj/33989931</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/weak/6771151088</v>
+        <v>https://music.apple.com/us/album/year-of-the-horse/6770590153</v>
       </c>
       <c r="L166" t="str">
-        <v>Weak - Naomi Sharon</v>
+        <v>Year of the Horse - Aly &amp; AJ</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>ALL NIGHT LONG</v>
+        <v>Miss Me More</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/all-night-long/1893392645</v>
+        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E167" t="str">
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>A Rii Set</v>
+        <v>Confessions of a Lonely Heart</v>
       </c>
       <c r="G167" t="str">
-        <v>2:28</v>
+        <v>2:43</v>
       </c>
       <c r="H167" t="str">
-        <v>Pheelz</v>
+        <v>Eric Nam</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/all-night-long/1893392643</v>
+        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
       </c>
       <c r="L167" t="str">
-        <v>ALL NIGHT LONG - Pheelz</v>
+        <v>Miss Me More - Eric Nam</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Every Life</v>
+        <v>Rituals</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/every-life/6764110978</v>
+        <v>https://music.apple.com/us/song/rituals/6769628916</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E168" t="str">
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Promising Young Woman - EP</v>
+        <v>Rituals - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:18</v>
+        <v>2:10</v>
       </c>
       <c r="H168" t="str">
-        <v>Isabel LaRosa</v>
+        <v>Rico Nasty</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/isabel-larosa/1578296103</v>
+        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/every-life/1895644574</v>
+        <v>https://music.apple.com/us/album/rituals/6769628915</v>
       </c>
       <c r="L168" t="str">
-        <v>Every Life - Isabel LaRosa</v>
+        <v>Rituals - Rico Nasty</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Home</v>
+        <v>Honeysuckle</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/home/6774718029</v>
+        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E169" t="str">
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Good Grief</v>
+        <v>Honeysuckle - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>4:53</v>
+        <v>3:15</v>
       </c>
       <c r="H169" t="str">
-        <v>Sara Bareilles</v>
+        <v>Dylan Gossett</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/sara-bareilles/64398046</v>
+        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/home/6774718027</v>
+        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
       </c>
       <c r="L169" t="str">
-        <v>Home - Sara Bareilles</v>
+        <v>Honeysuckle - Dylan Gossett</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Satalanaaa</v>
+        <v>listen…</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/satalanaaa/6764347861</v>
+        <v>https://music.apple.com/us/song/listen/6775576508</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E170" t="str">
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Satalanaaa - Single</v>
+        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G170" t="str">
-        <v>2:06</v>
+        <v>4:08</v>
       </c>
       <c r="H170" t="str">
-        <v>Pitbull</v>
+        <v>John Williams</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/john-williams/63748</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/satalanaaa/1895743033</v>
+        <v>https://music.apple.com/us/album/listen/6775576506</v>
       </c>
       <c r="L170" t="str">
-        <v>Satalanaaa - Pitbull</v>
+        <v>listen… - John Williams</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Miss Me More</v>
+        <v>DEADMEAT</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/miss-me-more/6771525581</v>
+        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E171" t="str">
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Confessions of a Lonely Heart</v>
+        <v>DEADMEAT - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>2:43</v>
+        <v>2:52</v>
       </c>
       <c r="H171" t="str">
-        <v>Eric Nam</v>
+        <v>South Arcade</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/eric-nam/595893565</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/miss-me-more/6771525227</v>
+        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
       </c>
       <c r="L171" t="str">
-        <v>Miss Me More - Eric Nam</v>
+        <v>DEADMEAT - South Arcade</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Rituals</v>
+        <v>Ugly and Rotten</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/rituals/6769628916</v>
+        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E172" t="str">
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Rituals - Single</v>
+        <v>Ugly and Rotten - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:10</v>
+        <v>2:49</v>
       </c>
       <c r="H172" t="str">
-        <v>Rico Nasty</v>
+        <v>Mckenna Grace</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/rico-nasty/1158173683</v>
+        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/rituals/6769628915</v>
+        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
       </c>
       <c r="L172" t="str">
-        <v>Rituals - Rico Nasty</v>
+        <v>Ugly and Rotten - Mckenna Grace</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Honeysuckle</v>
+        <v>Whisper</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/honeysuckle/6771903359</v>
+        <v>https://music.apple.com/us/song/whisper/6772254272</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E173" t="str">
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Honeysuckle - Single</v>
+        <v>Whisper - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:15</v>
+        <v>2:47</v>
       </c>
       <c r="H173" t="str">
-        <v>Dylan Gossett</v>
+        <v>Blu DeTiger</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/dylan-gossett/1526025679</v>
+        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/honeysuckle/6771903356</v>
+        <v>https://music.apple.com/us/album/whisper/6772254268</v>
       </c>
       <c r="L173" t="str">
-        <v>Honeysuckle - Dylan Gossett</v>
+        <v>Whisper - Blu DeTiger</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>listen…</v>
+        <v>Gecko (feat. Haley Bridge)</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/listen/6775576508</v>
+        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E174" t="str">
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Disclosure Day (Original Motion Picture Soundtrack)</v>
+        <v>How dare you tryna love me? - EP</v>
       </c>
       <c r="G174" t="str">
-        <v>4:08</v>
+        <v>2:46</v>
       </c>
       <c r="H174" t="str">
-        <v>John Williams</v>
+        <v>Olga Myko</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/john-williams/63748</v>
+        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/listen/6775576506</v>
+        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
       </c>
       <c r="L174" t="str">
-        <v>listen… - John Williams</v>
+        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>DEADMEAT</v>
+        <v>Compa Primo</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/deadmeat/6771186647</v>
+        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E175" t="str">
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>DEADMEAT - Single</v>
+        <v>Compa Primo - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:52</v>
+        <v>3:12</v>
       </c>
       <c r="H175" t="str">
-        <v>South Arcade</v>
+        <v>Nueva H</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/deadmeat/6771186644</v>
+        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
       </c>
       <c r="L175" t="str">
-        <v>DEADMEAT - South Arcade</v>
+        <v>Compa Primo - Nueva H</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Ugly and Rotten</v>
+        <v>Parachute</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/ugly-and-rotten/6767713625</v>
+        <v>https://music.apple.com/us/song/parachute/6768841410</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E176" t="str">
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Ugly and Rotten - Single</v>
+        <v>Parachute - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:49</v>
+        <v>3:11</v>
       </c>
       <c r="H176" t="str">
-        <v>Mckenna Grace</v>
+        <v>Tyler James Bellinger</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/mckenna-grace/1594459561</v>
+        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/ugly-and-rotten/6767713622</v>
+        <v>https://music.apple.com/us/album/parachute/6768841409</v>
       </c>
       <c r="L176" t="str">
-        <v>Ugly and Rotten - Mckenna Grace</v>
+        <v>Parachute - Tyler James Bellinger</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Whisper</v>
+        <v>Like a Bubble</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/whisper/6772254272</v>
+        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E177" t="str">
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Whisper - Single</v>
+        <v>Imperfect-I'mperfect - EP</v>
       </c>
       <c r="G177" t="str">
-        <v>2:47</v>
+        <v>3:08</v>
       </c>
       <c r="H177" t="str">
-        <v>Blu DeTiger</v>
+        <v>FIFTY FIFTY</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/blu-detiger/1449334298</v>
+        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/whisper/6772254268</v>
+        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
       </c>
       <c r="L177" t="str">
-        <v>Whisper - Blu DeTiger</v>
+        <v>Like a Bubble - FIFTY FIFTY</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Gecko (feat. Haley Bridge)</v>
+        <v>Hustle and Opulence in America</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/gecko-feat-haley-bridge/6767384870</v>
+        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E178" t="str">
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>How dare you tryna love me? - EP</v>
+        <v>AK Cuts: Vol. 4 - EP</v>
       </c>
       <c r="G178" t="str">
-        <v>2:46</v>
+        <v>3:07</v>
       </c>
       <c r="H178" t="str">
-        <v>Olga Myko</v>
+        <v>Anish Kumar</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/olga-myko/1788720794</v>
+        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/gecko-feat-haley-bridge/6767384866</v>
+        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
       </c>
       <c r="L178" t="str">
-        <v>Gecko (feat. Haley Bridge) - Olga Myko</v>
+        <v>Hustle and Opulence in America - Anish Kumar</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Compa Primo</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/compa-primo/6768821230</v>
+        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E179" t="str">
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Compa Primo - Single</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>3:12</v>
+        <v>2:47</v>
       </c>
       <c r="H179" t="str">
-        <v>Nueva H</v>
+        <v>ivri</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/nueva-h/1709738240</v>
+        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/compa-primo/6768821227</v>
+        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
       </c>
       <c r="L179" t="str">
-        <v>Compa Primo - Nueva H</v>
+        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Parachute</v>
+        <v>CLEAN SWEEP</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/parachute/6768841410</v>
+        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E180" t="str">
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Parachute - Single</v>
+        <v>CLEAN SWEEP - Single</v>
       </c>
       <c r="G180" t="str">
         <v>3:11</v>
       </c>
       <c r="H180" t="str">
-        <v>Tyler James Bellinger</v>
+        <v>Storm Reid</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/tyler-james-bellinger/1394603081</v>
+        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/parachute/6768841409</v>
+        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
       </c>
       <c r="L180" t="str">
-        <v>Parachute - Tyler James Bellinger</v>
+        <v>CLEAN SWEEP - Storm Reid</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Like a Bubble</v>
+        <v>CANDYLAND!</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/like-a-bubble/6770401105</v>
+        <v>https://music.apple.com/us/song/candyland/6766927008</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E181" t="str">
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Imperfect-I'mperfect - EP</v>
+        <v>CANDYLAND! - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:08</v>
+        <v>3:15</v>
       </c>
       <c r="H181" t="str">
-        <v>FIFTY FIFTY</v>
+        <v>Natanya</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/fifty-fifty/1654860606</v>
+        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/like-a-bubble/6770401101</v>
+        <v>https://music.apple.com/us/album/candyland/6766927000</v>
       </c>
       <c r="L181" t="str">
-        <v>Like a Bubble - FIFTY FIFTY</v>
+        <v>CANDYLAND! - Natanya</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Hustle and Opulence in America</v>
+        <v>Double C</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/hustle-and-opulence-in-america/6764616334</v>
+        <v>https://music.apple.com/us/song/double-c/6771836555</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E182" t="str">
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>AK Cuts: Vol. 4 - EP</v>
+        <v>Double C - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:07</v>
+        <v>2:21</v>
       </c>
       <c r="H182" t="str">
-        <v>Anish Kumar</v>
+        <v>Sk8star</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/anish-kumar/1510744726</v>
+        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/hustle-and-opulence-in-america/1895850742</v>
+        <v>https://music.apple.com/us/album/double-c/6771836554</v>
       </c>
       <c r="L182" t="str">
-        <v>Hustle and Opulence in America - Anish Kumar</v>
+        <v>Double C - Sk8star</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE)</v>
+        <v>madera</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/whoever-you-want-me-to-be-nothing-more/6771179701</v>
+        <v>https://music.apple.com/us/song/madera/6764638112</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E183" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - Single</v>
+        <v>madera/un camino luminoso - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:47</v>
+        <v>5:41</v>
       </c>
       <c r="H183" t="str">
-        <v>ivri</v>
+        <v>Lumtz</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/ivri/1349563025</v>
+        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/whoever-you-want-me-to-be-nothing-more/6771179167</v>
+        <v>https://music.apple.com/us/album/madera/6764638109</v>
       </c>
       <c r="L183" t="str">
-        <v>WHOEVER YOU WANT ME TO BE (NOTHING MORE) - ivri</v>
+        <v>madera - Lumtz</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>CLEAN SWEEP</v>
+        <v>Slip the Noose</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/clean-sweep/6776345916</v>
+        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E184" t="str">
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>CLEAN SWEEP - Single</v>
+        <v>Hum of Hurt</v>
       </c>
       <c r="G184" t="str">
-        <v>3:11</v>
+        <v>1:43</v>
       </c>
       <c r="H184" t="str">
-        <v>Storm Reid</v>
+        <v>Converge</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/storm-reid/6776344721</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/clean-sweep/6776345910</v>
+        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
       </c>
       <c r="L184" t="str">
-        <v>CLEAN SWEEP - Storm Reid</v>
+        <v>Slip the Noose - Converge</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>CANDYLAND!</v>
+        <v>Crying Fire</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/candyland/6766927008</v>
+        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E185" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>CANDYLAND! - Single</v>
+        <v>Crying Fire - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:15</v>
+        <v>4:08</v>
       </c>
       <c r="H185" t="str">
-        <v>Natanya</v>
+        <v>Avatar</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/natanya/1559940828</v>
+        <v>https://music.apple.com/us/artist/avatar/187616241</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/candyland/6766927000</v>
+        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
       </c>
       <c r="L185" t="str">
-        <v>CANDYLAND! - Natanya</v>
+        <v>Crying Fire - Avatar</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Double C</v>
+        <v>NI NA’</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/double-c/6771836555</v>
+        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Double C - Single</v>
+        <v>sorry si soy GRRRIS</v>
       </c>
       <c r="G186" t="str">
-        <v>2:21</v>
+        <v>2:53</v>
       </c>
       <c r="H186" t="str">
-        <v>Sk8star</v>
+        <v>ROBI</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/sk8star/1511246116</v>
+        <v>https://music.apple.com/us/artist/robi/1458047972</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/double-c/6771836554</v>
+        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
       </c>
       <c r="L186" t="str">
-        <v>Double C - Sk8star</v>
+        <v>NI NA’ - ROBI</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>madera</v>
+        <v>Holding Back</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/madera/6764638112</v>
+        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E187" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>madera/un camino luminoso - Single</v>
+        <v>AMA</v>
       </c>
       <c r="G187" t="str">
-        <v>5:41</v>
+        <v>3:19</v>
       </c>
       <c r="H187" t="str">
-        <v>Lumtz</v>
+        <v>Ama</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/lumtz/1615289779</v>
+        <v>https://music.apple.com/us/artist/ama/1801560081</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/madera/6764638109</v>
+        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
       </c>
       <c r="L187" t="str">
-        <v>madera - Lumtz</v>
+        <v>Holding Back - Ama</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Slip the Noose</v>
+        <v>you're still mine</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/slip-the-noose/1883081838</v>
+        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Hum of Hurt</v>
+        <v>you're still mine - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>1:43</v>
+        <v>3:19</v>
       </c>
       <c r="H188" t="str">
-        <v>Converge</v>
+        <v>Lexi Jayde</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/slip-the-noose/1883081837</v>
+        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
       </c>
       <c r="L188" t="str">
-        <v>Slip the Noose - Converge</v>
+        <v>you're still mine - Lexi Jayde</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Crying Fire</v>
+        <v>teksi</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/crying-fire/6766303435</v>
+        <v>https://music.apple.com/us/song/teksi/6769899742</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Crying Fire - Single</v>
+        <v>pOCHO</v>
       </c>
       <c r="G189" t="str">
-        <v>4:08</v>
+        <v>2:48</v>
       </c>
       <c r="H189" t="str">
-        <v>Avatar</v>
+        <v>8onthebeat</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/avatar/187616241</v>
+        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/crying-fire/1896273209</v>
+        <v>https://music.apple.com/us/album/teksi/6769899739</v>
       </c>
       <c r="L189" t="str">
-        <v>Crying Fire - Avatar</v>
+        <v>teksi - 8onthebeat</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>NI NA’</v>
+        <v>Let You Go</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/ni-na/6768820889</v>
+        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>sorry si soy GRRRIS</v>
+        <v>Let You Go - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:53</v>
+        <v>1:37</v>
       </c>
       <c r="H190" t="str">
-        <v>ROBI</v>
+        <v>Nate Sib</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/robi/1458047972</v>
+        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/ni-na/6768820873</v>
+        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
       </c>
       <c r="L190" t="str">
-        <v>NI NA’ - ROBI</v>
+        <v>Let You Go - Nate Sib</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Holding Back</v>
+        <v>Dis-Moi</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/holding-back/6773986881</v>
+        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E191" t="str">
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>AMA</v>
+        <v>CINNA</v>
       </c>
       <c r="G191" t="str">
-        <v>3:19</v>
+        <v>2:27</v>
       </c>
       <c r="H191" t="str">
-        <v>Ama</v>
+        <v>Cannelle</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/ama/1801560081</v>
+        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/holding-back/6773986679</v>
+        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
       </c>
       <c r="L191" t="str">
-        <v>Holding Back - Ama</v>
+        <v>Dis-Moi - Cannelle</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>you're still mine</v>
+        <v>Leverage</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/youre-still-mine/6771456062</v>
+        <v>https://music.apple.com/us/song/leverage/6776432312</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E192" t="str">
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>you're still mine - Single</v>
+        <v>Heaven on Mars</v>
       </c>
       <c r="G192" t="str">
-        <v>3:19</v>
+        <v>3:04</v>
       </c>
       <c r="H192" t="str">
-        <v>Lexi Jayde</v>
+        <v>NoCap</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/lexi-jayde/1318476177</v>
+        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/youre-still-mine/6771456060</v>
+        <v>https://music.apple.com/us/album/leverage/6776432217</v>
       </c>
       <c r="L192" t="str">
-        <v>you're still mine - Lexi Jayde</v>
+        <v>Leverage - NoCap</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>teksi</v>
+        <v>Kool Aid</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/teksi/6769899742</v>
+        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E193" t="str">
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>pOCHO</v>
+        <v>Where Have All The Good Men Gone? - EP</v>
       </c>
       <c r="G193" t="str">
-        <v>2:48</v>
+        <v>3:40</v>
       </c>
       <c r="H193" t="str">
-        <v>8onthebeat</v>
+        <v>Debbii Dawson</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/8onthebeat/1538770341</v>
+        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/teksi/6769899739</v>
+        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
       </c>
       <c r="L193" t="str">
-        <v>teksi - 8onthebeat</v>
+        <v>Kool Aid - Debbii Dawson</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Let You Go</v>
+        <v>Pieces</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/let-you-go/6771980871</v>
+        <v>https://music.apple.com/us/song/pieces/6771861156</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E194" t="str">
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Let You Go - Single</v>
+        <v>Pieces - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>1:37</v>
+        <v>2:19</v>
       </c>
       <c r="H194" t="str">
-        <v>Nate Sib</v>
+        <v>Dom Innarella</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/nate-sib/1709203739</v>
+        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/let-you-go/6771980867</v>
+        <v>https://music.apple.com/us/album/pieces/6771861155</v>
       </c>
       <c r="L194" t="str">
-        <v>Let You Go - Nate Sib</v>
+        <v>Pieces - Dom Innarella</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Dis-Moi</v>
+        <v>Mesmerized</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/dis-moi/6772359986</v>
+        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E195" t="str">
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>CINNA</v>
+        <v>Mesmerized - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:27</v>
+        <v>2:38</v>
       </c>
       <c r="H195" t="str">
-        <v>Cannelle</v>
+        <v>The Aces</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/cannelle/1754623505</v>
+        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/dis-moi/6772359981</v>
+        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
       </c>
       <c r="L195" t="str">
-        <v>Dis-Moi - Cannelle</v>
+        <v>Mesmerized - The Aces</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Leverage</v>
+        <v>Perfect 10</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/leverage/6776432312</v>
+        <v>https://music.apple.com/us/song/perfect-10/6767008734</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E196" t="str">
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Heaven on Mars</v>
+        <v>No Hard Feelings (Deluxe)</v>
       </c>
       <c r="G196" t="str">
-        <v>3:04</v>
+        <v>2:51</v>
       </c>
       <c r="H196" t="str">
-        <v>NoCap</v>
+        <v>The Beaches</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/nocap/1237732480</v>
+        <v>https://music.apple.com/us/artist/the-beaches/1150145182</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/leverage/6776432217</v>
+        <v>https://music.apple.com/us/album/perfect-10/6767008094</v>
       </c>
       <c r="L196" t="str">
-        <v>Leverage - NoCap</v>
+        <v>Perfect 10 - The Beaches</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Kool Aid</v>
+        <v>Recognize</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/kool-aid/6765484428</v>
+        <v>https://music.apple.com/us/song/recognize/6769164705</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E197" t="str">
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Where Have All The Good Men Gone? - EP</v>
+        <v>Recognize - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:40</v>
+        <v>2:05</v>
       </c>
       <c r="H197" t="str">
-        <v>Debbii Dawson</v>
+        <v>Fana Hues</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
+        <v>https://music.apple.com/us/artist/fana-hues/1486304617</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/kool-aid/1895967802</v>
+        <v>https://music.apple.com/us/album/recognize/6769164704</v>
       </c>
       <c r="L197" t="str">
-        <v>Kool Aid - Debbii Dawson</v>
+        <v>Recognize - Fana Hues</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Pieces</v>
+        <v>Feel The Vibe</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/pieces/6771861156</v>
+        <v>https://music.apple.com/us/song/feel-the-vibe/6767232864</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E198" t="str">
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Pieces - Single</v>
+        <v>Feel The Vibe</v>
       </c>
       <c r="G198" t="str">
-        <v>2:19</v>
+        <v>3:28</v>
       </c>
       <c r="H198" t="str">
-        <v>Dom Innarella</v>
+        <v>Above &amp; Beyond</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/dom-innarella/1799787707</v>
+        <v>https://music.apple.com/us/artist/above-beyond/20318188</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/pieces/6771861155</v>
+        <v>https://music.apple.com/us/album/feel-the-vibe/1896435191</v>
       </c>
       <c r="L198" t="str">
-        <v>Pieces - Dom Innarella</v>
+        <v>Feel The Vibe - Above &amp; Beyond</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Mesmerized</v>
+        <v>I Never Knew</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/mesmerized/6769170390</v>
+        <v>https://music.apple.com/us/song/i-never-knew/6764351468</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="E199" t="str">
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Mesmerized - Single</v>
+        <v>I Never Knew - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:38</v>
+        <v>3:51</v>
       </c>
       <c r="H199" t="str">
-        <v>The Aces</v>
+        <v>Adam Ten</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/the-aces/1238525085</v>
+        <v>https://music.apple.com/us/artist/adam-ten/1472226854</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/mesmerized/6769170389</v>
+        <v>https://music.apple.com/us/album/i-never-knew/1895744479</v>
       </c>
       <c r="L199" t="str">
-        <v>Mesmerized - The Aces</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="